--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -4367,11 +4367,11 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4391,11 +4391,11 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>10988</v>
+        <v>7874</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Movimento - Analise de Balanço Lucro Presumido</t>
+          <t>Movimento - Analise de Balanço Lucro Real</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -4422,11 +4422,11 @@
         <v>2026</v>
       </c>
       <c r="P39" t="n">
-        <v>16962441</v>
+        <v>17399317</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="V39" t="inlineStr"/>
@@ -4462,17 +4462,17 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -4523,11 +4523,11 @@
         <v>2026</v>
       </c>
       <c r="P40" t="n">
-        <v>17399317</v>
+        <v>17407858</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="V40" t="inlineStr"/>
@@ -4563,17 +4563,17 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -4624,7 +4624,7 @@
         <v>2026</v>
       </c>
       <c r="P41" t="n">
-        <v>17407858</v>
+        <v>17206041</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -4670,11 +4670,11 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -4725,11 +4725,11 @@
         <v>2026</v>
       </c>
       <c r="P42" t="n">
-        <v>17206041</v>
+        <v>17539825</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="V42" t="inlineStr"/>
@@ -4765,17 +4765,17 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>6278</v>
+        <v>6486</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4826,11 +4826,11 @@
         <v>2026</v>
       </c>
       <c r="P43" t="n">
-        <v>17539825</v>
+        <v>18130460</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Ryan Godinho</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="V43" t="inlineStr"/>
@@ -4866,17 +4866,17 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4927,11 +4927,11 @@
         <v>2026</v>
       </c>
       <c r="P44" t="n">
-        <v>18130460</v>
+        <v>18096764</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Ryan Godinho</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="V44" t="inlineStr"/>
@@ -4967,17 +4967,17 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>6704</v>
+        <v>6949</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4997,42 +4997,46 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>7874</v>
+        <v>11617</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Movimento - Analise de Balanço Lucro Real</t>
+          <t>Envio de ATA de Implantação - EF I</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" s="1" t="n">
-        <v>46198</v>
-      </c>
-      <c r="M45" t="inlineStr"/>
+        <v>46203</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
       <c r="N45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O45" t="n">
         <v>2026</v>
       </c>
       <c r="P45" t="n">
-        <v>18096764</v>
+        <v>18166588</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -5042,14 +5046,19 @@
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr"/>
+          <t>TEC GRUA</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 30/06/2026 
+AINDA NÃO HOUVE A REUNIÃO DE IMPLANTAÇÃO - Data Comentário: 10/06/2026 16:18</t>
+        </is>
+      </c>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
@@ -5068,17 +5077,17 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5121,11 +5130,7 @@
       <c r="L46" s="1" t="n">
         <v>46203</v>
       </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
         <v>6</v>
       </c>
@@ -5133,7 +5138,7 @@
         <v>2026</v>
       </c>
       <c r="P46" t="n">
-        <v>18166588</v>
+        <v>18186565</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -5151,13 +5156,12 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 30/06/2026 
-AINDA NÃO HOUVE A REUNIÃO DE IMPLANTAÇÃO - Data Comentário: 10/06/2026 16:18</t>
+          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6962; Tarefa Incluida: 11617; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: pvolpe - Data Comentário: 17/06/2026 11:09</t>
         </is>
       </c>
       <c r="W46" t="inlineStr"/>
@@ -5184,11 +5188,11 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5239,7 +5243,7 @@
         <v>2026</v>
       </c>
       <c r="P47" t="n">
-        <v>18186565</v>
+        <v>18186566</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -5262,7 +5266,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6962; Tarefa Incluida: 11617; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: pvolpe - Data Comentário: 17/06/2026 11:09</t>
+          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6963; Tarefa Incluida: 11617; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: pvolpe - Data Comentário: 17/06/2026 11:09</t>
         </is>
       </c>
       <c r="W47" t="inlineStr"/>
@@ -5289,11 +5293,11 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>6963</v>
+        <v>6548</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5313,11 +5317,11 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>11617</v>
+        <v>7026</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -5329,26 +5333,26 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - EF I</t>
+          <t>Movimento - Sistema de Análise</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" s="1" t="n">
-        <v>46203</v>
+        <v>46196</v>
       </c>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O48" t="n">
         <v>2026</v>
       </c>
       <c r="P48" t="n">
-        <v>18186566</v>
+        <v>18094896</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -5358,16 +5362,16 @@
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6963; Tarefa Incluida: 11617; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: pvolpe - Data Comentário: 17/06/2026 11:09</t>
+          <t>Reaberto via API integração MGC x Sistema de Analise Fiscal em 23/06/2026 11:10:26. - Data Comentário: 23/06/2026 11:08</t>
         </is>
       </c>
       <c r="W48" t="inlineStr"/>
@@ -5576,7 +5580,11 @@
           <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr"/>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Reaberto via API integração MGC x Sistema de Analise Fiscal em 23/06/2026 12:20:33. - Data Comentário: 23/06/2026 12:19</t>
+        </is>
+      </c>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
@@ -5906,11 +5914,11 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>6419</v>
+        <v>6404</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA (FILIAL 1)</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5920,7 +5928,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5961,7 +5969,7 @@
         <v>2026</v>
       </c>
       <c r="P54" t="n">
-        <v>17100270</v>
+        <v>16962451</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -5979,12 +5987,12 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>MACHADO</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>Reaberto via API integração MGC x Analise Balanço em 11/06/2026 10:11:42. - Data Comentário: 11/06/2026 10:08</t>
+          <t>Reaberto via API integração MGC x Analise Balanço em 23/06/2026 10:58:14. - Data Comentário: 23/06/2026 10:57</t>
         </is>
       </c>
       <c r="W54" t="inlineStr"/>
@@ -6007,11 +6015,11 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>5617</v>
+        <v>6419</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA (FILIAL 1)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6035,24 +6043,24 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>11056</v>
+        <v>11001</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Agenda de Reunião</t>
+          <t>Movimento - Analise de Balanço Lucro Presumido</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" s="1" t="n">
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
@@ -6062,11 +6070,11 @@
         <v>2026</v>
       </c>
       <c r="P55" t="n">
-        <v>18183612</v>
+        <v>17100270</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -6076,16 +6084,16 @@
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>MACHADO</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>AGUARDANDO CONFIRMAÇÃO - Data Comentário: 12/06/2026 09:17</t>
+          <t>Reaberto via API integração MGC x Analise Balanço em 11/06/2026 10:11:42. - Data Comentário: 11/06/2026 10:08</t>
         </is>
       </c>
       <c r="W55" t="inlineStr"/>
@@ -14578,11 +14586,11 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -14633,11 +14641,11 @@
         <v>2026</v>
       </c>
       <c r="P136" t="n">
-        <v>18112915</v>
+        <v>16962441</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>Ryan Godinho</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -14646,19 +14654,19 @@
         </is>
       </c>
       <c r="S136" s="1" t="n">
-        <v>46189.75679984954</v>
+        <v>46196.45711527778</v>
       </c>
       <c r="T136" t="n">
         <v>-2</v>
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="V136" t="inlineStr">
         <is>
-          <t>Baixado via API integração MGC x Analise Balanço em 16/06/2026 18:09:47. - Data Comentário: 16/06/2026 18:09</t>
+          <t>Baixado via API integração MGC x Analise Balanço em 23/06/2026 10:58:14. - Data Comentário: 23/06/2026 10:57</t>
         </is>
       </c>
       <c r="W136" t="inlineStr"/>
@@ -14683,17 +14691,17 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>6705</v>
+        <v>6703</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -14703,7 +14711,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -14717,7 +14725,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>9762</v>
+        <v>10988</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -14729,7 +14737,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Movimento - Analise de Balanço Simples Nacional</t>
+          <t>Movimento - Analise de Balanço Lucro Presumido</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -14744,11 +14752,11 @@
         <v>2026</v>
       </c>
       <c r="P137" t="n">
-        <v>18096936</v>
+        <v>18112915</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Ryan Godinho</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -14757,19 +14765,19 @@
         </is>
       </c>
       <c r="S137" s="1" t="n">
-        <v>46191.38272704861</v>
+        <v>46189.75679984954</v>
       </c>
       <c r="T137" t="n">
         <v>-2</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>Baixado via API integração MGC x Analise Balanço em 18/06/2026 09:09:53. - Data Comentário: 18/06/2026 09:09</t>
+          <t>Baixado via API integração MGC x Analise Balanço em 16/06/2026 18:09:47. - Data Comentário: 16/06/2026 18:09</t>
         </is>
       </c>
       <c r="W137" t="inlineStr"/>
@@ -14794,17 +14802,17 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -14855,7 +14863,7 @@
         <v>2026</v>
       </c>
       <c r="P138" t="n">
-        <v>18130481</v>
+        <v>18096936</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -14868,7 +14876,7 @@
         </is>
       </c>
       <c r="S138" s="1" t="n">
-        <v>46191.54525443287</v>
+        <v>46191.38272704861</v>
       </c>
       <c r="T138" t="n">
         <v>-2</v>
@@ -14880,7 +14888,7 @@
       </c>
       <c r="V138" t="inlineStr">
         <is>
-          <t>Baixado via API integração MGC x Analise Balanço em 18/06/2026 13:04:07. - Data Comentário: 18/06/2026 13:03</t>
+          <t>Baixado via API integração MGC x Analise Balanço em 18/06/2026 09:09:53. - Data Comentário: 18/06/2026 09:09</t>
         </is>
       </c>
       <c r="W138" t="inlineStr"/>
@@ -14911,11 +14919,11 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>6885</v>
+        <v>6779</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -14966,11 +14974,11 @@
         <v>2026</v>
       </c>
       <c r="P139" t="n">
-        <v>18129424</v>
+        <v>18130481</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -14979,19 +14987,19 @@
         </is>
       </c>
       <c r="S139" s="1" t="n">
-        <v>46188.37637295139</v>
+        <v>46191.54525443287</v>
       </c>
       <c r="T139" t="n">
         <v>-2</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>Baixado via API integração MGC x Analise Balanço em 15/06/2026 09:01:58. - Data Comentário: 15/06/2026 09:01</t>
+          <t>Baixado via API integração MGC x Analise Balanço em 18/06/2026 13:04:07. - Data Comentário: 18/06/2026 13:03</t>
         </is>
       </c>
       <c r="W139" t="inlineStr"/>
@@ -15022,11 +15030,11 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>5417</v>
+        <v>6885</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -15036,7 +15044,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -15046,14 +15054,14 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>1628</v>
+        <v>9762</v>
       </c>
       <c r="H140" t="n">
-        <v>1581</v>
+        <v>0</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -15062,12 +15070,12 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Outras Receitas</t>
+          <t>Movimento - Analise de Balanço Simples Nacional</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
       <c r="L140" s="1" t="n">
-        <v>46195</v>
+        <v>46198</v>
       </c>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="n">
@@ -15077,11 +15085,11 @@
         <v>2026</v>
       </c>
       <c r="P140" t="n">
-        <v>17398922</v>
+        <v>18129424</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -15090,17 +15098,21 @@
         </is>
       </c>
       <c r="S140" s="1" t="n">
-        <v>46189.37311814815</v>
+        <v>46188.37637295139</v>
       </c>
       <c r="T140" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
-        </is>
-      </c>
-      <c r="V140" t="inlineStr"/>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Baixado via API integração MGC x Analise Balanço em 15/06/2026 09:01:58. - Data Comentário: 15/06/2026 09:01</t>
+        </is>
+      </c>
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="inlineStr"/>
@@ -15109,7 +15121,7 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>ex-funcionario</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr"/>
@@ -15123,17 +15135,17 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>6224</v>
+        <v>5417</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -15153,7 +15165,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -15184,11 +15196,11 @@
         <v>2026</v>
       </c>
       <c r="P141" t="n">
-        <v>17688650</v>
+        <v>17398922</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -15197,14 +15209,14 @@
         </is>
       </c>
       <c r="S141" s="1" t="n">
-        <v>46195.6807522338</v>
+        <v>46189.37311814815</v>
       </c>
       <c r="T141" t="n">
         <v>1</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="V141" t="inlineStr"/>
@@ -15216,7 +15228,7 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr"/>
@@ -15230,17 +15242,17 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Karina Santos</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>6278</v>
+        <v>6224</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -15250,7 +15262,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -15260,7 +15272,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -15291,11 +15303,11 @@
         <v>2026</v>
       </c>
       <c r="P142" t="n">
-        <v>17539751</v>
+        <v>17688650</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -15304,14 +15316,14 @@
         </is>
       </c>
       <c r="S142" s="1" t="n">
-        <v>46175.35234628472</v>
+        <v>46195.6807522338</v>
       </c>
       <c r="T142" t="n">
         <v>1</v>
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="V142" t="inlineStr"/>
@@ -15323,7 +15335,7 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr"/>
@@ -15337,17 +15349,17 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>6279</v>
+        <v>6278</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -15357,7 +15369,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -15367,7 +15379,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -15398,7 +15410,7 @@
         <v>2026</v>
       </c>
       <c r="P143" t="n">
-        <v>17645954</v>
+        <v>17539751</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
@@ -15411,7 +15423,7 @@
         </is>
       </c>
       <c r="S143" s="1" t="n">
-        <v>46175.3523468287</v>
+        <v>46175.35234628472</v>
       </c>
       <c r="T143" t="n">
         <v>1</v>
@@ -15450,11 +15462,11 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>6404</v>
+        <v>6279</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -15474,7 +15486,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -15505,7 +15517,7 @@
         <v>2026</v>
       </c>
       <c r="P144" t="n">
-        <v>16962138</v>
+        <v>17645954</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
@@ -15518,14 +15530,14 @@
         </is>
       </c>
       <c r="S144" s="1" t="n">
-        <v>46175.35234844907</v>
+        <v>46175.3523468287</v>
       </c>
       <c r="T144" t="n">
         <v>1</v>
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="V144" t="inlineStr"/>
@@ -15557,11 +15569,11 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -15612,11 +15624,11 @@
         <v>2026</v>
       </c>
       <c r="P145" t="n">
-        <v>17955173</v>
+        <v>16962138</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>Ryan Godinho</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -15625,14 +15637,14 @@
         </is>
       </c>
       <c r="S145" s="1" t="n">
-        <v>46195.37223452546</v>
+        <v>46175.35234844907</v>
       </c>
       <c r="T145" t="n">
         <v>1</v>
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="V145" t="inlineStr"/>
@@ -15644,7 +15656,7 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>Ryan Godinho</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr"/>
@@ -15658,17 +15670,17 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -15678,7 +15690,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -15719,11 +15731,11 @@
         <v>2026</v>
       </c>
       <c r="P146" t="n">
-        <v>17955381</v>
+        <v>17955173</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Ryan Godinho</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -15732,14 +15744,14 @@
         </is>
       </c>
       <c r="S146" s="1" t="n">
-        <v>46176.48076974537</v>
+        <v>46195.37223452546</v>
       </c>
       <c r="T146" t="n">
         <v>1</v>
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="V146" t="inlineStr"/>
@@ -15751,7 +15763,7 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Ryan Godinho</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr"/>
@@ -15765,17 +15777,17 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -15785,7 +15797,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -15826,7 +15838,7 @@
         <v>2026</v>
       </c>
       <c r="P147" t="n">
-        <v>17955235</v>
+        <v>17955381</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
@@ -15839,7 +15851,7 @@
         </is>
       </c>
       <c r="S147" s="1" t="n">
-        <v>46176.48077083333</v>
+        <v>46176.48076974537</v>
       </c>
       <c r="T147" t="n">
         <v>1</v>
@@ -15878,11 +15890,11 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -15933,7 +15945,7 @@
         <v>2026</v>
       </c>
       <c r="P148" t="n">
-        <v>18056726</v>
+        <v>17955235</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
@@ -15946,7 +15958,7 @@
         </is>
       </c>
       <c r="S148" s="1" t="n">
-        <v>46176.48077190972</v>
+        <v>46176.48077083333</v>
       </c>
       <c r="T148" t="n">
         <v>1</v>
@@ -15985,11 +15997,11 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>6885</v>
+        <v>6779</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -16040,11 +16052,11 @@
         <v>2026</v>
       </c>
       <c r="P149" t="n">
-        <v>18128695</v>
+        <v>18056726</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -16053,14 +16065,14 @@
         </is>
       </c>
       <c r="S149" s="1" t="n">
-        <v>46175.35235043982</v>
+        <v>46176.48077190972</v>
       </c>
       <c r="T149" t="n">
         <v>1</v>
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="V149" t="inlineStr"/>
@@ -16072,7 +16084,7 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr"/>
@@ -16092,11 +16104,11 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>5417</v>
+        <v>6885</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -16106,7 +16118,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -16116,14 +16128,14 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>11297</v>
+        <v>1628</v>
       </c>
       <c r="H150" t="n">
-        <v>0</v>
+        <v>1581</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -16132,12 +16144,12 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Retorno do Check-List</t>
+          <t>Outras Receitas</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
       <c r="L150" s="1" t="n">
-        <v>46185</v>
+        <v>46195</v>
       </c>
       <c r="M150" t="inlineStr"/>
       <c r="N150" t="n">
@@ -16147,11 +16159,11 @@
         <v>2026</v>
       </c>
       <c r="P150" t="n">
-        <v>17399441</v>
+        <v>18128695</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -16160,14 +16172,14 @@
         </is>
       </c>
       <c r="S150" s="1" t="n">
-        <v>46174.77831076389</v>
+        <v>46175.35235043982</v>
       </c>
       <c r="T150" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="V150" t="inlineStr"/>
@@ -16179,7 +16191,7 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>Juan Rodrigues</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr"/>
@@ -16193,17 +16205,17 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>5617</v>
+        <v>5417</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -16223,7 +16235,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -16254,11 +16266,11 @@
         <v>2026</v>
       </c>
       <c r="P151" t="n">
-        <v>17407952</v>
+        <v>17399441</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -16267,14 +16279,14 @@
         </is>
       </c>
       <c r="S151" s="1" t="n">
-        <v>46174.77831438657</v>
+        <v>46174.77831076389</v>
       </c>
       <c r="T151" t="n">
         <v>11</v>
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="V151" t="inlineStr"/>
@@ -16300,17 +16312,17 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Karina Santos</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>6224</v>
+        <v>5617</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -16330,7 +16342,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -16361,7 +16373,7 @@
         <v>2026</v>
       </c>
       <c r="P152" t="n">
-        <v>17689060</v>
+        <v>17407952</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
@@ -16374,7 +16386,7 @@
         </is>
       </c>
       <c r="S152" s="1" t="n">
-        <v>46174.77832376157</v>
+        <v>46174.77831438657</v>
       </c>
       <c r="T152" t="n">
         <v>11</v>
@@ -16413,11 +16425,11 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>6278</v>
+        <v>6224</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -16427,7 +16439,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -16437,7 +16449,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -16468,11 +16480,11 @@
         <v>2026</v>
       </c>
       <c r="P153" t="n">
-        <v>17539887</v>
+        <v>17689060</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -16481,14 +16493,14 @@
         </is>
       </c>
       <c r="S153" s="1" t="n">
-        <v>46174.77832450232</v>
+        <v>46174.77832376157</v>
       </c>
       <c r="T153" t="n">
         <v>11</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="V153" t="inlineStr"/>
@@ -16514,17 +16526,17 @@
       </c>
       <c r="AG153" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>6704</v>
+        <v>6278</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -16534,7 +16546,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -16575,11 +16587,11 @@
         <v>2026</v>
       </c>
       <c r="P154" t="n">
-        <v>17955431</v>
+        <v>17539887</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -16588,14 +16600,14 @@
         </is>
       </c>
       <c r="S154" s="1" t="n">
-        <v>46174.77833082176</v>
+        <v>46174.77832450232</v>
       </c>
       <c r="T154" t="n">
         <v>11</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="V154" t="inlineStr"/>
@@ -16627,11 +16639,11 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -16641,7 +16653,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -16682,7 +16694,7 @@
         <v>2026</v>
       </c>
       <c r="P155" t="n">
-        <v>17955271</v>
+        <v>17955431</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -16695,7 +16707,7 @@
         </is>
       </c>
       <c r="S155" s="1" t="n">
-        <v>46174.77833136574</v>
+        <v>46174.77833082176</v>
       </c>
       <c r="T155" t="n">
         <v>11</v>
@@ -16734,11 +16746,11 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -16789,7 +16801,7 @@
         <v>2026</v>
       </c>
       <c r="P156" t="n">
-        <v>18056829</v>
+        <v>17955271</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -16802,7 +16814,7 @@
         </is>
       </c>
       <c r="S156" s="1" t="n">
-        <v>46174.77833190972</v>
+        <v>46174.77833136574</v>
       </c>
       <c r="T156" t="n">
         <v>11</v>
@@ -16841,11 +16853,11 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>6885</v>
+        <v>6779</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -16896,11 +16908,11 @@
         <v>2026</v>
       </c>
       <c r="P157" t="n">
-        <v>18128900</v>
+        <v>18056829</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -16909,14 +16921,14 @@
         </is>
       </c>
       <c r="S157" s="1" t="n">
-        <v>46174.77833336806</v>
+        <v>46174.77833190972</v>
       </c>
       <c r="T157" t="n">
         <v>11</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="V157" t="inlineStr"/>
@@ -16948,11 +16960,11 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>6949</v>
+        <v>6885</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -16962,7 +16974,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -16972,61 +16984,61 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>9792</v>
+        <v>11297</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Aplicação de Modelo - Pendente</t>
+          <t>Retorno do Check-List</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
       <c r="L158" s="1" t="n">
-        <v>46181</v>
+        <v>46185</v>
       </c>
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O158" t="n">
         <v>2026</v>
       </c>
       <c r="P158" t="n">
-        <v>18166582</v>
-      </c>
-      <c r="Q158" t="inlineStr"/>
+        <v>18128900</v>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>Isabela Lemos</t>
+        </is>
+      </c>
       <c r="R158" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S158" s="1" t="n">
-        <v>46178.66434606481</v>
+        <v>46174.77833336806</v>
       </c>
       <c r="T158" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="U158" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
-        </is>
-      </c>
-      <c r="V158" t="inlineStr">
-        <is>
-          <t>Rotina de Cliente Sem Modelo - CodCliente: 6949; Tarefa Incluida: 9792; Vencimento: 02/06/2026 00:00:00; UsuarioResponsavel: pvolpe - Data Comentário: 01/06/2026 10:03</t>
-        </is>
-      </c>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr"/>
       <c r="W158" t="inlineStr"/>
       <c r="X158" t="inlineStr"/>
       <c r="Y158" t="inlineStr"/>
@@ -17035,7 +17047,7 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Juan Rodrigues</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr"/>
@@ -17047,15 +17059,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG158" t="inlineStr"/>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>Fernanda Araujo</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -17096,7 +17112,7 @@
       </c>
       <c r="K159" t="inlineStr"/>
       <c r="L159" s="1" t="n">
-        <v>46191</v>
+        <v>46181</v>
       </c>
       <c r="M159" t="inlineStr"/>
       <c r="N159" t="n">
@@ -17106,7 +17122,7 @@
         <v>2026</v>
       </c>
       <c r="P159" t="n">
-        <v>18186547</v>
+        <v>18166582</v>
       </c>
       <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr">
@@ -17115,19 +17131,19 @@
         </is>
       </c>
       <c r="S159" s="1" t="n">
-        <v>46190.68306622685</v>
+        <v>46178.66434606481</v>
       </c>
       <c r="T159" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
+          <t>TEC GRUA</t>
         </is>
       </c>
       <c r="V159" t="inlineStr">
         <is>
-          <t>Rotina de Cliente Sem Modelo - CodCliente: 6962; Tarefa Incluida: 9792; Vencimento: 18/06/2026 00:00:00; UsuarioResponsavel: pvolpe - Data Comentário: 17/06/2026 11:09</t>
+          <t>Rotina de Cliente Sem Modelo - CodCliente: 6949; Tarefa Incluida: 9792; Vencimento: 02/06/2026 00:00:00; UsuarioResponsavel: pvolpe - Data Comentário: 01/06/2026 10:03</t>
         </is>
       </c>
       <c r="W159" t="inlineStr"/>
@@ -17154,11 +17170,11 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -17209,7 +17225,7 @@
         <v>2026</v>
       </c>
       <c r="P160" t="n">
-        <v>18186548</v>
+        <v>18186547</v>
       </c>
       <c r="Q160" t="inlineStr"/>
       <c r="R160" t="inlineStr">
@@ -17218,7 +17234,7 @@
         </is>
       </c>
       <c r="S160" s="1" t="n">
-        <v>46190.68306658565</v>
+        <v>46190.68306622685</v>
       </c>
       <c r="T160" t="n">
         <v>5</v>
@@ -17230,7 +17246,7 @@
       </c>
       <c r="V160" t="inlineStr">
         <is>
-          <t>Rotina de Cliente Sem Modelo - CodCliente: 6963; Tarefa Incluida: 9792; Vencimento: 18/06/2026 00:00:00; UsuarioResponsavel: pvolpe - Data Comentário: 17/06/2026 11:09</t>
+          <t>Rotina de Cliente Sem Modelo - CodCliente: 6962; Tarefa Incluida: 9792; Vencimento: 18/06/2026 00:00:00; UsuarioResponsavel: pvolpe - Data Comentário: 17/06/2026 11:09</t>
         </is>
       </c>
       <c r="W160" t="inlineStr"/>
@@ -17257,11 +17273,11 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>6548</v>
+        <v>6963</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -17281,14 +17297,14 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>11550</v>
+        <v>9792</v>
       </c>
       <c r="H161" t="n">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -17297,45 +17313,45 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Bloco K</t>
+          <t>Aplicação de Modelo - Pendente</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
       <c r="L161" s="1" t="n">
-        <v>46195</v>
+        <v>46191</v>
       </c>
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O161" t="n">
         <v>2026</v>
       </c>
       <c r="P161" t="n">
-        <v>17988600</v>
-      </c>
-      <c r="Q161" t="inlineStr">
-        <is>
-          <t>Cristiana Grizostomo</t>
-        </is>
-      </c>
+        <v>18186548</v>
+      </c>
+      <c r="Q161" t="inlineStr"/>
       <c r="R161" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S161" s="1" t="n">
-        <v>46175.37756516204</v>
+        <v>46190.68306658565</v>
       </c>
       <c r="T161" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
-        </is>
-      </c>
-      <c r="V161" t="inlineStr"/>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Rotina de Cliente Sem Modelo - CodCliente: 6963; Tarefa Incluida: 9792; Vencimento: 18/06/2026 00:00:00; UsuarioResponsavel: pvolpe - Data Comentário: 17/06/2026 11:09</t>
+        </is>
+      </c>
       <c r="W161" t="inlineStr"/>
       <c r="X161" t="inlineStr"/>
       <c r="Y161" t="inlineStr"/>
@@ -17344,7 +17360,7 @@
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr"/>
@@ -17356,19 +17372,15 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG161" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+      <c r="AG161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -17383,7 +17395,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -17419,11 +17431,11 @@
         <v>2026</v>
       </c>
       <c r="P162" t="n">
-        <v>18048490</v>
+        <v>17988600</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -17432,14 +17444,14 @@
         </is>
       </c>
       <c r="S162" s="1" t="n">
-        <v>46175.79373244213</v>
+        <v>46175.37756516204</v>
       </c>
       <c r="T162" t="n">
         <v>1</v>
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="V162" t="inlineStr"/>
@@ -17451,7 +17463,7 @@
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr"/>
@@ -17463,15 +17475,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG162" t="inlineStr"/>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -17486,19 +17502,19 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>11645</v>
+        <v>11550</v>
       </c>
       <c r="H163" t="n">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -17507,50 +17523,45 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Cadastro SCI Web</t>
+          <t>Bloco K</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
       <c r="L163" s="1" t="n">
-        <v>46192</v>
-      </c>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
+        <v>46195</v>
+      </c>
+      <c r="M163" t="inlineStr"/>
       <c r="N163" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O163" t="n">
         <v>2026</v>
       </c>
       <c r="P163" t="n">
-        <v>18166587</v>
-      </c>
-      <c r="Q163" t="inlineStr"/>
+        <v>18048490</v>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>Denis Reis</t>
+        </is>
+      </c>
       <c r="R163" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S163" s="1" t="n">
-        <v>46192.44789648148</v>
+        <v>46175.79373244213</v>
       </c>
       <c r="T163" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
-        </is>
-      </c>
-      <c r="V163" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 30/06/2026 
-AGUARDANDO IMPLANTAÇÃO DO CLIENTE - Data Comentário: 08/06/2026 17:44</t>
-        </is>
-      </c>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr"/>
       <c r="W163" t="inlineStr"/>
       <c r="X163" t="inlineStr"/>
       <c r="Y163" t="inlineStr"/>
@@ -17559,7 +17570,7 @@
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>Nicole Oliveira</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr"/>
@@ -17575,11 +17586,11 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -17620,9 +17631,13 @@
       </c>
       <c r="K164" t="inlineStr"/>
       <c r="L164" s="1" t="n">
-        <v>46190</v>
-      </c>
-      <c r="M164" t="inlineStr"/>
+        <v>46192</v>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
       <c r="N164" t="n">
         <v>6</v>
       </c>
@@ -17630,7 +17645,7 @@
         <v>2026</v>
       </c>
       <c r="P164" t="n">
-        <v>18186561</v>
+        <v>18166587</v>
       </c>
       <c r="Q164" t="inlineStr"/>
       <c r="R164" t="inlineStr">
@@ -17639,19 +17654,20 @@
         </is>
       </c>
       <c r="S164" s="1" t="n">
-        <v>46190.62401390047</v>
+        <v>46192.44789648148</v>
       </c>
       <c r="T164" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
+          <t>TEC GRUA</t>
         </is>
       </c>
       <c r="V164" t="inlineStr">
         <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6962; Tarefa Incluida: 11645; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: pvolpe - Data Comentário: 17/06/2026 11:09</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 30/06/2026 
+AGUARDANDO IMPLANTAÇÃO DO CLIENTE - Data Comentário: 08/06/2026 17:44</t>
         </is>
       </c>
       <c r="W164" t="inlineStr"/>
@@ -17678,11 +17694,11 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -17733,7 +17749,7 @@
         <v>2026</v>
       </c>
       <c r="P165" t="n">
-        <v>18186562</v>
+        <v>18186561</v>
       </c>
       <c r="Q165" t="inlineStr"/>
       <c r="R165" t="inlineStr">
@@ -17742,7 +17758,7 @@
         </is>
       </c>
       <c r="S165" s="1" t="n">
-        <v>46190.62440369213</v>
+        <v>46190.62401390047</v>
       </c>
       <c r="T165" t="n">
         <v>6</v>
@@ -17754,7 +17770,7 @@
       </c>
       <c r="V165" t="inlineStr">
         <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6963; Tarefa Incluida: 11645; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: pvolpe - Data Comentário: 17/06/2026 11:09</t>
+          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6962; Tarefa Incluida: 11645; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: pvolpe - Data Comentário: 17/06/2026 11:09</t>
         </is>
       </c>
       <c r="W165" t="inlineStr"/>
@@ -17781,11 +17797,11 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>6627</v>
+        <v>6963</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -17800,19 +17816,19 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G166" t="n">
-        <v>11752</v>
+        <v>11645</v>
       </c>
       <c r="H166" t="n">
-        <v>11751</v>
+        <v>0</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -17821,45 +17837,45 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Cobrança da Carta de Correção</t>
+          <t>Cadastro SCI Web</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
       <c r="L166" s="1" t="n">
-        <v>46175</v>
+        <v>46190</v>
       </c>
       <c r="M166" t="inlineStr"/>
       <c r="N166" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O166" t="n">
         <v>2026</v>
       </c>
       <c r="P166" t="n">
-        <v>18173140</v>
-      </c>
-      <c r="Q166" t="inlineStr">
-        <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
+        <v>18186562</v>
+      </c>
+      <c r="Q166" t="inlineStr"/>
       <c r="R166" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S166" s="1" t="n">
-        <v>46175.79371145833</v>
+        <v>46190.62440369213</v>
       </c>
       <c r="T166" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="U166" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="V166" t="inlineStr"/>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6963; Tarefa Incluida: 11645; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: pvolpe - Data Comentário: 17/06/2026 11:09</t>
+        </is>
+      </c>
       <c r="W166" t="inlineStr"/>
       <c r="X166" t="inlineStr"/>
       <c r="Y166" t="inlineStr"/>
@@ -17868,7 +17884,7 @@
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Nicole Oliveira</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr"/>
@@ -17912,10 +17928,10 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>11748</v>
+        <v>11752</v>
       </c>
       <c r="H167" t="n">
-        <v>11747</v>
+        <v>11751</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -17924,7 +17940,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Cobrança da Primeira NFe</t>
+          <t>Cobrança da Carta de Correção</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -17939,7 +17955,7 @@
         <v>2026</v>
       </c>
       <c r="P167" t="n">
-        <v>18173124</v>
+        <v>18173140</v>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
@@ -17952,7 +17968,7 @@
         </is>
       </c>
       <c r="S167" s="1" t="n">
-        <v>46175.79322700232</v>
+        <v>46175.79371145833</v>
       </c>
       <c r="T167" t="n">
         <v>21</v>
@@ -17987,11 +18003,11 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -18001,7 +18017,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -18042,7 +18058,7 @@
         <v>2026</v>
       </c>
       <c r="P168" t="n">
-        <v>18170383</v>
+        <v>18173124</v>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
@@ -18055,7 +18071,7 @@
         </is>
       </c>
       <c r="S168" s="1" t="n">
-        <v>46176.29345100695</v>
+        <v>46175.79322700232</v>
       </c>
       <c r="T168" t="n">
         <v>21</v>
@@ -18090,11 +18106,11 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -18104,7 +18120,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -18118,10 +18134,10 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>11750</v>
+        <v>11748</v>
       </c>
       <c r="H169" t="n">
-        <v>11749</v>
+        <v>11747</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -18130,7 +18146,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Cobrança da Última NFe</t>
+          <t>Cobrança da Primeira NFe</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -18145,7 +18161,7 @@
         <v>2026</v>
       </c>
       <c r="P169" t="n">
-        <v>18173132</v>
+        <v>18170383</v>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
@@ -18158,7 +18174,7 @@
         </is>
       </c>
       <c r="S169" s="1" t="n">
-        <v>46175.7934002662</v>
+        <v>46176.29345100695</v>
       </c>
       <c r="T169" t="n">
         <v>21</v>
@@ -18193,11 +18209,11 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -18207,7 +18223,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -18248,7 +18264,7 @@
         <v>2026</v>
       </c>
       <c r="P170" t="n">
-        <v>18170391</v>
+        <v>18173132</v>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
@@ -18261,7 +18277,7 @@
         </is>
       </c>
       <c r="S170" s="1" t="n">
-        <v>46176.29361072917</v>
+        <v>46175.7934002662</v>
       </c>
       <c r="T170" t="n">
         <v>21</v>
@@ -18296,11 +18312,11 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>6358</v>
+        <v>6628</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -18310,12 +18326,12 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -18324,10 +18340,10 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>6889</v>
+        <v>11750</v>
       </c>
       <c r="H171" t="n">
-        <v>1862</v>
+        <v>11749</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -18336,12 +18352,12 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Cobrança de conta de energia elétrica</t>
+          <t>Cobrança da Última NFe</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
       <c r="L171" s="1" t="n">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="n">
@@ -18351,23 +18367,27 @@
         <v>2026</v>
       </c>
       <c r="P171" t="n">
-        <v>17104929</v>
-      </c>
-      <c r="Q171" t="inlineStr"/>
+        <v>18170391</v>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>Denis Reis</t>
+        </is>
+      </c>
       <c r="R171" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S171" s="1" t="n">
-        <v>46175.45935876157</v>
+        <v>46176.29361072917</v>
       </c>
       <c r="T171" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>MACHADO</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="V171" t="inlineStr"/>
@@ -18379,7 +18399,7 @@
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>Rosilene Santos</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr"/>
@@ -18395,11 +18415,11 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>6627</v>
+        <v>6358</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -18414,7 +18434,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -18450,27 +18470,23 @@
         <v>2026</v>
       </c>
       <c r="P172" t="n">
-        <v>18048460</v>
-      </c>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
+        <v>17104929</v>
+      </c>
+      <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S172" s="1" t="n">
-        <v>46175.79252688657</v>
+        <v>46175.45935876157</v>
       </c>
       <c r="T172" t="n">
         <v>20</v>
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>MACHADO</t>
         </is>
       </c>
       <c r="V172" t="inlineStr"/>
@@ -18482,7 +18498,7 @@
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Rosilene Santos</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr"/>
@@ -18526,10 +18542,10 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>11760</v>
+        <v>6889</v>
       </c>
       <c r="H173" t="n">
-        <v>11759</v>
+        <v>1862</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -18538,12 +18554,12 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Cobrança de Faturamento</t>
+          <t>Cobrança de conta de energia elétrica</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
       <c r="L173" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="n">
@@ -18553,7 +18569,7 @@
         <v>2026</v>
       </c>
       <c r="P173" t="n">
-        <v>18173148</v>
+        <v>18048460</v>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
@@ -18566,10 +18582,10 @@
         </is>
       </c>
       <c r="S173" s="1" t="n">
-        <v>46175.79349667824</v>
+        <v>46175.79252688657</v>
       </c>
       <c r="T173" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U173" t="inlineStr">
         <is>
@@ -18601,11 +18617,11 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -18615,7 +18631,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -18656,7 +18672,7 @@
         <v>2026</v>
       </c>
       <c r="P174" t="n">
-        <v>18170399</v>
+        <v>18173148</v>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
@@ -18669,7 +18685,7 @@
         </is>
       </c>
       <c r="S174" s="1" t="n">
-        <v>46176.29370952546</v>
+        <v>46175.79349667824</v>
       </c>
       <c r="T174" t="n">
         <v>21</v>
@@ -18704,11 +18720,11 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>6358</v>
+        <v>6628</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -18718,12 +18734,12 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -18732,10 +18748,10 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>6223</v>
+        <v>11760</v>
       </c>
       <c r="H175" t="n">
-        <v>6222</v>
+        <v>11759</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -18744,7 +18760,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Cobrança de NF saída (Mensal)</t>
+          <t>Cobrança de Faturamento</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -18759,23 +18775,27 @@
         <v>2026</v>
       </c>
       <c r="P175" t="n">
-        <v>18176265</v>
-      </c>
-      <c r="Q175" t="inlineStr"/>
+        <v>18170399</v>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>Denis Reis</t>
+        </is>
+      </c>
       <c r="R175" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S175" s="1" t="n">
-        <v>46175.45924872685</v>
+        <v>46176.29370952546</v>
       </c>
       <c r="T175" t="n">
         <v>21</v>
       </c>
       <c r="U175" t="inlineStr">
         <is>
-          <t>MACHADO</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="V175" t="inlineStr"/>
@@ -18787,7 +18807,7 @@
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>ex-funcionario</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr"/>
@@ -18803,11 +18823,11 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>6419</v>
+        <v>6358</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA (FILIAL 1)</t>
+          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -18858,7 +18878,7 @@
         <v>2026</v>
       </c>
       <c r="P176" t="n">
-        <v>18173728</v>
+        <v>18176265</v>
       </c>
       <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr">
@@ -18867,7 +18887,7 @@
         </is>
       </c>
       <c r="S176" s="1" t="n">
-        <v>46175.45924846065</v>
+        <v>46175.45924872685</v>
       </c>
       <c r="T176" t="n">
         <v>21</v>
@@ -18902,11 +18922,11 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>6627</v>
+        <v>6419</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA (FILIAL 1)</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -18921,7 +18941,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -18930,10 +18950,10 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>11766</v>
+        <v>6223</v>
       </c>
       <c r="H177" t="n">
-        <v>11765</v>
+        <v>6222</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -18942,7 +18962,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Cobrança de NF's Canceladas</t>
+          <t>Cobrança de NF saída (Mensal)</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -18957,27 +18977,23 @@
         <v>2026</v>
       </c>
       <c r="P177" t="n">
-        <v>18173156</v>
-      </c>
-      <c r="Q177" t="inlineStr">
-        <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
+        <v>18173728</v>
+      </c>
+      <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S177" s="1" t="n">
-        <v>46175.79356550926</v>
+        <v>46175.45924846065</v>
       </c>
       <c r="T177" t="n">
         <v>21</v>
       </c>
       <c r="U177" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>MACHADO</t>
         </is>
       </c>
       <c r="V177" t="inlineStr"/>
@@ -18989,7 +19005,7 @@
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>ex-funcionario</t>
         </is>
       </c>
       <c r="AB177" t="inlineStr"/>
@@ -19005,11 +19021,11 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -19019,7 +19035,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -19060,7 +19076,7 @@
         <v>2026</v>
       </c>
       <c r="P178" t="n">
-        <v>18170407</v>
+        <v>18173156</v>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
@@ -19073,7 +19089,7 @@
         </is>
       </c>
       <c r="S178" s="1" t="n">
-        <v>46176.29379065972</v>
+        <v>46175.79356550926</v>
       </c>
       <c r="T178" t="n">
         <v>21</v>
@@ -19108,11 +19124,11 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -19122,7 +19138,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -19136,10 +19152,10 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>11768</v>
+        <v>11766</v>
       </c>
       <c r="H179" t="n">
-        <v>11767</v>
+        <v>11765</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -19148,7 +19164,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Cobrança de NF's Inutilizadas</t>
+          <t>Cobrança de NF's Canceladas</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -19163,7 +19179,7 @@
         <v>2026</v>
       </c>
       <c r="P179" t="n">
-        <v>18173164</v>
+        <v>18170407</v>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
@@ -19176,7 +19192,7 @@
         </is>
       </c>
       <c r="S179" s="1" t="n">
-        <v>46175.79363005787</v>
+        <v>46176.29379065972</v>
       </c>
       <c r="T179" t="n">
         <v>21</v>
@@ -19211,11 +19227,11 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -19225,7 +19241,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -19266,7 +19282,7 @@
         <v>2026</v>
       </c>
       <c r="P180" t="n">
-        <v>18170415</v>
+        <v>18173164</v>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
@@ -19279,7 +19295,7 @@
         </is>
       </c>
       <c r="S180" s="1" t="n">
-        <v>46176.29387045139</v>
+        <v>46175.79363005787</v>
       </c>
       <c r="T180" t="n">
         <v>21</v>
@@ -19314,11 +19330,11 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>6548</v>
+        <v>6628</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -19328,12 +19344,12 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -19342,10 +19358,10 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>1913</v>
+        <v>11768</v>
       </c>
       <c r="H181" t="n">
-        <v>1862</v>
+        <v>11767</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -19354,12 +19370,12 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Depreciação</t>
+          <t>Cobrança de NF's Inutilizadas</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
       <c r="L181" s="1" t="n">
-        <v>46195</v>
+        <v>46175</v>
       </c>
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="n">
@@ -19369,11 +19385,11 @@
         <v>2026</v>
       </c>
       <c r="P181" t="n">
-        <v>17988576</v>
+        <v>18170415</v>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
@@ -19382,14 +19398,14 @@
         </is>
       </c>
       <c r="S181" s="1" t="n">
-        <v>46195.44681893518</v>
+        <v>46176.29387045139</v>
       </c>
       <c r="T181" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="U181" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="V181" t="inlineStr"/>
@@ -19413,19 +19429,15 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG181" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+      <c r="AG181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -19440,7 +19452,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -19476,11 +19488,11 @@
         <v>2026</v>
       </c>
       <c r="P182" t="n">
-        <v>18048430</v>
+        <v>17988576</v>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
@@ -19489,14 +19501,14 @@
         </is>
       </c>
       <c r="S182" s="1" t="n">
-        <v>46195.36181645833</v>
+        <v>46195.44681893518</v>
       </c>
       <c r="T182" t="n">
         <v>1</v>
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="V182" t="inlineStr"/>
@@ -19508,7 +19520,7 @@
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr"/>
@@ -19520,15 +19532,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG182" t="inlineStr"/>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>6945</v>
+        <v>6627</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -19538,7 +19554,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -19552,10 +19568,10 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>11617</v>
+        <v>1913</v>
       </c>
       <c r="H183" t="n">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -19564,18 +19580,14 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - EF I</t>
+          <t>Depreciação</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
       <c r="L183" s="1" t="n">
-        <v>46192</v>
-      </c>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
+        <v>46195</v>
+      </c>
+      <c r="M183" t="inlineStr"/>
       <c r="N183" t="n">
         <v>5</v>
       </c>
@@ -19583,31 +19595,30 @@
         <v>2026</v>
       </c>
       <c r="P183" t="n">
-        <v>18163277</v>
-      </c>
-      <c r="Q183" t="inlineStr"/>
+        <v>18048430</v>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>Denis Reis</t>
+        </is>
+      </c>
       <c r="R183" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S183" s="1" t="n">
-        <v>46189.73474795139</v>
+        <v>46195.36181645833</v>
       </c>
       <c r="T183" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U183" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="V183" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 30/06/2026 
-AINDA NÃO HOUVE A REUNIÃO DE IMPLANTAÇÃO - Data Comentário: 10/06/2026 16:18</t>
-        </is>
-      </c>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr"/>
       <c r="W183" t="inlineStr"/>
       <c r="X183" t="inlineStr"/>
       <c r="Y183" t="inlineStr"/>
@@ -19616,7 +19627,7 @@
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>Juan Rodrigues</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="AB183" t="inlineStr"/>
@@ -19632,11 +19643,11 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>6548</v>
+        <v>6945</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -19646,12 +19657,12 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -19660,7 +19671,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>1876</v>
+        <v>11617</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -19672,14 +19683,18 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Est - ICMS RPA - CÓD. 046-2</t>
+          <t>Envio de ATA de Implantação - EF I</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
       <c r="L184" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="M184" t="inlineStr"/>
+        <v>46192</v>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
       <c r="N184" t="n">
         <v>5</v>
       </c>
@@ -19687,32 +19702,29 @@
         <v>2026</v>
       </c>
       <c r="P184" t="n">
-        <v>17988552</v>
-      </c>
-      <c r="Q184" t="inlineStr">
-        <is>
-          <t>Cristiana Grizostomo</t>
-        </is>
-      </c>
+        <v>18163277</v>
+      </c>
+      <c r="Q184" t="inlineStr"/>
       <c r="R184" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S184" s="1" t="n">
-        <v>46188.76686311343</v>
+        <v>46189.73474795139</v>
       </c>
       <c r="T184" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U184" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="V184" t="inlineStr">
         <is>
-          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 15/06/2026 18:24:08. - Data Comentário: 15/06/2026 18:23</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 30/06/2026 
+AINDA NÃO HOUVE A REUNIÃO DE IMPLANTAÇÃO - Data Comentário: 10/06/2026 16:18</t>
         </is>
       </c>
       <c r="W184" t="inlineStr"/>
@@ -19723,7 +19735,7 @@
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>ex-funcionario</t>
+          <t>Juan Rodrigues</t>
         </is>
       </c>
       <c r="AB184" t="inlineStr"/>
@@ -19732,22 +19744,18 @@
       <c r="AE184" t="inlineStr"/>
       <c r="AF184" t="inlineStr">
         <is>
-          <t>Imposto</t>
-        </is>
-      </c>
-      <c r="AG184" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>6358</v>
+        <v>6548</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -19771,7 +19779,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>11411</v>
+        <v>1876</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -19783,7 +19791,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Est - ICMS RPA - CÓD. 046-2 (GO)</t>
+          <t>Est - ICMS RPA - CÓD. 046-2</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -19798,28 +19806,32 @@
         <v>2026</v>
       </c>
       <c r="P185" t="n">
-        <v>17105179</v>
-      </c>
-      <c r="Q185" t="inlineStr"/>
+        <v>17988552</v>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>Cristiana Grizostomo</t>
+        </is>
+      </c>
       <c r="R185" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S185" s="1" t="n">
-        <v>46189.52284545139</v>
+        <v>46188.76686311343</v>
       </c>
       <c r="T185" t="n">
         <v>5</v>
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>MACHADO</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="V185" t="inlineStr">
         <is>
-          <t>Imposto enviado via SCI Report - Data Comentário: 16/06/2026 09:31</t>
+          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 15/06/2026 18:24:08. - Data Comentário: 15/06/2026 18:23</t>
         </is>
       </c>
       <c r="W185" t="inlineStr"/>
@@ -19830,7 +19842,7 @@
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>Juan Rodrigues</t>
+          <t>ex-funcionario</t>
         </is>
       </c>
       <c r="AB185" t="inlineStr"/>
@@ -19842,15 +19854,19 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG185" t="inlineStr"/>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>6419</v>
+        <v>6358</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA (FILIAL 1)</t>
+          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -19901,7 +19917,7 @@
         <v>2026</v>
       </c>
       <c r="P186" t="n">
-        <v>17100302</v>
+        <v>17105179</v>
       </c>
       <c r="Q186" t="inlineStr"/>
       <c r="R186" t="inlineStr">
@@ -19910,7 +19926,7 @@
         </is>
       </c>
       <c r="S186" s="1" t="n">
-        <v>46189.40379987269</v>
+        <v>46189.52284545139</v>
       </c>
       <c r="T186" t="n">
         <v>5</v>
@@ -19920,7 +19936,11 @@
           <t>MACHADO</t>
         </is>
       </c>
-      <c r="V186" t="inlineStr"/>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Imposto enviado via SCI Report - Data Comentário: 16/06/2026 09:31</t>
+        </is>
+      </c>
       <c r="W186" t="inlineStr"/>
       <c r="X186" t="inlineStr"/>
       <c r="Y186" t="inlineStr"/>
@@ -19929,7 +19949,7 @@
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>Rosilene Santos</t>
+          <t>Juan Rodrigues</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr"/>
@@ -19945,11 +19965,11 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>6627</v>
+        <v>6419</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA (FILIAL 1)</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -19964,7 +19984,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -20000,34 +20020,26 @@
         <v>2026</v>
       </c>
       <c r="P187" t="n">
-        <v>18048480</v>
-      </c>
-      <c r="Q187" t="inlineStr">
-        <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
+        <v>17100302</v>
+      </c>
+      <c r="Q187" t="inlineStr"/>
       <c r="R187" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S187" s="1" t="n">
-        <v>46190.45459201389</v>
+        <v>46189.40379987269</v>
       </c>
       <c r="T187" t="n">
         <v>5</v>
       </c>
       <c r="U187" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="V187" t="inlineStr">
-        <is>
-          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 17/06/2026 10:54:36. - Data Comentário: 17/06/2026 10:53</t>
-        </is>
-      </c>
+          <t>MACHADO</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr"/>
       <c r="W187" t="inlineStr"/>
       <c r="X187" t="inlineStr"/>
       <c r="Y187" t="inlineStr"/>
@@ -20036,7 +20048,7 @@
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>ex-funcionario</t>
+          <t>Rosilene Santos</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr"/>
@@ -20052,11 +20064,11 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -20066,7 +20078,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -20080,7 +20092,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>1875</v>
+        <v>11411</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -20092,12 +20104,12 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Est - Sintegra Interestadual</t>
+          <t>Est - ICMS RPA - CÓD. 046-2 (GO)</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
       <c r="L188" s="1" t="n">
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="M188" t="inlineStr"/>
       <c r="N188" t="n">
@@ -20107,7 +20119,7 @@
         <v>2026</v>
       </c>
       <c r="P188" t="n">
-        <v>17988659</v>
+        <v>18048480</v>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
@@ -20120,17 +20132,21 @@
         </is>
       </c>
       <c r="S188" s="1" t="n">
-        <v>46188.42692672454</v>
+        <v>46190.45459201389</v>
       </c>
       <c r="T188" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U188" t="inlineStr">
         <is>
           <t xml:space="preserve">GTG </t>
         </is>
       </c>
-      <c r="V188" t="inlineStr"/>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 17/06/2026 10:54:36. - Data Comentário: 17/06/2026 10:53</t>
+        </is>
+      </c>
       <c r="W188" t="inlineStr"/>
       <c r="X188" t="inlineStr"/>
       <c r="Y188" t="inlineStr"/>
@@ -20139,7 +20155,7 @@
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>ex-funcionario</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr"/>
@@ -20148,18 +20164,18 @@
       <c r="AE188" t="inlineStr"/>
       <c r="AF188" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>6359</v>
+        <v>6628</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>MACHADO PRESTACAO DE SERVICOS LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -20174,7 +20190,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -20183,7 +20199,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>1862</v>
+        <v>1875</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -20195,12 +20211,12 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Fechamento Mensal</t>
+          <t>Est - Sintegra Interestadual</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
       <c r="L189" s="1" t="n">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="n">
@@ -20210,23 +20226,27 @@
         <v>2026</v>
       </c>
       <c r="P189" t="n">
-        <v>17919470</v>
-      </c>
-      <c r="Q189" t="inlineStr"/>
+        <v>17988659</v>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>Denis Reis</t>
+        </is>
+      </c>
       <c r="R189" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S189" s="1" t="n">
-        <v>46173.00377197917</v>
+        <v>46188.42692672454</v>
       </c>
       <c r="T189" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U189" t="inlineStr">
         <is>
-          <t>MACHADO</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="V189" t="inlineStr"/>
@@ -20238,7 +20258,7 @@
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>Rosilene Santos</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr"/>
@@ -20247,18 +20267,18 @@
       <c r="AE189" t="inlineStr"/>
       <c r="AF189" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>6419</v>
+        <v>6359</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA (FILIAL 1)</t>
+          <t>MACHADO PRESTACAO DE SERVICOS LTDA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -20268,7 +20288,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -20309,7 +20329,7 @@
         <v>2026</v>
       </c>
       <c r="P190" t="n">
-        <v>17919634</v>
+        <v>17919470</v>
       </c>
       <c r="Q190" t="inlineStr"/>
       <c r="R190" t="inlineStr">
@@ -20318,7 +20338,7 @@
         </is>
       </c>
       <c r="S190" s="1" t="n">
-        <v>46173.00377278935</v>
+        <v>46173.00377197917</v>
       </c>
       <c r="T190" t="n">
         <v>7</v>
@@ -20353,11 +20373,11 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>6628</v>
+        <v>6419</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA (FILIAL 1)</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -20367,12 +20387,12 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -20408,27 +20428,23 @@
         <v>2026</v>
       </c>
       <c r="P191" t="n">
-        <v>18047769</v>
-      </c>
-      <c r="Q191" t="inlineStr">
-        <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
+        <v>17919634</v>
+      </c>
+      <c r="Q191" t="inlineStr"/>
       <c r="R191" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S191" s="1" t="n">
-        <v>46173.00379158564</v>
+        <v>46173.00377278935</v>
       </c>
       <c r="T191" t="n">
         <v>7</v>
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>MACHADO</t>
         </is>
       </c>
       <c r="V191" t="inlineStr"/>
@@ -20440,7 +20456,7 @@
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>ex-funcionario</t>
+          <t>Rosilene Santos</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr"/>
@@ -20456,11 +20472,11 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>6359</v>
+        <v>6628</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>MACHADO PRESTACAO DE SERVICOS LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -20475,7 +20491,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -20484,7 +20500,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>1879</v>
+        <v>1862</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -20496,12 +20512,12 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Fed - DAS</t>
+          <t>Fechamento Mensal</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
       <c r="L192" s="1" t="n">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="M192" t="inlineStr"/>
       <c r="N192" t="n">
@@ -20511,30 +20527,30 @@
         <v>2026</v>
       </c>
       <c r="P192" t="n">
-        <v>17108151</v>
-      </c>
-      <c r="Q192" t="inlineStr"/>
+        <v>18047769</v>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>Denis Reis</t>
+        </is>
+      </c>
       <c r="R192" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S192" s="1" t="n">
-        <v>46185.50688966435</v>
+        <v>46173.00379158564</v>
       </c>
       <c r="T192" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>MACHADO</t>
-        </is>
-      </c>
-      <c r="V192" t="inlineStr">
-        <is>
-          <t>Imposto enviado via SCI Report - Data Comentário: 10/06/2026 15:24</t>
-        </is>
-      </c>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr"/>
       <c r="W192" t="inlineStr"/>
       <c r="X192" t="inlineStr"/>
       <c r="Y192" t="inlineStr"/>
@@ -20543,7 +20559,7 @@
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>Juan Rodrigues</t>
+          <t>ex-funcionario</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr"/>
@@ -20552,18 +20568,18 @@
       <c r="AE192" t="inlineStr"/>
       <c r="AF192" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>6628</v>
+        <v>6359</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>MACHADO PRESTACAO DE SERVICOS LTDA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -20578,7 +20594,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -20614,32 +20630,28 @@
         <v>2026</v>
       </c>
       <c r="P193" t="n">
-        <v>17988681</v>
-      </c>
-      <c r="Q193" t="inlineStr">
-        <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
+        <v>17108151</v>
+      </c>
+      <c r="Q193" t="inlineStr"/>
       <c r="R193" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S193" s="1" t="n">
-        <v>46190.5532321412</v>
+        <v>46185.50688966435</v>
       </c>
       <c r="T193" t="n">
         <v>5</v>
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>MACHADO</t>
         </is>
       </c>
       <c r="V193" t="inlineStr">
         <is>
-          <t>Imposto enviado via SCI Report - Data Comentário: 17/06/2026 11:24</t>
+          <t>Imposto enviado via SCI Report - Data Comentário: 10/06/2026 15:24</t>
         </is>
       </c>
       <c r="W193" t="inlineStr"/>
@@ -20666,11 +20678,11 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>6358</v>
+        <v>6628</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -20680,12 +20692,12 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -20694,7 +20706,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>6805</v>
+        <v>1879</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -20706,18 +20718,14 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Fed - EFD - REINF - Entrega e PDF</t>
+          <t>Fed - DAS</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
       <c r="L194" s="1" t="n">
-        <v>46185</v>
-      </c>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
+        <v>46191</v>
+      </c>
+      <c r="M194" t="inlineStr"/>
       <c r="N194" t="n">
         <v>5</v>
       </c>
@@ -20725,28 +20733,32 @@
         <v>2026</v>
       </c>
       <c r="P194" t="n">
-        <v>17104882</v>
-      </c>
-      <c r="Q194" t="inlineStr"/>
+        <v>17988681</v>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>Denis Reis</t>
+        </is>
+      </c>
       <c r="R194" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S194" s="1" t="n">
-        <v>46182.69610043982</v>
+        <v>46190.5532321412</v>
       </c>
       <c r="T194" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="U194" t="inlineStr">
         <is>
-          <t>MACHADO</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="V194" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 09/06/2026 - Data Comentário: 09/06/2026 15:56</t>
+          <t>Imposto enviado via SCI Report - Data Comentário: 17/06/2026 11:24</t>
         </is>
       </c>
       <c r="W194" t="inlineStr"/>
@@ -20757,7 +20769,7 @@
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>Rosilene Santos</t>
+          <t>Juan Rodrigues</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr"/>
@@ -20766,18 +20778,18 @@
       <c r="AE194" t="inlineStr"/>
       <c r="AF194" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>6359</v>
+        <v>6358</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>MACHADO PRESTACAO DE SERVICOS LTDA</t>
+          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -20787,7 +20799,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -20832,7 +20844,7 @@
         <v>2026</v>
       </c>
       <c r="P195" t="n">
-        <v>17108429</v>
+        <v>17104882</v>
       </c>
       <c r="Q195" t="inlineStr"/>
       <c r="R195" t="inlineStr">
@@ -20841,7 +20853,7 @@
         </is>
       </c>
       <c r="S195" s="1" t="n">
-        <v>46182.7295358912</v>
+        <v>46182.69610043982</v>
       </c>
       <c r="T195" t="n">
         <v>11</v>
@@ -20880,11 +20892,11 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>6548</v>
+        <v>6359</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>MACHADO PRESTACAO DE SERVICOS LTDA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -20894,7 +20906,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -20929,7 +20941,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="N196" t="n">
@@ -20939,32 +20951,28 @@
         <v>2026</v>
       </c>
       <c r="P196" t="n">
-        <v>17222739</v>
-      </c>
-      <c r="Q196" t="inlineStr">
-        <is>
-          <t>Cristiana Grizostomo</t>
-        </is>
-      </c>
+        <v>17108429</v>
+      </c>
+      <c r="Q196" t="inlineStr"/>
       <c r="R196" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S196" s="1" t="n">
-        <v>46183.3528408912</v>
+        <v>46182.7295358912</v>
       </c>
       <c r="T196" t="n">
         <v>11</v>
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t>MACHADO</t>
         </is>
       </c>
       <c r="V196" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 10/06/2026 - Data Comentário: 09/06/2026 19:01</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 09/06/2026 - Data Comentário: 09/06/2026 15:56</t>
         </is>
       </c>
       <c r="W196" t="inlineStr"/>
@@ -20975,7 +20983,7 @@
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Rosilene Santos</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr"/>
@@ -20987,19 +20995,15 @@
           <t>Obrigação Acessória</t>
         </is>
       </c>
-      <c r="AG196" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+      <c r="AG196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -21014,7 +21018,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -21044,7 +21048,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="N197" t="n">
@@ -21054,11 +21058,11 @@
         <v>2026</v>
       </c>
       <c r="P197" t="n">
-        <v>18085516</v>
+        <v>17222739</v>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
@@ -21067,19 +21071,19 @@
         </is>
       </c>
       <c r="S197" s="1" t="n">
-        <v>46188.62121726852</v>
+        <v>46183.3528408912</v>
       </c>
       <c r="T197" t="n">
         <v>11</v>
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>Atraso da Operação, processo em elaboração conforme data prevista  Previsão para conclusão dia 16/06/2026 - Data Comentário: 15/06/2026 10:52</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 10/06/2026 - Data Comentário: 09/06/2026 19:01</t>
         </is>
       </c>
       <c r="W197" t="inlineStr"/>
@@ -21090,7 +21094,7 @@
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr"/>
@@ -21102,15 +21106,19 @@
           <t>Obrigação Acessória</t>
         </is>
       </c>
-      <c r="AG197" t="inlineStr"/>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -21120,7 +21128,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -21165,7 +21173,7 @@
         <v>2026</v>
       </c>
       <c r="P198" t="n">
-        <v>17988706</v>
+        <v>18085516</v>
       </c>
       <c r="Q198" t="inlineStr">
         <is>
@@ -21178,7 +21186,7 @@
         </is>
       </c>
       <c r="S198" s="1" t="n">
-        <v>46188.65584328704</v>
+        <v>46188.62121726852</v>
       </c>
       <c r="T198" t="n">
         <v>11</v>
@@ -21201,7 +21209,7 @@
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr"/>
@@ -21217,11 +21225,11 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>6358</v>
+        <v>6628</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -21231,12 +21239,12 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -21245,7 +21253,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>1894</v>
+        <v>6805</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -21257,14 +21265,18 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Fed - IPI Mensal - 5123</t>
+          <t>Fed - EFD - REINF - Entrega e PDF</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
       <c r="L199" s="1" t="n">
-        <v>46196</v>
-      </c>
-      <c r="M199" t="inlineStr"/>
+        <v>46185</v>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
       <c r="N199" t="n">
         <v>5</v>
       </c>
@@ -21272,28 +21284,32 @@
         <v>2026</v>
       </c>
       <c r="P199" t="n">
-        <v>17104685</v>
-      </c>
-      <c r="Q199" t="inlineStr"/>
+        <v>17988706</v>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>Denis Reis</t>
+        </is>
+      </c>
       <c r="R199" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S199" s="1" t="n">
-        <v>46192.46956674768</v>
+        <v>46188.65584328704</v>
       </c>
       <c r="T199" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>MACHADO</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="V199" t="inlineStr">
         <is>
-          <t>Imposto enviado via SCI Report - Data Comentário: 16/06/2026 09:30</t>
+          <t>Atraso da Operação, processo em elaboração conforme data prevista  Previsão para conclusão dia 16/06/2026 - Data Comentário: 15/06/2026 10:52</t>
         </is>
       </c>
       <c r="W199" t="inlineStr"/>
@@ -21304,7 +21320,7 @@
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>Juan Rodrigues</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr"/>
@@ -21313,18 +21329,18 @@
       <c r="AE199" t="inlineStr"/>
       <c r="AF199" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>6419</v>
+        <v>6358</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA (FILIAL 1)</t>
+          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -21375,7 +21391,7 @@
         <v>2026</v>
       </c>
       <c r="P200" t="n">
-        <v>17100120</v>
+        <v>17104685</v>
       </c>
       <c r="Q200" t="inlineStr"/>
       <c r="R200" t="inlineStr">
@@ -21384,7 +21400,7 @@
         </is>
       </c>
       <c r="S200" s="1" t="n">
-        <v>46189.4075749537</v>
+        <v>46192.46956674768</v>
       </c>
       <c r="T200" t="n">
         <v>0</v>
@@ -21394,7 +21410,11 @@
           <t>MACHADO</t>
         </is>
       </c>
-      <c r="V200" t="inlineStr"/>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Imposto enviado via SCI Report - Data Comentário: 16/06/2026 09:30</t>
+        </is>
+      </c>
       <c r="W200" t="inlineStr"/>
       <c r="X200" t="inlineStr"/>
       <c r="Y200" t="inlineStr"/>
@@ -21403,7 +21423,7 @@
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>Rosilene Santos</t>
+          <t>Juan Rodrigues</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr"/>
@@ -21419,11 +21439,11 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>6358</v>
+        <v>6419</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA</t>
+          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA (FILIAL 1)</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -21447,7 +21467,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>1885</v>
+        <v>1894</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -21459,22 +21479,22 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Fed - IRPJ/CSLL 3ª Quota corrigida</t>
+          <t>Fed - IPI Mensal - 5123</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
       <c r="L201" s="1" t="n">
-        <v>46199</v>
+        <v>46196</v>
       </c>
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O201" t="n">
         <v>2026</v>
       </c>
       <c r="P201" t="n">
-        <v>17104671</v>
+        <v>17100120</v>
       </c>
       <c r="Q201" t="inlineStr"/>
       <c r="R201" t="inlineStr">
@@ -21483,21 +21503,17 @@
         </is>
       </c>
       <c r="S201" s="1" t="n">
-        <v>46141.64666539352</v>
+        <v>46189.4075749537</v>
       </c>
       <c r="T201" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="U201" t="inlineStr">
         <is>
           <t>MACHADO</t>
         </is>
       </c>
-      <c r="V201" t="inlineStr">
-        <is>
-          <t>Tarefa baixada automaticamente, cliente baixado com prejuizo na 1 Quota. - Data Comentário: 29/04/2026 15:30</t>
-        </is>
-      </c>
+      <c r="V201" t="inlineStr"/>
       <c r="W201" t="inlineStr"/>
       <c r="X201" t="inlineStr"/>
       <c r="Y201" t="inlineStr"/>
@@ -21506,7 +21522,7 @@
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>ex-funcionario</t>
+          <t>Rosilene Santos</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr"/>
@@ -21550,7 +21566,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>1881</v>
+        <v>1885</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -21562,22 +21578,22 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>Fed - PIS/COFINS Cumulativo - 2172</t>
+          <t>Fed - IRPJ/CSLL 3ª Quota corrigida</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
       <c r="L202" s="1" t="n">
-        <v>46195</v>
+        <v>46199</v>
       </c>
       <c r="M202" t="inlineStr"/>
       <c r="N202" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O202" t="n">
         <v>2026</v>
       </c>
       <c r="P202" t="n">
-        <v>17104652</v>
+        <v>17104671</v>
       </c>
       <c r="Q202" t="inlineStr"/>
       <c r="R202" t="inlineStr">
@@ -21586,10 +21602,10 @@
         </is>
       </c>
       <c r="S202" s="1" t="n">
-        <v>46192.39896137732</v>
+        <v>46141.64666539352</v>
       </c>
       <c r="T202" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="U202" t="inlineStr">
         <is>
@@ -21598,7 +21614,7 @@
       </c>
       <c r="V202" t="inlineStr">
         <is>
-          <t>Imposto enviado via SCI Report - Data Comentário: 17/06/2026 17:53</t>
+          <t>Tarefa baixada automaticamente, cliente baixado com prejuizo na 1 Quota. - Data Comentário: 29/04/2026 15:30</t>
         </is>
       </c>
       <c r="W202" t="inlineStr"/>
@@ -21609,7 +21625,7 @@
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>Juan Rodrigues</t>
+          <t>ex-funcionario</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr"/>
@@ -21625,11 +21641,11 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>6627</v>
+        <v>6358</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -21644,7 +21660,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -21653,7 +21669,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -21665,7 +21681,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
+          <t>Fed - PIS/COFINS Cumulativo - 2172</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -21680,32 +21696,28 @@
         <v>2026</v>
       </c>
       <c r="P203" t="n">
-        <v>17968387</v>
-      </c>
-      <c r="Q203" t="inlineStr">
-        <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
+        <v>17104652</v>
+      </c>
+      <c r="Q203" t="inlineStr"/>
       <c r="R203" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S203" s="1" t="n">
-        <v>46191.33530436343</v>
+        <v>46192.39896137732</v>
       </c>
       <c r="T203" t="n">
         <v>1</v>
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>MACHADO</t>
         </is>
       </c>
       <c r="V203" t="inlineStr">
         <is>
-          <t>Tarefa baixada via Rotina SisAnalise x MGC - ExecutarPisCofinsZeradosOuComCredito. - Data Comentário: 18/06/2026 08:02</t>
+          <t>Imposto enviado via SCI Report - Data Comentário: 17/06/2026 17:53</t>
         </is>
       </c>
       <c r="W203" t="inlineStr"/>
@@ -21716,7 +21728,7 @@
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>ex-funcionario</t>
+          <t>Juan Rodrigues</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr"/>
@@ -21732,11 +21744,11 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -21751,7 +21763,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -21760,7 +21772,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>7026</v>
+        <v>1882</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -21772,12 +21784,12 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>Movimento - Sistema de Análise</t>
+          <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
       <c r="L204" s="1" t="n">
-        <v>46196</v>
+        <v>46195</v>
       </c>
       <c r="M204" t="inlineStr"/>
       <c r="N204" t="n">
@@ -21787,11 +21799,11 @@
         <v>2026</v>
       </c>
       <c r="P204" t="n">
-        <v>18094896</v>
+        <v>17968387</v>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
@@ -21800,19 +21812,19 @@
         </is>
       </c>
       <c r="S204" s="1" t="n">
-        <v>46195.59735277778</v>
+        <v>46191.33530436343</v>
       </c>
       <c r="T204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="V204" t="inlineStr">
         <is>
-          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 22/06/2026 14:15:49. - Data Comentário: 22/06/2026 14:15</t>
+          <t>Tarefa baixada via Rotina SisAnalise x MGC - ExecutarPisCofinsZeradosOuComCredito. - Data Comentário: 18/06/2026 08:02</t>
         </is>
       </c>
       <c r="W204" t="inlineStr"/>
@@ -21832,14 +21844,10 @@
       <c r="AE204" t="inlineStr"/>
       <c r="AF204" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG204" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -70239,11 +70247,11 @@
     </row>
     <row r="665">
       <c r="A665" t="n">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -70253,7 +70261,7 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
@@ -70263,11 +70271,11 @@
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G665" t="n">
-        <v>11001</v>
+        <v>7877</v>
       </c>
       <c r="H665" t="n">
         <v>0</v>
@@ -70279,7 +70287,7 @@
       </c>
       <c r="J665" t="inlineStr">
         <is>
-          <t>Movimento - Analise de Balanço Lucro Presumido</t>
+          <t>Movimento - Analise de Balanço Lucro Real</t>
         </is>
       </c>
       <c r="K665" t="inlineStr"/>
@@ -70294,7 +70302,7 @@
         <v>2026</v>
       </c>
       <c r="P665" t="n">
-        <v>16962451</v>
+        <v>17399327</v>
       </c>
       <c r="Q665" t="inlineStr">
         <is>
@@ -70307,19 +70315,19 @@
         </is>
       </c>
       <c r="S665" s="1" t="n">
-        <v>46143.12560633102</v>
+        <v>46143.12549351852</v>
       </c>
       <c r="T665" t="n">
         <v>-6</v>
       </c>
       <c r="U665" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="V665" t="inlineStr">
         <is>
-          <t>Baixado via rotina MGC x Analise Balanço em 01/05/2026 03:00:52. - Data Comentário: 01/05/2026 02:57</t>
+          <t>Baixado via rotina MGC x Analise Balanço em 01/05/2026 03:00:42. - Data Comentário: 01/05/2026 02:56</t>
         </is>
       </c>
       <c r="W665" t="inlineStr"/>
@@ -70346,11 +70354,11 @@
     </row>
     <row r="666">
       <c r="A666" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -70370,7 +70378,7 @@
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G666" t="n">
@@ -70401,7 +70409,7 @@
         <v>2026</v>
       </c>
       <c r="P666" t="n">
-        <v>17399327</v>
+        <v>18076497</v>
       </c>
       <c r="Q666" t="inlineStr">
         <is>
@@ -70414,14 +70422,14 @@
         </is>
       </c>
       <c r="S666" s="1" t="n">
-        <v>46143.12549351852</v>
+        <v>46143.12548776621</v>
       </c>
       <c r="T666" t="n">
         <v>-6</v>
       </c>
       <c r="U666" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="V666" t="inlineStr">
@@ -70453,11 +70461,11 @@
     </row>
     <row r="667">
       <c r="A667" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -70477,7 +70485,7 @@
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G667" t="n">
@@ -70508,7 +70516,7 @@
         <v>2026</v>
       </c>
       <c r="P667" t="n">
-        <v>18076497</v>
+        <v>18076567</v>
       </c>
       <c r="Q667" t="inlineStr">
         <is>
@@ -70521,7 +70529,7 @@
         </is>
       </c>
       <c r="S667" s="1" t="n">
-        <v>46143.12548776621</v>
+        <v>46143.12547268518</v>
       </c>
       <c r="T667" t="n">
         <v>-6</v>
@@ -70533,7 +70541,7 @@
       </c>
       <c r="V667" t="inlineStr">
         <is>
-          <t>Baixado via rotina MGC x Analise Balanço em 01/05/2026 03:00:42. - Data Comentário: 01/05/2026 02:56</t>
+          <t>Baixado via rotina MGC x Analise Balanço em 01/05/2026 03:00:40. - Data Comentário: 01/05/2026 02:56</t>
         </is>
       </c>
       <c r="W667" t="inlineStr"/>
@@ -70560,11 +70568,11 @@
     </row>
     <row r="668">
       <c r="A668" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -70574,7 +70582,7 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
@@ -70584,7 +70592,7 @@
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G668" t="n">
@@ -70615,7 +70623,7 @@
         <v>2026</v>
       </c>
       <c r="P668" t="n">
-        <v>18076567</v>
+        <v>17539835</v>
       </c>
       <c r="Q668" t="inlineStr">
         <is>
@@ -70628,19 +70636,19 @@
         </is>
       </c>
       <c r="S668" s="1" t="n">
-        <v>46143.12547268518</v>
+        <v>46143.12549505787</v>
       </c>
       <c r="T668" t="n">
         <v>-6</v>
       </c>
       <c r="U668" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="V668" t="inlineStr">
         <is>
-          <t>Baixado via rotina MGC x Analise Balanço em 01/05/2026 03:00:40. - Data Comentário: 01/05/2026 02:56</t>
+          <t>Baixado via rotina MGC x Analise Balanço em 01/05/2026 03:00:42. - Data Comentário: 01/05/2026 02:56</t>
         </is>
       </c>
       <c r="W668" t="inlineStr"/>
@@ -70667,11 +70675,11 @@
     </row>
     <row r="669">
       <c r="A669" t="n">
-        <v>6278</v>
+        <v>6358</v>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -70681,7 +70689,7 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
@@ -70722,32 +70730,28 @@
         <v>2026</v>
       </c>
       <c r="P669" t="n">
-        <v>17539835</v>
-      </c>
-      <c r="Q669" t="inlineStr">
-        <is>
-          <t>Sergio Fernandes</t>
-        </is>
-      </c>
+        <v>18074887</v>
+      </c>
+      <c r="Q669" t="inlineStr"/>
       <c r="R669" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S669" s="1" t="n">
-        <v>46143.12549505787</v>
+        <v>46143.12549876158</v>
       </c>
       <c r="T669" t="n">
         <v>-6</v>
       </c>
       <c r="U669" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>MACHADO</t>
         </is>
       </c>
       <c r="V669" t="inlineStr">
         <is>
-          <t>Baixado via rotina MGC x Analise Balanço em 01/05/2026 03:00:42. - Data Comentário: 01/05/2026 02:56</t>
+          <t>Baixado via rotina MGC x Analise Balanço em 01/05/2026 03:00:43. - Data Comentário: 01/05/2026 02:56</t>
         </is>
       </c>
       <c r="W669" t="inlineStr"/>
@@ -70774,11 +70778,11 @@
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>6358</v>
+        <v>6486</v>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -70802,7 +70806,7 @@
         </is>
       </c>
       <c r="G670" t="n">
-        <v>7877</v>
+        <v>9774</v>
       </c>
       <c r="H670" t="n">
         <v>0</v>
@@ -70814,12 +70818,12 @@
       </c>
       <c r="J670" t="inlineStr">
         <is>
-          <t>Movimento - Analise de Balanço Lucro Real</t>
+          <t>Movimento - Analise de Balanço Simples Nacional</t>
         </is>
       </c>
       <c r="K670" t="inlineStr"/>
       <c r="L670" s="1" t="n">
-        <v>46202</v>
+        <v>46189</v>
       </c>
       <c r="M670" t="inlineStr"/>
       <c r="N670" t="n">
@@ -70829,28 +70833,32 @@
         <v>2026</v>
       </c>
       <c r="P670" t="n">
-        <v>18074887</v>
-      </c>
-      <c r="Q670" t="inlineStr"/>
+        <v>16976318</v>
+      </c>
+      <c r="Q670" t="inlineStr">
+        <is>
+          <t>Sergio Fernandes</t>
+        </is>
+      </c>
       <c r="R670" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S670" s="1" t="n">
-        <v>46143.12549876158</v>
+        <v>46143.12581516203</v>
       </c>
       <c r="T670" t="n">
-        <v>-6</v>
+        <v>7</v>
       </c>
       <c r="U670" t="inlineStr">
         <is>
-          <t>MACHADO</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="V670" t="inlineStr">
         <is>
-          <t>Baixado via rotina MGC x Analise Balanço em 01/05/2026 03:00:43. - Data Comentário: 01/05/2026 02:56</t>
+          <t>Baixado via rotina MGC x Analise Balanço em 01/05/2026 03:01:10. - Data Comentário: 01/05/2026 02:57</t>
         </is>
       </c>
       <c r="W670" t="inlineStr"/>
@@ -70877,11 +70885,11 @@
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -70901,11 +70909,11 @@
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G671" t="n">
-        <v>9774</v>
+        <v>7027</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -70917,12 +70925,12 @@
       </c>
       <c r="J671" t="inlineStr">
         <is>
-          <t>Movimento - Analise de Balanço Simples Nacional</t>
+          <t>Movimento - Sistema de Análise</t>
         </is>
       </c>
       <c r="K671" t="inlineStr"/>
       <c r="L671" s="1" t="n">
-        <v>46189</v>
+        <v>46197</v>
       </c>
       <c r="M671" t="inlineStr"/>
       <c r="N671" t="n">
@@ -70932,7 +70940,7 @@
         <v>2026</v>
       </c>
       <c r="P671" t="n">
-        <v>16976318</v>
+        <v>17399287</v>
       </c>
       <c r="Q671" t="inlineStr">
         <is>
@@ -70945,19 +70953,19 @@
         </is>
       </c>
       <c r="S671" s="1" t="n">
-        <v>46143.12581516203</v>
+        <v>46191.74713402778</v>
       </c>
       <c r="T671" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="U671" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="V671" t="inlineStr">
         <is>
-          <t>Baixado via rotina MGC x Analise Balanço em 01/05/2026 03:01:10. - Data Comentário: 01/05/2026 02:57</t>
+          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 18/06/2026 17:55:33. - Data Comentário: 18/06/2026 17:55</t>
         </is>
       </c>
       <c r="W671" t="inlineStr"/>
@@ -70984,11 +70992,11 @@
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -71008,7 +71016,7 @@
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G672" t="n">
@@ -71039,7 +71047,7 @@
         <v>2026</v>
       </c>
       <c r="P672" t="n">
-        <v>17399287</v>
+        <v>17407828</v>
       </c>
       <c r="Q672" t="inlineStr">
         <is>
@@ -71052,19 +71060,19 @@
         </is>
       </c>
       <c r="S672" s="1" t="n">
-        <v>46191.74713402778</v>
+        <v>46196.5142659375</v>
       </c>
       <c r="T672" t="n">
         <v>-1</v>
       </c>
       <c r="U672" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="V672" t="inlineStr">
         <is>
-          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 18/06/2026 17:55:33. - Data Comentário: 18/06/2026 17:55</t>
+          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 23/06/2026 12:19:53. - Data Comentário: 23/06/2026 12:19</t>
         </is>
       </c>
       <c r="W672" t="inlineStr"/>
@@ -71091,11 +71099,11 @@
     </row>
     <row r="673">
       <c r="A673" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -71115,7 +71123,7 @@
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G673" t="n">
@@ -71146,13 +71154,9 @@
         <v>2026</v>
       </c>
       <c r="P673" t="n">
-        <v>17407828</v>
-      </c>
-      <c r="Q673" t="inlineStr">
-        <is>
-          <t>Sergio Fernandes</t>
-        </is>
-      </c>
+        <v>17688956</v>
+      </c>
+      <c r="Q673" t="inlineStr"/>
       <c r="R673" t="inlineStr">
         <is>
           <t>Baixado</t>
@@ -71194,11 +71198,11 @@
     </row>
     <row r="674">
       <c r="A674" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -71208,7 +71212,7 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
@@ -71218,7 +71222,7 @@
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G674" t="n">
@@ -71249,26 +71253,36 @@
         <v>2026</v>
       </c>
       <c r="P674" t="n">
-        <v>17688956</v>
-      </c>
-      <c r="Q674" t="inlineStr"/>
+        <v>17539795</v>
+      </c>
+      <c r="Q674" t="inlineStr">
+        <is>
+          <t>Sergio Fernandes</t>
+        </is>
+      </c>
       <c r="R674" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="S674" s="1" t="n">
-        <v>46143.04106913194</v>
+        <v>46185.6294380787</v>
       </c>
       <c r="T674" t="n">
         <v>-1</v>
       </c>
       <c r="U674" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
-        </is>
-      </c>
-      <c r="V674" t="inlineStr"/>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="V674" t="inlineStr">
+        <is>
+          <t>Integração com Sistema de Análise 
+ICMS liberado, aguardo a validação do SPED Contribuições 
+Data Simulação: 12/06/2026 15:06:24 - Data Comentário: 12/06/2026 16:04</t>
+        </is>
+      </c>
       <c r="W674" t="inlineStr"/>
       <c r="X674" t="inlineStr"/>
       <c r="Y674" t="inlineStr"/>
@@ -71293,11 +71307,11 @@
     </row>
     <row r="675">
       <c r="A675" t="n">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -71307,7 +71321,7 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
@@ -71317,7 +71331,7 @@
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G675" t="n">
@@ -71348,7 +71362,7 @@
         <v>2026</v>
       </c>
       <c r="P675" t="n">
-        <v>17539795</v>
+        <v>17646101</v>
       </c>
       <c r="Q675" t="inlineStr">
         <is>
@@ -71361,7 +71375,7 @@
         </is>
       </c>
       <c r="S675" s="1" t="n">
-        <v>46185.6294380787</v>
+        <v>46185.63050633102</v>
       </c>
       <c r="T675" t="n">
         <v>-1</v>
@@ -71373,9 +71387,7 @@
       </c>
       <c r="V675" t="inlineStr">
         <is>
-          <t>Integração com Sistema de Análise 
-ICMS liberado, aguardo a validação do SPED Contribuições 
-Data Simulação: 12/06/2026 15:06:24 - Data Comentário: 12/06/2026 16:04</t>
+          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 12/06/2026 15:07:58. - Data Comentário: 12/06/2026 15:07</t>
         </is>
       </c>
       <c r="W675" t="inlineStr"/>
@@ -71402,11 +71414,11 @@
     </row>
     <row r="676">
       <c r="A676" t="n">
-        <v>6279</v>
+        <v>6404</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -71426,7 +71438,7 @@
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G676" t="n">
@@ -71457,7 +71469,7 @@
         <v>2026</v>
       </c>
       <c r="P676" t="n">
-        <v>17646101</v>
+        <v>16962345</v>
       </c>
       <c r="Q676" t="inlineStr">
         <is>
@@ -71470,19 +71482,19 @@
         </is>
       </c>
       <c r="S676" s="1" t="n">
-        <v>46185.63050633102</v>
+        <v>46183.74690841435</v>
       </c>
       <c r="T676" t="n">
         <v>-1</v>
       </c>
       <c r="U676" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="V676" t="inlineStr">
         <is>
-          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 12/06/2026 15:07:58. - Data Comentário: 12/06/2026 15:07</t>
+          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 10/06/2026 17:55:41. - Data Comentário: 10/06/2026 17:54</t>
         </is>
       </c>
       <c r="W676" t="inlineStr"/>
@@ -71509,11 +71521,11 @@
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -71523,7 +71535,7 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
@@ -71564,7 +71576,7 @@
         <v>2026</v>
       </c>
       <c r="P677" t="n">
-        <v>16962345</v>
+        <v>16976234</v>
       </c>
       <c r="Q677" t="inlineStr">
         <is>
@@ -71577,19 +71589,19 @@
         </is>
       </c>
       <c r="S677" s="1" t="n">
-        <v>46183.74690841435</v>
+        <v>46190.78703885416</v>
       </c>
       <c r="T677" t="n">
         <v>-1</v>
       </c>
       <c r="U677" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="V677" t="inlineStr">
         <is>
-          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 10/06/2026 17:55:41. - Data Comentário: 10/06/2026 17:54</t>
+          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 17/06/2026 18:53:13. - Data Comentário: 17/06/2026 18:52</t>
         </is>
       </c>
       <c r="W677" t="inlineStr"/>
@@ -71616,11 +71628,11 @@
     </row>
     <row r="678">
       <c r="A678" t="n">
-        <v>6486</v>
+        <v>5617</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -71644,26 +71656,30 @@
         </is>
       </c>
       <c r="G678" t="n">
-        <v>7027</v>
+        <v>11056</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
       </c>
       <c r="I678" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="J678" t="inlineStr">
         <is>
-          <t>Movimento - Sistema de Análise</t>
+          <t>Agenda de Reunião</t>
         </is>
       </c>
       <c r="K678" t="inlineStr"/>
       <c r="L678" s="1" t="n">
-        <v>46197</v>
-      </c>
-      <c r="M678" t="inlineStr"/>
+        <v>46196</v>
+      </c>
+      <c r="M678" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
       <c r="N678" t="n">
         <v>5</v>
       </c>
@@ -71671,11 +71687,11 @@
         <v>2026</v>
       </c>
       <c r="P678" t="n">
-        <v>16976234</v>
+        <v>18183612</v>
       </c>
       <c r="Q678" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="R678" t="inlineStr">
@@ -71684,19 +71700,20 @@
         </is>
       </c>
       <c r="S678" s="1" t="n">
-        <v>46190.78703885416</v>
+        <v>46196.48606331019</v>
       </c>
       <c r="T678" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U678" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="V678" t="inlineStr">
         <is>
-          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 17/06/2026 18:53:13. - Data Comentário: 17/06/2026 18:52</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 23/06/2026 
+A reunião está confirmada com o cliente para hoje - Data Comentário: 23/06/2026 11:38</t>
         </is>
       </c>
       <c r="W678" t="inlineStr"/>
@@ -71707,7 +71724,7 @@
       </c>
       <c r="AA678" t="inlineStr">
         <is>
-          <t>ex-funcionario</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="AB678" t="inlineStr"/>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -13332,7 +13332,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -13364,8 +13364,8 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 30/06/2026 
-AINDA NÃO HOUVE A REUNIÃO DE IMPLANTAÇÃO - Data Comentário: 10/06/2026 16:18</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 31/07/2026 
+ainda não foi realizado as implantações - Data Comentário: 01/07/2026 13:38</t>
         </is>
       </c>
       <c r="V129" t="inlineStr"/>
@@ -13439,7 +13439,11 @@
       <c r="L130" s="1" t="n">
         <v>46206</v>
       </c>
-      <c r="M130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
       <c r="N130" t="inlineStr">
         <is>
           <t>06/2026</t>
@@ -13469,7 +13473,8 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6962; Tarefa Incluida: 11617; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: pvolpe - Data Comentário: 17/06/2026 11:09</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 31/07/2026 
+ainda não foi realizado as implantações - Data Comentário: 01/07/2026 13:38</t>
         </is>
       </c>
       <c r="V130" t="inlineStr"/>
@@ -13543,7 +13548,11 @@
       <c r="L131" s="1" t="n">
         <v>46206</v>
       </c>
-      <c r="M131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
       <c r="N131" t="inlineStr">
         <is>
           <t>06/2026</t>
@@ -13573,7 +13582,8 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6963; Tarefa Incluida: 11617; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: pvolpe - Data Comentário: 17/06/2026 11:09</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 31/07/2026 
+ainda não foi realizado as implantações - Data Comentário: 01/07/2026 13:38</t>
         </is>
       </c>
       <c r="V131" t="inlineStr"/>
@@ -78659,11 +78669,11 @@
     </row>
     <row r="784">
       <c r="A784" t="n">
-        <v>6358</v>
+        <v>6548</v>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -78708,7 +78718,7 @@
       </c>
       <c r="M784" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="N784" t="inlineStr">
@@ -78717,11 +78727,11 @@
         </is>
       </c>
       <c r="O784" t="n">
-        <v>18096517</v>
+        <v>18096231</v>
       </c>
       <c r="P784" t="inlineStr">
         <is>
-          <t>Emylle Souza</t>
+          <t>Thais Souza</t>
         </is>
       </c>
       <c r="Q784" t="inlineStr">
@@ -78735,12 +78745,12 @@
       </c>
       <c r="T784" t="inlineStr">
         <is>
-          <t>MACHADO</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U784" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 14/07/2026 - Data Comentário: 01/07/2026 09:04</t>
+          <t>Atraso da Operação, processo em elaboração conforme data prevista   Previsão para conclusão dia 02/07/2026 - Data Comentário: 01/07/2026 09:36</t>
         </is>
       </c>
       <c r="V784" t="inlineStr"/>
@@ -78759,17 +78769,17 @@
       </c>
       <c r="AF784" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Erika Santana</t>
         </is>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -78784,7 +78794,7 @@
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F785" t="inlineStr">
@@ -78812,22 +78822,18 @@
       <c r="L785" s="1" t="n">
         <v>46198</v>
       </c>
-      <c r="M785" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
+      <c r="M785" t="inlineStr"/>
       <c r="N785" t="inlineStr">
         <is>
           <t>05/2026</t>
         </is>
       </c>
       <c r="O785" t="n">
-        <v>18096231</v>
+        <v>18096484</v>
       </c>
       <c r="P785" t="inlineStr">
         <is>
-          <t>Thais Souza</t>
+          <t>Nathalia Lourenco</t>
         </is>
       </c>
       <c r="Q785" t="inlineStr">
@@ -78841,12 +78847,12 @@
       </c>
       <c r="T785" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U785" t="inlineStr">
         <is>
-          <t>Atraso da Operação, processo em elaboração conforme data prevista   Previsão para conclusão dia 02/07/2026 - Data Comentário: 01/07/2026 09:36</t>
+          <t>Reaberto via API integração MGC x Analise Balanço em 24/06/2026 12:07:35. - Data Comentário: 24/06/2026 12:06</t>
         </is>
       </c>
       <c r="V785" t="inlineStr"/>
@@ -78856,8 +78862,16 @@
       <c r="Z785" t="inlineStr"/>
       <c r="AA785" t="inlineStr"/>
       <c r="AB785" t="inlineStr"/>
-      <c r="AC785" t="inlineStr"/>
-      <c r="AD785" t="inlineStr"/>
+      <c r="AC785" t="inlineStr">
+        <is>
+          <t>Tarefa reaberta. A previsão de conclusão está prevista para 25/06/2026. - Data Comentário: 24/06/2026 12:06</t>
+        </is>
+      </c>
+      <c r="AD785" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
       <c r="AE785" t="inlineStr">
         <is>
           <t>Tarefa</t>
@@ -78865,17 +78879,17 @@
       </c>
       <c r="AF785" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="n">
-        <v>6627</v>
+        <v>5617</v>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -78890,7 +78904,7 @@
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F786" t="inlineStr">
@@ -78899,14 +78913,14 @@
         </is>
       </c>
       <c r="G786" t="n">
-        <v>7875</v>
+        <v>7874</v>
       </c>
       <c r="H786" t="n">
         <v>0</v>
       </c>
       <c r="I786" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J786" t="inlineStr">
@@ -78918,18 +78932,22 @@
       <c r="L786" s="1" t="n">
         <v>46198</v>
       </c>
-      <c r="M786" t="inlineStr"/>
+      <c r="M786" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
       <c r="N786" t="inlineStr">
         <is>
           <t>05/2026</t>
         </is>
       </c>
       <c r="O786" t="n">
-        <v>18096484</v>
+        <v>17407858</v>
       </c>
       <c r="P786" t="inlineStr">
         <is>
-          <t>Nathalia Lourenco</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="Q786" t="inlineStr">
@@ -78943,12 +78961,12 @@
       </c>
       <c r="T786" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U786" t="inlineStr">
         <is>
-          <t>Reaberto via API integração MGC x Analise Balanço em 24/06/2026 12:07:35. - Data Comentário: 24/06/2026 12:06</t>
+          <t>Atraso da Operação, processo em elaboração conforme data prevista  Previsão para conclusão dia 30/06/2026 - Data Comentário: 26/06/2026 14:11</t>
         </is>
       </c>
       <c r="V786" t="inlineStr"/>
@@ -78958,16 +78976,8 @@
       <c r="Z786" t="inlineStr"/>
       <c r="AA786" t="inlineStr"/>
       <c r="AB786" t="inlineStr"/>
-      <c r="AC786" t="inlineStr">
-        <is>
-          <t>Tarefa reaberta. A previsão de conclusão está prevista para 25/06/2026. - Data Comentário: 24/06/2026 12:06</t>
-        </is>
-      </c>
-      <c r="AD786" t="inlineStr">
-        <is>
-          <t>25/06/2026</t>
-        </is>
-      </c>
+      <c r="AC786" t="inlineStr"/>
+      <c r="AD786" t="inlineStr"/>
       <c r="AE786" t="inlineStr">
         <is>
           <t>Tarefa</t>
@@ -78975,17 +78985,17 @@
       </c>
       <c r="AF786" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -79005,7 +79015,7 @@
       </c>
       <c r="F787" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G787" t="n">
@@ -79039,7 +79049,7 @@
         </is>
       </c>
       <c r="O787" t="n">
-        <v>17407858</v>
+        <v>17206041</v>
       </c>
       <c r="P787" t="inlineStr">
         <is>
@@ -79087,11 +79097,11 @@
     </row>
     <row r="788">
       <c r="A788" t="n">
-        <v>6224</v>
+        <v>6704</v>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -79111,7 +79121,7 @@
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G788" t="n">
@@ -79134,22 +79144,18 @@
       <c r="L788" s="1" t="n">
         <v>46198</v>
       </c>
-      <c r="M788" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
+      <c r="M788" t="inlineStr"/>
       <c r="N788" t="inlineStr">
         <is>
           <t>05/2026</t>
         </is>
       </c>
       <c r="O788" t="n">
-        <v>17206041</v>
+        <v>18096764</v>
       </c>
       <c r="P788" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="Q788" t="inlineStr">
@@ -79163,12 +79169,12 @@
       </c>
       <c r="T788" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U788" t="inlineStr">
         <is>
-          <t>Atraso da Operação, processo em elaboração conforme data prevista  Previsão para conclusão dia 30/06/2026 - Data Comentário: 26/06/2026 14:11</t>
+          <t>Reaberto via API integração MGC x Analise Balanço em 29/06/2026 09:27:33. - Data Comentário: 29/06/2026 09:26</t>
         </is>
       </c>
       <c r="V788" t="inlineStr"/>
@@ -79178,8 +79184,16 @@
       <c r="Z788" t="inlineStr"/>
       <c r="AA788" t="inlineStr"/>
       <c r="AB788" t="inlineStr"/>
-      <c r="AC788" t="inlineStr"/>
-      <c r="AD788" t="inlineStr"/>
+      <c r="AC788" t="inlineStr">
+        <is>
+          <t>Tarefa reaberta. A previsão de conclusão está prevista para 30/06/2026. - Data Comentário: 29/06/2026 09:26</t>
+        </is>
+      </c>
+      <c r="AD788" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
       <c r="AE788" t="inlineStr">
         <is>
           <t>Tarefa</t>
@@ -79187,17 +79201,17 @@
       </c>
       <c r="AF788" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -79207,7 +79221,7 @@
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
@@ -79221,7 +79235,7 @@
         </is>
       </c>
       <c r="G789" t="n">
-        <v>7874</v>
+        <v>9762</v>
       </c>
       <c r="H789" t="n">
         <v>0</v>
@@ -79233,7 +79247,7 @@
       </c>
       <c r="J789" t="inlineStr">
         <is>
-          <t>Movimento - Analise de Balanço Lucro Real</t>
+          <t>Movimento - Analise de Balanço Simples Nacional</t>
         </is>
       </c>
       <c r="K789" t="inlineStr"/>
@@ -79247,7 +79261,7 @@
         </is>
       </c>
       <c r="O789" t="n">
-        <v>18096764</v>
+        <v>18096936</v>
       </c>
       <c r="P789" t="inlineStr">
         <is>
@@ -79270,7 +79284,7 @@
       </c>
       <c r="U789" t="inlineStr">
         <is>
-          <t>Reaberto via API integração MGC x Analise Balanço em 29/06/2026 09:27:33. - Data Comentário: 29/06/2026 09:26</t>
+          <t>Reaberto via API integração MGC x Analise Balanço em 29/06/2026 09:24:47. - Data Comentário: 29/06/2026 09:23</t>
         </is>
       </c>
       <c r="V789" t="inlineStr"/>
@@ -79282,7 +79296,7 @@
       <c r="AB789" t="inlineStr"/>
       <c r="AC789" t="inlineStr">
         <is>
-          <t>Tarefa reaberta. A previsão de conclusão está prevista para 30/06/2026. - Data Comentário: 29/06/2026 09:26</t>
+          <t>Tarefa reaberta. A previsão de conclusão está prevista para 30/06/2026. - Data Comentário: 29/06/2026 09:23</t>
         </is>
       </c>
       <c r="AD789" t="inlineStr">
@@ -79303,11 +79317,11 @@
     </row>
     <row r="790">
       <c r="A790" t="n">
-        <v>6705</v>
+        <v>6279</v>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -79317,7 +79331,7 @@
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
@@ -79327,41 +79341,41 @@
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G790" t="n">
-        <v>9762</v>
+        <v>5800</v>
       </c>
       <c r="H790" t="n">
-        <v>0</v>
+        <v>5776</v>
       </c>
       <c r="I790" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J790" t="inlineStr">
         <is>
-          <t>Movimento - Analise de Balanço Simples Nacional</t>
+          <t>CCT Lançamento Sd.508</t>
         </is>
       </c>
       <c r="K790" t="inlineStr"/>
       <c r="L790" s="1" t="n">
-        <v>46198</v>
+        <v>46203</v>
       </c>
       <c r="M790" t="inlineStr"/>
       <c r="N790" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>00/2026</t>
         </is>
       </c>
       <c r="O790" t="n">
-        <v>18096936</v>
+        <v>18087241</v>
       </c>
       <c r="P790" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q790" t="inlineStr">
@@ -79371,16 +79385,16 @@
       </c>
       <c r="R790" t="inlineStr"/>
       <c r="S790" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T790" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U790" t="inlineStr">
         <is>
-          <t>Reaberto via API integração MGC x Analise Balanço em 29/06/2026 09:24:47. - Data Comentário: 29/06/2026 09:23</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 30/06/2026 17:29</t>
         </is>
       </c>
       <c r="V790" t="inlineStr"/>
@@ -79392,12 +79406,12 @@
       <c r="AB790" t="inlineStr"/>
       <c r="AC790" t="inlineStr">
         <is>
-          <t>Tarefa reaberta. A previsão de conclusão está prevista para 30/06/2026. - Data Comentário: 29/06/2026 09:23</t>
+          <t>Aguardando liberação do sindicato - Data Comentário: 18/05/2026 17:19</t>
         </is>
       </c>
       <c r="AD790" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="AE790" t="inlineStr">
@@ -79407,17 +79421,17 @@
       </c>
       <c r="AF790" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="n">
-        <v>6279</v>
+        <v>6627</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -79427,51 +79441,55 @@
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G791" t="n">
-        <v>5800</v>
+        <v>7026</v>
       </c>
       <c r="H791" t="n">
-        <v>5776</v>
+        <v>0</v>
       </c>
       <c r="I791" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J791" t="inlineStr">
         <is>
-          <t>CCT Lançamento Sd.508</t>
+          <t>Movimento - Sistema de Análise</t>
         </is>
       </c>
       <c r="K791" t="inlineStr"/>
       <c r="L791" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="M791" t="inlineStr"/>
+        <v>46167</v>
+      </c>
+      <c r="M791" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
       <c r="N791" t="inlineStr">
         <is>
-          <t>00/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="O791" t="n">
-        <v>18087241</v>
+        <v>18048469</v>
       </c>
       <c r="P791" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q791" t="inlineStr">
@@ -79481,16 +79499,17 @@
       </c>
       <c r="R791" t="inlineStr"/>
       <c r="S791" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="T791" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U791" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 30/06/2026 17:29</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 26/06/2026 
+OPERAÇÃO X GC VALIDANDO COM SYS ANALISE - Data Comentário: 25/06/2026 16:00</t>
         </is>
       </c>
       <c r="V791" t="inlineStr"/>
@@ -79502,12 +79521,12 @@
       <c r="AB791" t="inlineStr"/>
       <c r="AC791" t="inlineStr">
         <is>
-          <t>Aguardando liberação do sindicato - Data Comentário: 18/05/2026 17:19</t>
+          <t>Operação e GC validando as informações errôneas no sistema de análise - Data Comentário: 24/06/2026 14:39</t>
         </is>
       </c>
       <c r="AD791" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="AE791" t="inlineStr">
@@ -79515,19 +79534,15 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AF791" t="inlineStr">
-        <is>
-          <t>David Bragança</t>
-        </is>
-      </c>
+      <c r="AF791" t="inlineStr"/>
     </row>
     <row r="792">
       <c r="A792" t="n">
-        <v>6627</v>
+        <v>6224</v>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -79542,50 +79557,46 @@
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G792" t="n">
-        <v>7026</v>
+        <v>1802</v>
       </c>
       <c r="H792" t="n">
         <v>0</v>
       </c>
       <c r="I792" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J792" t="inlineStr">
         <is>
-          <t>Movimento - Sistema de Análise</t>
+          <t>Est - ICMS RPA - CÓD. 046-2</t>
         </is>
       </c>
       <c r="K792" t="inlineStr"/>
       <c r="L792" s="1" t="n">
-        <v>46167</v>
-      </c>
-      <c r="M792" t="inlineStr">
-        <is>
-          <t>26/06/2026</t>
-        </is>
-      </c>
+        <v>46182</v>
+      </c>
+      <c r="M792" t="inlineStr"/>
       <c r="N792" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="O792" t="n">
-        <v>18048469</v>
+        <v>17688680</v>
       </c>
       <c r="P792" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q792" t="inlineStr">
@@ -79595,17 +79606,16 @@
       </c>
       <c r="R792" t="inlineStr"/>
       <c r="S792" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="T792" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U792" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 26/06/2026 
-OPERAÇÃO X GC VALIDANDO COM SYS ANALISE - Data Comentário: 25/06/2026 16:00</t>
+          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 25/06/2026 16:00</t>
         </is>
       </c>
       <c r="V792" t="inlineStr"/>
@@ -79617,7 +79627,7 @@
       <c r="AB792" t="inlineStr"/>
       <c r="AC792" t="inlineStr">
         <is>
-          <t>Operação e GC validando as informações errôneas no sistema de análise - Data Comentário: 24/06/2026 14:39</t>
+          <t>Atraso por parte do cliente, GC e GM acionado - CA03 - Data Comentário: 25/06/2026 18:14</t>
         </is>
       </c>
       <c r="AD792" t="inlineStr">
@@ -79627,10 +79637,14 @@
       </c>
       <c r="AE792" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AF792" t="inlineStr"/>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AF792" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
     </row>
     <row r="793">
       <c r="A793" t="n">
@@ -79662,7 +79676,7 @@
         </is>
       </c>
       <c r="G793" t="n">
-        <v>1802</v>
+        <v>1808</v>
       </c>
       <c r="H793" t="n">
         <v>0</v>
@@ -79674,12 +79688,12 @@
       </c>
       <c r="J793" t="inlineStr">
         <is>
-          <t>Est - ICMS RPA - CÓD. 046-2</t>
+          <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
         </is>
       </c>
       <c r="K793" t="inlineStr"/>
       <c r="L793" s="1" t="n">
-        <v>46182</v>
+        <v>46195</v>
       </c>
       <c r="M793" t="inlineStr"/>
       <c r="N793" t="inlineStr">
@@ -79688,7 +79702,7 @@
         </is>
       </c>
       <c r="O793" t="n">
-        <v>17688680</v>
+        <v>17688690</v>
       </c>
       <c r="P793" t="inlineStr">
         <is>
@@ -79702,7 +79716,7 @@
       </c>
       <c r="R793" t="inlineStr"/>
       <c r="S793" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="T793" t="inlineStr">
         <is>
@@ -79711,7 +79725,7 @@
       </c>
       <c r="U793" t="inlineStr">
         <is>
-          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 25/06/2026 16:00</t>
+          <t>Atraso de envio do cliente, consultar pendências no check list - Data Comentário: 23/06/2026 15:41</t>
         </is>
       </c>
       <c r="V793" t="inlineStr"/>
@@ -79723,7 +79737,7 @@
       <c r="AB793" t="inlineStr"/>
       <c r="AC793" t="inlineStr">
         <is>
-          <t>Atraso por parte do cliente, GC e GM acionado - CA03 - Data Comentário: 25/06/2026 18:14</t>
+          <t>Atraso por parte do cliente, GC e GM acionados - Data Comentário: 25/06/2026 18:14</t>
         </is>
       </c>
       <c r="AD793" t="inlineStr">
@@ -79744,11 +79758,11 @@
     </row>
     <row r="794">
       <c r="A794" t="n">
-        <v>6224</v>
+        <v>6404</v>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -79758,7 +79772,7 @@
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E794" t="inlineStr">
@@ -79768,41 +79782,45 @@
       </c>
       <c r="F794" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G794" t="n">
-        <v>1808</v>
+        <v>11001</v>
       </c>
       <c r="H794" t="n">
         <v>0</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J794" t="inlineStr">
         <is>
-          <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
+          <t>Movimento - Analise de Balanço Lucro Presumido</t>
         </is>
       </c>
       <c r="K794" t="inlineStr"/>
       <c r="L794" s="1" t="n">
-        <v>46195</v>
-      </c>
-      <c r="M794" t="inlineStr"/>
+        <v>46202</v>
+      </c>
+      <c r="M794" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
       <c r="N794" t="inlineStr">
         <is>
           <t>05/2026</t>
         </is>
       </c>
       <c r="O794" t="n">
-        <v>17688690</v>
+        <v>16962451</v>
       </c>
       <c r="P794" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q794" t="inlineStr">
@@ -79812,16 +79830,17 @@
       </c>
       <c r="R794" t="inlineStr"/>
       <c r="S794" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T794" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U794" t="inlineStr">
         <is>
-          <t>Atraso de envio do cliente, consultar pendências no check list - Data Comentário: 23/06/2026 15:41</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 02/07/2026 
+Analisar até 02/07/2026 - Data Comentário: 01/07/2026 07:26</t>
         </is>
       </c>
       <c r="V794" t="inlineStr"/>
@@ -79833,32 +79852,28 @@
       <c r="AB794" t="inlineStr"/>
       <c r="AC794" t="inlineStr">
         <is>
-          <t>Atraso por parte do cliente, GC e GM acionados - Data Comentário: 25/06/2026 18:14</t>
+          <t>Tarefa reaberta. A previsão de conclusão está prevista para 01/07/2026. - Data Comentário: 30/06/2026 08:45</t>
         </is>
       </c>
       <c r="AD794" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="AE794" t="inlineStr">
         <is>
-          <t>Imposto</t>
-        </is>
-      </c>
-      <c r="AF794" t="inlineStr">
-        <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AF794" t="inlineStr"/>
     </row>
     <row r="795">
       <c r="A795" t="n">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -79868,7 +79883,7 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
@@ -79878,11 +79893,11 @@
       </c>
       <c r="F795" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G795" t="n">
-        <v>11001</v>
+        <v>7877</v>
       </c>
       <c r="H795" t="n">
         <v>0</v>
@@ -79894,29 +79909,25 @@
       </c>
       <c r="J795" t="inlineStr">
         <is>
-          <t>Movimento - Analise de Balanço Lucro Presumido</t>
+          <t>Movimento - Analise de Balanço Lucro Real</t>
         </is>
       </c>
       <c r="K795" t="inlineStr"/>
       <c r="L795" s="1" t="n">
         <v>46202</v>
       </c>
-      <c r="M795" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
+      <c r="M795" t="inlineStr"/>
       <c r="N795" t="inlineStr">
         <is>
           <t>05/2026</t>
         </is>
       </c>
       <c r="O795" t="n">
-        <v>16962451</v>
+        <v>17399327</v>
       </c>
       <c r="P795" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q795" t="inlineStr">
@@ -79930,13 +79941,12 @@
       </c>
       <c r="T795" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U795" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 02/07/2026 
-Analisar até 02/07/2026 - Data Comentário: 01/07/2026 07:26</t>
+          <t>Reaberto via API integração MGC x Analise Balanço em 30/06/2026 18:03:37. - Data Comentário: 30/06/2026 18:02</t>
         </is>
       </c>
       <c r="V795" t="inlineStr"/>
@@ -79948,7 +79958,7 @@
       <c r="AB795" t="inlineStr"/>
       <c r="AC795" t="inlineStr">
         <is>
-          <t>Tarefa reaberta. A previsão de conclusão está prevista para 01/07/2026. - Data Comentário: 30/06/2026 08:45</t>
+          <t>Tarefa reaberta. A previsão de conclusão está prevista para 01/07/2026. - Data Comentário: 30/06/2026 18:02</t>
         </is>
       </c>
       <c r="AD795" t="inlineStr">
@@ -79965,11 +79975,11 @@
     </row>
     <row r="796">
       <c r="A796" t="n">
-        <v>5417</v>
+        <v>6224</v>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -79989,7 +79999,7 @@
       </c>
       <c r="F796" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G796" t="n">
@@ -80010,20 +80020,24 @@
       </c>
       <c r="K796" t="inlineStr"/>
       <c r="L796" s="1" t="n">
-        <v>46202</v>
-      </c>
-      <c r="M796" t="inlineStr"/>
+        <v>46171</v>
+      </c>
+      <c r="M796" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
       <c r="N796" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="O796" t="n">
-        <v>17399327</v>
+        <v>18076566</v>
       </c>
       <c r="P796" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q796" t="inlineStr">
@@ -80033,16 +80047,16 @@
       </c>
       <c r="R796" t="inlineStr"/>
       <c r="S796" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="T796" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U796" t="inlineStr">
         <is>
-          <t>Reaberto via API integração MGC x Analise Balanço em 30/06/2026 18:03:37. - Data Comentário: 30/06/2026 18:02</t>
+          <t>Reaberto via API integração MGC x Analise Balanço em 29/05/2026 11:16:37. - Data Comentário: 25/06/2026 16:00</t>
         </is>
       </c>
       <c r="V796" t="inlineStr"/>
@@ -80054,12 +80068,12 @@
       <c r="AB796" t="inlineStr"/>
       <c r="AC796" t="inlineStr">
         <is>
-          <t>Tarefa reaberta. A previsão de conclusão está prevista para 01/07/2026. - Data Comentário: 30/06/2026 18:02</t>
+          <t>Tarefa reaberta e já passadas para o GO Sérgio que disse que as mesmas serão conclupidas até o fim da semana - Data Comentário: 22/06/2026 17:05</t>
         </is>
       </c>
       <c r="AD796" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="AE796" t="inlineStr">
@@ -80071,11 +80085,11 @@
     </row>
     <row r="797">
       <c r="A797" t="n">
-        <v>6224</v>
+        <v>6358</v>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -80095,7 +80109,7 @@
       </c>
       <c r="F797" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G797" t="n">
@@ -80116,24 +80130,20 @@
       </c>
       <c r="K797" t="inlineStr"/>
       <c r="L797" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="M797" t="inlineStr">
-        <is>
-          <t>26/06/2026</t>
-        </is>
-      </c>
+        <v>46202</v>
+      </c>
+      <c r="M797" t="inlineStr"/>
       <c r="N797" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="O797" t="n">
-        <v>18076566</v>
+        <v>18074887</v>
       </c>
       <c r="P797" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q797" t="inlineStr">
@@ -80143,16 +80153,16 @@
       </c>
       <c r="R797" t="inlineStr"/>
       <c r="S797" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="T797" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>MACHADO</t>
         </is>
       </c>
       <c r="U797" t="inlineStr">
         <is>
-          <t>Reaberto via API integração MGC x Analise Balanço em 29/05/2026 11:16:37. - Data Comentário: 25/06/2026 16:00</t>
+          <t>Reaberto via API integração MGC x Analise Balanço em 01/07/2026 14:22:54. - Data Comentário: 01/07/2026 14:19</t>
         </is>
       </c>
       <c r="V797" t="inlineStr"/>
@@ -80164,12 +80174,12 @@
       <c r="AB797" t="inlineStr"/>
       <c r="AC797" t="inlineStr">
         <is>
-          <t>Tarefa reaberta e já passadas para o GO Sérgio que disse que as mesmas serão conclupidas até o fim da semana - Data Comentário: 22/06/2026 17:05</t>
+          <t>Tarefa reaberta. A previsão de conclusão está prevista para 02/07/2026. - Data Comentário: 01/07/2026 14:19</t>
         </is>
       </c>
       <c r="AD797" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="AE797" t="inlineStr">

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF801"/>
+  <dimension ref="A1:AF803"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,7 +946,7 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>3. Folha, Aguardando Resumo p/ Processamento   Previsão para conclusão dia 03/07/2026 - Data Comentário: 30/06/2026 16:54</t>
+          <t>3. Folha, Aguardando Resumo p/ Processamento   Previsão para conclusão dia 03/07/2026 - Data Comentário: 01/07/2026 16:28</t>
         </is>
       </c>
       <c r="V49" t="inlineStr"/>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>3. Folha, Aguardando Resumo p/ Processamento   Previsão para conclusão dia 02/07/2026 - Data Comentário: 26/06/2026 16:27</t>
+          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 03/07/2026 - Data Comentário: 01/07/2026 16:24</t>
         </is>
       </c>
       <c r="V50" t="inlineStr"/>
@@ -8231,7 +8231,11 @@
       <c r="L77" s="1" t="n">
         <v>46204</v>
       </c>
-      <c r="M77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr">
         <is>
           <t>06/2026</t>
@@ -8259,7 +8263,12 @@
           <t>LIMA MOTA</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr"/>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 02/07/2026 
+Em contato com o cliente, o mesmo informou que enviará até amanhã 02/07 - Data Comentário: 01/07/2026 16:29</t>
+        </is>
+      </c>
       <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
@@ -22196,7 +22205,7 @@
       </c>
       <c r="K218" t="inlineStr"/>
       <c r="L218" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr">
@@ -22219,7 +22228,7 @@
       </c>
       <c r="R218" t="inlineStr"/>
       <c r="S218" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -22296,7 +22305,7 @@
       </c>
       <c r="K219" t="inlineStr"/>
       <c r="L219" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr">
@@ -22319,7 +22328,7 @@
       </c>
       <c r="R219" t="inlineStr"/>
       <c r="S219" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -22396,7 +22405,7 @@
       </c>
       <c r="K220" t="inlineStr"/>
       <c r="L220" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr">
@@ -22419,7 +22428,7 @@
       </c>
       <c r="R220" t="inlineStr"/>
       <c r="S220" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -22496,7 +22505,7 @@
       </c>
       <c r="K221" t="inlineStr"/>
       <c r="L221" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr">
@@ -22519,7 +22528,7 @@
       </c>
       <c r="R221" t="inlineStr"/>
       <c r="S221" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -22596,7 +22605,7 @@
       </c>
       <c r="K222" t="inlineStr"/>
       <c r="L222" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M222" t="inlineStr"/>
       <c r="N222" t="inlineStr">
@@ -22619,7 +22628,7 @@
       </c>
       <c r="R222" t="inlineStr"/>
       <c r="S222" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -22696,7 +22705,7 @@
       </c>
       <c r="K223" t="inlineStr"/>
       <c r="L223" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M223" t="inlineStr"/>
       <c r="N223" t="inlineStr">
@@ -22719,7 +22728,7 @@
       </c>
       <c r="R223" t="inlineStr"/>
       <c r="S223" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -78885,11 +78894,11 @@
     </row>
     <row r="786">
       <c r="A786" t="n">
-        <v>5617</v>
+        <v>6704</v>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -78932,22 +78941,18 @@
       <c r="L786" s="1" t="n">
         <v>46198</v>
       </c>
-      <c r="M786" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
+      <c r="M786" t="inlineStr"/>
       <c r="N786" t="inlineStr">
         <is>
           <t>05/2026</t>
         </is>
       </c>
       <c r="O786" t="n">
-        <v>17407858</v>
+        <v>18096764</v>
       </c>
       <c r="P786" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="Q786" t="inlineStr">
@@ -78961,12 +78966,12 @@
       </c>
       <c r="T786" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U786" t="inlineStr">
         <is>
-          <t>Atraso da Operação, processo em elaboração conforme data prevista  Previsão para conclusão dia 30/06/2026 - Data Comentário: 26/06/2026 14:11</t>
+          <t>Reaberto via API integração MGC x Analise Balanço em 29/06/2026 09:27:33. - Data Comentário: 29/06/2026 09:26</t>
         </is>
       </c>
       <c r="V786" t="inlineStr"/>
@@ -78976,8 +78981,16 @@
       <c r="Z786" t="inlineStr"/>
       <c r="AA786" t="inlineStr"/>
       <c r="AB786" t="inlineStr"/>
-      <c r="AC786" t="inlineStr"/>
-      <c r="AD786" t="inlineStr"/>
+      <c r="AC786" t="inlineStr">
+        <is>
+          <t>Tarefa reaberta. A previsão de conclusão está prevista para 30/06/2026. - Data Comentário: 29/06/2026 09:26</t>
+        </is>
+      </c>
+      <c r="AD786" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
       <c r="AE786" t="inlineStr">
         <is>
           <t>Tarefa</t>
@@ -78985,17 +78998,17 @@
       </c>
       <c r="AF786" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="n">
-        <v>6224</v>
+        <v>6705</v>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -79005,7 +79018,7 @@
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E787" t="inlineStr">
@@ -79015,11 +79028,11 @@
       </c>
       <c r="F787" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G787" t="n">
-        <v>7874</v>
+        <v>9762</v>
       </c>
       <c r="H787" t="n">
         <v>0</v>
@@ -79031,29 +79044,25 @@
       </c>
       <c r="J787" t="inlineStr">
         <is>
-          <t>Movimento - Analise de Balanço Lucro Real</t>
+          <t>Movimento - Analise de Balanço Simples Nacional</t>
         </is>
       </c>
       <c r="K787" t="inlineStr"/>
       <c r="L787" s="1" t="n">
         <v>46198</v>
       </c>
-      <c r="M787" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
+      <c r="M787" t="inlineStr"/>
       <c r="N787" t="inlineStr">
         <is>
           <t>05/2026</t>
         </is>
       </c>
       <c r="O787" t="n">
-        <v>17206041</v>
+        <v>18096936</v>
       </c>
       <c r="P787" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="Q787" t="inlineStr">
@@ -79067,12 +79076,12 @@
       </c>
       <c r="T787" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U787" t="inlineStr">
         <is>
-          <t>Atraso da Operação, processo em elaboração conforme data prevista  Previsão para conclusão dia 30/06/2026 - Data Comentário: 26/06/2026 14:11</t>
+          <t>Reaberto via API integração MGC x Analise Balanço em 29/06/2026 09:24:47. - Data Comentário: 29/06/2026 09:23</t>
         </is>
       </c>
       <c r="V787" t="inlineStr"/>
@@ -79082,8 +79091,16 @@
       <c r="Z787" t="inlineStr"/>
       <c r="AA787" t="inlineStr"/>
       <c r="AB787" t="inlineStr"/>
-      <c r="AC787" t="inlineStr"/>
-      <c r="AD787" t="inlineStr"/>
+      <c r="AC787" t="inlineStr">
+        <is>
+          <t>Tarefa reaberta. A previsão de conclusão está prevista para 30/06/2026. - Data Comentário: 29/06/2026 09:23</t>
+        </is>
+      </c>
+      <c r="AD787" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
       <c r="AE787" t="inlineStr">
         <is>
           <t>Tarefa</t>
@@ -79091,17 +79108,17 @@
       </c>
       <c r="AF787" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="n">
-        <v>6704</v>
+        <v>6279</v>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -79111,7 +79128,7 @@
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
@@ -79121,41 +79138,41 @@
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G788" t="n">
-        <v>7874</v>
+        <v>5800</v>
       </c>
       <c r="H788" t="n">
-        <v>0</v>
+        <v>5776</v>
       </c>
       <c r="I788" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J788" t="inlineStr">
         <is>
-          <t>Movimento - Analise de Balanço Lucro Real</t>
+          <t>CCT Lançamento Sd.508</t>
         </is>
       </c>
       <c r="K788" t="inlineStr"/>
       <c r="L788" s="1" t="n">
-        <v>46198</v>
+        <v>46203</v>
       </c>
       <c r="M788" t="inlineStr"/>
       <c r="N788" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>00/2026</t>
         </is>
       </c>
       <c r="O788" t="n">
-        <v>18096764</v>
+        <v>18087241</v>
       </c>
       <c r="P788" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q788" t="inlineStr">
@@ -79165,16 +79182,16 @@
       </c>
       <c r="R788" t="inlineStr"/>
       <c r="S788" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T788" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U788" t="inlineStr">
         <is>
-          <t>Reaberto via API integração MGC x Analise Balanço em 29/06/2026 09:27:33. - Data Comentário: 29/06/2026 09:26</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 30/06/2026 17:29</t>
         </is>
       </c>
       <c r="V788" t="inlineStr"/>
@@ -79186,12 +79203,12 @@
       <c r="AB788" t="inlineStr"/>
       <c r="AC788" t="inlineStr">
         <is>
-          <t>Tarefa reaberta. A previsão de conclusão está prevista para 30/06/2026. - Data Comentário: 29/06/2026 09:26</t>
+          <t>Aguardando liberação do sindicato - Data Comentário: 18/05/2026 17:19</t>
         </is>
       </c>
       <c r="AD788" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="AE788" t="inlineStr">
@@ -79201,17 +79218,17 @@
       </c>
       <c r="AF788" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="n">
-        <v>6705</v>
+        <v>6627</v>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -79221,12 +79238,12 @@
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F789" t="inlineStr">
@@ -79235,37 +79252,41 @@
         </is>
       </c>
       <c r="G789" t="n">
-        <v>9762</v>
+        <v>7026</v>
       </c>
       <c r="H789" t="n">
         <v>0</v>
       </c>
       <c r="I789" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J789" t="inlineStr">
         <is>
-          <t>Movimento - Analise de Balanço Simples Nacional</t>
+          <t>Movimento - Sistema de Análise</t>
         </is>
       </c>
       <c r="K789" t="inlineStr"/>
       <c r="L789" s="1" t="n">
-        <v>46198</v>
-      </c>
-      <c r="M789" t="inlineStr"/>
+        <v>46167</v>
+      </c>
+      <c r="M789" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
       <c r="N789" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="O789" t="n">
-        <v>18096936</v>
+        <v>18048469</v>
       </c>
       <c r="P789" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q789" t="inlineStr">
@@ -79275,16 +79296,17 @@
       </c>
       <c r="R789" t="inlineStr"/>
       <c r="S789" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="T789" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U789" t="inlineStr">
         <is>
-          <t>Reaberto via API integração MGC x Analise Balanço em 29/06/2026 09:24:47. - Data Comentário: 29/06/2026 09:23</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 26/06/2026 
+OPERAÇÃO X GC VALIDANDO COM SYS ANALISE - Data Comentário: 25/06/2026 16:00</t>
         </is>
       </c>
       <c r="V789" t="inlineStr"/>
@@ -79296,12 +79318,12 @@
       <c r="AB789" t="inlineStr"/>
       <c r="AC789" t="inlineStr">
         <is>
-          <t>Tarefa reaberta. A previsão de conclusão está prevista para 30/06/2026. - Data Comentário: 29/06/2026 09:23</t>
+          <t>Operação e GC validando as informações errôneas no sistema de análise - Data Comentário: 24/06/2026 14:39</t>
         </is>
       </c>
       <c r="AD789" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="AE789" t="inlineStr">
@@ -79309,19 +79331,15 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AF789" t="inlineStr">
-        <is>
-          <t>Fernanda Araujo</t>
-        </is>
-      </c>
+      <c r="AF789" t="inlineStr"/>
     </row>
     <row r="790">
       <c r="A790" t="n">
-        <v>6279</v>
+        <v>6224</v>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -79331,7 +79349,7 @@
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
@@ -79345,37 +79363,37 @@
         </is>
       </c>
       <c r="G790" t="n">
-        <v>5800</v>
+        <v>1802</v>
       </c>
       <c r="H790" t="n">
-        <v>5776</v>
+        <v>0</v>
       </c>
       <c r="I790" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J790" t="inlineStr">
         <is>
-          <t>CCT Lançamento Sd.508</t>
+          <t>Est - ICMS RPA - CÓD. 046-2</t>
         </is>
       </c>
       <c r="K790" t="inlineStr"/>
       <c r="L790" s="1" t="n">
-        <v>46203</v>
+        <v>46182</v>
       </c>
       <c r="M790" t="inlineStr"/>
       <c r="N790" t="inlineStr">
         <is>
-          <t>00/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="O790" t="n">
-        <v>18087241</v>
+        <v>17688680</v>
       </c>
       <c r="P790" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q790" t="inlineStr">
@@ -79385,16 +79403,16 @@
       </c>
       <c r="R790" t="inlineStr"/>
       <c r="S790" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="T790" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U790" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 30/06/2026 17:29</t>
+          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 25/06/2026 16:00</t>
         </is>
       </c>
       <c r="V790" t="inlineStr"/>
@@ -79406,32 +79424,32 @@
       <c r="AB790" t="inlineStr"/>
       <c r="AC790" t="inlineStr">
         <is>
-          <t>Aguardando liberação do sindicato - Data Comentário: 18/05/2026 17:19</t>
+          <t>Atraso por parte do cliente, GC e GM acionado - CA03 - Data Comentário: 25/06/2026 18:14</t>
         </is>
       </c>
       <c r="AD790" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="AE790" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AF790" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="n">
-        <v>6627</v>
+        <v>6224</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -79446,50 +79464,46 @@
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G791" t="n">
-        <v>7026</v>
+        <v>1808</v>
       </c>
       <c r="H791" t="n">
         <v>0</v>
       </c>
       <c r="I791" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J791" t="inlineStr">
         <is>
-          <t>Movimento - Sistema de Análise</t>
+          <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
         </is>
       </c>
       <c r="K791" t="inlineStr"/>
       <c r="L791" s="1" t="n">
-        <v>46167</v>
-      </c>
-      <c r="M791" t="inlineStr">
-        <is>
-          <t>26/06/2026</t>
-        </is>
-      </c>
+        <v>46195</v>
+      </c>
+      <c r="M791" t="inlineStr"/>
       <c r="N791" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="O791" t="n">
-        <v>18048469</v>
+        <v>17688690</v>
       </c>
       <c r="P791" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q791" t="inlineStr">
@@ -79499,17 +79513,16 @@
       </c>
       <c r="R791" t="inlineStr"/>
       <c r="S791" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="T791" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U791" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 26/06/2026 
-OPERAÇÃO X GC VALIDANDO COM SYS ANALISE - Data Comentário: 25/06/2026 16:00</t>
+          <t>Atraso de envio do cliente, consultar pendências no check list - Data Comentário: 23/06/2026 15:41</t>
         </is>
       </c>
       <c r="V791" t="inlineStr"/>
@@ -79521,7 +79534,7 @@
       <c r="AB791" t="inlineStr"/>
       <c r="AC791" t="inlineStr">
         <is>
-          <t>Operação e GC validando as informações errôneas no sistema de análise - Data Comentário: 24/06/2026 14:39</t>
+          <t>Atraso por parte do cliente, GC e GM acionados - Data Comentário: 25/06/2026 18:14</t>
         </is>
       </c>
       <c r="AD791" t="inlineStr">
@@ -79531,18 +79544,22 @@
       </c>
       <c r="AE791" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AF791" t="inlineStr"/>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AF791" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
     </row>
     <row r="792">
       <c r="A792" t="n">
-        <v>6224</v>
+        <v>6404</v>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -79552,7 +79569,7 @@
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
@@ -79562,41 +79579,45 @@
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G792" t="n">
-        <v>1802</v>
+        <v>11001</v>
       </c>
       <c r="H792" t="n">
         <v>0</v>
       </c>
       <c r="I792" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J792" t="inlineStr">
         <is>
-          <t>Est - ICMS RPA - CÓD. 046-2</t>
+          <t>Movimento - Analise de Balanço Lucro Presumido</t>
         </is>
       </c>
       <c r="K792" t="inlineStr"/>
       <c r="L792" s="1" t="n">
-        <v>46182</v>
-      </c>
-      <c r="M792" t="inlineStr"/>
+        <v>46202</v>
+      </c>
+      <c r="M792" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
       <c r="N792" t="inlineStr">
         <is>
           <t>05/2026</t>
         </is>
       </c>
       <c r="O792" t="n">
-        <v>17688680</v>
+        <v>16962451</v>
       </c>
       <c r="P792" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q792" t="inlineStr">
@@ -79606,16 +79627,17 @@
       </c>
       <c r="R792" t="inlineStr"/>
       <c r="S792" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="T792" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U792" t="inlineStr">
         <is>
-          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 25/06/2026 16:00</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 02/07/2026 
+Analisar até 02/07/2026 - Data Comentário: 01/07/2026 07:26</t>
         </is>
       </c>
       <c r="V792" t="inlineStr"/>
@@ -79627,32 +79649,28 @@
       <c r="AB792" t="inlineStr"/>
       <c r="AC792" t="inlineStr">
         <is>
-          <t>Atraso por parte do cliente, GC e GM acionado - CA03 - Data Comentário: 25/06/2026 18:14</t>
+          <t>Tarefa reaberta. A previsão de conclusão está prevista para 01/07/2026. - Data Comentário: 30/06/2026 08:45</t>
         </is>
       </c>
       <c r="AD792" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="AE792" t="inlineStr">
         <is>
-          <t>Imposto</t>
-        </is>
-      </c>
-      <c r="AF792" t="inlineStr">
-        <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AF792" t="inlineStr"/>
     </row>
     <row r="793">
       <c r="A793" t="n">
-        <v>6224</v>
+        <v>5417</v>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -79672,28 +79690,28 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G793" t="n">
-        <v>1808</v>
+        <v>7877</v>
       </c>
       <c r="H793" t="n">
         <v>0</v>
       </c>
       <c r="I793" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J793" t="inlineStr">
         <is>
-          <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
+          <t>Movimento - Analise de Balanço Lucro Real</t>
         </is>
       </c>
       <c r="K793" t="inlineStr"/>
       <c r="L793" s="1" t="n">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="M793" t="inlineStr"/>
       <c r="N793" t="inlineStr">
@@ -79702,11 +79720,11 @@
         </is>
       </c>
       <c r="O793" t="n">
-        <v>17688690</v>
+        <v>17399327</v>
       </c>
       <c r="P793" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q793" t="inlineStr">
@@ -79716,16 +79734,16 @@
       </c>
       <c r="R793" t="inlineStr"/>
       <c r="S793" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T793" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U793" t="inlineStr">
         <is>
-          <t>Atraso de envio do cliente, consultar pendências no check list - Data Comentário: 23/06/2026 15:41</t>
+          <t>Reaberto via API integração MGC x Analise Balanço em 30/06/2026 18:03:37. - Data Comentário: 30/06/2026 18:02</t>
         </is>
       </c>
       <c r="V793" t="inlineStr"/>
@@ -79737,32 +79755,28 @@
       <c r="AB793" t="inlineStr"/>
       <c r="AC793" t="inlineStr">
         <is>
-          <t>Atraso por parte do cliente, GC e GM acionados - Data Comentário: 25/06/2026 18:14</t>
+          <t>Tarefa reaberta. A previsão de conclusão está prevista para 01/07/2026. - Data Comentário: 30/06/2026 18:02</t>
         </is>
       </c>
       <c r="AD793" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="AE793" t="inlineStr">
         <is>
-          <t>Imposto</t>
-        </is>
-      </c>
-      <c r="AF793" t="inlineStr">
-        <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AF793" t="inlineStr"/>
     </row>
     <row r="794">
       <c r="A794" t="n">
-        <v>6404</v>
+        <v>5617</v>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -79772,7 +79786,7 @@
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E794" t="inlineStr">
@@ -79786,7 +79800,7 @@
         </is>
       </c>
       <c r="G794" t="n">
-        <v>11001</v>
+        <v>7877</v>
       </c>
       <c r="H794" t="n">
         <v>0</v>
@@ -79798,29 +79812,25 @@
       </c>
       <c r="J794" t="inlineStr">
         <is>
-          <t>Movimento - Analise de Balanço Lucro Presumido</t>
+          <t>Movimento - Analise de Balanço Lucro Real</t>
         </is>
       </c>
       <c r="K794" t="inlineStr"/>
       <c r="L794" s="1" t="n">
         <v>46202</v>
       </c>
-      <c r="M794" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
+      <c r="M794" t="inlineStr"/>
       <c r="N794" t="inlineStr">
         <is>
           <t>05/2026</t>
         </is>
       </c>
       <c r="O794" t="n">
-        <v>16962451</v>
+        <v>18076497</v>
       </c>
       <c r="P794" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q794" t="inlineStr">
@@ -79834,13 +79844,12 @@
       </c>
       <c r="T794" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U794" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 02/07/2026 
-Analisar até 02/07/2026 - Data Comentário: 01/07/2026 07:26</t>
+          <t>Reaberto via API integração MGC x Analise Balanço em 01/07/2026 15:44:06. - Data Comentário: 01/07/2026 15:44</t>
         </is>
       </c>
       <c r="V794" t="inlineStr"/>
@@ -79852,12 +79861,12 @@
       <c r="AB794" t="inlineStr"/>
       <c r="AC794" t="inlineStr">
         <is>
-          <t>Tarefa reaberta. A previsão de conclusão está prevista para 01/07/2026. - Data Comentário: 30/06/2026 08:45</t>
+          <t>Tarefa reaberta. A previsão de conclusão está prevista para 02/07/2026. - Data Comentário: 01/07/2026 15:44</t>
         </is>
       </c>
       <c r="AD794" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="AE794" t="inlineStr">
@@ -79869,11 +79878,11 @@
     </row>
     <row r="795">
       <c r="A795" t="n">
-        <v>5417</v>
+        <v>6224</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -79893,7 +79902,7 @@
       </c>
       <c r="F795" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G795" t="n">
@@ -79914,20 +79923,24 @@
       </c>
       <c r="K795" t="inlineStr"/>
       <c r="L795" s="1" t="n">
-        <v>46202</v>
-      </c>
-      <c r="M795" t="inlineStr"/>
+        <v>46171</v>
+      </c>
+      <c r="M795" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
       <c r="N795" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="O795" t="n">
-        <v>17399327</v>
+        <v>18076566</v>
       </c>
       <c r="P795" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q795" t="inlineStr">
@@ -79937,16 +79950,16 @@
       </c>
       <c r="R795" t="inlineStr"/>
       <c r="S795" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="T795" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U795" t="inlineStr">
         <is>
-          <t>Reaberto via API integração MGC x Analise Balanço em 30/06/2026 18:03:37. - Data Comentário: 30/06/2026 18:02</t>
+          <t>Reaberto via API integração MGC x Analise Balanço em 29/05/2026 11:16:37. - Data Comentário: 25/06/2026 16:00</t>
         </is>
       </c>
       <c r="V795" t="inlineStr"/>
@@ -79958,12 +79971,12 @@
       <c r="AB795" t="inlineStr"/>
       <c r="AC795" t="inlineStr">
         <is>
-          <t>Tarefa reaberta. A previsão de conclusão está prevista para 01/07/2026. - Data Comentário: 30/06/2026 18:02</t>
+          <t>Tarefa reaberta e já passadas para o GO Sérgio que disse que as mesmas serão conclupidas até o fim da semana - Data Comentário: 22/06/2026 17:05</t>
         </is>
       </c>
       <c r="AD795" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="AE795" t="inlineStr">
@@ -80020,20 +80033,16 @@
       </c>
       <c r="K796" t="inlineStr"/>
       <c r="L796" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="M796" t="inlineStr">
-        <is>
-          <t>26/06/2026</t>
-        </is>
-      </c>
+        <v>46202</v>
+      </c>
+      <c r="M796" t="inlineStr"/>
       <c r="N796" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="O796" t="n">
-        <v>18076566</v>
+        <v>18076567</v>
       </c>
       <c r="P796" t="inlineStr">
         <is>
@@ -80047,7 +80056,7 @@
       </c>
       <c r="R796" t="inlineStr"/>
       <c r="S796" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="T796" t="inlineStr">
         <is>
@@ -80056,7 +80065,7 @@
       </c>
       <c r="U796" t="inlineStr">
         <is>
-          <t>Reaberto via API integração MGC x Analise Balanço em 29/05/2026 11:16:37. - Data Comentário: 25/06/2026 16:00</t>
+          <t>Reaberto via API integração MGC x Analise Balanço em 01/07/2026 15:36:41. - Data Comentário: 01/07/2026 15:37</t>
         </is>
       </c>
       <c r="V796" t="inlineStr"/>
@@ -80068,12 +80077,12 @@
       <c r="AB796" t="inlineStr"/>
       <c r="AC796" t="inlineStr">
         <is>
-          <t>Tarefa reaberta e já passadas para o GO Sérgio que disse que as mesmas serão conclupidas até o fim da semana - Data Comentário: 22/06/2026 17:05</t>
+          <t>Tarefa reaberta. A previsão de conclusão está prevista para 02/07/2026. - Data Comentário: 01/07/2026 15:37</t>
         </is>
       </c>
       <c r="AD796" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="AE796" t="inlineStr">
@@ -80400,11 +80409,11 @@
     </row>
     <row r="800">
       <c r="A800" t="n">
-        <v>6981</v>
+        <v>5417</v>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIZ GOMES DA SILVA - O GOIANO </t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -80424,11 +80433,11 @@
       </c>
       <c r="F800" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G800" t="n">
-        <v>11616</v>
+        <v>11815</v>
       </c>
       <c r="H800" t="n">
         <v>0</v>
@@ -80440,7 +80449,7 @@
       </c>
       <c r="J800" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - DP - SP</t>
+          <t>Cálculo de férias individuais - ERICA MIRELE DA SILVA</t>
         </is>
       </c>
       <c r="K800" t="inlineStr"/>
@@ -80454,11 +80463,11 @@
         </is>
       </c>
       <c r="O800" t="n">
-        <v>18195071</v>
+        <v>18196300</v>
       </c>
       <c r="P800" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="Q800" t="inlineStr">
@@ -80472,14 +80481,10 @@
       </c>
       <c r="T800" t="inlineStr">
         <is>
-          <t>SUPERMERCADO AVENIDA</t>
-        </is>
-      </c>
-      <c r="U800" t="inlineStr">
-        <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6981; Tarefa Incluida: 11616; Vencimento: 01/07/2026 00:00:00; UsuarioResponsavel: mauricio - Data Comentário: 01/07/2026 09:04</t>
-        </is>
-      </c>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U800" t="inlineStr"/>
       <c r="V800" t="inlineStr"/>
       <c r="W800" t="inlineStr"/>
       <c r="X800" t="inlineStr"/>
@@ -80498,11 +80503,11 @@
     </row>
     <row r="801">
       <c r="A801" t="n">
-        <v>6981</v>
+        <v>5417</v>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIZ GOMES DA SILVA - O GOIANO </t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -80522,23 +80527,23 @@
       </c>
       <c r="F801" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G801" t="n">
-        <v>11618</v>
+        <v>11815</v>
       </c>
       <c r="H801" t="n">
         <v>0</v>
       </c>
       <c r="I801" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J801" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - EF V - SP</t>
+          <t>Cálculo de férias individuais - PEDRO HENRIQUE LIMA ANDRADE</t>
         </is>
       </c>
       <c r="K801" t="inlineStr"/>
@@ -80552,11 +80557,11 @@
         </is>
       </c>
       <c r="O801" t="n">
-        <v>18195073</v>
+        <v>18196299</v>
       </c>
       <c r="P801" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="Q801" t="inlineStr">
@@ -80570,14 +80575,10 @@
       </c>
       <c r="T801" t="inlineStr">
         <is>
-          <t>SUPERMERCADO AVENIDA</t>
-        </is>
-      </c>
-      <c r="U801" t="inlineStr">
-        <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6981; Tarefa Incluida: 11618; Vencimento: 01/07/2026 00:00:00; UsuarioResponsavel: Claudineia - Data Comentário: 01/07/2026 09:04</t>
-        </is>
-      </c>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U801" t="inlineStr"/>
       <c r="V801" t="inlineStr"/>
       <c r="W801" t="inlineStr"/>
       <c r="X801" t="inlineStr"/>
@@ -80594,6 +80595,202 @@
       </c>
       <c r="AF801" t="inlineStr"/>
     </row>
+    <row r="802">
+      <c r="A802" t="n">
+        <v>6981</v>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUIZ GOMES DA SILVA - O GOIANO </t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>GOIAS</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>Federal - L Real -Trimestral</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>Ricardo Ferreira</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>Reynaldo Santos</t>
+        </is>
+      </c>
+      <c r="G802" t="n">
+        <v>11616</v>
+      </c>
+      <c r="H802" t="n">
+        <v>0</v>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>DP - DEPTO. PESSOAL</t>
+        </is>
+      </c>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>Envio de ATA de Implantação - DP - SP</t>
+        </is>
+      </c>
+      <c r="K802" t="inlineStr"/>
+      <c r="L802" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="M802" t="inlineStr"/>
+      <c r="N802" t="inlineStr">
+        <is>
+          <t>07/2026</t>
+        </is>
+      </c>
+      <c r="O802" t="n">
+        <v>18195071</v>
+      </c>
+      <c r="P802" t="inlineStr">
+        <is>
+          <t>Mauricio Lermen</t>
+        </is>
+      </c>
+      <c r="Q802" t="inlineStr">
+        <is>
+          <t>Em Aberto</t>
+        </is>
+      </c>
+      <c r="R802" t="inlineStr"/>
+      <c r="S802" t="n">
+        <v>0</v>
+      </c>
+      <c r="T802" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO AVENIDA</t>
+        </is>
+      </c>
+      <c r="U802" t="inlineStr">
+        <is>
+          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6981; Tarefa Incluida: 11616; Vencimento: 01/07/2026 00:00:00; UsuarioResponsavel: mauricio - Data Comentário: 01/07/2026 09:04</t>
+        </is>
+      </c>
+      <c r="V802" t="inlineStr"/>
+      <c r="W802" t="inlineStr"/>
+      <c r="X802" t="inlineStr"/>
+      <c r="Y802" t="inlineStr"/>
+      <c r="Z802" t="inlineStr"/>
+      <c r="AA802" t="inlineStr"/>
+      <c r="AB802" t="inlineStr"/>
+      <c r="AC802" t="inlineStr"/>
+      <c r="AD802" t="inlineStr"/>
+      <c r="AE802" t="inlineStr">
+        <is>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AF802" t="inlineStr"/>
+    </row>
+    <row r="803">
+      <c r="A803" t="n">
+        <v>6981</v>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUIZ GOMES DA SILVA - O GOIANO </t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>GOIAS</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>Federal - L Real -Trimestral</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>Ricardo Ferreira</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>Reynaldo Santos</t>
+        </is>
+      </c>
+      <c r="G803" t="n">
+        <v>11618</v>
+      </c>
+      <c r="H803" t="n">
+        <v>0</v>
+      </c>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>EF - VAREJO</t>
+        </is>
+      </c>
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>Envio de ATA de Implantação - EF V - SP</t>
+        </is>
+      </c>
+      <c r="K803" t="inlineStr"/>
+      <c r="L803" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="M803" t="inlineStr"/>
+      <c r="N803" t="inlineStr">
+        <is>
+          <t>07/2026</t>
+        </is>
+      </c>
+      <c r="O803" t="n">
+        <v>18195073</v>
+      </c>
+      <c r="P803" t="inlineStr">
+        <is>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="Q803" t="inlineStr">
+        <is>
+          <t>Em Aberto</t>
+        </is>
+      </c>
+      <c r="R803" t="inlineStr"/>
+      <c r="S803" t="n">
+        <v>0</v>
+      </c>
+      <c r="T803" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO AVENIDA</t>
+        </is>
+      </c>
+      <c r="U803" t="inlineStr">
+        <is>
+          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6981; Tarefa Incluida: 11618; Vencimento: 01/07/2026 00:00:00; UsuarioResponsavel: Claudineia - Data Comentário: 01/07/2026 09:04</t>
+        </is>
+      </c>
+      <c r="V803" t="inlineStr"/>
+      <c r="W803" t="inlineStr"/>
+      <c r="X803" t="inlineStr"/>
+      <c r="Y803" t="inlineStr"/>
+      <c r="Z803" t="inlineStr"/>
+      <c r="AA803" t="inlineStr"/>
+      <c r="AB803" t="inlineStr"/>
+      <c r="AC803" t="inlineStr"/>
+      <c r="AD803" t="inlineStr"/>
+      <c r="AE803" t="inlineStr">
+        <is>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AF803" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8268" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8270" uniqueCount="341">
   <si>
     <t>CodCliente</t>
   </si>
@@ -565,10 +565,10 @@
     <t>08/09/2026</t>
   </si>
   <si>
-    <t>09/09/2026</t>
+    <t>10/09/2026</t>
   </si>
   <si>
-    <t>10/09/2026</t>
+    <t>09/09/2026</t>
   </si>
   <si>
     <t>14/09/2026</t>
@@ -750,6 +750,9 @@
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/09/2026 
 Enviado somente após finalizar a FP - Data Comentário: 08/09/2026 08:27</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 10/09/2026 - Data Comentário: 08/09/2026 11:43</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 09/09/2026 - Data Comentário: 04/09/2026 16:13</t>
@@ -1557,10 +1560,10 @@
         <v>0</v>
       </c>
       <c r="AF2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:33">
@@ -1619,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:33">
@@ -1656,6 +1659,9 @@
       <c r="L4" s="1">
         <v>46275</v>
       </c>
+      <c r="M4" t="s">
+        <v>183</v>
+      </c>
       <c r="N4" t="s">
         <v>193</v>
       </c>
@@ -1674,14 +1680,17 @@
       <c r="T4" t="s">
         <v>228</v>
       </c>
+      <c r="V4" t="s">
+        <v>245</v>
+      </c>
       <c r="Z4">
         <v>0</v>
       </c>
       <c r="AF4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:33">
@@ -1719,7 +1728,7 @@
         <v>46275</v>
       </c>
       <c r="M5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N5" t="s">
         <v>193</v>
@@ -1740,16 +1749,16 @@
         <v>230</v>
       </c>
       <c r="V5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Z5">
         <v>0</v>
       </c>
       <c r="AF5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:33">
@@ -1787,7 +1796,7 @@
         <v>46275</v>
       </c>
       <c r="M6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N6" t="s">
         <v>193</v>
@@ -1808,16 +1817,16 @@
         <v>231</v>
       </c>
       <c r="V6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Z6">
         <v>0</v>
       </c>
       <c r="AF6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="7" spans="1:33">
@@ -1855,7 +1864,7 @@
         <v>46275</v>
       </c>
       <c r="M7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N7" t="s">
         <v>193</v>
@@ -1876,16 +1885,16 @@
         <v>231</v>
       </c>
       <c r="V7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Z7">
         <v>0</v>
       </c>
       <c r="AF7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8" spans="1:33">
@@ -1923,7 +1932,7 @@
         <v>46275</v>
       </c>
       <c r="M8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N8" t="s">
         <v>193</v>
@@ -1944,16 +1953,16 @@
         <v>232</v>
       </c>
       <c r="V8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Z8">
         <v>0</v>
       </c>
       <c r="AF8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" spans="1:33">
@@ -2012,10 +2021,10 @@
         <v>0</v>
       </c>
       <c r="AF9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10" spans="1:33">
@@ -2074,10 +2083,10 @@
         <v>0</v>
       </c>
       <c r="AF10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" spans="1:33">
@@ -2136,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="AF11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="12" spans="1:33">
@@ -2195,10 +2204,10 @@
         <v>0</v>
       </c>
       <c r="AF12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13" spans="1:33">
@@ -2257,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="AF13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="14" spans="1:33">
@@ -2316,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AF14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="15" spans="1:33">
@@ -2378,16 +2387,16 @@
         <v>235</v>
       </c>
       <c r="V15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Z15">
         <v>0</v>
       </c>
       <c r="AF15" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG15" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="16" spans="1:33">
@@ -2446,10 +2455,10 @@
         <v>0</v>
       </c>
       <c r="AF16" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG16" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="17" spans="1:33">
@@ -2508,10 +2517,10 @@
         <v>0</v>
       </c>
       <c r="AF17" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG17" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="18" spans="1:33">
@@ -2570,10 +2579,10 @@
         <v>0</v>
       </c>
       <c r="AF18" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG18" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="19" spans="1:33">
@@ -2632,16 +2641,16 @@
         <v>232</v>
       </c>
       <c r="V19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Z19">
         <v>0</v>
       </c>
       <c r="AF19" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG19" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="20" spans="1:33">
@@ -2700,10 +2709,10 @@
         <v>0</v>
       </c>
       <c r="AF20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG20" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="21" spans="1:33">
@@ -2762,10 +2771,10 @@
         <v>0</v>
       </c>
       <c r="AF21" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG21" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="22" spans="1:33">
@@ -2824,10 +2833,10 @@
         <v>0</v>
       </c>
       <c r="AF22" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG22" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="23" spans="1:33">
@@ -2865,7 +2874,7 @@
         <v>46275</v>
       </c>
       <c r="M23" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N23" t="s">
         <v>194</v>
@@ -2886,16 +2895,16 @@
         <v>231</v>
       </c>
       <c r="V23" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Z23">
         <v>0</v>
       </c>
       <c r="AF23" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG23" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="24" spans="1:33">
@@ -2933,7 +2942,7 @@
         <v>46275</v>
       </c>
       <c r="M24" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N24" t="s">
         <v>194</v>
@@ -2954,16 +2963,16 @@
         <v>231</v>
       </c>
       <c r="V24" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Z24">
         <v>0</v>
       </c>
       <c r="AF24" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG24" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="25" spans="1:33">
@@ -3001,7 +3010,7 @@
         <v>46274</v>
       </c>
       <c r="M25" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N25" t="s">
         <v>194</v>
@@ -3022,16 +3031,16 @@
         <v>234</v>
       </c>
       <c r="V25" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Z25">
         <v>0</v>
       </c>
       <c r="AF25" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG25" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="26" spans="1:33">
@@ -3090,7 +3099,7 @@
         <v>0</v>
       </c>
       <c r="AF26" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG26" t="s">
         <v>206</v>
@@ -3131,7 +3140,7 @@
         <v>46276</v>
       </c>
       <c r="M27" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N27" t="s">
         <v>193</v>
@@ -3152,13 +3161,13 @@
         <v>235</v>
       </c>
       <c r="V27" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Z27">
         <v>0</v>
       </c>
       <c r="AF27" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG27" t="s">
         <v>206</v>
@@ -3220,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="AF28" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG28" t="s">
         <v>206</v>
@@ -3282,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="AF29" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG29" t="s">
         <v>206</v>
@@ -3344,13 +3353,13 @@
         <v>233</v>
       </c>
       <c r="V30" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Z30">
         <v>0</v>
       </c>
       <c r="AF30" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="31" spans="1:33">
@@ -3409,13 +3418,13 @@
         <v>234</v>
       </c>
       <c r="V31" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Z31">
         <v>0</v>
       </c>
       <c r="AF31" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG31" t="s">
         <v>206</v>
@@ -3477,13 +3486,13 @@
         <v>237</v>
       </c>
       <c r="V32" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Z32">
         <v>0</v>
       </c>
       <c r="AF32" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG32" t="s">
         <v>206</v>
@@ -3545,13 +3554,13 @@
         <v>237</v>
       </c>
       <c r="V33" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Z33">
         <v>0</v>
       </c>
       <c r="AF33" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG33" t="s">
         <v>206</v>
@@ -3613,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="AF34" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG34" t="s">
         <v>206</v>
@@ -3654,7 +3663,7 @@
         <v>46274</v>
       </c>
       <c r="M35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N35" t="s">
         <v>193</v>
@@ -3675,13 +3684,13 @@
         <v>234</v>
       </c>
       <c r="V35" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Z35">
         <v>0</v>
       </c>
       <c r="AF35" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG35" t="s">
         <v>206</v>
@@ -3743,7 +3752,7 @@
         <v>0</v>
       </c>
       <c r="AF36" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG36" t="s">
         <v>206</v>
@@ -3805,7 +3814,7 @@
         <v>0</v>
       </c>
       <c r="AF37" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s">
         <v>206</v>
@@ -3867,13 +3876,13 @@
         <v>235</v>
       </c>
       <c r="V38" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Z38">
         <v>0</v>
       </c>
       <c r="AF38" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG38" t="s">
         <v>206</v>
@@ -3935,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="AF39" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG39" t="s">
         <v>206</v>
@@ -3997,13 +4006,13 @@
         <v>233</v>
       </c>
       <c r="V40" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Z40">
         <v>0</v>
       </c>
       <c r="AF40" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="41" spans="1:33">
@@ -4062,13 +4071,13 @@
         <v>234</v>
       </c>
       <c r="V41" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Z41">
         <v>0</v>
       </c>
       <c r="AF41" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG41" t="s">
         <v>206</v>
@@ -4130,7 +4139,7 @@
         <v>0</v>
       </c>
       <c r="AF42" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG42" t="s">
         <v>206</v>
@@ -4192,7 +4201,7 @@
         <v>0</v>
       </c>
       <c r="AF43" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG43" t="s">
         <v>206</v>
@@ -4254,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="AF44" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="45" spans="1:33">
@@ -4313,7 +4322,7 @@
         <v>0</v>
       </c>
       <c r="AF45" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG45" t="s">
         <v>206</v>
@@ -4375,7 +4384,7 @@
         <v>0</v>
       </c>
       <c r="AF46" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG46" t="s">
         <v>206</v>
@@ -4437,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="AF47" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="48" spans="1:33">
@@ -4496,7 +4505,7 @@
         <v>0</v>
       </c>
       <c r="AF48" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG48" t="s">
         <v>206</v>
@@ -4558,7 +4567,7 @@
         <v>0</v>
       </c>
       <c r="AF49" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG49" t="s">
         <v>206</v>
@@ -4620,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="AF50" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG50" t="s">
         <v>206</v>
@@ -4682,10 +4691,10 @@
         <v>0</v>
       </c>
       <c r="AF51" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG51" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="52" spans="1:33">
@@ -4744,10 +4753,10 @@
         <v>0</v>
       </c>
       <c r="AF52" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG52" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="53" spans="1:33">
@@ -4806,10 +4815,10 @@
         <v>0</v>
       </c>
       <c r="AF53" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG53" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="54" spans="1:33">
@@ -4868,10 +4877,10 @@
         <v>0</v>
       </c>
       <c r="AF54" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG54" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="55" spans="1:33">
@@ -4930,10 +4939,10 @@
         <v>0</v>
       </c>
       <c r="AF55" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG55" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="56" spans="1:33">
@@ -4992,10 +5001,10 @@
         <v>0</v>
       </c>
       <c r="AF56" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG56" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="57" spans="1:33">
@@ -5054,10 +5063,10 @@
         <v>0</v>
       </c>
       <c r="AF57" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG57" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="58" spans="1:33">
@@ -5116,10 +5125,10 @@
         <v>0</v>
       </c>
       <c r="AF58" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG58" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="59" spans="1:33">
@@ -5178,10 +5187,10 @@
         <v>0</v>
       </c>
       <c r="AF59" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG59" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="60" spans="1:33">
@@ -5240,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="AF60" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="61" spans="1:33">
@@ -5302,10 +5311,10 @@
         <v>0</v>
       </c>
       <c r="AF61" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG61" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="62" spans="1:33">
@@ -5364,10 +5373,10 @@
         <v>0</v>
       </c>
       <c r="AF62" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG62" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="63" spans="1:33">
@@ -5426,10 +5435,10 @@
         <v>0</v>
       </c>
       <c r="AF63" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG63" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="64" spans="1:33">
@@ -5488,10 +5497,10 @@
         <v>0</v>
       </c>
       <c r="AF64" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG64" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="65" spans="1:33">
@@ -5550,10 +5559,10 @@
         <v>0</v>
       </c>
       <c r="AF65" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG65" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="66" spans="1:33">
@@ -5612,10 +5621,10 @@
         <v>0</v>
       </c>
       <c r="AF66" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG66" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="67" spans="1:33">
@@ -5674,10 +5683,10 @@
         <v>0</v>
       </c>
       <c r="AF67" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG67" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="68" spans="1:33">
@@ -5736,10 +5745,10 @@
         <v>0</v>
       </c>
       <c r="AF68" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG68" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="69" spans="1:33">
@@ -5798,10 +5807,10 @@
         <v>0</v>
       </c>
       <c r="AF69" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG69" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:33">
@@ -5860,10 +5869,10 @@
         <v>0</v>
       </c>
       <c r="AF70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG70" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:33">
@@ -5922,10 +5931,10 @@
         <v>0</v>
       </c>
       <c r="AF71" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG71" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:33">
@@ -5984,10 +5993,10 @@
         <v>0</v>
       </c>
       <c r="AF72" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG72" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:33">
@@ -6046,10 +6055,10 @@
         <v>0</v>
       </c>
       <c r="AF73" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:33">
@@ -6108,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="AF74" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG74" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:33">
@@ -6170,10 +6179,10 @@
         <v>0</v>
       </c>
       <c r="AF75" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG75" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:33">
@@ -6232,10 +6241,10 @@
         <v>0</v>
       </c>
       <c r="AF76" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG76" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:33">
@@ -6294,10 +6303,10 @@
         <v>0</v>
       </c>
       <c r="AF77" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG77" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="78" spans="1:33">
@@ -6356,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="AF78" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG78" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="79" spans="1:33">
@@ -6418,10 +6427,10 @@
         <v>0</v>
       </c>
       <c r="AF79" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG79" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="80" spans="1:33">
@@ -6480,10 +6489,10 @@
         <v>0</v>
       </c>
       <c r="AF80" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG80" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="81" spans="1:33">
@@ -6542,10 +6551,10 @@
         <v>0</v>
       </c>
       <c r="AF81" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG81" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="82" spans="1:33">
@@ -6604,7 +6613,7 @@
         <v>0</v>
       </c>
       <c r="AF82" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="83" spans="1:33">
@@ -6663,7 +6672,7 @@
         <v>0</v>
       </c>
       <c r="AF83" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="84" spans="1:33">
@@ -6722,7 +6731,7 @@
         <v>0</v>
       </c>
       <c r="AF84" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="85" spans="1:33">
@@ -6781,7 +6790,7 @@
         <v>0</v>
       </c>
       <c r="AF85" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="86" spans="1:33">
@@ -6840,7 +6849,7 @@
         <v>0</v>
       </c>
       <c r="AF86" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="87" spans="1:33">
@@ -6899,7 +6908,7 @@
         <v>0</v>
       </c>
       <c r="AF87" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="88" spans="1:33">
@@ -6958,7 +6967,7 @@
         <v>0</v>
       </c>
       <c r="AF88" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="89" spans="1:33">
@@ -7017,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="AF89" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="90" spans="1:33">
@@ -7076,7 +7085,7 @@
         <v>0</v>
       </c>
       <c r="AF90" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="91" spans="1:33">
@@ -7135,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="AF91" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="92" spans="1:33">
@@ -7194,7 +7203,7 @@
         <v>0</v>
       </c>
       <c r="AF92" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="93" spans="1:33">
@@ -7253,7 +7262,7 @@
         <v>0</v>
       </c>
       <c r="AF93" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="94" spans="1:33">
@@ -7312,7 +7321,7 @@
         <v>0</v>
       </c>
       <c r="AF94" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="95" spans="1:33">
@@ -7371,7 +7380,7 @@
         <v>0</v>
       </c>
       <c r="AF95" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="96" spans="1:33">
@@ -7430,7 +7439,7 @@
         <v>0</v>
       </c>
       <c r="AF96" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="97" spans="1:33">
@@ -7489,7 +7498,7 @@
         <v>0</v>
       </c>
       <c r="AF97" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="98" spans="1:33">
@@ -7548,7 +7557,7 @@
         <v>0</v>
       </c>
       <c r="AF98" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="99" spans="1:33">
@@ -7607,7 +7616,7 @@
         <v>0</v>
       </c>
       <c r="AF99" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="100" spans="1:33">
@@ -7666,7 +7675,7 @@
         <v>0</v>
       </c>
       <c r="AF100" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="101" spans="1:33">
@@ -7728,13 +7737,13 @@
         <v>0</v>
       </c>
       <c r="AA101" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AF101" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG101" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="102" spans="1:33">
@@ -7796,13 +7805,13 @@
         <v>0</v>
       </c>
       <c r="AA102" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AF102" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG102" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="103" spans="1:33">
@@ -7864,13 +7873,13 @@
         <v>0</v>
       </c>
       <c r="AA103" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AF103" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG103" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="104" spans="1:33">
@@ -7932,13 +7941,13 @@
         <v>0</v>
       </c>
       <c r="AA104" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AF104" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG104" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="105" spans="1:33">
@@ -8000,13 +8009,13 @@
         <v>0</v>
       </c>
       <c r="AA105" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AF105" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG105" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="106" spans="1:33">
@@ -8068,13 +8077,13 @@
         <v>0</v>
       </c>
       <c r="AA106" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AF106" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG106" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="107" spans="1:33">
@@ -8136,13 +8145,13 @@
         <v>0</v>
       </c>
       <c r="AA107" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AF107" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG107" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="108" spans="1:33">
@@ -8204,13 +8213,13 @@
         <v>0</v>
       </c>
       <c r="AA108" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AF108" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG108" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="109" spans="1:33">
@@ -8272,13 +8281,13 @@
         <v>0</v>
       </c>
       <c r="AA109" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AF109" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG109" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="110" spans="1:33">
@@ -8340,13 +8349,13 @@
         <v>0</v>
       </c>
       <c r="AA110" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AF110" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG110" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="111" spans="1:33">
@@ -8408,13 +8417,13 @@
         <v>0</v>
       </c>
       <c r="AA111" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AF111" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG111" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="112" spans="1:33">
@@ -8476,7 +8485,7 @@
         <v>231</v>
       </c>
       <c r="V112" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Z112">
         <v>0</v>
@@ -8485,10 +8494,10 @@
         <v>200</v>
       </c>
       <c r="AF112" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG112" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="113" spans="1:33">
@@ -8553,10 +8562,10 @@
         <v>202</v>
       </c>
       <c r="AF113" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG113" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="114" spans="1:33">
@@ -8618,7 +8627,7 @@
         <v>234</v>
       </c>
       <c r="V114" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Z114">
         <v>0</v>
@@ -8627,10 +8636,10 @@
         <v>203</v>
       </c>
       <c r="AF114" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG114" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="115" spans="1:33">
@@ -8692,7 +8701,7 @@
         <v>229</v>
       </c>
       <c r="V115" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z115">
         <v>0</v>
@@ -8701,7 +8710,7 @@
         <v>199</v>
       </c>
       <c r="AF115" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="116" spans="1:33">
@@ -8766,10 +8775,10 @@
         <v>200</v>
       </c>
       <c r="AF116" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG116" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="117" spans="1:33">
@@ -8831,7 +8840,7 @@
         <v>235</v>
       </c>
       <c r="V117" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Z117">
         <v>0</v>
@@ -8840,10 +8849,10 @@
         <v>204</v>
       </c>
       <c r="AF117" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG117" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="118" spans="1:33">
@@ -8905,7 +8914,7 @@
         <v>236</v>
       </c>
       <c r="V118" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z118">
         <v>0</v>
@@ -8914,10 +8923,10 @@
         <v>205</v>
       </c>
       <c r="AF118" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG118" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="119" spans="1:33">
@@ -8982,10 +8991,10 @@
         <v>203</v>
       </c>
       <c r="AF119" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG119" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="120" spans="1:33">
@@ -9047,7 +9056,7 @@
         <v>235</v>
       </c>
       <c r="V120" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Z120">
         <v>0</v>
@@ -9056,10 +9065,10 @@
         <v>204</v>
       </c>
       <c r="AF120" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG120" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="121" spans="1:33">
@@ -9121,7 +9130,7 @@
         <v>236</v>
       </c>
       <c r="V121" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Z121">
         <v>0</v>
@@ -9130,10 +9139,10 @@
         <v>205</v>
       </c>
       <c r="AF121" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG121" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="122" spans="1:33">
@@ -9195,16 +9204,16 @@
         <v>229</v>
       </c>
       <c r="V122" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Z122">
         <v>0</v>
       </c>
       <c r="AA122" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AF122" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="123" spans="1:33">
@@ -9266,7 +9275,7 @@
         <v>230</v>
       </c>
       <c r="V123" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Z123">
         <v>0</v>
@@ -9275,10 +9284,10 @@
         <v>200</v>
       </c>
       <c r="AF123" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG123" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="124" spans="1:33">
@@ -9340,7 +9349,7 @@
         <v>231</v>
       </c>
       <c r="V124" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Z124">
         <v>0</v>
@@ -9349,10 +9358,10 @@
         <v>200</v>
       </c>
       <c r="AF124" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG124" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="125" spans="1:33">
@@ -9414,7 +9423,7 @@
         <v>231</v>
       </c>
       <c r="V125" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Z125">
         <v>0</v>
@@ -9423,10 +9432,10 @@
         <v>200</v>
       </c>
       <c r="AF125" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG125" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="126" spans="1:33">
@@ -9488,7 +9497,7 @@
         <v>236</v>
       </c>
       <c r="V126" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Z126">
         <v>0</v>
@@ -9497,10 +9506,10 @@
         <v>205</v>
       </c>
       <c r="AF126" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG126" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="127" spans="1:33">
@@ -9562,7 +9571,7 @@
         <v>232</v>
       </c>
       <c r="V127" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Z127">
         <v>0</v>
@@ -9571,10 +9580,10 @@
         <v>201</v>
       </c>
       <c r="AF127" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG127" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="128" spans="1:33">
@@ -9636,7 +9645,7 @@
         <v>233</v>
       </c>
       <c r="V128" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Z128">
         <v>0</v>
@@ -9645,10 +9654,10 @@
         <v>202</v>
       </c>
       <c r="AF128" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG128" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="129" spans="1:33">
@@ -9710,7 +9719,7 @@
         <v>234</v>
       </c>
       <c r="V129" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Z129">
         <v>0</v>
@@ -9719,10 +9728,10 @@
         <v>203</v>
       </c>
       <c r="AF129" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG129" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="130" spans="1:33">
@@ -9787,10 +9796,10 @@
         <v>200</v>
       </c>
       <c r="AF130" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG130" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="131" spans="1:33">
@@ -9855,10 +9864,10 @@
         <v>200</v>
       </c>
       <c r="AF131" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG131" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="132" spans="1:33">
@@ -9923,10 +9932,10 @@
         <v>200</v>
       </c>
       <c r="AF132" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG132" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="133" spans="1:33">
@@ -9991,10 +10000,10 @@
         <v>205</v>
       </c>
       <c r="AF133" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG133" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="134" spans="1:33">
@@ -10059,10 +10068,10 @@
         <v>201</v>
       </c>
       <c r="AF134" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG134" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="135" spans="1:33">
@@ -10127,10 +10136,10 @@
         <v>203</v>
       </c>
       <c r="AF135" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG135" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="136" spans="1:33">
@@ -10195,7 +10204,7 @@
         <v>199</v>
       </c>
       <c r="AF136" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="137" spans="1:33">
@@ -10260,10 +10269,10 @@
         <v>200</v>
       </c>
       <c r="AF137" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG137" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="138" spans="1:33">
@@ -10325,7 +10334,7 @@
         <v>235</v>
       </c>
       <c r="V138" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Z138">
         <v>0</v>
@@ -10334,10 +10343,10 @@
         <v>204</v>
       </c>
       <c r="AF138" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG138" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="139" spans="1:33">
@@ -10399,7 +10408,7 @@
         <v>236</v>
       </c>
       <c r="V139" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z139">
         <v>0</v>
@@ -10408,10 +10417,10 @@
         <v>205</v>
       </c>
       <c r="AF139" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG139" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="140" spans="1:33">
@@ -10476,10 +10485,10 @@
         <v>203</v>
       </c>
       <c r="AF140" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG140" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="141" spans="1:33">
@@ -10544,7 +10553,7 @@
         <v>199</v>
       </c>
       <c r="AF141" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="142" spans="1:33">
@@ -10609,10 +10618,10 @@
         <v>200</v>
       </c>
       <c r="AF142" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG142" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="143" spans="1:33">
@@ -10677,10 +10686,10 @@
         <v>204</v>
       </c>
       <c r="AF143" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG143" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="144" spans="1:33">
@@ -10745,10 +10754,10 @@
         <v>200</v>
       </c>
       <c r="AF144" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG144" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="145" spans="1:33">
@@ -10813,10 +10822,10 @@
         <v>200</v>
       </c>
       <c r="AF145" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG145" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="146" spans="1:33">
@@ -10881,10 +10890,10 @@
         <v>201</v>
       </c>
       <c r="AF146" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG146" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="147" spans="1:33">
@@ -10949,10 +10958,10 @@
         <v>202</v>
       </c>
       <c r="AF147" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG147" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="148" spans="1:33">
@@ -11017,10 +11026,10 @@
         <v>203</v>
       </c>
       <c r="AF148" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG148" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="149" spans="1:33">
@@ -11082,7 +11091,7 @@
         <v>230</v>
       </c>
       <c r="V149" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Z149">
         <v>0</v>
@@ -11091,10 +11100,10 @@
         <v>200</v>
       </c>
       <c r="AF149" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG149" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="150" spans="1:33">
@@ -11156,7 +11165,7 @@
         <v>231</v>
       </c>
       <c r="V150" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Z150">
         <v>0</v>
@@ -11165,10 +11174,10 @@
         <v>200</v>
       </c>
       <c r="AF150" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG150" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="151" spans="1:33">
@@ -11230,7 +11239,7 @@
         <v>231</v>
       </c>
       <c r="V151" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Z151">
         <v>0</v>
@@ -11239,10 +11248,10 @@
         <v>200</v>
       </c>
       <c r="AF151" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG151" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="152" spans="1:33">
@@ -11304,7 +11313,7 @@
         <v>236</v>
       </c>
       <c r="V152" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Z152">
         <v>0</v>
@@ -11313,10 +11322,10 @@
         <v>205</v>
       </c>
       <c r="AF152" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG152" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="153" spans="1:33">
@@ -11381,10 +11390,10 @@
         <v>204</v>
       </c>
       <c r="AF153" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG153" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="154" spans="1:33">
@@ -11446,7 +11455,7 @@
         <v>229</v>
       </c>
       <c r="V154" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Z154">
         <v>0</v>
@@ -11455,7 +11464,7 @@
         <v>199</v>
       </c>
       <c r="AF154" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="155" spans="1:33">
@@ -11517,7 +11526,7 @@
         <v>230</v>
       </c>
       <c r="V155" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Z155">
         <v>0</v>
@@ -11526,10 +11535,10 @@
         <v>200</v>
       </c>
       <c r="AF155" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG155" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="156" spans="1:33">
@@ -11591,7 +11600,7 @@
         <v>231</v>
       </c>
       <c r="V156" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Z156">
         <v>0</v>
@@ -11600,10 +11609,10 @@
         <v>200</v>
       </c>
       <c r="AF156" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG156" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="157" spans="1:33">
@@ -11665,7 +11674,7 @@
         <v>231</v>
       </c>
       <c r="V157" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Z157">
         <v>0</v>
@@ -11674,10 +11683,10 @@
         <v>200</v>
       </c>
       <c r="AF157" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG157" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="158" spans="1:33">
@@ -11739,7 +11748,7 @@
         <v>236</v>
       </c>
       <c r="V158" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Z158">
         <v>0</v>
@@ -11748,10 +11757,10 @@
         <v>205</v>
       </c>
       <c r="AF158" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG158" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="159" spans="1:33">
@@ -11813,7 +11822,7 @@
         <v>232</v>
       </c>
       <c r="V159" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Z159">
         <v>0</v>
@@ -11822,10 +11831,10 @@
         <v>201</v>
       </c>
       <c r="AF159" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG159" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="160" spans="1:33">
@@ -11887,7 +11896,7 @@
         <v>233</v>
       </c>
       <c r="V160" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Z160">
         <v>0</v>
@@ -11896,10 +11905,10 @@
         <v>202</v>
       </c>
       <c r="AF160" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG160" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="161" spans="1:33">
@@ -11961,7 +11970,7 @@
         <v>234</v>
       </c>
       <c r="V161" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Z161">
         <v>0</v>
@@ -11970,10 +11979,10 @@
         <v>203</v>
       </c>
       <c r="AF161" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG161" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="162" spans="1:33">
@@ -12035,7 +12044,7 @@
         <v>230</v>
       </c>
       <c r="V162" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Z162">
         <v>0</v>
@@ -12044,10 +12053,10 @@
         <v>200</v>
       </c>
       <c r="AF162" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG162" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="163" spans="1:33">
@@ -12112,7 +12121,7 @@
         <v>199</v>
       </c>
       <c r="AF163" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="164" spans="1:33">
@@ -12177,10 +12186,10 @@
         <v>200</v>
       </c>
       <c r="AF164" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG164" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="165" spans="1:33">
@@ -12245,10 +12254,10 @@
         <v>200</v>
       </c>
       <c r="AF165" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG165" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="166" spans="1:33">
@@ -12313,10 +12322,10 @@
         <v>200</v>
       </c>
       <c r="AF166" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG166" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="167" spans="1:33">
@@ -12381,10 +12390,10 @@
         <v>205</v>
       </c>
       <c r="AF167" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG167" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="168" spans="1:33">
@@ -12449,10 +12458,10 @@
         <v>201</v>
       </c>
       <c r="AF168" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG168" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="169" spans="1:33">
@@ -12517,10 +12526,10 @@
         <v>202</v>
       </c>
       <c r="AF169" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG169" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="170" spans="1:33">
@@ -12585,10 +12594,10 @@
         <v>203</v>
       </c>
       <c r="AF170" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG170" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="171" spans="1:33">
@@ -12653,7 +12662,7 @@
         <v>206</v>
       </c>
       <c r="AF171" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG171" t="s">
         <v>206</v>
@@ -12721,7 +12730,7 @@
         <v>206</v>
       </c>
       <c r="AF172" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG172" t="s">
         <v>206</v>
@@ -12786,7 +12795,7 @@
         <v>233</v>
       </c>
       <c r="V173" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Z173">
         <v>0</v>
@@ -12795,7 +12804,7 @@
         <v>206</v>
       </c>
       <c r="AF173" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="174" spans="1:33">
@@ -12860,7 +12869,7 @@
         <v>209</v>
       </c>
       <c r="AF174" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG174" t="s">
         <v>206</v>
@@ -12928,7 +12937,7 @@
         <v>206</v>
       </c>
       <c r="AF175" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG175" t="s">
         <v>206</v>
@@ -12996,7 +13005,7 @@
         <v>206</v>
       </c>
       <c r="AF176" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG176" t="s">
         <v>206</v>
@@ -13064,7 +13073,7 @@
         <v>206</v>
       </c>
       <c r="AF177" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG177" t="s">
         <v>206</v>
@@ -13132,7 +13141,7 @@
         <v>206</v>
       </c>
       <c r="AF178" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="179" spans="1:33">
@@ -13197,7 +13206,7 @@
         <v>209</v>
       </c>
       <c r="AF179" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG179" t="s">
         <v>206</v>
@@ -13265,7 +13274,7 @@
         <v>206</v>
       </c>
       <c r="AF180" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG180" t="s">
         <v>206</v>
@@ -13333,7 +13342,7 @@
         <v>206</v>
       </c>
       <c r="AF181" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG181" t="s">
         <v>206</v>
@@ -13401,7 +13410,7 @@
         <v>206</v>
       </c>
       <c r="AF182" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG182" t="s">
         <v>206</v>
@@ -13469,7 +13478,7 @@
         <v>206</v>
       </c>
       <c r="AF183" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="184" spans="1:33">
@@ -13534,7 +13543,7 @@
         <v>209</v>
       </c>
       <c r="AF184" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG184" t="s">
         <v>206</v>
@@ -13602,7 +13611,7 @@
         <v>206</v>
       </c>
       <c r="AF185" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG185" t="s">
         <v>206</v>
@@ -13670,7 +13679,7 @@
         <v>206</v>
       </c>
       <c r="AF186" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG186" t="s">
         <v>206</v>
@@ -13738,7 +13747,7 @@
         <v>209</v>
       </c>
       <c r="AF187" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG187" t="s">
         <v>206</v>
@@ -13803,7 +13812,7 @@
         <v>237</v>
       </c>
       <c r="V188" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Z188">
         <v>0</v>
@@ -13812,7 +13821,7 @@
         <v>206</v>
       </c>
       <c r="AF188" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG188" t="s">
         <v>206</v>
@@ -13880,7 +13889,7 @@
         <v>206</v>
       </c>
       <c r="AF189" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="190" spans="1:33">
@@ -13945,7 +13954,7 @@
         <v>206</v>
       </c>
       <c r="AF190" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG190" t="s">
         <v>206</v>
@@ -14013,7 +14022,7 @@
         <v>206</v>
       </c>
       <c r="AF191" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG191" t="s">
         <v>206</v>
@@ -14081,7 +14090,7 @@
         <v>206</v>
       </c>
       <c r="AF192" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG192" t="s">
         <v>206</v>
@@ -14149,7 +14158,7 @@
         <v>206</v>
       </c>
       <c r="AF193" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="194" spans="1:33">
@@ -14214,7 +14223,7 @@
         <v>209</v>
       </c>
       <c r="AF194" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG194" t="s">
         <v>206</v>
@@ -14282,7 +14291,7 @@
         <v>206</v>
       </c>
       <c r="AF195" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG195" t="s">
         <v>206</v>
@@ -14350,7 +14359,7 @@
         <v>206</v>
       </c>
       <c r="AF196" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG196" t="s">
         <v>206</v>
@@ -14418,7 +14427,7 @@
         <v>206</v>
       </c>
       <c r="AF197" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="198" spans="1:33">
@@ -14483,7 +14492,7 @@
         <v>209</v>
       </c>
       <c r="AF198" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG198" t="s">
         <v>206</v>
@@ -14548,10 +14557,10 @@
         <v>0</v>
       </c>
       <c r="AA199" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF199" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="200" spans="1:33">
@@ -14613,10 +14622,10 @@
         <v>0</v>
       </c>
       <c r="AA200" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF200" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG200" t="s">
         <v>206</v>
@@ -14681,10 +14690,10 @@
         <v>0</v>
       </c>
       <c r="AA201" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF201" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG201" t="s">
         <v>206</v>
@@ -14749,10 +14758,10 @@
         <v>0</v>
       </c>
       <c r="AA202" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF202" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="203" spans="1:33">
@@ -14814,10 +14823,10 @@
         <v>0</v>
       </c>
       <c r="AA203" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF203" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG203" t="s">
         <v>206</v>
@@ -14885,7 +14894,7 @@
         <v>206</v>
       </c>
       <c r="AF204" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG204" t="s">
         <v>206</v>
@@ -14953,7 +14962,7 @@
         <v>206</v>
       </c>
       <c r="AF205" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG205" t="s">
         <v>206</v>
@@ -15021,7 +15030,7 @@
         <v>206</v>
       </c>
       <c r="AF206" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG206" t="s">
         <v>206</v>
@@ -15089,7 +15098,7 @@
         <v>206</v>
       </c>
       <c r="AF207" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="208" spans="1:33">
@@ -15154,7 +15163,7 @@
         <v>209</v>
       </c>
       <c r="AF208" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG208" t="s">
         <v>206</v>
@@ -15222,7 +15231,7 @@
         <v>206</v>
       </c>
       <c r="AF209" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG209" t="s">
         <v>206</v>
@@ -15290,7 +15299,7 @@
         <v>206</v>
       </c>
       <c r="AF210" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG210" t="s">
         <v>206</v>
@@ -15358,7 +15367,7 @@
         <v>206</v>
       </c>
       <c r="AF211" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG211" t="s">
         <v>206</v>
@@ -15426,7 +15435,7 @@
         <v>206</v>
       </c>
       <c r="AF212" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="213" spans="1:33">
@@ -15491,7 +15500,7 @@
         <v>209</v>
       </c>
       <c r="AF213" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG213" t="s">
         <v>206</v>
@@ -15559,10 +15568,10 @@
         <v>211</v>
       </c>
       <c r="AF214" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG214" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="215" spans="1:33">
@@ -15627,10 +15636,10 @@
         <v>211</v>
       </c>
       <c r="AF215" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG215" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="216" spans="1:33">
@@ -15692,7 +15701,7 @@
         <v>230</v>
       </c>
       <c r="V216" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z216">
         <v>0</v>
@@ -15701,10 +15710,10 @@
         <v>211</v>
       </c>
       <c r="AF216" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG216" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="217" spans="1:33">
@@ -15769,10 +15778,10 @@
         <v>211</v>
       </c>
       <c r="AF217" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG217" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="218" spans="1:33">
@@ -15837,10 +15846,10 @@
         <v>211</v>
       </c>
       <c r="AF218" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG218" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="219" spans="1:33">
@@ -15905,10 +15914,10 @@
         <v>211</v>
       </c>
       <c r="AF219" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG219" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="220" spans="1:33">
@@ -15973,10 +15982,10 @@
         <v>211</v>
       </c>
       <c r="AF220" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG220" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="221" spans="1:33">
@@ -16038,7 +16047,7 @@
         <v>230</v>
       </c>
       <c r="V221" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z221">
         <v>0</v>
@@ -16047,10 +16056,10 @@
         <v>211</v>
       </c>
       <c r="AF221" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG221" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="222" spans="1:33">
@@ -16115,10 +16124,10 @@
         <v>211</v>
       </c>
       <c r="AF222" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG222" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="223" spans="1:33">
@@ -16180,13 +16189,13 @@
         <v>0</v>
       </c>
       <c r="AA223" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF223" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG223" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="224" spans="1:33">
@@ -16248,13 +16257,13 @@
         <v>0</v>
       </c>
       <c r="AA224" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF224" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG224" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="225" spans="1:33">
@@ -16316,19 +16325,19 @@
         <v>230</v>
       </c>
       <c r="V225" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z225">
         <v>0</v>
       </c>
       <c r="AA225" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF225" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG225" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="226" spans="1:33">
@@ -16390,13 +16399,13 @@
         <v>0</v>
       </c>
       <c r="AA226" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF226" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG226" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="227" spans="1:33">
@@ -16458,13 +16467,13 @@
         <v>0</v>
       </c>
       <c r="AA227" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF227" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG227" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="228" spans="1:33">
@@ -16526,13 +16535,13 @@
         <v>0</v>
       </c>
       <c r="AA228" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF228" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG228" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="229" spans="1:33">
@@ -16594,7 +16603,7 @@
         <v>230</v>
       </c>
       <c r="V229" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Z229">
         <v>0</v>
@@ -16603,10 +16612,10 @@
         <v>211</v>
       </c>
       <c r="AF229" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG229" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="230" spans="1:33">
@@ -16671,10 +16680,10 @@
         <v>211</v>
       </c>
       <c r="AF230" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG230" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="231" spans="1:33">
@@ -16736,13 +16745,13 @@
         <v>0</v>
       </c>
       <c r="AA231" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AF231" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG231" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="232" spans="1:33">
@@ -16801,16 +16810,16 @@
         <v>236</v>
       </c>
       <c r="V232" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Z232">
         <v>0</v>
       </c>
       <c r="AA232" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF232" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="233" spans="1:33">
@@ -16872,10 +16881,10 @@
         <v>0</v>
       </c>
       <c r="AA233" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF233" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="234" spans="1:33">
@@ -16934,16 +16943,16 @@
         <v>234</v>
       </c>
       <c r="V234" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Z234">
         <v>0</v>
       </c>
       <c r="AA234" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF234" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="235" spans="1:33">
@@ -17005,10 +17014,10 @@
         <v>0</v>
       </c>
       <c r="AA235" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF235" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="236" spans="1:33">
@@ -17070,10 +17079,10 @@
         <v>0</v>
       </c>
       <c r="AA236" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF236" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="237" spans="1:33">
@@ -17132,16 +17141,16 @@
         <v>235</v>
       </c>
       <c r="V237" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Z237">
         <v>0</v>
       </c>
       <c r="AA237" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF237" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="238" spans="1:33">
@@ -17200,16 +17209,16 @@
         <v>236</v>
       </c>
       <c r="V238" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Z238">
         <v>0</v>
       </c>
       <c r="AA238" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF238" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="239" spans="1:33">
@@ -17271,10 +17280,10 @@
         <v>0</v>
       </c>
       <c r="AA239" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF239" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="240" spans="1:33">
@@ -17336,10 +17345,10 @@
         <v>0</v>
       </c>
       <c r="AA240" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF240" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="241" spans="1:32">
@@ -17398,16 +17407,16 @@
         <v>232</v>
       </c>
       <c r="V241" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Z241">
         <v>0</v>
       </c>
       <c r="AA241" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF241" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="242" spans="1:32">
@@ -17466,16 +17475,16 @@
         <v>233</v>
       </c>
       <c r="V242" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Z242">
         <v>0</v>
       </c>
       <c r="AA242" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF242" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="243" spans="1:32">
@@ -17534,16 +17543,16 @@
         <v>234</v>
       </c>
       <c r="V243" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Z243">
         <v>0</v>
       </c>
       <c r="AA243" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF243" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="244" spans="1:32">
@@ -17605,10 +17614,10 @@
         <v>0</v>
       </c>
       <c r="AA244" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF244" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="245" spans="1:32">
@@ -17670,10 +17679,10 @@
         <v>0</v>
       </c>
       <c r="AA245" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF245" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="246" spans="1:32">
@@ -17735,16 +17744,16 @@
         <v>229</v>
       </c>
       <c r="V246" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Z246">
         <v>0</v>
       </c>
       <c r="AA246" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF246" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="247" spans="1:32">
@@ -17806,16 +17815,16 @@
         <v>228</v>
       </c>
       <c r="V247" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Z247">
         <v>0</v>
       </c>
       <c r="AA247" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF247" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="248" spans="1:32">
@@ -17877,16 +17886,16 @@
         <v>230</v>
       </c>
       <c r="V248" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Z248">
         <v>0</v>
       </c>
       <c r="AA248" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF248" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="249" spans="1:32">
@@ -17948,16 +17957,16 @@
         <v>235</v>
       </c>
       <c r="V249" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Z249">
         <v>0</v>
       </c>
       <c r="AA249" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF249" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="250" spans="1:32">
@@ -18019,16 +18028,16 @@
         <v>231</v>
       </c>
       <c r="V250" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Z250">
         <v>0</v>
       </c>
       <c r="AA250" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF250" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="251" spans="1:32">
@@ -18090,16 +18099,16 @@
         <v>231</v>
       </c>
       <c r="V251" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Z251">
         <v>0</v>
       </c>
       <c r="AA251" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF251" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="252" spans="1:32">
@@ -18161,16 +18170,16 @@
         <v>236</v>
       </c>
       <c r="V252" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Z252">
         <v>0</v>
       </c>
       <c r="AA252" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF252" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="253" spans="1:32">
@@ -18232,16 +18241,16 @@
         <v>232</v>
       </c>
       <c r="V253" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Z253">
         <v>0</v>
       </c>
       <c r="AA253" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF253" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="254" spans="1:32">
@@ -18303,16 +18312,16 @@
         <v>232</v>
       </c>
       <c r="V254" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Z254">
         <v>0</v>
       </c>
       <c r="AA254" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF254" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="255" spans="1:32">
@@ -18374,16 +18383,16 @@
         <v>232</v>
       </c>
       <c r="V255" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Z255">
         <v>0</v>
       </c>
       <c r="AA255" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF255" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="256" spans="1:32">
@@ -18445,16 +18454,16 @@
         <v>233</v>
       </c>
       <c r="V256" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Z256">
         <v>0</v>
       </c>
       <c r="AA256" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF256" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="257" spans="1:32">
@@ -18516,16 +18525,16 @@
         <v>234</v>
       </c>
       <c r="V257" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Z257">
         <v>0</v>
       </c>
       <c r="AA257" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF257" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="258" spans="1:32">
@@ -18587,16 +18596,16 @@
         <v>237</v>
       </c>
       <c r="V258" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Z258">
         <v>0</v>
       </c>
       <c r="AA258" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF258" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="259" spans="1:32">
@@ -18658,16 +18667,16 @@
         <v>237</v>
       </c>
       <c r="V259" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Z259">
         <v>0</v>
       </c>
       <c r="AA259" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF259" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="260" spans="1:32">
@@ -18729,10 +18738,10 @@
         <v>0</v>
       </c>
       <c r="AA260" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF260" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="261" spans="1:32">
@@ -18794,10 +18803,10 @@
         <v>0</v>
       </c>
       <c r="AA261" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF261" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="262" spans="1:32">
@@ -18859,10 +18868,10 @@
         <v>0</v>
       </c>
       <c r="AA262" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AF262" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="263" spans="1:32">
@@ -18924,10 +18933,10 @@
         <v>0</v>
       </c>
       <c r="AA263" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AF263" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="264" spans="1:32">
@@ -18989,10 +18998,10 @@
         <v>0</v>
       </c>
       <c r="AA264" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF264" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="265" spans="1:32">
@@ -19054,10 +19063,10 @@
         <v>0</v>
       </c>
       <c r="AA265" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF265" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="266" spans="1:32">
@@ -19122,7 +19131,7 @@
         <v>212</v>
       </c>
       <c r="AF266" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="267" spans="1:32">
@@ -19187,7 +19196,7 @@
         <v>212</v>
       </c>
       <c r="AF267" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="268" spans="1:32">
@@ -19252,7 +19261,7 @@
         <v>212</v>
       </c>
       <c r="AF268" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="269" spans="1:32">
@@ -19317,7 +19326,7 @@
         <v>212</v>
       </c>
       <c r="AF269" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="270" spans="1:32">
@@ -19382,7 +19391,7 @@
         <v>212</v>
       </c>
       <c r="AF270" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="271" spans="1:32">
@@ -19447,7 +19456,7 @@
         <v>212</v>
       </c>
       <c r="AF271" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="272" spans="1:32">
@@ -19512,7 +19521,7 @@
         <v>212</v>
       </c>
       <c r="AF272" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="273" spans="1:32">
@@ -19574,10 +19583,10 @@
         <v>0</v>
       </c>
       <c r="AA273" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF273" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="274" spans="1:32">
@@ -19639,10 +19648,10 @@
         <v>0</v>
       </c>
       <c r="AA274" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF274" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="275" spans="1:32">
@@ -19704,10 +19713,10 @@
         <v>0</v>
       </c>
       <c r="AA275" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF275" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="276" spans="1:32">
@@ -19769,10 +19778,10 @@
         <v>0</v>
       </c>
       <c r="AA276" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF276" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="277" spans="1:32">
@@ -19834,10 +19843,10 @@
         <v>0</v>
       </c>
       <c r="AA277" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF277" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="278" spans="1:32">
@@ -19899,10 +19908,10 @@
         <v>0</v>
       </c>
       <c r="AA278" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF278" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="279" spans="1:32">
@@ -19964,10 +19973,10 @@
         <v>0</v>
       </c>
       <c r="AA279" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF279" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="280" spans="1:32">
@@ -20029,10 +20038,10 @@
         <v>0</v>
       </c>
       <c r="AA280" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF280" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="281" spans="1:32">
@@ -20094,10 +20103,10 @@
         <v>0</v>
       </c>
       <c r="AA281" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF281" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="282" spans="1:32">
@@ -20159,10 +20168,10 @@
         <v>0</v>
       </c>
       <c r="AA282" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF282" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="283" spans="1:32">
@@ -20224,10 +20233,10 @@
         <v>0</v>
       </c>
       <c r="AA283" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF283" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="284" spans="1:32">
@@ -20289,10 +20298,10 @@
         <v>0</v>
       </c>
       <c r="AA284" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF284" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="285" spans="1:32">
@@ -20354,10 +20363,10 @@
         <v>0</v>
       </c>
       <c r="AA285" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF285" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="286" spans="1:32">
@@ -20419,10 +20428,10 @@
         <v>0</v>
       </c>
       <c r="AA286" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF286" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="287" spans="1:32">
@@ -20484,10 +20493,10 @@
         <v>0</v>
       </c>
       <c r="AA287" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF287" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="288" spans="1:32">
@@ -20549,10 +20558,10 @@
         <v>0</v>
       </c>
       <c r="AA288" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF288" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="289" spans="1:33">
@@ -20614,10 +20623,10 @@
         <v>0</v>
       </c>
       <c r="AA289" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AF289" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="290" spans="1:33">
@@ -20679,10 +20688,10 @@
         <v>0</v>
       </c>
       <c r="AA290" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AF290" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="291" spans="1:33">
@@ -20744,10 +20753,10 @@
         <v>0</v>
       </c>
       <c r="AA291" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF291" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="292" spans="1:33">
@@ -20809,10 +20818,10 @@
         <v>0</v>
       </c>
       <c r="AA292" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF292" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="293" spans="1:33">
@@ -20871,16 +20880,16 @@
         <v>233</v>
       </c>
       <c r="V293" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Z293">
         <v>0</v>
       </c>
       <c r="AA293" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AF293" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="294" spans="1:33">
@@ -20939,10 +20948,10 @@
         <v>0</v>
       </c>
       <c r="AF294" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG294" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="295" spans="1:33">
@@ -21001,10 +21010,10 @@
         <v>0</v>
       </c>
       <c r="AF295" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG295" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="296" spans="1:33">
@@ -21063,10 +21072,10 @@
         <v>0</v>
       </c>
       <c r="AF296" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG296" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="297" spans="1:33">
@@ -21125,10 +21134,10 @@
         <v>0</v>
       </c>
       <c r="AF297" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG297" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="298" spans="1:33">
@@ -21187,10 +21196,10 @@
         <v>0</v>
       </c>
       <c r="AF298" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG298" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="299" spans="1:33">
@@ -21249,10 +21258,10 @@
         <v>0</v>
       </c>
       <c r="AF299" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG299" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="300" spans="1:33">
@@ -21311,10 +21320,10 @@
         <v>0</v>
       </c>
       <c r="AF300" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG300" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="301" spans="1:33">
@@ -21373,10 +21382,10 @@
         <v>0</v>
       </c>
       <c r="AF301" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG301" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="302" spans="1:33">
@@ -21435,10 +21444,10 @@
         <v>0</v>
       </c>
       <c r="AF302" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG302" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="303" spans="1:33">
@@ -21497,10 +21506,10 @@
         <v>0</v>
       </c>
       <c r="AF303" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG303" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="304" spans="1:33">
@@ -21559,10 +21568,10 @@
         <v>0</v>
       </c>
       <c r="AF304" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG304" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="305" spans="1:33">
@@ -21621,10 +21630,10 @@
         <v>0</v>
       </c>
       <c r="AF305" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG305" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="306" spans="1:33">
@@ -21683,10 +21692,10 @@
         <v>0</v>
       </c>
       <c r="AF306" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG306" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="307" spans="1:33">
@@ -21745,10 +21754,10 @@
         <v>0</v>
       </c>
       <c r="AF307" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG307" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="308" spans="1:33">
@@ -21807,10 +21816,10 @@
         <v>0</v>
       </c>
       <c r="AF308" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG308" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="309" spans="1:33">
@@ -21869,10 +21878,10 @@
         <v>0</v>
       </c>
       <c r="AF309" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG309" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="310" spans="1:33">
@@ -21931,10 +21940,10 @@
         <v>0</v>
       </c>
       <c r="AF310" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG310" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="311" spans="1:33">
@@ -21993,10 +22002,10 @@
         <v>0</v>
       </c>
       <c r="AF311" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG311" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="312" spans="1:33">
@@ -22055,10 +22064,10 @@
         <v>0</v>
       </c>
       <c r="AF312" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG312" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="313" spans="1:33">
@@ -22117,10 +22126,10 @@
         <v>0</v>
       </c>
       <c r="AF313" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG313" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="314" spans="1:33">
@@ -22179,10 +22188,10 @@
         <v>0</v>
       </c>
       <c r="AF314" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG314" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="315" spans="1:33">
@@ -22241,10 +22250,10 @@
         <v>0</v>
       </c>
       <c r="AF315" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG315" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="316" spans="1:33">
@@ -22303,10 +22312,10 @@
         <v>0</v>
       </c>
       <c r="AF316" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG316" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="317" spans="1:33">
@@ -22365,10 +22374,10 @@
         <v>0</v>
       </c>
       <c r="AF317" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG317" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="318" spans="1:33">
@@ -22427,10 +22436,10 @@
         <v>0</v>
       </c>
       <c r="AF318" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG318" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="319" spans="1:33">
@@ -22489,10 +22498,10 @@
         <v>0</v>
       </c>
       <c r="AF319" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG319" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="320" spans="1:33">
@@ -22551,10 +22560,10 @@
         <v>0</v>
       </c>
       <c r="AF320" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG320" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="321" spans="1:33">
@@ -22613,10 +22622,10 @@
         <v>0</v>
       </c>
       <c r="AF321" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG321" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="322" spans="1:33">
@@ -22675,10 +22684,10 @@
         <v>0</v>
       </c>
       <c r="AF322" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG322" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="323" spans="1:33">
@@ -22737,10 +22746,10 @@
         <v>0</v>
       </c>
       <c r="AF323" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG323" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="324" spans="1:33">
@@ -22799,10 +22808,10 @@
         <v>0</v>
       </c>
       <c r="AF324" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG324" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="325" spans="1:33">
@@ -22861,10 +22870,10 @@
         <v>0</v>
       </c>
       <c r="AF325" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG325" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="326" spans="1:33">
@@ -22923,10 +22932,10 @@
         <v>0</v>
       </c>
       <c r="AF326" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG326" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="327" spans="1:33">
@@ -22985,10 +22994,10 @@
         <v>0</v>
       </c>
       <c r="AF327" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG327" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="328" spans="1:33">
@@ -23047,10 +23056,10 @@
         <v>0</v>
       </c>
       <c r="AF328" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG328" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="329" spans="1:33">
@@ -23109,10 +23118,10 @@
         <v>0</v>
       </c>
       <c r="AF329" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG329" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="330" spans="1:33">
@@ -23171,10 +23180,10 @@
         <v>0</v>
       </c>
       <c r="AF330" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG330" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="331" spans="1:33">
@@ -23233,10 +23242,10 @@
         <v>0</v>
       </c>
       <c r="AF331" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG331" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="332" spans="1:33">
@@ -23295,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AF332" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG332" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="333" spans="1:33">
@@ -23357,10 +23366,10 @@
         <v>0</v>
       </c>
       <c r="AF333" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG333" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="334" spans="1:33">
@@ -23419,10 +23428,10 @@
         <v>0</v>
       </c>
       <c r="AF334" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG334" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="335" spans="1:33">
@@ -23481,10 +23490,10 @@
         <v>0</v>
       </c>
       <c r="AF335" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG335" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="336" spans="1:33">
@@ -23543,10 +23552,10 @@
         <v>0</v>
       </c>
       <c r="AF336" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG336" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="337" spans="1:33">
@@ -23605,10 +23614,10 @@
         <v>0</v>
       </c>
       <c r="AF337" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG337" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="338" spans="1:33">
@@ -23667,10 +23676,10 @@
         <v>0</v>
       </c>
       <c r="AF338" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG338" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="339" spans="1:33">
@@ -23729,10 +23738,10 @@
         <v>0</v>
       </c>
       <c r="AF339" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG339" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="340" spans="1:33">
@@ -23791,10 +23800,10 @@
         <v>0</v>
       </c>
       <c r="AF340" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG340" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="341" spans="1:33">
@@ -23853,10 +23862,10 @@
         <v>0</v>
       </c>
       <c r="AF341" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG341" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="342" spans="1:33">
@@ -23915,10 +23924,10 @@
         <v>0</v>
       </c>
       <c r="AF342" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG342" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="343" spans="1:33">
@@ -23977,10 +23986,10 @@
         <v>0</v>
       </c>
       <c r="AF343" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG343" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="344" spans="1:33">
@@ -24039,10 +24048,10 @@
         <v>0</v>
       </c>
       <c r="AF344" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG344" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="345" spans="1:33">
@@ -24101,10 +24110,10 @@
         <v>0</v>
       </c>
       <c r="AF345" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG345" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="346" spans="1:33">
@@ -24163,10 +24172,10 @@
         <v>0</v>
       </c>
       <c r="AF346" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG346" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="347" spans="1:33">
@@ -24225,10 +24234,10 @@
         <v>0</v>
       </c>
       <c r="AF347" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG347" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="348" spans="1:33">
@@ -24287,10 +24296,10 @@
         <v>0</v>
       </c>
       <c r="AF348" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG348" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="349" spans="1:33">
@@ -24349,10 +24358,10 @@
         <v>0</v>
       </c>
       <c r="AF349" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG349" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="350" spans="1:33">
@@ -24411,10 +24420,10 @@
         <v>0</v>
       </c>
       <c r="AF350" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG350" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="351" spans="1:33">
@@ -24473,10 +24482,10 @@
         <v>0</v>
       </c>
       <c r="AF351" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG351" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="352" spans="1:33">
@@ -24535,10 +24544,10 @@
         <v>0</v>
       </c>
       <c r="AF352" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG352" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="353" spans="1:33">
@@ -24597,10 +24606,10 @@
         <v>0</v>
       </c>
       <c r="AF353" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG353" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="354" spans="1:33">
@@ -24659,10 +24668,10 @@
         <v>0</v>
       </c>
       <c r="AF354" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG354" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="355" spans="1:33">
@@ -24721,10 +24730,10 @@
         <v>0</v>
       </c>
       <c r="AF355" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG355" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="356" spans="1:33">
@@ -24783,10 +24792,10 @@
         <v>0</v>
       </c>
       <c r="AF356" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG356" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="357" spans="1:33">
@@ -24845,10 +24854,10 @@
         <v>0</v>
       </c>
       <c r="AF357" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG357" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="358" spans="1:33">
@@ -24907,10 +24916,10 @@
         <v>0</v>
       </c>
       <c r="AF358" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG358" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="359" spans="1:33">
@@ -24969,10 +24978,10 @@
         <v>0</v>
       </c>
       <c r="AF359" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG359" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="360" spans="1:33">
@@ -25031,10 +25040,10 @@
         <v>0</v>
       </c>
       <c r="AF360" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG360" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="361" spans="1:33">
@@ -25093,10 +25102,10 @@
         <v>0</v>
       </c>
       <c r="AF361" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG361" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="362" spans="1:33">
@@ -25155,7 +25164,7 @@
         <v>0</v>
       </c>
       <c r="AF362" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="363" spans="1:33">
@@ -25214,10 +25223,10 @@
         <v>0</v>
       </c>
       <c r="AF363" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG363" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="364" spans="1:33">
@@ -25276,10 +25285,10 @@
         <v>0</v>
       </c>
       <c r="AF364" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG364" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="365" spans="1:33">
@@ -25338,10 +25347,10 @@
         <v>0</v>
       </c>
       <c r="AF365" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG365" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="366" spans="1:33">
@@ -25400,10 +25409,10 @@
         <v>0</v>
       </c>
       <c r="AF366" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG366" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="367" spans="1:33">
@@ -25462,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AF367" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG367" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="368" spans="1:33">
@@ -25524,10 +25533,10 @@
         <v>0</v>
       </c>
       <c r="AF368" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG368" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="369" spans="1:33">
@@ -25586,10 +25595,10 @@
         <v>0</v>
       </c>
       <c r="AF369" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG369" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="370" spans="1:33">
@@ -25648,10 +25657,10 @@
         <v>0</v>
       </c>
       <c r="AF370" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG370" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="371" spans="1:33">
@@ -25710,7 +25719,7 @@
         <v>0</v>
       </c>
       <c r="AF371" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="372" spans="1:33">
@@ -25769,10 +25778,10 @@
         <v>0</v>
       </c>
       <c r="AF372" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG372" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="373" spans="1:33">
@@ -25831,10 +25840,10 @@
         <v>0</v>
       </c>
       <c r="AF373" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG373" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="374" spans="1:33">
@@ -25893,10 +25902,10 @@
         <v>0</v>
       </c>
       <c r="AF374" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG374" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="375" spans="1:33">
@@ -25955,10 +25964,10 @@
         <v>0</v>
       </c>
       <c r="AF375" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG375" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="376" spans="1:33">
@@ -26017,10 +26026,10 @@
         <v>0</v>
       </c>
       <c r="AF376" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG376" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="377" spans="1:33">
@@ -26079,10 +26088,10 @@
         <v>0</v>
       </c>
       <c r="AF377" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG377" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="378" spans="1:33">
@@ -26141,10 +26150,10 @@
         <v>0</v>
       </c>
       <c r="AF378" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG378" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="379" spans="1:33">
@@ -26203,10 +26212,10 @@
         <v>0</v>
       </c>
       <c r="AF379" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG379" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="380" spans="1:33">
@@ -26265,7 +26274,7 @@
         <v>0</v>
       </c>
       <c r="AF380" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="381" spans="1:33">
@@ -26324,10 +26333,10 @@
         <v>0</v>
       </c>
       <c r="AF381" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG381" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="382" spans="1:33">
@@ -26386,10 +26395,10 @@
         <v>0</v>
       </c>
       <c r="AF382" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG382" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="383" spans="1:33">
@@ -26448,10 +26457,10 @@
         <v>0</v>
       </c>
       <c r="AF383" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG383" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="384" spans="1:33">
@@ -26510,10 +26519,10 @@
         <v>0</v>
       </c>
       <c r="AF384" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG384" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="385" spans="1:33">
@@ -26572,10 +26581,10 @@
         <v>0</v>
       </c>
       <c r="AF385" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG385" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="386" spans="1:33">
@@ -26634,10 +26643,10 @@
         <v>0</v>
       </c>
       <c r="AF386" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG386" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="387" spans="1:33">
@@ -26696,10 +26705,10 @@
         <v>0</v>
       </c>
       <c r="AF387" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG387" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="388" spans="1:33">
@@ -26758,10 +26767,10 @@
         <v>0</v>
       </c>
       <c r="AF388" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG388" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="389" spans="1:33">
@@ -26820,10 +26829,10 @@
         <v>0</v>
       </c>
       <c r="AF389" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG389" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="390" spans="1:33">
@@ -26882,10 +26891,10 @@
         <v>0</v>
       </c>
       <c r="AF390" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG390" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="391" spans="1:33">
@@ -26944,7 +26953,7 @@
         <v>0</v>
       </c>
       <c r="AF391" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="392" spans="1:33">
@@ -27003,10 +27012,10 @@
         <v>0</v>
       </c>
       <c r="AF392" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG392" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="393" spans="1:33">
@@ -27065,10 +27074,10 @@
         <v>0</v>
       </c>
       <c r="AF393" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG393" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="394" spans="1:33">
@@ -27127,10 +27136,10 @@
         <v>0</v>
       </c>
       <c r="AF394" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG394" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="395" spans="1:33">
@@ -27189,10 +27198,10 @@
         <v>0</v>
       </c>
       <c r="AF395" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG395" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="396" spans="1:33">
@@ -27251,10 +27260,10 @@
         <v>0</v>
       </c>
       <c r="AF396" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG396" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="397" spans="1:33">
@@ -27313,10 +27322,10 @@
         <v>0</v>
       </c>
       <c r="AF397" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG397" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="398" spans="1:33">
@@ -27375,10 +27384,10 @@
         <v>0</v>
       </c>
       <c r="AF398" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG398" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="399" spans="1:33">
@@ -27437,10 +27446,10 @@
         <v>0</v>
       </c>
       <c r="AF399" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG399" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="400" spans="1:33">
@@ -27499,10 +27508,10 @@
         <v>0</v>
       </c>
       <c r="AF400" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG400" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="401" spans="1:33">
@@ -27561,10 +27570,10 @@
         <v>0</v>
       </c>
       <c r="AF401" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG401" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="402" spans="1:33">
@@ -27623,10 +27632,10 @@
         <v>0</v>
       </c>
       <c r="AF402" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG402" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="403" spans="1:33">
@@ -27685,7 +27694,7 @@
         <v>0</v>
       </c>
       <c r="AF403" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="404" spans="1:33">
@@ -27744,10 +27753,10 @@
         <v>0</v>
       </c>
       <c r="AF404" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG404" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="405" spans="1:33">
@@ -27806,10 +27815,10 @@
         <v>0</v>
       </c>
       <c r="AF405" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG405" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="406" spans="1:33">
@@ -27868,10 +27877,10 @@
         <v>0</v>
       </c>
       <c r="AF406" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG406" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="407" spans="1:33">
@@ -27930,10 +27939,10 @@
         <v>0</v>
       </c>
       <c r="AF407" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG407" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="408" spans="1:33">
@@ -27992,10 +28001,10 @@
         <v>0</v>
       </c>
       <c r="AF408" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG408" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="409" spans="1:33">
@@ -28054,10 +28063,10 @@
         <v>0</v>
       </c>
       <c r="AF409" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG409" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="410" spans="1:33">
@@ -28116,10 +28125,10 @@
         <v>0</v>
       </c>
       <c r="AF410" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG410" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="411" spans="1:33">
@@ -28178,7 +28187,7 @@
         <v>0</v>
       </c>
       <c r="AF411" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="412" spans="1:33">
@@ -28237,10 +28246,10 @@
         <v>0</v>
       </c>
       <c r="AF412" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG412" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="413" spans="1:33">
@@ -28299,10 +28308,10 @@
         <v>0</v>
       </c>
       <c r="AF413" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG413" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="414" spans="1:33">
@@ -28361,10 +28370,10 @@
         <v>0</v>
       </c>
       <c r="AF414" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG414" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="415" spans="1:33">
@@ -28423,10 +28432,10 @@
         <v>0</v>
       </c>
       <c r="AF415" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG415" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="416" spans="1:33">
@@ -28485,7 +28494,7 @@
         <v>0</v>
       </c>
       <c r="AF416" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG416" t="s">
         <v>206</v>
@@ -28547,7 +28556,7 @@
         <v>0</v>
       </c>
       <c r="AF417" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG417" t="s">
         <v>206</v>
@@ -28609,7 +28618,7 @@
         <v>0</v>
       </c>
       <c r="AF418" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG418" t="s">
         <v>206</v>
@@ -28671,13 +28680,13 @@
         <v>237</v>
       </c>
       <c r="V419" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Z419">
         <v>0</v>
       </c>
       <c r="AF419" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG419" t="s">
         <v>206</v>
@@ -28739,13 +28748,13 @@
         <v>237</v>
       </c>
       <c r="V420" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Z420">
         <v>0</v>
       </c>
       <c r="AF420" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG420" t="s">
         <v>206</v>
@@ -28807,13 +28816,13 @@
         <v>237</v>
       </c>
       <c r="V421" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Z421">
         <v>0</v>
       </c>
       <c r="AF421" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG421" t="s">
         <v>206</v>
@@ -28875,13 +28884,13 @@
         <v>237</v>
       </c>
       <c r="V422" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Z422">
         <v>0</v>
       </c>
       <c r="AF422" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG422" t="s">
         <v>206</v>
@@ -28943,7 +28952,7 @@
         <v>0</v>
       </c>
       <c r="AF423" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="424" spans="1:33">
@@ -29002,7 +29011,7 @@
         <v>0</v>
       </c>
       <c r="AF424" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG424" t="s">
         <v>206</v>
@@ -29064,7 +29073,7 @@
         <v>0</v>
       </c>
       <c r="AF425" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG425" t="s">
         <v>206</v>
@@ -29126,7 +29135,7 @@
         <v>0</v>
       </c>
       <c r="AF426" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG426" t="s">
         <v>206</v>
@@ -29188,7 +29197,7 @@
         <v>0</v>
       </c>
       <c r="AF427" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG427" t="s">
         <v>206</v>
@@ -29250,7 +29259,7 @@
         <v>0</v>
       </c>
       <c r="AF428" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="429" spans="1:33">
@@ -29309,7 +29318,7 @@
         <v>0</v>
       </c>
       <c r="AF429" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="430" spans="1:33">
@@ -29368,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="AF430" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG430" t="s">
         <v>206</v>
@@ -29430,7 +29439,7 @@
         <v>0</v>
       </c>
       <c r="AF431" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="432" spans="1:33">
@@ -29489,7 +29498,7 @@
         <v>0</v>
       </c>
       <c r="AF432" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG432" t="s">
         <v>206</v>
@@ -29551,7 +29560,7 @@
         <v>0</v>
       </c>
       <c r="AF433" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG433" t="s">
         <v>206</v>
@@ -29613,7 +29622,7 @@
         <v>0</v>
       </c>
       <c r="AF434" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG434" t="s">
         <v>206</v>
@@ -29675,7 +29684,7 @@
         <v>0</v>
       </c>
       <c r="AF435" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG435" t="s">
         <v>206</v>
@@ -29737,7 +29746,7 @@
         <v>0</v>
       </c>
       <c r="AF436" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG436" t="s">
         <v>206</v>
@@ -29799,7 +29808,7 @@
         <v>0</v>
       </c>
       <c r="AF437" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG437" t="s">
         <v>206</v>
@@ -29861,7 +29870,7 @@
         <v>0</v>
       </c>
       <c r="AF438" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG438" t="s">
         <v>206</v>
@@ -29923,7 +29932,7 @@
         <v>0</v>
       </c>
       <c r="AF439" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG439" t="s">
         <v>206</v>
@@ -29985,7 +29994,7 @@
         <v>0</v>
       </c>
       <c r="AF440" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG440" t="s">
         <v>206</v>
@@ -30047,7 +30056,7 @@
         <v>0</v>
       </c>
       <c r="AF441" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG441" t="s">
         <v>206</v>
@@ -30109,10 +30118,10 @@
         <v>0</v>
       </c>
       <c r="AF442" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG442" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="443" spans="1:33">
@@ -30171,10 +30180,10 @@
         <v>0</v>
       </c>
       <c r="AF443" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG443" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="444" spans="1:33">
@@ -30233,10 +30242,10 @@
         <v>0</v>
       </c>
       <c r="AF444" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG444" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="445" spans="1:33">
@@ -30295,10 +30304,10 @@
         <v>0</v>
       </c>
       <c r="AF445" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG445" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="446" spans="1:33">
@@ -30357,10 +30366,10 @@
         <v>0</v>
       </c>
       <c r="AF446" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG446" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="447" spans="1:33">
@@ -30419,10 +30428,10 @@
         <v>0</v>
       </c>
       <c r="AF447" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG447" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="448" spans="1:33">
@@ -30481,10 +30490,10 @@
         <v>0</v>
       </c>
       <c r="AF448" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG448" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="449" spans="1:33">
@@ -30543,10 +30552,10 @@
         <v>0</v>
       </c>
       <c r="AF449" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG449" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="450" spans="1:33">
@@ -30605,10 +30614,10 @@
         <v>0</v>
       </c>
       <c r="AF450" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG450" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="451" spans="1:33">
@@ -30667,10 +30676,10 @@
         <v>0</v>
       </c>
       <c r="AF451" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG451" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="452" spans="1:33">
@@ -30729,10 +30738,10 @@
         <v>0</v>
       </c>
       <c r="AF452" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG452" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="453" spans="1:33">
@@ -30791,10 +30800,10 @@
         <v>0</v>
       </c>
       <c r="AF453" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG453" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="454" spans="1:33">
@@ -30853,10 +30862,10 @@
         <v>0</v>
       </c>
       <c r="AF454" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG454" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="455" spans="1:33">
@@ -30915,10 +30924,10 @@
         <v>0</v>
       </c>
       <c r="AF455" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG455" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="456" spans="1:33">
@@ -30977,10 +30986,10 @@
         <v>0</v>
       </c>
       <c r="AF456" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG456" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="457" spans="1:33">
@@ -31039,10 +31048,10 @@
         <v>0</v>
       </c>
       <c r="AF457" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG457" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="458" spans="1:33">
@@ -31101,10 +31110,10 @@
         <v>0</v>
       </c>
       <c r="AF458" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG458" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="459" spans="1:33">
@@ -31163,10 +31172,10 @@
         <v>0</v>
       </c>
       <c r="AF459" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG459" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="460" spans="1:33">
@@ -31225,10 +31234,10 @@
         <v>0</v>
       </c>
       <c r="AF460" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG460" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="461" spans="1:33">
@@ -31287,10 +31296,10 @@
         <v>0</v>
       </c>
       <c r="AF461" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG461" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="462" spans="1:33">
@@ -31349,10 +31358,10 @@
         <v>0</v>
       </c>
       <c r="AF462" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG462" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="463" spans="1:33">
@@ -31411,10 +31420,10 @@
         <v>0</v>
       </c>
       <c r="AF463" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG463" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="464" spans="1:33">
@@ -31473,10 +31482,10 @@
         <v>0</v>
       </c>
       <c r="AF464" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG464" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="465" spans="1:33">
@@ -31535,10 +31544,10 @@
         <v>0</v>
       </c>
       <c r="AF465" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG465" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="466" spans="1:33">
@@ -31597,7 +31606,7 @@
         <v>0</v>
       </c>
       <c r="AF466" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="467" spans="1:33">
@@ -31656,7 +31665,7 @@
         <v>0</v>
       </c>
       <c r="AF467" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="468" spans="1:33">
@@ -31715,7 +31724,7 @@
         <v>0</v>
       </c>
       <c r="AF468" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="469" spans="1:33">
@@ -31774,7 +31783,7 @@
         <v>0</v>
       </c>
       <c r="AF469" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="470" spans="1:33">
@@ -31833,7 +31842,7 @@
         <v>0</v>
       </c>
       <c r="AF470" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="471" spans="1:33">
@@ -31892,7 +31901,7 @@
         <v>0</v>
       </c>
       <c r="AF471" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="472" spans="1:33">
@@ -31951,7 +31960,7 @@
         <v>0</v>
       </c>
       <c r="AF472" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="473" spans="1:33">
@@ -32010,7 +32019,7 @@
         <v>0</v>
       </c>
       <c r="AF473" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="474" spans="1:33">
@@ -32069,7 +32078,7 @@
         <v>0</v>
       </c>
       <c r="AF474" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="475" spans="1:33">
@@ -32128,7 +32137,7 @@
         <v>0</v>
       </c>
       <c r="AF475" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="476" spans="1:33">
@@ -32187,7 +32196,7 @@
         <v>0</v>
       </c>
       <c r="AF476" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="477" spans="1:33">
@@ -32246,7 +32255,7 @@
         <v>0</v>
       </c>
       <c r="AF477" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="478" spans="1:33">
@@ -32305,7 +32314,7 @@
         <v>0</v>
       </c>
       <c r="AF478" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="479" spans="1:33">
@@ -32364,7 +32373,7 @@
         <v>0</v>
       </c>
       <c r="AF479" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="480" spans="1:33">
@@ -32423,7 +32432,7 @@
         <v>0</v>
       </c>
       <c r="AF480" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="481" spans="1:32">
@@ -32482,7 +32491,7 @@
         <v>0</v>
       </c>
       <c r="AF481" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="482" spans="1:32">
@@ -32541,7 +32550,7 @@
         <v>0</v>
       </c>
       <c r="AF482" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="483" spans="1:32">
@@ -32600,7 +32609,7 @@
         <v>0</v>
       </c>
       <c r="AF483" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="484" spans="1:32">
@@ -32659,7 +32668,7 @@
         <v>0</v>
       </c>
       <c r="AF484" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="485" spans="1:32">
@@ -32718,7 +32727,7 @@
         <v>0</v>
       </c>
       <c r="AF485" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="486" spans="1:32">
@@ -32777,7 +32786,7 @@
         <v>0</v>
       </c>
       <c r="AF486" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="487" spans="1:32">
@@ -32836,7 +32845,7 @@
         <v>0</v>
       </c>
       <c r="AF487" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="488" spans="1:32">
@@ -32895,7 +32904,7 @@
         <v>0</v>
       </c>
       <c r="AF488" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="489" spans="1:32">
@@ -32954,7 +32963,7 @@
         <v>0</v>
       </c>
       <c r="AF489" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="490" spans="1:32">
@@ -33013,7 +33022,7 @@
         <v>0</v>
       </c>
       <c r="AF490" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="491" spans="1:32">
@@ -33072,7 +33081,7 @@
         <v>0</v>
       </c>
       <c r="AF491" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="492" spans="1:32">
@@ -33131,7 +33140,7 @@
         <v>0</v>
       </c>
       <c r="AF492" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="493" spans="1:32">
@@ -33190,7 +33199,7 @@
         <v>0</v>
       </c>
       <c r="AF493" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="494" spans="1:32">
@@ -33249,7 +33258,7 @@
         <v>0</v>
       </c>
       <c r="AF494" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="495" spans="1:32">
@@ -33308,7 +33317,7 @@
         <v>0</v>
       </c>
       <c r="AF495" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="496" spans="1:32">
@@ -33367,7 +33376,7 @@
         <v>0</v>
       </c>
       <c r="AF496" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="497" spans="1:32">
@@ -33426,7 +33435,7 @@
         <v>0</v>
       </c>
       <c r="AF497" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="498" spans="1:32">
@@ -33485,7 +33494,7 @@
         <v>0</v>
       </c>
       <c r="AF498" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="499" spans="1:32">
@@ -33544,7 +33553,7 @@
         <v>0</v>
       </c>
       <c r="AF499" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="500" spans="1:32">
@@ -33603,7 +33612,7 @@
         <v>0</v>
       </c>
       <c r="AF500" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="501" spans="1:32">
@@ -33662,7 +33671,7 @@
         <v>0</v>
       </c>
       <c r="AF501" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="502" spans="1:32">
@@ -33721,7 +33730,7 @@
         <v>0</v>
       </c>
       <c r="AF502" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="503" spans="1:32">
@@ -33780,7 +33789,7 @@
         <v>0</v>
       </c>
       <c r="AF503" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="504" spans="1:32">
@@ -33839,7 +33848,7 @@
         <v>0</v>
       </c>
       <c r="AF504" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="505" spans="1:32">
@@ -33898,7 +33907,7 @@
         <v>0</v>
       </c>
       <c r="AF505" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="506" spans="1:32">
@@ -33957,7 +33966,7 @@
         <v>0</v>
       </c>
       <c r="AF506" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="507" spans="1:32">
@@ -34016,7 +34025,7 @@
         <v>0</v>
       </c>
       <c r="AF507" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="508" spans="1:32">
@@ -34075,7 +34084,7 @@
         <v>0</v>
       </c>
       <c r="AF508" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="509" spans="1:32">
@@ -34134,7 +34143,7 @@
         <v>0</v>
       </c>
       <c r="AF509" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="510" spans="1:32">
@@ -34193,7 +34202,7 @@
         <v>0</v>
       </c>
       <c r="AF510" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="511" spans="1:32">
@@ -34252,7 +34261,7 @@
         <v>0</v>
       </c>
       <c r="AF511" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="512" spans="1:32">
@@ -34311,7 +34320,7 @@
         <v>0</v>
       </c>
       <c r="AF512" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="513" spans="1:33">
@@ -34370,7 +34379,7 @@
         <v>0</v>
       </c>
       <c r="AF513" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="514" spans="1:33">
@@ -34429,7 +34438,7 @@
         <v>0</v>
       </c>
       <c r="AF514" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="515" spans="1:33">
@@ -34488,7 +34497,7 @@
         <v>0</v>
       </c>
       <c r="AF515" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="516" spans="1:33">
@@ -34547,7 +34556,7 @@
         <v>0</v>
       </c>
       <c r="AF516" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="517" spans="1:33">
@@ -34606,7 +34615,7 @@
         <v>0</v>
       </c>
       <c r="AF517" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="518" spans="1:33">
@@ -34665,7 +34674,7 @@
         <v>0</v>
       </c>
       <c r="AF518" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="519" spans="1:33">
@@ -34724,7 +34733,7 @@
         <v>0</v>
       </c>
       <c r="AF519" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="520" spans="1:33">
@@ -34783,7 +34792,7 @@
         <v>0</v>
       </c>
       <c r="AF520" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="521" spans="1:33">
@@ -34842,7 +34851,7 @@
         <v>0</v>
       </c>
       <c r="AF521" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="522" spans="1:33">
@@ -34901,7 +34910,7 @@
         <v>0</v>
       </c>
       <c r="AF522" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="523" spans="1:33">
@@ -34960,7 +34969,7 @@
         <v>0</v>
       </c>
       <c r="AF523" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="524" spans="1:33">
@@ -35019,7 +35028,7 @@
         <v>0</v>
       </c>
       <c r="AF524" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="525" spans="1:33">
@@ -35078,7 +35087,7 @@
         <v>0</v>
       </c>
       <c r="AF525" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="526" spans="1:33">
@@ -35137,7 +35146,7 @@
         <v>0</v>
       </c>
       <c r="AF526" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="527" spans="1:33">
@@ -35199,13 +35208,13 @@
         <v>0</v>
       </c>
       <c r="AA527" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF527" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG527" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="528" spans="1:33">
@@ -35267,13 +35276,13 @@
         <v>0</v>
       </c>
       <c r="AA528" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF528" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG528" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="529" spans="1:33">
@@ -35332,19 +35341,19 @@
         <v>235</v>
       </c>
       <c r="V529" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Z529">
         <v>0</v>
       </c>
       <c r="AA529" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF529" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG529" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="530" spans="1:33">
@@ -35403,19 +35412,19 @@
         <v>231</v>
       </c>
       <c r="V530" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Z530">
         <v>0</v>
       </c>
       <c r="AA530" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF530" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG530" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="531" spans="1:33">
@@ -35480,10 +35489,10 @@
         <v>219</v>
       </c>
       <c r="AF531" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG531" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="532" spans="1:33">
@@ -35545,13 +35554,13 @@
         <v>0</v>
       </c>
       <c r="AA532" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AF532" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG532" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="533" spans="1:33">
@@ -35613,13 +35622,13 @@
         <v>0</v>
       </c>
       <c r="AA533" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AF533" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG533" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="534" spans="1:33">
@@ -35684,10 +35693,10 @@
         <v>218</v>
       </c>
       <c r="AF534" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG534" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="535" spans="1:33">
@@ -35746,10 +35755,10 @@
         <v>0</v>
       </c>
       <c r="AA535" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AF535" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="536" spans="1:33">
@@ -35808,10 +35817,10 @@
         <v>0</v>
       </c>
       <c r="AA536" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AF536" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="537" spans="1:33">
@@ -35867,16 +35876,16 @@
         <v>239</v>
       </c>
       <c r="V537" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Z537">
         <v>0</v>
       </c>
       <c r="AA537" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF537" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="538" spans="1:33">
@@ -35941,10 +35950,10 @@
         <v>221</v>
       </c>
       <c r="AF538" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG538" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="539" spans="1:33">
@@ -36009,10 +36018,10 @@
         <v>219</v>
       </c>
       <c r="AF539" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG539" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="540" spans="1:33">
@@ -36077,10 +36086,10 @@
         <v>220</v>
       </c>
       <c r="AF540" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG540" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="541" spans="1:33">
@@ -36145,10 +36154,10 @@
         <v>219</v>
       </c>
       <c r="AF541" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG541" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="542" spans="1:33">
@@ -36213,10 +36222,10 @@
         <v>219</v>
       </c>
       <c r="AF542" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG542" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="543" spans="1:33">
@@ -36281,10 +36290,10 @@
         <v>219</v>
       </c>
       <c r="AF543" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG543" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="544" spans="1:33">
@@ -36349,10 +36358,10 @@
         <v>205</v>
       </c>
       <c r="AF544" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG544" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="545" spans="1:33">
@@ -36414,13 +36423,13 @@
         <v>0</v>
       </c>
       <c r="AA545" t="s">
+        <v>322</v>
+      </c>
+      <c r="AF545" t="s">
+        <v>333</v>
+      </c>
+      <c r="AG545" t="s">
         <v>321</v>
-      </c>
-      <c r="AF545" t="s">
-        <v>332</v>
-      </c>
-      <c r="AG545" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="546" spans="1:33">
@@ -36482,13 +36491,13 @@
         <v>0</v>
       </c>
       <c r="AA546" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF546" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG546" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="547" spans="1:33">
@@ -36550,13 +36559,13 @@
         <v>0</v>
       </c>
       <c r="AA547" t="s">
+        <v>322</v>
+      </c>
+      <c r="AF547" t="s">
+        <v>332</v>
+      </c>
+      <c r="AG547" t="s">
         <v>321</v>
-      </c>
-      <c r="AF547" t="s">
-        <v>331</v>
-      </c>
-      <c r="AG547" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="548" spans="1:33">
@@ -36618,13 +36627,13 @@
         <v>0</v>
       </c>
       <c r="AA548" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF548" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG548" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="549" spans="1:33">
@@ -36689,7 +36698,7 @@
         <v>206</v>
       </c>
       <c r="AF549" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG549" t="s">
         <v>206</v>
@@ -36757,7 +36766,7 @@
         <v>206</v>
       </c>
       <c r="AF550" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG550" t="s">
         <v>206</v>
@@ -36825,7 +36834,7 @@
         <v>209</v>
       </c>
       <c r="AF551" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG551" t="s">
         <v>206</v>
@@ -36890,10 +36899,10 @@
         <v>0</v>
       </c>
       <c r="AA552" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF552" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG552" t="s">
         <v>206</v>
@@ -36961,10 +36970,10 @@
         <v>211</v>
       </c>
       <c r="AF553" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG553" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="554" spans="1:33">
@@ -37026,13 +37035,13 @@
         <v>0</v>
       </c>
       <c r="AA554" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AF554" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG554" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="555" spans="1:33">
@@ -37091,16 +37100,16 @@
         <v>231</v>
       </c>
       <c r="V555" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Z555">
         <v>0</v>
       </c>
       <c r="AA555" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF555" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="556" spans="1:33">
@@ -37162,10 +37171,10 @@
         <v>0</v>
       </c>
       <c r="AA556" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF556" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="557" spans="1:33">
@@ -37224,16 +37233,16 @@
         <v>232</v>
       </c>
       <c r="V557" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Z557">
         <v>0</v>
       </c>
       <c r="AA557" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF557" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="558" spans="1:33">
@@ -37292,16 +37301,16 @@
         <v>233</v>
       </c>
       <c r="V558" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Z558">
         <v>0</v>
       </c>
       <c r="AA558" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF558" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="559" spans="1:33">
@@ -37360,16 +37369,16 @@
         <v>229</v>
       </c>
       <c r="V559" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Z559">
         <v>0</v>
       </c>
       <c r="AA559" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF559" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="560" spans="1:33">
@@ -37428,10 +37437,10 @@
         <v>0</v>
       </c>
       <c r="AA560" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF560" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="561" spans="1:32">
@@ -37490,16 +37499,16 @@
         <v>228</v>
       </c>
       <c r="V561" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Z561">
         <v>0</v>
       </c>
       <c r="AA561" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF561" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="562" spans="1:32">
@@ -37558,16 +37567,16 @@
         <v>236</v>
       </c>
       <c r="V562" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Z562">
         <v>0</v>
       </c>
       <c r="AA562" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF562" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="563" spans="1:32">
@@ -37629,10 +37638,10 @@
         <v>0</v>
       </c>
       <c r="AA563" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF563" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="564" spans="1:32">
@@ -37691,16 +37700,16 @@
         <v>229</v>
       </c>
       <c r="V564" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Z564">
         <v>0</v>
       </c>
       <c r="AA564" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF564" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="565" spans="1:32">
@@ -37759,10 +37768,10 @@
         <v>0</v>
       </c>
       <c r="AA565" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF565" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="566" spans="1:32">
@@ -37821,16 +37830,16 @@
         <v>228</v>
       </c>
       <c r="V566" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Z566">
         <v>0</v>
       </c>
       <c r="AA566" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF566" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="567" spans="1:32">
@@ -37889,16 +37898,16 @@
         <v>231</v>
       </c>
       <c r="V567" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Z567">
         <v>0</v>
       </c>
       <c r="AA567" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF567" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="568" spans="1:32">
@@ -37957,16 +37966,16 @@
         <v>236</v>
       </c>
       <c r="V568" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Z568">
         <v>0</v>
       </c>
       <c r="AA568" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF568" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="569" spans="1:32">
@@ -38028,10 +38037,10 @@
         <v>0</v>
       </c>
       <c r="AA569" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF569" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="570" spans="1:32">
@@ -38090,16 +38099,16 @@
         <v>234</v>
       </c>
       <c r="V570" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Z570">
         <v>0</v>
       </c>
       <c r="AA570" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF570" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="571" spans="1:32">
@@ -38161,10 +38170,10 @@
         <v>0</v>
       </c>
       <c r="AA571" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF571" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="572" spans="1:32">
@@ -38226,10 +38235,10 @@
         <v>0</v>
       </c>
       <c r="AA572" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF572" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="573" spans="1:32">
@@ -38288,16 +38297,16 @@
         <v>229</v>
       </c>
       <c r="V573" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Z573">
         <v>0</v>
       </c>
       <c r="AA573" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF573" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="574" spans="1:32">
@@ -38356,16 +38365,16 @@
         <v>231</v>
       </c>
       <c r="V574" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Z574">
         <v>0</v>
       </c>
       <c r="AA574" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF574" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="575" spans="1:32">
@@ -38424,16 +38433,16 @@
         <v>232</v>
       </c>
       <c r="V575" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Z575">
         <v>0</v>
       </c>
       <c r="AA575" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF575" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="576" spans="1:32">
@@ -38495,10 +38504,10 @@
         <v>0</v>
       </c>
       <c r="AA576" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF576" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="577" spans="1:33">
@@ -38557,16 +38566,16 @@
         <v>234</v>
       </c>
       <c r="V577" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Z577">
         <v>0</v>
       </c>
       <c r="AA577" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF577" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="578" spans="1:33">
@@ -38628,10 +38637,10 @@
         <v>0</v>
       </c>
       <c r="AA578" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF578" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="579" spans="1:33">
@@ -38693,10 +38702,10 @@
         <v>0</v>
       </c>
       <c r="AA579" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF579" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="580" spans="1:33">
@@ -38755,16 +38764,16 @@
         <v>228</v>
       </c>
       <c r="V580" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Z580">
         <v>0</v>
       </c>
       <c r="AA580" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF580" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="581" spans="1:33">
@@ -38823,16 +38832,16 @@
         <v>229</v>
       </c>
       <c r="V581" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Z581">
         <v>0</v>
       </c>
       <c r="AA581" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF581" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="582" spans="1:33">
@@ -38891,16 +38900,16 @@
         <v>230</v>
       </c>
       <c r="V582" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Z582">
         <v>0</v>
       </c>
       <c r="AA582" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF582" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="583" spans="1:33">
@@ -38962,10 +38971,10 @@
         <v>0</v>
       </c>
       <c r="AA583" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF583" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="584" spans="1:33">
@@ -39027,10 +39036,10 @@
         <v>0</v>
       </c>
       <c r="AA584" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF584" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="585" spans="1:33">
@@ -39092,10 +39101,10 @@
         <v>0</v>
       </c>
       <c r="AA585" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF585" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="586" spans="1:33">
@@ -39154,16 +39163,16 @@
         <v>240</v>
       </c>
       <c r="V586" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AD586" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AE586" t="s">
         <v>191</v>
       </c>
       <c r="AF586" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="587" spans="1:33">
@@ -39222,16 +39231,16 @@
         <v>240</v>
       </c>
       <c r="V587" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AD587" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AE587" t="s">
         <v>191</v>
       </c>
       <c r="AF587" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="588" spans="1:33">
@@ -39290,16 +39299,16 @@
         <v>241</v>
       </c>
       <c r="V588" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AD588" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AE588" t="s">
         <v>191</v>
       </c>
       <c r="AF588" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="589" spans="1:33">
@@ -39358,13 +39367,13 @@
         <v>242</v>
       </c>
       <c r="V589" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AF589" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG589" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="590" spans="1:33">
@@ -39423,10 +39432,10 @@
         <v>242</v>
       </c>
       <c r="V590" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AF590" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG590" t="s">
         <v>224</v>
@@ -39488,10 +39497,10 @@
         <v>242</v>
       </c>
       <c r="V591" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AF591" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG591" t="s">
         <v>224</v>
@@ -39553,16 +39562,16 @@
         <v>229</v>
       </c>
       <c r="V592" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AD592" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AE592" t="s">
         <v>191</v>
       </c>
       <c r="AF592" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="593" spans="1:33">
@@ -39621,16 +39630,16 @@
         <v>230</v>
       </c>
       <c r="V593" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AD593" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AE593" t="s">
         <v>182</v>
       </c>
       <c r="AF593" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="594" spans="1:33">
@@ -39668,7 +39677,7 @@
         <v>46273</v>
       </c>
       <c r="M594" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N594" t="s">
         <v>193</v>
@@ -39689,13 +39698,13 @@
         <v>243</v>
       </c>
       <c r="V594" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AF594" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG594" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="595" spans="1:33">
@@ -39751,10 +39760,10 @@
         <v>229</v>
       </c>
       <c r="AF595" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG595" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="596" spans="1:33">
@@ -39810,10 +39819,10 @@
         <v>228</v>
       </c>
       <c r="AF596" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG596" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="597" spans="1:33">
@@ -39869,10 +39878,10 @@
         <v>236</v>
       </c>
       <c r="AF597" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG597" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="598" spans="1:33">
@@ -39928,10 +39937,10 @@
         <v>232</v>
       </c>
       <c r="AF598" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG598" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="599" spans="1:33">
@@ -39987,10 +39996,10 @@
         <v>232</v>
       </c>
       <c r="AF599" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG599" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="600" spans="1:33">
@@ -40046,10 +40055,10 @@
         <v>229</v>
       </c>
       <c r="AF600" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG600" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="601" spans="1:33">
@@ -40105,7 +40114,7 @@
         <v>242</v>
       </c>
       <c r="AF601" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG601" t="s">
         <v>224</v>
@@ -40164,7 +40173,7 @@
         <v>242</v>
       </c>
       <c r="AF602" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG602" t="s">
         <v>224</v>
@@ -40223,10 +40232,10 @@
         <v>243</v>
       </c>
       <c r="AF603" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG603" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="604" spans="1:33">
@@ -40282,10 +40291,10 @@
         <v>243</v>
       </c>
       <c r="AF604" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG604" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="605" spans="1:33">
@@ -40341,10 +40350,10 @@
         <v>243</v>
       </c>
       <c r="AF605" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG605" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="606" spans="1:33">
@@ -40400,7 +40409,7 @@
         <v>242</v>
       </c>
       <c r="AF606" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG606" t="s">
         <v>224</v>
@@ -40459,7 +40468,7 @@
         <v>242</v>
       </c>
       <c r="AF607" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG607" t="s">
         <v>224</v>
@@ -40518,7 +40527,7 @@
         <v>242</v>
       </c>
       <c r="AF608" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG608" t="s">
         <v>224</v>
@@ -40577,7 +40586,7 @@
         <v>242</v>
       </c>
       <c r="AF609" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="610" spans="1:32">
@@ -40633,7 +40642,7 @@
         <v>242</v>
       </c>
       <c r="AF610" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="611" spans="1:32">
@@ -40689,7 +40698,7 @@
         <v>243</v>
       </c>
       <c r="AF611" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="612" spans="1:32">
@@ -40745,7 +40754,7 @@
         <v>240</v>
       </c>
       <c r="AF612" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="613" spans="1:32">
@@ -40801,7 +40810,7 @@
         <v>240</v>
       </c>
       <c r="AF613" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="614" spans="1:32">
@@ -40857,7 +40866,7 @@
         <v>237</v>
       </c>
       <c r="AF614" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="615" spans="1:32">
@@ -40913,7 +40922,7 @@
         <v>241</v>
       </c>
       <c r="AF615" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="616" spans="1:32">
@@ -40969,7 +40978,7 @@
         <v>241</v>
       </c>
       <c r="AF616" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="617" spans="1:32">
@@ -41025,7 +41034,7 @@
         <v>234</v>
       </c>
       <c r="AF617" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8093" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8093" uniqueCount="339">
   <si>
     <t>CodCliente</t>
   </si>
@@ -986,13 +986,11 @@
     <t>Baixado via rotina MGC x Analise Balanço em 01/08/2026 01:02:56. - Data Comentário: 01/08/2026 01:01</t>
   </si>
   <si>
-    <t>Documentos necessários não foram encaminhados assim gerando o atraso da baixa da tarefa - Data Comentário: 04/09/2026 16:49</t>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 11/09/2026 
+Sem informações que permite identificar e aplicar modelo - Data Comentário: 08/09/2026 17:53</t>
   </si>
   <si>
-    <t>Reaberto via API integração MGC x Analise Balanço em 03/09/2026 13:08:32. - Data Comentário: 03/09/2026 18:32</t>
-  </si>
-  <si>
-    <t>Reaberto via API integração MGC x Analise Balanço em 04/09/2026 09:10:19. - Data Comentário: 04/09/2026 16:55 - Data Comentário: 04/09/2026 17:05</t>
+    <t>Atraso da operação - Data Comentário: 08/09/2026 18:05</t>
   </si>
   <si>
     <t>Juan Rodrigues</t>
@@ -1557,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:33">
@@ -1622,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="AF3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:33">
@@ -1690,10 +1688,10 @@
         <v>0</v>
       </c>
       <c r="AF4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:33">
@@ -1758,10 +1756,10 @@
         <v>0</v>
       </c>
       <c r="AF5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:33">
@@ -1826,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="AF6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" spans="1:33">
@@ -1894,10 +1892,10 @@
         <v>0</v>
       </c>
       <c r="AF7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" spans="1:33">
@@ -1956,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="AF8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9" spans="1:33">
@@ -2018,7 +2016,7 @@
         <v>0</v>
       </c>
       <c r="AF9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10" spans="1:33">
@@ -2077,10 +2075,10 @@
         <v>0</v>
       </c>
       <c r="AF10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" spans="1:33">
@@ -2145,10 +2143,10 @@
         <v>0</v>
       </c>
       <c r="AF11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG11" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="12" spans="1:33">
@@ -2207,10 +2205,10 @@
         <v>0</v>
       </c>
       <c r="AF12" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="13" spans="1:33">
@@ -2269,10 +2267,10 @@
         <v>0</v>
       </c>
       <c r="AF13" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14" spans="1:33">
@@ -2331,10 +2329,10 @@
         <v>0</v>
       </c>
       <c r="AF14" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG14" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" spans="1:33">
@@ -2399,10 +2397,10 @@
         <v>0</v>
       </c>
       <c r="AF15" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG15" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16" spans="1:33">
@@ -2461,10 +2459,10 @@
         <v>0</v>
       </c>
       <c r="AF16" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG16" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="17" spans="1:33">
@@ -2523,10 +2521,10 @@
         <v>0</v>
       </c>
       <c r="AF17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG17" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="18" spans="1:33">
@@ -2591,10 +2589,10 @@
         <v>0</v>
       </c>
       <c r="AF18" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG18" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="19" spans="1:33">
@@ -2659,10 +2657,10 @@
         <v>0</v>
       </c>
       <c r="AF19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG19" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="20" spans="1:33">
@@ -2721,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="AF20" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG20" t="s">
         <v>202</v>
@@ -2789,7 +2787,7 @@
         <v>0</v>
       </c>
       <c r="AF21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG21" t="s">
         <v>202</v>
@@ -2851,7 +2849,7 @@
         <v>0</v>
       </c>
       <c r="AF22" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG22" t="s">
         <v>202</v>
@@ -2913,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="AF23" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG23" t="s">
         <v>202</v>
@@ -2981,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="AF24" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="25" spans="1:33">
@@ -3046,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="AF25" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG25" t="s">
         <v>202</v>
@@ -3114,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="AF26" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG26" t="s">
         <v>202</v>
@@ -3182,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="AF27" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG27" t="s">
         <v>202</v>
@@ -3244,7 +3242,7 @@
         <v>0</v>
       </c>
       <c r="AF28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG28" t="s">
         <v>202</v>
@@ -3306,7 +3304,7 @@
         <v>0</v>
       </c>
       <c r="AF29" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG29" t="s">
         <v>202</v>
@@ -3368,7 +3366,7 @@
         <v>0</v>
       </c>
       <c r="AF30" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG30" t="s">
         <v>202</v>
@@ -3436,7 +3434,7 @@
         <v>0</v>
       </c>
       <c r="AF31" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG31" t="s">
         <v>202</v>
@@ -3498,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="AF32" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG32" t="s">
         <v>202</v>
@@ -3566,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="AF33" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="34" spans="1:33">
@@ -3625,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="AF34" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG34" t="s">
         <v>202</v>
@@ -3687,7 +3685,7 @@
         <v>0</v>
       </c>
       <c r="AF35" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG35" t="s">
         <v>202</v>
@@ -3749,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="AF36" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="37" spans="1:33">
@@ -3808,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="AF37" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG37" t="s">
         <v>202</v>
@@ -3870,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="AF38" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG38" t="s">
         <v>202</v>
@@ -3932,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="AF39" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="40" spans="1:33">
@@ -3991,7 +3989,7 @@
         <v>0</v>
       </c>
       <c r="AF40" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG40" t="s">
         <v>202</v>
@@ -4053,7 +4051,7 @@
         <v>0</v>
       </c>
       <c r="AF41" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG41" t="s">
         <v>202</v>
@@ -4115,7 +4113,7 @@
         <v>0</v>
       </c>
       <c r="AF42" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG42" t="s">
         <v>202</v>
@@ -4177,10 +4175,10 @@
         <v>0</v>
       </c>
       <c r="AF43" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG43" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="44" spans="1:33">
@@ -4239,10 +4237,10 @@
         <v>0</v>
       </c>
       <c r="AF44" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG44" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="45" spans="1:33">
@@ -4301,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AF45" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG45" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="46" spans="1:33">
@@ -4363,10 +4361,10 @@
         <v>0</v>
       </c>
       <c r="AF46" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG46" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="47" spans="1:33">
@@ -4425,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AF47" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG47" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="48" spans="1:33">
@@ -4487,10 +4485,10 @@
         <v>0</v>
       </c>
       <c r="AF48" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG48" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="49" spans="1:33">
@@ -4549,10 +4547,10 @@
         <v>0</v>
       </c>
       <c r="AF49" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG49" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="50" spans="1:33">
@@ -4611,10 +4609,10 @@
         <v>0</v>
       </c>
       <c r="AF50" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG50" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="51" spans="1:33">
@@ -4673,10 +4671,10 @@
         <v>0</v>
       </c>
       <c r="AF51" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG51" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="52" spans="1:33">
@@ -4735,10 +4733,10 @@
         <v>0</v>
       </c>
       <c r="AF52" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG52" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="53" spans="1:33">
@@ -4797,10 +4795,10 @@
         <v>0</v>
       </c>
       <c r="AF53" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG53" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="54" spans="1:33">
@@ -4859,10 +4857,10 @@
         <v>0</v>
       </c>
       <c r="AF54" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG54" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="55" spans="1:33">
@@ -4921,10 +4919,10 @@
         <v>0</v>
       </c>
       <c r="AF55" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG55" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="56" spans="1:33">
@@ -4983,10 +4981,10 @@
         <v>0</v>
       </c>
       <c r="AF56" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG56" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="57" spans="1:33">
@@ -5045,10 +5043,10 @@
         <v>0</v>
       </c>
       <c r="AF57" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG57" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="58" spans="1:33">
@@ -5107,10 +5105,10 @@
         <v>0</v>
       </c>
       <c r="AF58" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG58" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="59" spans="1:33">
@@ -5169,10 +5167,10 @@
         <v>0</v>
       </c>
       <c r="AF59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG59" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="60" spans="1:33">
@@ -5231,10 +5229,10 @@
         <v>0</v>
       </c>
       <c r="AF60" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG60" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="61" spans="1:33">
@@ -5293,10 +5291,10 @@
         <v>0</v>
       </c>
       <c r="AF61" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG61" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="62" spans="1:33">
@@ -5355,10 +5353,10 @@
         <v>0</v>
       </c>
       <c r="AF62" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG62" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="63" spans="1:33">
@@ -5417,10 +5415,10 @@
         <v>0</v>
       </c>
       <c r="AF63" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG63" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="64" spans="1:33">
@@ -5479,10 +5477,10 @@
         <v>0</v>
       </c>
       <c r="AF64" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG64" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="65" spans="1:33">
@@ -5541,10 +5539,10 @@
         <v>0</v>
       </c>
       <c r="AF65" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG65" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="66" spans="1:33">
@@ -5603,10 +5601,10 @@
         <v>0</v>
       </c>
       <c r="AF66" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG66" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="67" spans="1:33">
@@ -5668,7 +5666,7 @@
         <v>0</v>
       </c>
       <c r="AF67" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:33">
@@ -5727,7 +5725,7 @@
         <v>0</v>
       </c>
       <c r="AF68" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:33">
@@ -5789,7 +5787,7 @@
         <v>0</v>
       </c>
       <c r="AF69" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:33">
@@ -5848,7 +5846,7 @@
         <v>0</v>
       </c>
       <c r="AF70" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:33">
@@ -5907,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="AF71" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72" spans="1:33">
@@ -5966,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="AF72" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="73" spans="1:33">
@@ -6025,7 +6023,7 @@
         <v>0</v>
       </c>
       <c r="AF73" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="74" spans="1:33">
@@ -6084,7 +6082,7 @@
         <v>0</v>
       </c>
       <c r="AF74" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="75" spans="1:33">
@@ -6143,7 +6141,7 @@
         <v>0</v>
       </c>
       <c r="AF75" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="76" spans="1:33">
@@ -6202,7 +6200,7 @@
         <v>0</v>
       </c>
       <c r="AF76" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="77" spans="1:33">
@@ -6261,7 +6259,7 @@
         <v>0</v>
       </c>
       <c r="AF77" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="78" spans="1:33">
@@ -6320,7 +6318,7 @@
         <v>0</v>
       </c>
       <c r="AF78" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="79" spans="1:33">
@@ -6379,7 +6377,7 @@
         <v>0</v>
       </c>
       <c r="AF79" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="80" spans="1:33">
@@ -6438,7 +6436,7 @@
         <v>0</v>
       </c>
       <c r="AF80" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="81" spans="1:33">
@@ -6497,7 +6495,7 @@
         <v>0</v>
       </c>
       <c r="AF81" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="82" spans="1:33">
@@ -6556,7 +6554,7 @@
         <v>0</v>
       </c>
       <c r="AF82" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="83" spans="1:33">
@@ -6615,7 +6613,7 @@
         <v>0</v>
       </c>
       <c r="AF83" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="84" spans="1:33">
@@ -6674,7 +6672,7 @@
         <v>0</v>
       </c>
       <c r="AF84" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="85" spans="1:33">
@@ -6733,7 +6731,7 @@
         <v>0</v>
       </c>
       <c r="AF85" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="86" spans="1:33">
@@ -6792,7 +6790,7 @@
         <v>0</v>
       </c>
       <c r="AF86" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="87" spans="1:33">
@@ -6851,7 +6849,7 @@
         <v>0</v>
       </c>
       <c r="AF87" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="88" spans="1:33">
@@ -6913,13 +6911,13 @@
         <v>0</v>
       </c>
       <c r="AA88" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AF88" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG88" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="89" spans="1:33">
@@ -6981,13 +6979,13 @@
         <v>0</v>
       </c>
       <c r="AA89" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AF89" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG89" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="90" spans="1:33">
@@ -7049,13 +7047,13 @@
         <v>0</v>
       </c>
       <c r="AA90" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AF90" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG90" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="91" spans="1:33">
@@ -7117,13 +7115,13 @@
         <v>0</v>
       </c>
       <c r="AA91" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AF91" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG91" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="92" spans="1:33">
@@ -7185,13 +7183,13 @@
         <v>0</v>
       </c>
       <c r="AA92" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AF92" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG92" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="93" spans="1:33">
@@ -7253,13 +7251,13 @@
         <v>0</v>
       </c>
       <c r="AA93" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AF93" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG93" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="94" spans="1:33">
@@ -7321,13 +7319,13 @@
         <v>0</v>
       </c>
       <c r="AA94" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AF94" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG94" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="95" spans="1:33">
@@ -7389,13 +7387,13 @@
         <v>0</v>
       </c>
       <c r="AA95" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AF95" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG95" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="96" spans="1:33">
@@ -7457,13 +7455,13 @@
         <v>0</v>
       </c>
       <c r="AA96" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AF96" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG96" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="97" spans="1:33">
@@ -7525,13 +7523,13 @@
         <v>0</v>
       </c>
       <c r="AA97" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AF97" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG97" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="98" spans="1:33">
@@ -7593,13 +7591,13 @@
         <v>0</v>
       </c>
       <c r="AA98" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AF98" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG98" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="99" spans="1:33">
@@ -7670,10 +7668,10 @@
         <v>196</v>
       </c>
       <c r="AF99" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG99" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="100" spans="1:33">
@@ -7738,10 +7736,10 @@
         <v>198</v>
       </c>
       <c r="AF100" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG100" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="101" spans="1:33">
@@ -7812,10 +7810,10 @@
         <v>199</v>
       </c>
       <c r="AF101" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG101" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="102" spans="1:33">
@@ -7886,7 +7884,7 @@
         <v>195</v>
       </c>
       <c r="AF102" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="103" spans="1:33">
@@ -7951,10 +7949,10 @@
         <v>196</v>
       </c>
       <c r="AF103" t="s">
+        <v>331</v>
+      </c>
+      <c r="AG103" t="s">
         <v>332</v>
-      </c>
-      <c r="AG103" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="104" spans="1:33">
@@ -8025,10 +8023,10 @@
         <v>200</v>
       </c>
       <c r="AF104" t="s">
+        <v>331</v>
+      </c>
+      <c r="AG104" t="s">
         <v>332</v>
-      </c>
-      <c r="AG104" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="105" spans="1:33">
@@ -8099,10 +8097,10 @@
         <v>201</v>
       </c>
       <c r="AF105" t="s">
+        <v>331</v>
+      </c>
+      <c r="AG105" t="s">
         <v>332</v>
-      </c>
-      <c r="AG105" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="106" spans="1:33">
@@ -8167,10 +8165,10 @@
         <v>199</v>
       </c>
       <c r="AF106" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG106" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="107" spans="1:33">
@@ -8241,10 +8239,10 @@
         <v>216</v>
       </c>
       <c r="AF107" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG107" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="108" spans="1:33">
@@ -8315,10 +8313,10 @@
         <v>200</v>
       </c>
       <c r="AF108" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG108" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="109" spans="1:33">
@@ -8389,10 +8387,10 @@
         <v>201</v>
       </c>
       <c r="AF109" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG109" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="110" spans="1:33">
@@ -8460,10 +8458,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AF110" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="111" spans="1:33">
@@ -8534,10 +8532,10 @@
         <v>196</v>
       </c>
       <c r="AF111" t="s">
+        <v>331</v>
+      </c>
+      <c r="AG111" t="s">
         <v>332</v>
-      </c>
-      <c r="AG111" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="112" spans="1:33">
@@ -8608,10 +8606,10 @@
         <v>196</v>
       </c>
       <c r="AF112" t="s">
+        <v>331</v>
+      </c>
+      <c r="AG112" t="s">
         <v>332</v>
-      </c>
-      <c r="AG112" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="113" spans="1:33">
@@ -8682,10 +8680,10 @@
         <v>196</v>
       </c>
       <c r="AF113" t="s">
+        <v>331</v>
+      </c>
+      <c r="AG113" t="s">
         <v>332</v>
-      </c>
-      <c r="AG113" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="114" spans="1:33">
@@ -8756,10 +8754,10 @@
         <v>201</v>
       </c>
       <c r="AF114" t="s">
+        <v>331</v>
+      </c>
+      <c r="AG114" t="s">
         <v>332</v>
-      </c>
-      <c r="AG114" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="115" spans="1:33">
@@ -8830,10 +8828,10 @@
         <v>197</v>
       </c>
       <c r="AF115" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG115" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="116" spans="1:33">
@@ -8904,10 +8902,10 @@
         <v>198</v>
       </c>
       <c r="AF116" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG116" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="117" spans="1:33">
@@ -8978,10 +8976,10 @@
         <v>199</v>
       </c>
       <c r="AF117" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG117" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="118" spans="1:33">
@@ -9046,7 +9044,7 @@
         <v>195</v>
       </c>
       <c r="AF118" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="119" spans="1:33">
@@ -9111,10 +9109,10 @@
         <v>196</v>
       </c>
       <c r="AF119" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG119" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="120" spans="1:33">
@@ -9179,10 +9177,10 @@
         <v>196</v>
       </c>
       <c r="AF120" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG120" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="121" spans="1:33">
@@ -9247,10 +9245,10 @@
         <v>196</v>
       </c>
       <c r="AF121" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG121" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="122" spans="1:33">
@@ -9315,10 +9313,10 @@
         <v>201</v>
       </c>
       <c r="AF122" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG122" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="123" spans="1:33">
@@ -9383,10 +9381,10 @@
         <v>197</v>
       </c>
       <c r="AF123" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG123" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="124" spans="1:33">
@@ -9457,10 +9455,10 @@
         <v>198</v>
       </c>
       <c r="AF124" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG124" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="125" spans="1:33">
@@ -9525,10 +9523,10 @@
         <v>199</v>
       </c>
       <c r="AF125" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG125" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="126" spans="1:33">
@@ -9593,7 +9591,7 @@
         <v>195</v>
       </c>
       <c r="AF126" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="127" spans="1:33">
@@ -9658,10 +9656,10 @@
         <v>196</v>
       </c>
       <c r="AF127" t="s">
+        <v>331</v>
+      </c>
+      <c r="AG127" t="s">
         <v>332</v>
-      </c>
-      <c r="AG127" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="128" spans="1:33">
@@ -9732,10 +9730,10 @@
         <v>200</v>
       </c>
       <c r="AF128" t="s">
+        <v>331</v>
+      </c>
+      <c r="AG128" t="s">
         <v>332</v>
-      </c>
-      <c r="AG128" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="129" spans="1:33">
@@ -9806,10 +9804,10 @@
         <v>201</v>
       </c>
       <c r="AF129" t="s">
+        <v>331</v>
+      </c>
+      <c r="AG129" t="s">
         <v>332</v>
-      </c>
-      <c r="AG129" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="130" spans="1:33">
@@ -9874,10 +9872,10 @@
         <v>199</v>
       </c>
       <c r="AF130" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG130" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="131" spans="1:33">
@@ -9942,7 +9940,7 @@
         <v>195</v>
       </c>
       <c r="AF131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="132" spans="1:33">
@@ -10007,10 +10005,10 @@
         <v>196</v>
       </c>
       <c r="AF132" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG132" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="133" spans="1:33">
@@ -10075,10 +10073,10 @@
         <v>200</v>
       </c>
       <c r="AF133" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG133" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="134" spans="1:33">
@@ -10143,10 +10141,10 @@
         <v>196</v>
       </c>
       <c r="AF134" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG134" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="135" spans="1:33">
@@ -10211,10 +10209,10 @@
         <v>196</v>
       </c>
       <c r="AF135" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG135" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="136" spans="1:33">
@@ -10279,10 +10277,10 @@
         <v>197</v>
       </c>
       <c r="AF136" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG136" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="137" spans="1:33">
@@ -10347,10 +10345,10 @@
         <v>198</v>
       </c>
       <c r="AF137" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG137" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="138" spans="1:33">
@@ -10415,10 +10413,10 @@
         <v>199</v>
       </c>
       <c r="AF138" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG138" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="139" spans="1:33">
@@ -10489,10 +10487,10 @@
         <v>196</v>
       </c>
       <c r="AF139" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG139" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="140" spans="1:33">
@@ -10563,10 +10561,10 @@
         <v>196</v>
       </c>
       <c r="AF140" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG140" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="141" spans="1:33">
@@ -10637,10 +10635,10 @@
         <v>196</v>
       </c>
       <c r="AF141" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG141" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="142" spans="1:33">
@@ -10711,10 +10709,10 @@
         <v>201</v>
       </c>
       <c r="AF142" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG142" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="143" spans="1:33">
@@ -10779,10 +10777,10 @@
         <v>200</v>
       </c>
       <c r="AF143" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG143" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="144" spans="1:33">
@@ -10853,7 +10851,7 @@
         <v>195</v>
       </c>
       <c r="AF144" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="145" spans="1:33">
@@ -10924,10 +10922,10 @@
         <v>216</v>
       </c>
       <c r="AF145" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG145" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="146" spans="1:33">
@@ -10998,10 +10996,10 @@
         <v>196</v>
       </c>
       <c r="AF146" t="s">
+        <v>331</v>
+      </c>
+      <c r="AG146" t="s">
         <v>332</v>
-      </c>
-      <c r="AG146" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="147" spans="1:33">
@@ -11072,10 +11070,10 @@
         <v>196</v>
       </c>
       <c r="AF147" t="s">
+        <v>331</v>
+      </c>
+      <c r="AG147" t="s">
         <v>332</v>
-      </c>
-      <c r="AG147" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="148" spans="1:33">
@@ -11146,10 +11144,10 @@
         <v>196</v>
       </c>
       <c r="AF148" t="s">
+        <v>331</v>
+      </c>
+      <c r="AG148" t="s">
         <v>332</v>
-      </c>
-      <c r="AG148" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="149" spans="1:33">
@@ -11220,10 +11218,10 @@
         <v>201</v>
       </c>
       <c r="AF149" t="s">
+        <v>331</v>
+      </c>
+      <c r="AG149" t="s">
         <v>332</v>
-      </c>
-      <c r="AG149" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="150" spans="1:33">
@@ -11294,10 +11292,10 @@
         <v>197</v>
       </c>
       <c r="AF150" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG150" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="151" spans="1:33">
@@ -11368,10 +11366,10 @@
         <v>198</v>
       </c>
       <c r="AF151" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG151" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="152" spans="1:33">
@@ -11442,10 +11440,10 @@
         <v>199</v>
       </c>
       <c r="AF152" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG152" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="153" spans="1:33">
@@ -11516,10 +11514,10 @@
         <v>196</v>
       </c>
       <c r="AF153" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG153" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="154" spans="1:33">
@@ -11584,7 +11582,7 @@
         <v>195</v>
       </c>
       <c r="AF154" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="155" spans="1:33">
@@ -11649,10 +11647,10 @@
         <v>216</v>
       </c>
       <c r="AF155" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG155" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="156" spans="1:33">
@@ -11717,10 +11715,10 @@
         <v>196</v>
       </c>
       <c r="AF156" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG156" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="157" spans="1:33">
@@ -11785,10 +11783,10 @@
         <v>196</v>
       </c>
       <c r="AF157" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG157" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="158" spans="1:33">
@@ -11853,10 +11851,10 @@
         <v>196</v>
       </c>
       <c r="AF158" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG158" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="159" spans="1:33">
@@ -11921,10 +11919,10 @@
         <v>201</v>
       </c>
       <c r="AF159" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG159" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="160" spans="1:33">
@@ -11989,10 +11987,10 @@
         <v>197</v>
       </c>
       <c r="AF160" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG160" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="161" spans="1:33">
@@ -12057,10 +12055,10 @@
         <v>198</v>
       </c>
       <c r="AF161" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG161" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="162" spans="1:33">
@@ -12125,10 +12123,10 @@
         <v>199</v>
       </c>
       <c r="AF162" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG162" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="163" spans="1:33">
@@ -12199,10 +12197,10 @@
         <v>199</v>
       </c>
       <c r="AF163" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG163" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="164" spans="1:33">
@@ -12273,10 +12271,10 @@
         <v>199</v>
       </c>
       <c r="AF164" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG164" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="165" spans="1:33">
@@ -12347,10 +12345,10 @@
         <v>199</v>
       </c>
       <c r="AF165" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG165" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="166" spans="1:33">
@@ -12415,7 +12413,7 @@
         <v>202</v>
       </c>
       <c r="AF166" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG166" t="s">
         <v>202</v>
@@ -12483,7 +12481,7 @@
         <v>202</v>
       </c>
       <c r="AF167" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG167" t="s">
         <v>202</v>
@@ -12557,7 +12555,7 @@
         <v>202</v>
       </c>
       <c r="AF168" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="169" spans="1:33">
@@ -12622,7 +12620,7 @@
         <v>205</v>
       </c>
       <c r="AF169" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG169" t="s">
         <v>202</v>
@@ -12690,7 +12688,7 @@
         <v>202</v>
       </c>
       <c r="AF170" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG170" t="s">
         <v>202</v>
@@ -12758,7 +12756,7 @@
         <v>202</v>
       </c>
       <c r="AF171" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG171" t="s">
         <v>202</v>
@@ -12826,7 +12824,7 @@
         <v>202</v>
       </c>
       <c r="AF172" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG172" t="s">
         <v>202</v>
@@ -12894,7 +12892,7 @@
         <v>202</v>
       </c>
       <c r="AF173" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="174" spans="1:33">
@@ -12959,7 +12957,7 @@
         <v>205</v>
       </c>
       <c r="AF174" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG174" t="s">
         <v>202</v>
@@ -13027,7 +13025,7 @@
         <v>202</v>
       </c>
       <c r="AF175" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG175" t="s">
         <v>202</v>
@@ -13095,7 +13093,7 @@
         <v>202</v>
       </c>
       <c r="AF176" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG176" t="s">
         <v>202</v>
@@ -13163,7 +13161,7 @@
         <v>202</v>
       </c>
       <c r="AF177" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG177" t="s">
         <v>202</v>
@@ -13231,7 +13229,7 @@
         <v>202</v>
       </c>
       <c r="AF178" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="179" spans="1:33">
@@ -13296,7 +13294,7 @@
         <v>205</v>
       </c>
       <c r="AF179" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG179" t="s">
         <v>202</v>
@@ -13364,7 +13362,7 @@
         <v>202</v>
       </c>
       <c r="AF180" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG180" t="s">
         <v>202</v>
@@ -13432,7 +13430,7 @@
         <v>202</v>
       </c>
       <c r="AF181" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG181" t="s">
         <v>202</v>
@@ -13500,7 +13498,7 @@
         <v>205</v>
       </c>
       <c r="AF182" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG182" t="s">
         <v>202</v>
@@ -13574,7 +13572,7 @@
         <v>202</v>
       </c>
       <c r="AF183" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG183" t="s">
         <v>202</v>
@@ -13642,7 +13640,7 @@
         <v>202</v>
       </c>
       <c r="AF184" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="185" spans="1:33">
@@ -13707,7 +13705,7 @@
         <v>202</v>
       </c>
       <c r="AF185" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG185" t="s">
         <v>202</v>
@@ -13775,7 +13773,7 @@
         <v>202</v>
       </c>
       <c r="AF186" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG186" t="s">
         <v>202</v>
@@ -13843,7 +13841,7 @@
         <v>202</v>
       </c>
       <c r="AF187" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG187" t="s">
         <v>202</v>
@@ -13911,7 +13909,7 @@
         <v>202</v>
       </c>
       <c r="AF188" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="189" spans="1:33">
@@ -13976,7 +13974,7 @@
         <v>205</v>
       </c>
       <c r="AF189" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG189" t="s">
         <v>202</v>
@@ -14044,7 +14042,7 @@
         <v>202</v>
       </c>
       <c r="AF190" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG190" t="s">
         <v>202</v>
@@ -14112,7 +14110,7 @@
         <v>202</v>
       </c>
       <c r="AF191" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG191" t="s">
         <v>202</v>
@@ -14180,7 +14178,7 @@
         <v>202</v>
       </c>
       <c r="AF192" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="193" spans="1:33">
@@ -14245,7 +14243,7 @@
         <v>205</v>
       </c>
       <c r="AF193" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG193" t="s">
         <v>202</v>
@@ -14310,10 +14308,10 @@
         <v>0</v>
       </c>
       <c r="AA194" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF194" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="195" spans="1:33">
@@ -14375,10 +14373,10 @@
         <v>0</v>
       </c>
       <c r="AA195" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF195" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG195" t="s">
         <v>202</v>
@@ -14443,10 +14441,10 @@
         <v>0</v>
       </c>
       <c r="AA196" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF196" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG196" t="s">
         <v>202</v>
@@ -14511,10 +14509,10 @@
         <v>0</v>
       </c>
       <c r="AA197" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF197" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="198" spans="1:33">
@@ -14576,10 +14574,10 @@
         <v>0</v>
       </c>
       <c r="AA198" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF198" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG198" t="s">
         <v>202</v>
@@ -14647,7 +14645,7 @@
         <v>202</v>
       </c>
       <c r="AF199" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG199" t="s">
         <v>202</v>
@@ -14715,7 +14713,7 @@
         <v>202</v>
       </c>
       <c r="AF200" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG200" t="s">
         <v>202</v>
@@ -14783,7 +14781,7 @@
         <v>202</v>
       </c>
       <c r="AF201" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG201" t="s">
         <v>202</v>
@@ -14851,7 +14849,7 @@
         <v>202</v>
       </c>
       <c r="AF202" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="203" spans="1:33">
@@ -14916,7 +14914,7 @@
         <v>205</v>
       </c>
       <c r="AF203" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG203" t="s">
         <v>202</v>
@@ -14984,7 +14982,7 @@
         <v>202</v>
       </c>
       <c r="AF204" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG204" t="s">
         <v>202</v>
@@ -15052,7 +15050,7 @@
         <v>202</v>
       </c>
       <c r="AF205" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG205" t="s">
         <v>202</v>
@@ -15120,7 +15118,7 @@
         <v>202</v>
       </c>
       <c r="AF206" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG206" t="s">
         <v>202</v>
@@ -15188,7 +15186,7 @@
         <v>202</v>
       </c>
       <c r="AF207" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="208" spans="1:33">
@@ -15253,7 +15251,7 @@
         <v>205</v>
       </c>
       <c r="AF208" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG208" t="s">
         <v>202</v>
@@ -15327,7 +15325,7 @@
         <v>205</v>
       </c>
       <c r="AF209" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG209" t="s">
         <v>202</v>
@@ -15401,7 +15399,7 @@
         <v>205</v>
       </c>
       <c r="AF210" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG210" t="s">
         <v>202</v>
@@ -15469,10 +15467,10 @@
         <v>207</v>
       </c>
       <c r="AF211" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG211" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="212" spans="1:33">
@@ -15537,10 +15535,10 @@
         <v>207</v>
       </c>
       <c r="AF212" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG212" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="213" spans="1:33">
@@ -15611,10 +15609,10 @@
         <v>207</v>
       </c>
       <c r="AF213" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG213" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="214" spans="1:33">
@@ -15679,10 +15677,10 @@
         <v>207</v>
       </c>
       <c r="AF214" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG214" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="215" spans="1:33">
@@ -15747,10 +15745,10 @@
         <v>207</v>
       </c>
       <c r="AF215" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG215" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="216" spans="1:33">
@@ -15815,10 +15813,10 @@
         <v>207</v>
       </c>
       <c r="AF216" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG216" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="217" spans="1:33">
@@ -15883,10 +15881,10 @@
         <v>207</v>
       </c>
       <c r="AF217" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG217" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="218" spans="1:33">
@@ -15957,10 +15955,10 @@
         <v>207</v>
       </c>
       <c r="AF218" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG218" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="219" spans="1:33">
@@ -16025,10 +16023,10 @@
         <v>207</v>
       </c>
       <c r="AF219" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG219" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="220" spans="1:33">
@@ -16090,13 +16088,13 @@
         <v>0</v>
       </c>
       <c r="AA220" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF220" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG220" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="221" spans="1:33">
@@ -16158,13 +16156,13 @@
         <v>0</v>
       </c>
       <c r="AA221" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF221" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG221" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="222" spans="1:33">
@@ -16232,13 +16230,13 @@
         <v>0</v>
       </c>
       <c r="AA222" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF222" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG222" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="223" spans="1:33">
@@ -16300,13 +16298,13 @@
         <v>0</v>
       </c>
       <c r="AA223" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF223" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG223" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="224" spans="1:33">
@@ -16368,13 +16366,13 @@
         <v>0</v>
       </c>
       <c r="AA224" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF224" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG224" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="225" spans="1:33">
@@ -16436,13 +16434,13 @@
         <v>0</v>
       </c>
       <c r="AA225" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF225" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG225" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="226" spans="1:33">
@@ -16507,10 +16505,10 @@
         <v>207</v>
       </c>
       <c r="AF226" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG226" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="227" spans="1:33">
@@ -16572,13 +16570,13 @@
         <v>0</v>
       </c>
       <c r="AA227" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF227" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG227" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="228" spans="1:33">
@@ -16640,13 +16638,13 @@
         <v>0</v>
       </c>
       <c r="AA228" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF228" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG228" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="229" spans="1:33">
@@ -16708,13 +16706,13 @@
         <v>0</v>
       </c>
       <c r="AA229" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF229" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG229" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="230" spans="1:33">
@@ -16776,13 +16774,13 @@
         <v>0</v>
       </c>
       <c r="AA230" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF230" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG230" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="231" spans="1:33">
@@ -16844,13 +16842,13 @@
         <v>0</v>
       </c>
       <c r="AA231" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF231" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG231" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="232" spans="1:33">
@@ -16921,10 +16919,10 @@
         <v>207</v>
       </c>
       <c r="AF232" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG232" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="233" spans="1:33">
@@ -16989,10 +16987,10 @@
         <v>207</v>
       </c>
       <c r="AF233" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG233" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="234" spans="1:33">
@@ -17057,10 +17055,10 @@
         <v>207</v>
       </c>
       <c r="AF234" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG234" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="235" spans="1:33">
@@ -17122,13 +17120,13 @@
         <v>0</v>
       </c>
       <c r="AA235" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AF235" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG235" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="236" spans="1:33">
@@ -17193,10 +17191,10 @@
         <v>0</v>
       </c>
       <c r="AA236" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF236" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="237" spans="1:33">
@@ -17258,10 +17256,10 @@
         <v>0</v>
       </c>
       <c r="AA237" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF237" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="238" spans="1:33">
@@ -17323,10 +17321,10 @@
         <v>0</v>
       </c>
       <c r="AA238" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF238" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="239" spans="1:33">
@@ -17388,10 +17386,10 @@
         <v>0</v>
       </c>
       <c r="AA239" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF239" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="240" spans="1:33">
@@ -17456,10 +17454,10 @@
         <v>0</v>
       </c>
       <c r="AA240" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF240" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="241" spans="1:32">
@@ -17524,10 +17522,10 @@
         <v>0</v>
       </c>
       <c r="AA241" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF241" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="242" spans="1:32">
@@ -17589,10 +17587,10 @@
         <v>0</v>
       </c>
       <c r="AA242" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF242" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="243" spans="1:32">
@@ -17654,10 +17652,10 @@
         <v>0</v>
       </c>
       <c r="AA243" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF243" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="244" spans="1:32">
@@ -17722,10 +17720,10 @@
         <v>0</v>
       </c>
       <c r="AA244" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF244" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="245" spans="1:32">
@@ -17790,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AA245" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF245" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="246" spans="1:32">
@@ -17855,10 +17853,10 @@
         <v>0</v>
       </c>
       <c r="AA246" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF246" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="247" spans="1:32">
@@ -17920,10 +17918,10 @@
         <v>0</v>
       </c>
       <c r="AA247" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF247" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="248" spans="1:32">
@@ -17991,10 +17989,10 @@
         <v>0</v>
       </c>
       <c r="AA248" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF248" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="249" spans="1:32">
@@ -18062,10 +18060,10 @@
         <v>0</v>
       </c>
       <c r="AA249" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF249" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="250" spans="1:32">
@@ -18133,10 +18131,10 @@
         <v>0</v>
       </c>
       <c r="AA250" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF250" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="251" spans="1:32">
@@ -18204,10 +18202,10 @@
         <v>0</v>
       </c>
       <c r="AA251" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF251" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="252" spans="1:32">
@@ -18275,10 +18273,10 @@
         <v>0</v>
       </c>
       <c r="AA252" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF252" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="253" spans="1:32">
@@ -18346,10 +18344,10 @@
         <v>0</v>
       </c>
       <c r="AA253" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF253" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="254" spans="1:32">
@@ -18417,10 +18415,10 @@
         <v>0</v>
       </c>
       <c r="AA254" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF254" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="255" spans="1:32">
@@ -18488,10 +18486,10 @@
         <v>0</v>
       </c>
       <c r="AA255" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF255" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="256" spans="1:32">
@@ -18559,10 +18557,10 @@
         <v>0</v>
       </c>
       <c r="AA256" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF256" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="257" spans="1:32">
@@ -18630,10 +18628,10 @@
         <v>0</v>
       </c>
       <c r="AA257" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF257" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="258" spans="1:32">
@@ -18701,10 +18699,10 @@
         <v>0</v>
       </c>
       <c r="AA258" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF258" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="259" spans="1:32">
@@ -18772,10 +18770,10 @@
         <v>0</v>
       </c>
       <c r="AA259" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF259" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="260" spans="1:32">
@@ -18843,10 +18841,10 @@
         <v>0</v>
       </c>
       <c r="AA260" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF260" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="261" spans="1:32">
@@ -18914,10 +18912,10 @@
         <v>0</v>
       </c>
       <c r="AA261" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF261" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="262" spans="1:32">
@@ -18979,10 +18977,10 @@
         <v>0</v>
       </c>
       <c r="AA262" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF262" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="263" spans="1:32">
@@ -19044,10 +19042,10 @@
         <v>0</v>
       </c>
       <c r="AA263" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF263" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="264" spans="1:32">
@@ -19109,10 +19107,10 @@
         <v>0</v>
       </c>
       <c r="AA264" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AF264" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="265" spans="1:32">
@@ -19174,10 +19172,10 @@
         <v>0</v>
       </c>
       <c r="AA265" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AF265" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="266" spans="1:32">
@@ -19239,10 +19237,10 @@
         <v>0</v>
       </c>
       <c r="AA266" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF266" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="267" spans="1:32">
@@ -19304,10 +19302,10 @@
         <v>0</v>
       </c>
       <c r="AA267" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF267" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="268" spans="1:32">
@@ -19372,7 +19370,7 @@
         <v>208</v>
       </c>
       <c r="AF268" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="269" spans="1:32">
@@ -19437,7 +19435,7 @@
         <v>208</v>
       </c>
       <c r="AF269" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="270" spans="1:32">
@@ -19502,7 +19500,7 @@
         <v>208</v>
       </c>
       <c r="AF270" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="271" spans="1:32">
@@ -19567,7 +19565,7 @@
         <v>208</v>
       </c>
       <c r="AF271" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="272" spans="1:32">
@@ -19632,7 +19630,7 @@
         <v>208</v>
       </c>
       <c r="AF272" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="273" spans="1:32">
@@ -19697,7 +19695,7 @@
         <v>208</v>
       </c>
       <c r="AF273" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="274" spans="1:32">
@@ -19762,7 +19760,7 @@
         <v>208</v>
       </c>
       <c r="AF274" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="275" spans="1:32">
@@ -19824,10 +19822,10 @@
         <v>0</v>
       </c>
       <c r="AA275" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF275" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="276" spans="1:32">
@@ -19889,10 +19887,10 @@
         <v>0</v>
       </c>
       <c r="AA276" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF276" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="277" spans="1:32">
@@ -19954,10 +19952,10 @@
         <v>0</v>
       </c>
       <c r="AA277" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF277" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="278" spans="1:32">
@@ -20019,10 +20017,10 @@
         <v>0</v>
       </c>
       <c r="AA278" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF278" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="279" spans="1:32">
@@ -20084,10 +20082,10 @@
         <v>0</v>
       </c>
       <c r="AA279" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF279" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="280" spans="1:32">
@@ -20149,10 +20147,10 @@
         <v>0</v>
       </c>
       <c r="AA280" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF280" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="281" spans="1:32">
@@ -20214,10 +20212,10 @@
         <v>0</v>
       </c>
       <c r="AA281" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF281" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="282" spans="1:32">
@@ -20279,10 +20277,10 @@
         <v>0</v>
       </c>
       <c r="AA282" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF282" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="283" spans="1:32">
@@ -20344,10 +20342,10 @@
         <v>0</v>
       </c>
       <c r="AA283" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF283" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="284" spans="1:32">
@@ -20409,10 +20407,10 @@
         <v>0</v>
       </c>
       <c r="AA284" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF284" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="285" spans="1:32">
@@ -20474,10 +20472,10 @@
         <v>0</v>
       </c>
       <c r="AA285" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF285" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="286" spans="1:32">
@@ -20539,10 +20537,10 @@
         <v>0</v>
       </c>
       <c r="AA286" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF286" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="287" spans="1:32">
@@ -20604,10 +20602,10 @@
         <v>0</v>
       </c>
       <c r="AA287" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF287" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="288" spans="1:32">
@@ -20669,10 +20667,10 @@
         <v>0</v>
       </c>
       <c r="AA288" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF288" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="289" spans="1:33">
@@ -20734,10 +20732,10 @@
         <v>0</v>
       </c>
       <c r="AA289" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF289" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="290" spans="1:33">
@@ -20799,10 +20797,10 @@
         <v>0</v>
       </c>
       <c r="AA290" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF290" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="291" spans="1:33">
@@ -20864,10 +20862,10 @@
         <v>0</v>
       </c>
       <c r="AA291" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AF291" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="292" spans="1:33">
@@ -20929,10 +20927,10 @@
         <v>0</v>
       </c>
       <c r="AA292" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AF292" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="293" spans="1:33">
@@ -20994,10 +20992,10 @@
         <v>0</v>
       </c>
       <c r="AA293" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF293" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="294" spans="1:33">
@@ -21059,10 +21057,10 @@
         <v>0</v>
       </c>
       <c r="AA294" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF294" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="295" spans="1:33">
@@ -21127,10 +21125,10 @@
         <v>0</v>
       </c>
       <c r="AA295" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AF295" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="296" spans="1:33">
@@ -21189,10 +21187,10 @@
         <v>0</v>
       </c>
       <c r="AF296" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG296" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="297" spans="1:33">
@@ -21251,10 +21249,10 @@
         <v>0</v>
       </c>
       <c r="AF297" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG297" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="298" spans="1:33">
@@ -21313,10 +21311,10 @@
         <v>0</v>
       </c>
       <c r="AF298" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG298" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="299" spans="1:33">
@@ -21375,10 +21373,10 @@
         <v>0</v>
       </c>
       <c r="AF299" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG299" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="300" spans="1:33">
@@ -21437,10 +21435,10 @@
         <v>0</v>
       </c>
       <c r="AF300" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG300" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="301" spans="1:33">
@@ -21499,10 +21497,10 @@
         <v>0</v>
       </c>
       <c r="AF301" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG301" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="302" spans="1:33">
@@ -21561,10 +21559,10 @@
         <v>0</v>
       </c>
       <c r="AF302" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG302" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="303" spans="1:33">
@@ -21623,10 +21621,10 @@
         <v>0</v>
       </c>
       <c r="AF303" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG303" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="304" spans="1:33">
@@ -21685,10 +21683,10 @@
         <v>0</v>
       </c>
       <c r="AF304" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG304" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="305" spans="1:33">
@@ -21747,10 +21745,10 @@
         <v>0</v>
       </c>
       <c r="AF305" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG305" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="306" spans="1:33">
@@ -21809,10 +21807,10 @@
         <v>0</v>
       </c>
       <c r="AF306" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG306" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="307" spans="1:33">
@@ -21871,10 +21869,10 @@
         <v>0</v>
       </c>
       <c r="AF307" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG307" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="308" spans="1:33">
@@ -21933,10 +21931,10 @@
         <v>0</v>
       </c>
       <c r="AF308" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG308" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="309" spans="1:33">
@@ -21995,10 +21993,10 @@
         <v>0</v>
       </c>
       <c r="AF309" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG309" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="310" spans="1:33">
@@ -22057,10 +22055,10 @@
         <v>0</v>
       </c>
       <c r="AF310" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG310" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="311" spans="1:33">
@@ -22119,10 +22117,10 @@
         <v>0</v>
       </c>
       <c r="AF311" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG311" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="312" spans="1:33">
@@ -22181,10 +22179,10 @@
         <v>0</v>
       </c>
       <c r="AF312" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG312" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="313" spans="1:33">
@@ -22243,10 +22241,10 @@
         <v>0</v>
       </c>
       <c r="AF313" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG313" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="314" spans="1:33">
@@ -22305,10 +22303,10 @@
         <v>0</v>
       </c>
       <c r="AF314" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG314" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="315" spans="1:33">
@@ -22367,10 +22365,10 @@
         <v>0</v>
       </c>
       <c r="AF315" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG315" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="316" spans="1:33">
@@ -22429,10 +22427,10 @@
         <v>0</v>
       </c>
       <c r="AF316" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG316" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="317" spans="1:33">
@@ -22491,10 +22489,10 @@
         <v>0</v>
       </c>
       <c r="AF317" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG317" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="318" spans="1:33">
@@ -22553,10 +22551,10 @@
         <v>0</v>
       </c>
       <c r="AF318" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG318" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="319" spans="1:33">
@@ -22615,10 +22613,10 @@
         <v>0</v>
       </c>
       <c r="AF319" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG319" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="320" spans="1:33">
@@ -22677,10 +22675,10 @@
         <v>0</v>
       </c>
       <c r="AF320" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG320" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="321" spans="1:33">
@@ -22739,10 +22737,10 @@
         <v>0</v>
       </c>
       <c r="AF321" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG321" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="322" spans="1:33">
@@ -22801,10 +22799,10 @@
         <v>0</v>
       </c>
       <c r="AF322" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG322" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="323" spans="1:33">
@@ -22863,10 +22861,10 @@
         <v>0</v>
       </c>
       <c r="AF323" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG323" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="324" spans="1:33">
@@ -22925,10 +22923,10 @@
         <v>0</v>
       </c>
       <c r="AF324" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG324" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="325" spans="1:33">
@@ -22987,10 +22985,10 @@
         <v>0</v>
       </c>
       <c r="AF325" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG325" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="326" spans="1:33">
@@ -23049,10 +23047,10 @@
         <v>0</v>
       </c>
       <c r="AF326" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG326" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="327" spans="1:33">
@@ -23111,10 +23109,10 @@
         <v>0</v>
       </c>
       <c r="AF327" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG327" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="328" spans="1:33">
@@ -23173,10 +23171,10 @@
         <v>0</v>
       </c>
       <c r="AF328" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG328" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="329" spans="1:33">
@@ -23235,10 +23233,10 @@
         <v>0</v>
       </c>
       <c r="AF329" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG329" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="330" spans="1:33">
@@ -23297,10 +23295,10 @@
         <v>0</v>
       </c>
       <c r="AF330" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG330" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="331" spans="1:33">
@@ -23359,10 +23357,10 @@
         <v>0</v>
       </c>
       <c r="AF331" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG331" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="332" spans="1:33">
@@ -23421,10 +23419,10 @@
         <v>0</v>
       </c>
       <c r="AF332" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG332" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="333" spans="1:33">
@@ -23483,10 +23481,10 @@
         <v>0</v>
       </c>
       <c r="AF333" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG333" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="334" spans="1:33">
@@ -23545,10 +23543,10 @@
         <v>0</v>
       </c>
       <c r="AF334" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG334" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="335" spans="1:33">
@@ -23607,10 +23605,10 @@
         <v>0</v>
       </c>
       <c r="AF335" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG335" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="336" spans="1:33">
@@ -23669,10 +23667,10 @@
         <v>0</v>
       </c>
       <c r="AF336" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG336" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="337" spans="1:33">
@@ -23731,10 +23729,10 @@
         <v>0</v>
       </c>
       <c r="AF337" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG337" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="338" spans="1:33">
@@ -23793,10 +23791,10 @@
         <v>0</v>
       </c>
       <c r="AF338" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG338" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="339" spans="1:33">
@@ -23855,10 +23853,10 @@
         <v>0</v>
       </c>
       <c r="AF339" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG339" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="340" spans="1:33">
@@ -23917,10 +23915,10 @@
         <v>0</v>
       </c>
       <c r="AF340" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG340" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="341" spans="1:33">
@@ -23979,10 +23977,10 @@
         <v>0</v>
       </c>
       <c r="AF341" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG341" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="342" spans="1:33">
@@ -24041,10 +24039,10 @@
         <v>0</v>
       </c>
       <c r="AF342" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG342" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="343" spans="1:33">
@@ -24103,10 +24101,10 @@
         <v>0</v>
       </c>
       <c r="AF343" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG343" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="344" spans="1:33">
@@ -24165,10 +24163,10 @@
         <v>0</v>
       </c>
       <c r="AF344" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG344" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="345" spans="1:33">
@@ -24227,10 +24225,10 @@
         <v>0</v>
       </c>
       <c r="AF345" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG345" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="346" spans="1:33">
@@ -24289,10 +24287,10 @@
         <v>0</v>
       </c>
       <c r="AF346" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG346" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="347" spans="1:33">
@@ -24351,10 +24349,10 @@
         <v>0</v>
       </c>
       <c r="AF347" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG347" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="348" spans="1:33">
@@ -24413,10 +24411,10 @@
         <v>0</v>
       </c>
       <c r="AF348" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG348" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="349" spans="1:33">
@@ -24475,10 +24473,10 @@
         <v>0</v>
       </c>
       <c r="AF349" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG349" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="350" spans="1:33">
@@ -24537,10 +24535,10 @@
         <v>0</v>
       </c>
       <c r="AF350" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG350" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="351" spans="1:33">
@@ -24599,10 +24597,10 @@
         <v>0</v>
       </c>
       <c r="AF351" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG351" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="352" spans="1:33">
@@ -24661,10 +24659,10 @@
         <v>0</v>
       </c>
       <c r="AF352" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG352" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="353" spans="1:33">
@@ -24723,10 +24721,10 @@
         <v>0</v>
       </c>
       <c r="AF353" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG353" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="354" spans="1:33">
@@ -24785,10 +24783,10 @@
         <v>0</v>
       </c>
       <c r="AF354" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG354" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="355" spans="1:33">
@@ -24847,10 +24845,10 @@
         <v>0</v>
       </c>
       <c r="AF355" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG355" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="356" spans="1:33">
@@ -24909,10 +24907,10 @@
         <v>0</v>
       </c>
       <c r="AF356" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG356" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="357" spans="1:33">
@@ -24971,10 +24969,10 @@
         <v>0</v>
       </c>
       <c r="AF357" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG357" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="358" spans="1:33">
@@ -25033,10 +25031,10 @@
         <v>0</v>
       </c>
       <c r="AF358" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG358" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="359" spans="1:33">
@@ -25095,10 +25093,10 @@
         <v>0</v>
       </c>
       <c r="AF359" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG359" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="360" spans="1:33">
@@ -25157,10 +25155,10 @@
         <v>0</v>
       </c>
       <c r="AF360" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG360" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="361" spans="1:33">
@@ -25219,10 +25217,10 @@
         <v>0</v>
       </c>
       <c r="AF361" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG361" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="362" spans="1:33">
@@ -25281,10 +25279,10 @@
         <v>0</v>
       </c>
       <c r="AF362" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG362" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="363" spans="1:33">
@@ -25343,10 +25341,10 @@
         <v>0</v>
       </c>
       <c r="AF363" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG363" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="364" spans="1:33">
@@ -25405,7 +25403,7 @@
         <v>0</v>
       </c>
       <c r="AF364" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="365" spans="1:33">
@@ -25464,10 +25462,10 @@
         <v>0</v>
       </c>
       <c r="AF365" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG365" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="366" spans="1:33">
@@ -25526,10 +25524,10 @@
         <v>0</v>
       </c>
       <c r="AF366" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG366" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="367" spans="1:33">
@@ -25588,10 +25586,10 @@
         <v>0</v>
       </c>
       <c r="AF367" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG367" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="368" spans="1:33">
@@ -25650,10 +25648,10 @@
         <v>0</v>
       </c>
       <c r="AF368" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG368" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="369" spans="1:33">
@@ -25712,10 +25710,10 @@
         <v>0</v>
       </c>
       <c r="AF369" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG369" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="370" spans="1:33">
@@ -25774,10 +25772,10 @@
         <v>0</v>
       </c>
       <c r="AF370" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG370" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="371" spans="1:33">
@@ -25836,10 +25834,10 @@
         <v>0</v>
       </c>
       <c r="AF371" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG371" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="372" spans="1:33">
@@ -25898,10 +25896,10 @@
         <v>0</v>
       </c>
       <c r="AF372" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG372" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="373" spans="1:33">
@@ -25960,7 +25958,7 @@
         <v>0</v>
       </c>
       <c r="AF373" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="374" spans="1:33">
@@ -26019,10 +26017,10 @@
         <v>0</v>
       </c>
       <c r="AF374" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG374" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="375" spans="1:33">
@@ -26081,10 +26079,10 @@
         <v>0</v>
       </c>
       <c r="AF375" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG375" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="376" spans="1:33">
@@ -26143,10 +26141,10 @@
         <v>0</v>
       </c>
       <c r="AF376" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG376" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="377" spans="1:33">
@@ -26205,10 +26203,10 @@
         <v>0</v>
       </c>
       <c r="AF377" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG377" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="378" spans="1:33">
@@ -26267,10 +26265,10 @@
         <v>0</v>
       </c>
       <c r="AF378" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG378" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="379" spans="1:33">
@@ -26329,10 +26327,10 @@
         <v>0</v>
       </c>
       <c r="AF379" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG379" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="380" spans="1:33">
@@ -26391,10 +26389,10 @@
         <v>0</v>
       </c>
       <c r="AF380" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG380" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="381" spans="1:33">
@@ -26453,10 +26451,10 @@
         <v>0</v>
       </c>
       <c r="AF381" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG381" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="382" spans="1:33">
@@ -26515,7 +26513,7 @@
         <v>0</v>
       </c>
       <c r="AF382" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="383" spans="1:33">
@@ -26574,10 +26572,10 @@
         <v>0</v>
       </c>
       <c r="AF383" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG383" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="384" spans="1:33">
@@ -26636,10 +26634,10 @@
         <v>0</v>
       </c>
       <c r="AF384" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG384" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="385" spans="1:33">
@@ -26698,10 +26696,10 @@
         <v>0</v>
       </c>
       <c r="AF385" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG385" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="386" spans="1:33">
@@ -26760,10 +26758,10 @@
         <v>0</v>
       </c>
       <c r="AF386" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG386" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="387" spans="1:33">
@@ -26822,10 +26820,10 @@
         <v>0</v>
       </c>
       <c r="AF387" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG387" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="388" spans="1:33">
@@ -26884,10 +26882,10 @@
         <v>0</v>
       </c>
       <c r="AF388" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG388" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="389" spans="1:33">
@@ -26946,10 +26944,10 @@
         <v>0</v>
       </c>
       <c r="AF389" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG389" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="390" spans="1:33">
@@ -27008,10 +27006,10 @@
         <v>0</v>
       </c>
       <c r="AF390" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG390" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="391" spans="1:33">
@@ -27070,10 +27068,10 @@
         <v>0</v>
       </c>
       <c r="AF391" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG391" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="392" spans="1:33">
@@ -27132,10 +27130,10 @@
         <v>0</v>
       </c>
       <c r="AF392" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG392" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="393" spans="1:33">
@@ -27194,7 +27192,7 @@
         <v>0</v>
       </c>
       <c r="AF393" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="394" spans="1:33">
@@ -27253,10 +27251,10 @@
         <v>0</v>
       </c>
       <c r="AF394" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG394" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="395" spans="1:33">
@@ -27315,10 +27313,10 @@
         <v>0</v>
       </c>
       <c r="AF395" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG395" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="396" spans="1:33">
@@ -27377,10 +27375,10 @@
         <v>0</v>
       </c>
       <c r="AF396" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG396" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="397" spans="1:33">
@@ -27439,10 +27437,10 @@
         <v>0</v>
       </c>
       <c r="AF397" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG397" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="398" spans="1:33">
@@ -27501,10 +27499,10 @@
         <v>0</v>
       </c>
       <c r="AF398" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG398" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="399" spans="1:33">
@@ -27563,10 +27561,10 @@
         <v>0</v>
       </c>
       <c r="AF399" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG399" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="400" spans="1:33">
@@ -27625,10 +27623,10 @@
         <v>0</v>
       </c>
       <c r="AF400" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG400" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="401" spans="1:33">
@@ -27687,10 +27685,10 @@
         <v>0</v>
       </c>
       <c r="AF401" t="s">
+        <v>331</v>
+      </c>
+      <c r="AG401" t="s">
         <v>332</v>
-      </c>
-      <c r="AG401" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="402" spans="1:33">
@@ -27749,10 +27747,10 @@
         <v>0</v>
       </c>
       <c r="AF402" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG402" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="403" spans="1:33">
@@ -27811,10 +27809,10 @@
         <v>0</v>
       </c>
       <c r="AF403" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG403" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="404" spans="1:33">
@@ -27873,10 +27871,10 @@
         <v>0</v>
       </c>
       <c r="AF404" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG404" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="405" spans="1:33">
@@ -27935,7 +27933,7 @@
         <v>0</v>
       </c>
       <c r="AF405" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="406" spans="1:33">
@@ -27994,10 +27992,10 @@
         <v>0</v>
       </c>
       <c r="AF406" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG406" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="407" spans="1:33">
@@ -28056,10 +28054,10 @@
         <v>0</v>
       </c>
       <c r="AF407" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG407" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="408" spans="1:33">
@@ -28118,10 +28116,10 @@
         <v>0</v>
       </c>
       <c r="AF408" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG408" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="409" spans="1:33">
@@ -28180,10 +28178,10 @@
         <v>0</v>
       </c>
       <c r="AF409" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG409" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="410" spans="1:33">
@@ -28242,10 +28240,10 @@
         <v>0</v>
       </c>
       <c r="AF410" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG410" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="411" spans="1:33">
@@ -28304,10 +28302,10 @@
         <v>0</v>
       </c>
       <c r="AF411" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG411" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="412" spans="1:33">
@@ -28366,10 +28364,10 @@
         <v>0</v>
       </c>
       <c r="AF412" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG412" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="413" spans="1:33">
@@ -28428,7 +28426,7 @@
         <v>0</v>
       </c>
       <c r="AF413" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="414" spans="1:33">
@@ -28487,10 +28485,10 @@
         <v>0</v>
       </c>
       <c r="AF414" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG414" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="415" spans="1:33">
@@ -28549,10 +28547,10 @@
         <v>0</v>
       </c>
       <c r="AF415" t="s">
+        <v>331</v>
+      </c>
+      <c r="AG415" t="s">
         <v>332</v>
-      </c>
-      <c r="AG415" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="416" spans="1:33">
@@ -28611,10 +28609,10 @@
         <v>0</v>
       </c>
       <c r="AF416" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG416" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="417" spans="1:33">
@@ -28673,10 +28671,10 @@
         <v>0</v>
       </c>
       <c r="AF417" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG417" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="418" spans="1:33">
@@ -28735,7 +28733,7 @@
         <v>0</v>
       </c>
       <c r="AF418" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG418" t="s">
         <v>202</v>
@@ -28797,7 +28795,7 @@
         <v>0</v>
       </c>
       <c r="AF419" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG419" t="s">
         <v>202</v>
@@ -28859,7 +28857,7 @@
         <v>0</v>
       </c>
       <c r="AF420" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG420" t="s">
         <v>202</v>
@@ -28927,7 +28925,7 @@
         <v>0</v>
       </c>
       <c r="AF421" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG421" t="s">
         <v>202</v>
@@ -28995,7 +28993,7 @@
         <v>0</v>
       </c>
       <c r="AF422" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG422" t="s">
         <v>202</v>
@@ -29063,7 +29061,7 @@
         <v>0</v>
       </c>
       <c r="AF423" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG423" t="s">
         <v>202</v>
@@ -29131,7 +29129,7 @@
         <v>0</v>
       </c>
       <c r="AF424" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG424" t="s">
         <v>202</v>
@@ -29193,7 +29191,7 @@
         <v>0</v>
       </c>
       <c r="AF425" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="426" spans="1:33">
@@ -29252,7 +29250,7 @@
         <v>0</v>
       </c>
       <c r="AF426" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG426" t="s">
         <v>202</v>
@@ -29314,7 +29312,7 @@
         <v>0</v>
       </c>
       <c r="AF427" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG427" t="s">
         <v>202</v>
@@ -29376,7 +29374,7 @@
         <v>0</v>
       </c>
       <c r="AF428" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG428" t="s">
         <v>202</v>
@@ -29438,7 +29436,7 @@
         <v>0</v>
       </c>
       <c r="AF429" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG429" t="s">
         <v>202</v>
@@ -29500,7 +29498,7 @@
         <v>0</v>
       </c>
       <c r="AF430" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="431" spans="1:33">
@@ -29559,7 +29557,7 @@
         <v>0</v>
       </c>
       <c r="AF431" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="432" spans="1:33">
@@ -29618,7 +29616,7 @@
         <v>0</v>
       </c>
       <c r="AF432" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG432" t="s">
         <v>202</v>
@@ -29680,7 +29678,7 @@
         <v>0</v>
       </c>
       <c r="AF433" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="434" spans="1:33">
@@ -29739,7 +29737,7 @@
         <v>0</v>
       </c>
       <c r="AF434" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG434" t="s">
         <v>202</v>
@@ -29801,7 +29799,7 @@
         <v>0</v>
       </c>
       <c r="AF435" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG435" t="s">
         <v>202</v>
@@ -29863,7 +29861,7 @@
         <v>0</v>
       </c>
       <c r="AF436" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG436" t="s">
         <v>202</v>
@@ -29925,7 +29923,7 @@
         <v>0</v>
       </c>
       <c r="AF437" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG437" t="s">
         <v>202</v>
@@ -29987,7 +29985,7 @@
         <v>0</v>
       </c>
       <c r="AF438" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG438" t="s">
         <v>202</v>
@@ -30049,7 +30047,7 @@
         <v>0</v>
       </c>
       <c r="AF439" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG439" t="s">
         <v>202</v>
@@ -30111,7 +30109,7 @@
         <v>0</v>
       </c>
       <c r="AF440" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG440" t="s">
         <v>202</v>
@@ -30173,7 +30171,7 @@
         <v>0</v>
       </c>
       <c r="AF441" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG441" t="s">
         <v>202</v>
@@ -30235,7 +30233,7 @@
         <v>0</v>
       </c>
       <c r="AF442" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG442" t="s">
         <v>202</v>
@@ -30297,7 +30295,7 @@
         <v>0</v>
       </c>
       <c r="AF443" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG443" t="s">
         <v>202</v>
@@ -30359,10 +30357,10 @@
         <v>0</v>
       </c>
       <c r="AF444" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG444" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="445" spans="1:33">
@@ -30421,10 +30419,10 @@
         <v>0</v>
       </c>
       <c r="AF445" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG445" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="446" spans="1:33">
@@ -30483,10 +30481,10 @@
         <v>0</v>
       </c>
       <c r="AF446" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG446" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="447" spans="1:33">
@@ -30545,10 +30543,10 @@
         <v>0</v>
       </c>
       <c r="AF447" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG447" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="448" spans="1:33">
@@ -30607,10 +30605,10 @@
         <v>0</v>
       </c>
       <c r="AF448" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG448" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="449" spans="1:33">
@@ -30669,10 +30667,10 @@
         <v>0</v>
       </c>
       <c r="AF449" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG449" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="450" spans="1:33">
@@ -30731,10 +30729,10 @@
         <v>0</v>
       </c>
       <c r="AF450" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG450" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="451" spans="1:33">
@@ -30793,10 +30791,10 @@
         <v>0</v>
       </c>
       <c r="AF451" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG451" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="452" spans="1:33">
@@ -30855,10 +30853,10 @@
         <v>0</v>
       </c>
       <c r="AF452" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG452" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="453" spans="1:33">
@@ -30917,10 +30915,10 @@
         <v>0</v>
       </c>
       <c r="AF453" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG453" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="454" spans="1:33">
@@ -30979,10 +30977,10 @@
         <v>0</v>
       </c>
       <c r="AF454" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG454" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="455" spans="1:33">
@@ -31041,10 +31039,10 @@
         <v>0</v>
       </c>
       <c r="AF455" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG455" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="456" spans="1:33">
@@ -31103,10 +31101,10 @@
         <v>0</v>
       </c>
       <c r="AF456" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG456" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="457" spans="1:33">
@@ -31165,10 +31163,10 @@
         <v>0</v>
       </c>
       <c r="AF457" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG457" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="458" spans="1:33">
@@ -31227,10 +31225,10 @@
         <v>0</v>
       </c>
       <c r="AF458" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG458" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="459" spans="1:33">
@@ -31289,10 +31287,10 @@
         <v>0</v>
       </c>
       <c r="AF459" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG459" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="460" spans="1:33">
@@ -31351,10 +31349,10 @@
         <v>0</v>
       </c>
       <c r="AF460" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG460" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="461" spans="1:33">
@@ -31413,10 +31411,10 @@
         <v>0</v>
       </c>
       <c r="AF461" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG461" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="462" spans="1:33">
@@ -31475,10 +31473,10 @@
         <v>0</v>
       </c>
       <c r="AF462" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG462" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="463" spans="1:33">
@@ -31537,10 +31535,10 @@
         <v>0</v>
       </c>
       <c r="AF463" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG463" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="464" spans="1:33">
@@ -31599,10 +31597,10 @@
         <v>0</v>
       </c>
       <c r="AF464" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG464" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="465" spans="1:33">
@@ -31661,10 +31659,10 @@
         <v>0</v>
       </c>
       <c r="AF465" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG465" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="466" spans="1:33">
@@ -31723,10 +31721,10 @@
         <v>0</v>
       </c>
       <c r="AF466" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG466" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="467" spans="1:33">
@@ -31785,10 +31783,10 @@
         <v>0</v>
       </c>
       <c r="AF467" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG467" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="468" spans="1:33">
@@ -31847,7 +31845,7 @@
         <v>0</v>
       </c>
       <c r="AF468" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="469" spans="1:33">
@@ -31906,7 +31904,7 @@
         <v>0</v>
       </c>
       <c r="AF469" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="470" spans="1:33">
@@ -31965,7 +31963,7 @@
         <v>0</v>
       </c>
       <c r="AF470" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="471" spans="1:33">
@@ -32024,7 +32022,7 @@
         <v>0</v>
       </c>
       <c r="AF471" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="472" spans="1:33">
@@ -32083,7 +32081,7 @@
         <v>0</v>
       </c>
       <c r="AF472" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="473" spans="1:33">
@@ -32142,7 +32140,7 @@
         <v>0</v>
       </c>
       <c r="AF473" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="474" spans="1:33">
@@ -32201,7 +32199,7 @@
         <v>0</v>
       </c>
       <c r="AF474" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="475" spans="1:33">
@@ -32260,7 +32258,7 @@
         <v>0</v>
       </c>
       <c r="AF475" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="476" spans="1:33">
@@ -32319,7 +32317,7 @@
         <v>0</v>
       </c>
       <c r="AF476" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="477" spans="1:33">
@@ -32378,7 +32376,7 @@
         <v>0</v>
       </c>
       <c r="AF477" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="478" spans="1:33">
@@ -32437,7 +32435,7 @@
         <v>0</v>
       </c>
       <c r="AF478" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="479" spans="1:33">
@@ -32496,7 +32494,7 @@
         <v>0</v>
       </c>
       <c r="AF479" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="480" spans="1:33">
@@ -32555,7 +32553,7 @@
         <v>0</v>
       </c>
       <c r="AF480" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="481" spans="1:32">
@@ -32614,7 +32612,7 @@
         <v>0</v>
       </c>
       <c r="AF481" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="482" spans="1:32">
@@ -32673,7 +32671,7 @@
         <v>0</v>
       </c>
       <c r="AF482" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="483" spans="1:32">
@@ -32732,7 +32730,7 @@
         <v>0</v>
       </c>
       <c r="AF483" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="484" spans="1:32">
@@ -32791,7 +32789,7 @@
         <v>0</v>
       </c>
       <c r="AF484" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="485" spans="1:32">
@@ -32850,7 +32848,7 @@
         <v>0</v>
       </c>
       <c r="AF485" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="486" spans="1:32">
@@ -32909,7 +32907,7 @@
         <v>0</v>
       </c>
       <c r="AF486" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="487" spans="1:32">
@@ -32968,7 +32966,7 @@
         <v>0</v>
       </c>
       <c r="AF487" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="488" spans="1:32">
@@ -33027,7 +33025,7 @@
         <v>0</v>
       </c>
       <c r="AF488" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="489" spans="1:32">
@@ -33086,7 +33084,7 @@
         <v>0</v>
       </c>
       <c r="AF489" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="490" spans="1:32">
@@ -33145,7 +33143,7 @@
         <v>0</v>
       </c>
       <c r="AF490" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="491" spans="1:32">
@@ -33204,7 +33202,7 @@
         <v>0</v>
       </c>
       <c r="AF491" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="492" spans="1:32">
@@ -33263,7 +33261,7 @@
         <v>0</v>
       </c>
       <c r="AF492" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="493" spans="1:32">
@@ -33322,7 +33320,7 @@
         <v>0</v>
       </c>
       <c r="AF493" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="494" spans="1:32">
@@ -33381,7 +33379,7 @@
         <v>0</v>
       </c>
       <c r="AF494" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="495" spans="1:32">
@@ -33440,7 +33438,7 @@
         <v>0</v>
       </c>
       <c r="AF495" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="496" spans="1:32">
@@ -33499,7 +33497,7 @@
         <v>0</v>
       </c>
       <c r="AF496" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="497" spans="1:32">
@@ -33558,7 +33556,7 @@
         <v>0</v>
       </c>
       <c r="AF497" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="498" spans="1:32">
@@ -33617,7 +33615,7 @@
         <v>0</v>
       </c>
       <c r="AF498" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="499" spans="1:32">
@@ -33676,7 +33674,7 @@
         <v>0</v>
       </c>
       <c r="AF499" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="500" spans="1:32">
@@ -33735,7 +33733,7 @@
         <v>0</v>
       </c>
       <c r="AF500" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="501" spans="1:32">
@@ -33794,7 +33792,7 @@
         <v>0</v>
       </c>
       <c r="AF501" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="502" spans="1:32">
@@ -33853,7 +33851,7 @@
         <v>0</v>
       </c>
       <c r="AF502" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="503" spans="1:32">
@@ -33912,7 +33910,7 @@
         <v>0</v>
       </c>
       <c r="AF503" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="504" spans="1:32">
@@ -33971,7 +33969,7 @@
         <v>0</v>
       </c>
       <c r="AF504" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="505" spans="1:32">
@@ -34030,7 +34028,7 @@
         <v>0</v>
       </c>
       <c r="AF505" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="506" spans="1:32">
@@ -34089,7 +34087,7 @@
         <v>0</v>
       </c>
       <c r="AF506" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="507" spans="1:32">
@@ -34148,7 +34146,7 @@
         <v>0</v>
       </c>
       <c r="AF507" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="508" spans="1:32">
@@ -34207,7 +34205,7 @@
         <v>0</v>
       </c>
       <c r="AF508" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="509" spans="1:32">
@@ -34266,7 +34264,7 @@
         <v>0</v>
       </c>
       <c r="AF509" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="510" spans="1:32">
@@ -34325,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="AF510" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="511" spans="1:32">
@@ -34384,7 +34382,7 @@
         <v>0</v>
       </c>
       <c r="AF511" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="512" spans="1:32">
@@ -34443,7 +34441,7 @@
         <v>0</v>
       </c>
       <c r="AF512" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="513" spans="1:32">
@@ -34502,7 +34500,7 @@
         <v>0</v>
       </c>
       <c r="AF513" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="514" spans="1:32">
@@ -34561,7 +34559,7 @@
         <v>0</v>
       </c>
       <c r="AF514" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="515" spans="1:32">
@@ -34620,7 +34618,7 @@
         <v>0</v>
       </c>
       <c r="AF515" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="516" spans="1:32">
@@ -34679,7 +34677,7 @@
         <v>0</v>
       </c>
       <c r="AF516" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="517" spans="1:32">
@@ -34738,7 +34736,7 @@
         <v>0</v>
       </c>
       <c r="AF517" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="518" spans="1:32">
@@ -34797,7 +34795,7 @@
         <v>0</v>
       </c>
       <c r="AF518" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="519" spans="1:32">
@@ -34856,7 +34854,7 @@
         <v>0</v>
       </c>
       <c r="AF519" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="520" spans="1:32">
@@ -34915,7 +34913,7 @@
         <v>0</v>
       </c>
       <c r="AF520" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="521" spans="1:32">
@@ -34974,7 +34972,7 @@
         <v>0</v>
       </c>
       <c r="AF521" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="522" spans="1:32">
@@ -35033,7 +35031,7 @@
         <v>0</v>
       </c>
       <c r="AF522" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="523" spans="1:32">
@@ -35092,7 +35090,7 @@
         <v>0</v>
       </c>
       <c r="AF523" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="524" spans="1:32">
@@ -35151,7 +35149,7 @@
         <v>0</v>
       </c>
       <c r="AF524" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="525" spans="1:32">
@@ -35210,7 +35208,7 @@
         <v>0</v>
       </c>
       <c r="AF525" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="526" spans="1:32">
@@ -35269,7 +35267,7 @@
         <v>0</v>
       </c>
       <c r="AF526" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="527" spans="1:32">
@@ -35328,7 +35326,7 @@
         <v>0</v>
       </c>
       <c r="AF527" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="528" spans="1:32">
@@ -35387,7 +35385,7 @@
         <v>0</v>
       </c>
       <c r="AF528" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="529" spans="1:33">
@@ -35449,13 +35447,13 @@
         <v>0</v>
       </c>
       <c r="AA529" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF529" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG529" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="530" spans="1:33">
@@ -35517,13 +35515,13 @@
         <v>0</v>
       </c>
       <c r="AA530" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF530" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG530" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="531" spans="1:33">
@@ -35588,13 +35586,13 @@
         <v>0</v>
       </c>
       <c r="AA531" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF531" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG531" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="532" spans="1:33">
@@ -35659,13 +35657,13 @@
         <v>0</v>
       </c>
       <c r="AA532" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF532" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG532" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="533" spans="1:33">
@@ -35730,10 +35728,10 @@
         <v>215</v>
       </c>
       <c r="AF533" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG533" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="534" spans="1:33">
@@ -35795,13 +35793,13 @@
         <v>0</v>
       </c>
       <c r="AA534" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AF534" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG534" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="535" spans="1:33">
@@ -35863,13 +35861,13 @@
         <v>0</v>
       </c>
       <c r="AA535" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AF535" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG535" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="536" spans="1:33">
@@ -35934,10 +35932,10 @@
         <v>214</v>
       </c>
       <c r="AF536" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG536" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="537" spans="1:33">
@@ -35996,10 +35994,10 @@
         <v>0</v>
       </c>
       <c r="AA537" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AF537" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="538" spans="1:33">
@@ -36058,10 +36056,10 @@
         <v>0</v>
       </c>
       <c r="AA538" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AF538" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="539" spans="1:33">
@@ -36123,10 +36121,10 @@
         <v>0</v>
       </c>
       <c r="AA539" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF539" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="540" spans="1:33">
@@ -36191,10 +36189,10 @@
         <v>218</v>
       </c>
       <c r="AF540" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG540" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="541" spans="1:33">
@@ -36259,10 +36257,10 @@
         <v>215</v>
       </c>
       <c r="AF541" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG541" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="542" spans="1:33">
@@ -36327,10 +36325,10 @@
         <v>217</v>
       </c>
       <c r="AF542" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG542" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="543" spans="1:33">
@@ -36395,10 +36393,10 @@
         <v>215</v>
       </c>
       <c r="AF543" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG543" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="544" spans="1:33">
@@ -36463,10 +36461,10 @@
         <v>215</v>
       </c>
       <c r="AF544" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG544" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="545" spans="1:33">
@@ -36531,10 +36529,10 @@
         <v>215</v>
       </c>
       <c r="AF545" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG545" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="546" spans="1:33">
@@ -36599,10 +36597,10 @@
         <v>201</v>
       </c>
       <c r="AF546" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG546" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="547" spans="1:33">
@@ -36664,13 +36662,13 @@
         <v>0</v>
       </c>
       <c r="AA547" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF547" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG547" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="548" spans="1:33">
@@ -36732,13 +36730,13 @@
         <v>0</v>
       </c>
       <c r="AA548" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF548" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG548" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="549" spans="1:33">
@@ -36800,13 +36798,13 @@
         <v>0</v>
       </c>
       <c r="AA549" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF549" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG549" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="550" spans="1:33">
@@ -36868,13 +36866,13 @@
         <v>0</v>
       </c>
       <c r="AA550" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF550" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG550" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="551" spans="1:33">
@@ -36939,7 +36937,7 @@
         <v>202</v>
       </c>
       <c r="AF551" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG551" t="s">
         <v>202</v>
@@ -37007,7 +37005,7 @@
         <v>202</v>
       </c>
       <c r="AF552" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG552" t="s">
         <v>202</v>
@@ -37075,7 +37073,7 @@
         <v>205</v>
       </c>
       <c r="AF553" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG553" t="s">
         <v>202</v>
@@ -37140,10 +37138,10 @@
         <v>0</v>
       </c>
       <c r="AA554" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF554" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG554" t="s">
         <v>202</v>
@@ -37211,10 +37209,10 @@
         <v>207</v>
       </c>
       <c r="AF555" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG555" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="556" spans="1:33">
@@ -37276,13 +37274,13 @@
         <v>0</v>
       </c>
       <c r="AA556" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AF556" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG556" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="557" spans="1:33">
@@ -37347,10 +37345,10 @@
         <v>0</v>
       </c>
       <c r="AA557" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF557" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="558" spans="1:33">
@@ -37412,10 +37410,10 @@
         <v>0</v>
       </c>
       <c r="AA558" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF558" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="559" spans="1:33">
@@ -37480,10 +37478,10 @@
         <v>0</v>
       </c>
       <c r="AA559" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF559" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="560" spans="1:33">
@@ -37548,10 +37546,10 @@
         <v>0</v>
       </c>
       <c r="AA560" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF560" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="561" spans="1:32">
@@ -37616,10 +37614,10 @@
         <v>0</v>
       </c>
       <c r="AA561" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF561" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="562" spans="1:32">
@@ -37678,10 +37676,10 @@
         <v>0</v>
       </c>
       <c r="AA562" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF562" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="563" spans="1:32">
@@ -37746,10 +37744,10 @@
         <v>0</v>
       </c>
       <c r="AA563" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF563" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="564" spans="1:32">
@@ -37814,10 +37812,10 @@
         <v>0</v>
       </c>
       <c r="AA564" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF564" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="565" spans="1:32">
@@ -37879,10 +37877,10 @@
         <v>0</v>
       </c>
       <c r="AA565" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF565" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="566" spans="1:32">
@@ -37947,10 +37945,10 @@
         <v>0</v>
       </c>
       <c r="AA566" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF566" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="567" spans="1:32">
@@ -38009,10 +38007,10 @@
         <v>0</v>
       </c>
       <c r="AA567" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF567" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="568" spans="1:32">
@@ -38077,10 +38075,10 @@
         <v>0</v>
       </c>
       <c r="AA568" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF568" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="569" spans="1:32">
@@ -38145,10 +38143,10 @@
         <v>0</v>
       </c>
       <c r="AA569" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF569" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="570" spans="1:32">
@@ -38213,10 +38211,10 @@
         <v>0</v>
       </c>
       <c r="AA570" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF570" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="571" spans="1:32">
@@ -38278,10 +38276,10 @@
         <v>0</v>
       </c>
       <c r="AA571" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF571" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="572" spans="1:32">
@@ -38346,10 +38344,10 @@
         <v>0</v>
       </c>
       <c r="AA572" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF572" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="573" spans="1:32">
@@ -38411,10 +38409,10 @@
         <v>0</v>
       </c>
       <c r="AA573" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF573" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="574" spans="1:32">
@@ -38476,10 +38474,10 @@
         <v>0</v>
       </c>
       <c r="AA574" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF574" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="575" spans="1:32">
@@ -38544,10 +38542,10 @@
         <v>0</v>
       </c>
       <c r="AA575" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF575" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="576" spans="1:32">
@@ -38612,10 +38610,10 @@
         <v>0</v>
       </c>
       <c r="AA576" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF576" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="577" spans="1:32">
@@ -38680,10 +38678,10 @@
         <v>0</v>
       </c>
       <c r="AA577" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF577" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="578" spans="1:32">
@@ -38745,10 +38743,10 @@
         <v>0</v>
       </c>
       <c r="AA578" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF578" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="579" spans="1:32">
@@ -38813,10 +38811,10 @@
         <v>0</v>
       </c>
       <c r="AA579" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF579" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="580" spans="1:32">
@@ -38878,10 +38876,10 @@
         <v>0</v>
       </c>
       <c r="AA580" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF580" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="581" spans="1:32">
@@ -38943,10 +38941,10 @@
         <v>0</v>
       </c>
       <c r="AA581" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF581" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="582" spans="1:32">
@@ -39011,10 +39009,10 @@
         <v>0</v>
       </c>
       <c r="AA582" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF582" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="583" spans="1:32">
@@ -39079,10 +39077,10 @@
         <v>0</v>
       </c>
       <c r="AA583" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF583" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="584" spans="1:32">
@@ -39147,10 +39145,10 @@
         <v>0</v>
       </c>
       <c r="AA584" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF584" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="585" spans="1:32">
@@ -39212,10 +39210,10 @@
         <v>0</v>
       </c>
       <c r="AA585" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF585" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="586" spans="1:32">
@@ -39277,10 +39275,10 @@
         <v>0</v>
       </c>
       <c r="AA586" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF586" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="587" spans="1:32">
@@ -39342,10 +39340,10 @@
         <v>0</v>
       </c>
       <c r="AA587" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF587" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="588" spans="1:32">
@@ -39383,7 +39381,7 @@
         <v>46269</v>
       </c>
       <c r="M588" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N588" t="s">
         <v>193</v>
@@ -39407,13 +39405,13 @@
         <v>316</v>
       </c>
       <c r="AD588" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AE588" t="s">
         <v>188</v>
       </c>
       <c r="AF588" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="589" spans="1:32">
@@ -39451,7 +39449,7 @@
         <v>46269</v>
       </c>
       <c r="M589" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N589" t="s">
         <v>193</v>
@@ -39475,13 +39473,13 @@
         <v>316</v>
       </c>
       <c r="AD589" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AE589" t="s">
         <v>188</v>
       </c>
       <c r="AF589" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="590" spans="1:32">
@@ -39519,7 +39517,7 @@
         <v>46269</v>
       </c>
       <c r="M590" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N590" t="s">
         <v>190</v>
@@ -39543,13 +39541,13 @@
         <v>316</v>
       </c>
       <c r="AD590" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AE590" t="s">
         <v>188</v>
       </c>
       <c r="AF590" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="591" spans="1:32">
@@ -39587,7 +39585,7 @@
         <v>46259</v>
       </c>
       <c r="M591" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="N591" t="s">
         <v>193</v>
@@ -39611,13 +39609,13 @@
         <v>317</v>
       </c>
       <c r="AD591" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AE591" t="s">
         <v>188</v>
       </c>
       <c r="AF591" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="592" spans="1:32">
@@ -39655,7 +39653,7 @@
         <v>46259</v>
       </c>
       <c r="M592" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="N592" t="s">
         <v>193</v>
@@ -39676,16 +39674,16 @@
         <v>225</v>
       </c>
       <c r="V592" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AD592" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AE592" t="s">
         <v>183</v>
       </c>
       <c r="AF592" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="593" spans="1:33">
@@ -39741,10 +39739,10 @@
         <v>224</v>
       </c>
       <c r="AF593" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG593" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="594" spans="1:33">
@@ -39800,10 +39798,10 @@
         <v>238</v>
       </c>
       <c r="AF594" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG594" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="595" spans="1:33">
@@ -39859,7 +39857,7 @@
         <v>239</v>
       </c>
       <c r="AF595" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="596" spans="1:33">
@@ -39915,7 +39913,7 @@
         <v>239</v>
       </c>
       <c r="AF596" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="597" spans="1:33">
@@ -39971,7 +39969,7 @@
         <v>238</v>
       </c>
       <c r="AF597" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="598" spans="1:33">
@@ -40027,7 +40025,7 @@
         <v>236</v>
       </c>
       <c r="AF598" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="599" spans="1:33">
@@ -40083,7 +40081,7 @@
         <v>236</v>
       </c>
       <c r="AF599" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="600" spans="1:33">
@@ -40139,7 +40137,7 @@
         <v>237</v>
       </c>
       <c r="AF600" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="601" spans="1:33">
@@ -40195,7 +40193,7 @@
         <v>237</v>
       </c>
       <c r="AF601" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="602" spans="1:33">
@@ -40251,7 +40249,7 @@
         <v>229</v>
       </c>
       <c r="AF602" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7860" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7861" uniqueCount="340">
   <si>
     <t>CodCliente</t>
   </si>
@@ -127,9 +127,6 @@
     <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
   </si>
   <si>
-    <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
-  </si>
-  <si>
     <t>PC GAMER GOIANIA LTDA</t>
   </si>
   <si>
@@ -137,6 +134,9 @@
   </si>
   <si>
     <t>CORDEIRO E CIA LTDA</t>
+  </si>
+  <si>
+    <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
   </si>
   <si>
     <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
@@ -601,9 +601,6 @@
     <t>Jakeline Silva</t>
   </si>
   <si>
-    <t>Santos Karina</t>
-  </si>
-  <si>
     <t>Evellin Bispo</t>
   </si>
   <si>
@@ -611,6 +608,9 @@
   </si>
   <si>
     <t>Kaique Souza</t>
+  </si>
+  <si>
+    <t>Santos Karina</t>
   </si>
   <si>
     <t>Gabriela Peres</t>
@@ -688,9 +688,6 @@
     <t xml:space="preserve">GTG </t>
   </si>
   <si>
-    <t>BRASIL DISTRIBUIDORA</t>
-  </si>
-  <si>
     <t>PC GAMER</t>
   </si>
   <si>
@@ -698,6 +695,9 @@
   </si>
   <si>
     <t>TECNO COM</t>
+  </si>
+  <si>
+    <t>BRASIL DISTRIBUIDORA</t>
   </si>
   <si>
     <t>TEC GRUA</t>
@@ -732,9 +732,6 @@
   </si>
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 09/09/2026 - Data Comentário: 04/09/2026 16:13</t>
-  </si>
-  <si>
-    <t>1. Folha em Processamento  Previsão para conclusão dia 10/09/2026 - Data Comentário: 08/09/2026 15:22</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 14/09/2026 - Data Comentário: 31/08/2026 12:04</t>
@@ -804,6 +801,9 @@
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/09/2026 
 Em processamento. - Data Comentário: 04/09/2026 08:41</t>
+  </si>
+  <si>
+    <t>1. Folha em Processamento  Previsão para conclusão dia 10/09/2026 - Data Comentário: 08/09/2026 15:22</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 03/09/2026 
@@ -1767,78 +1767,69 @@
     </row>
     <row r="6" spans="1:33">
       <c r="A6">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
         <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
         <v>59</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6">
-        <v>9746</v>
+        <v>5867</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I6" t="s">
         <v>65</v>
       </c>
       <c r="J6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L6" s="1">
-        <v>46275</v>
-      </c>
-      <c r="M6" t="s">
-        <v>177</v>
+        <v>46280</v>
       </c>
       <c r="N6" t="s">
         <v>187</v>
       </c>
       <c r="O6">
-        <v>18179154</v>
+        <v>17399056</v>
       </c>
       <c r="P6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="Q6" t="s">
         <v>219</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="T6" t="s">
-        <v>224</v>
-      </c>
-      <c r="V6" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="Z6">
         <v>0</v>
       </c>
       <c r="AF6" t="s">
-        <v>330</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7" spans="1:33">
       <c r="A7">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
         <v>55</v>
@@ -1871,10 +1862,10 @@
         <v>187</v>
       </c>
       <c r="O7">
-        <v>17399056</v>
+        <v>16976056</v>
       </c>
       <c r="P7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q7" t="s">
         <v>219</v>
@@ -1883,7 +1874,7 @@
         <v>-6</v>
       </c>
       <c r="T7" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1891,10 +1882,13 @@
       <c r="AF7" t="s">
         <v>331</v>
       </c>
+      <c r="AG7" t="s">
+        <v>334</v>
+      </c>
     </row>
     <row r="8" spans="1:33">
       <c r="A8">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -1926,14 +1920,17 @@
       <c r="L8" s="1">
         <v>46280</v>
       </c>
+      <c r="M8" t="s">
+        <v>178</v>
+      </c>
       <c r="N8" t="s">
         <v>187</v>
       </c>
       <c r="O8">
-        <v>16976056</v>
+        <v>17222618</v>
       </c>
       <c r="P8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q8" t="s">
         <v>219</v>
@@ -1944,6 +1941,9 @@
       <c r="T8" t="s">
         <v>225</v>
       </c>
+      <c r="V8" t="s">
+        <v>239</v>
+      </c>
       <c r="Z8">
         <v>0</v>
       </c>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="9" spans="1:33">
       <c r="A9">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
         <v>55</v>
@@ -1968,7 +1968,7 @@
         <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F9" t="s">
         <v>61</v>
@@ -1988,17 +1988,14 @@
       <c r="L9" s="1">
         <v>46280</v>
       </c>
-      <c r="M9" t="s">
-        <v>178</v>
-      </c>
       <c r="N9" t="s">
         <v>187</v>
       </c>
       <c r="O9">
-        <v>17222618</v>
+        <v>18068532</v>
       </c>
       <c r="P9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="Q9" t="s">
         <v>219</v>
@@ -2007,10 +2004,7 @@
         <v>-6</v>
       </c>
       <c r="T9" t="s">
-        <v>226</v>
-      </c>
-      <c r="V9" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2024,16 +2018,16 @@
     </row>
     <row r="10" spans="1:33">
       <c r="A10">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
         <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
         <v>60</v>
@@ -2060,7 +2054,7 @@
         <v>187</v>
       </c>
       <c r="O10">
-        <v>18068532</v>
+        <v>18052451</v>
       </c>
       <c r="P10" t="s">
         <v>194</v>
@@ -2086,19 +2080,19 @@
     </row>
     <row r="11" spans="1:33">
       <c r="A11">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
         <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F11" t="s">
         <v>61</v>
@@ -2122,10 +2116,10 @@
         <v>187</v>
       </c>
       <c r="O11">
-        <v>18052451</v>
+        <v>18077101</v>
       </c>
       <c r="P11" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q11" t="s">
         <v>219</v>
@@ -2134,7 +2128,7 @@
         <v>-6</v>
       </c>
       <c r="T11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2148,16 +2142,16 @@
     </row>
     <row r="12" spans="1:33">
       <c r="A12">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
         <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
         <v>59</v>
@@ -2180,11 +2174,14 @@
       <c r="L12" s="1">
         <v>46280</v>
       </c>
+      <c r="M12" t="s">
+        <v>178</v>
+      </c>
       <c r="N12" t="s">
         <v>187</v>
       </c>
       <c r="O12">
-        <v>18077101</v>
+        <v>18090178</v>
       </c>
       <c r="P12" t="s">
         <v>197</v>
@@ -2196,7 +2193,10 @@
         <v>-6</v>
       </c>
       <c r="T12" t="s">
-        <v>221</v>
+        <v>226</v>
+      </c>
+      <c r="V12" t="s">
+        <v>240</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2205,12 +2205,12 @@
         <v>331</v>
       </c>
       <c r="AG12" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13" spans="1:33">
       <c r="A13">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B13" t="s">
         <v>40</v>
@@ -2225,7 +2225,7 @@
         <v>59</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G13">
         <v>5867</v>
@@ -2242,14 +2242,11 @@
       <c r="L13" s="1">
         <v>46280</v>
       </c>
-      <c r="M13" t="s">
-        <v>178</v>
-      </c>
       <c r="N13" t="s">
         <v>187</v>
       </c>
       <c r="O13">
-        <v>18090178</v>
+        <v>18179103</v>
       </c>
       <c r="P13" t="s">
         <v>198</v>
@@ -2263,9 +2260,6 @@
       <c r="T13" t="s">
         <v>227</v>
       </c>
-      <c r="V13" t="s">
-        <v>241</v>
-      </c>
       <c r="Z13">
         <v>0</v>
       </c>
@@ -2273,21 +2267,21 @@
         <v>331</v>
       </c>
       <c r="AG13" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14" spans="1:33">
       <c r="A14">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
         <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
         <v>59</v>
@@ -2314,10 +2308,10 @@
         <v>187</v>
       </c>
       <c r="O14">
-        <v>18179103</v>
+        <v>18190413</v>
       </c>
       <c r="P14" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q14" t="s">
         <v>219</v>
@@ -2326,7 +2320,7 @@
         <v>-6</v>
       </c>
       <c r="T14" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2340,10 +2334,10 @@
     </row>
     <row r="15" spans="1:33">
       <c r="A15">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>55</v>
@@ -2352,43 +2346,49 @@
         <v>57</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G15">
-        <v>5867</v>
+        <v>6348</v>
       </c>
       <c r="H15">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I15" t="s">
         <v>65</v>
       </c>
       <c r="J15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L15" s="1">
-        <v>46280</v>
+        <v>46275</v>
+      </c>
+      <c r="M15" t="s">
+        <v>177</v>
       </c>
       <c r="N15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O15">
-        <v>18190413</v>
+        <v>18261361</v>
       </c>
       <c r="P15" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="Q15" t="s">
         <v>219</v>
       </c>
       <c r="S15">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="T15" t="s">
-        <v>228</v>
+        <v>223</v>
+      </c>
+      <c r="V15" t="s">
+        <v>241</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2397,21 +2397,21 @@
         <v>331</v>
       </c>
       <c r="AG15" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="16" spans="1:33">
       <c r="A16">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
         <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E16" t="s">
         <v>60</v>
@@ -2441,7 +2441,7 @@
         <v>188</v>
       </c>
       <c r="O16">
-        <v>18261361</v>
+        <v>18261362</v>
       </c>
       <c r="P16" t="s">
         <v>194</v>
@@ -2456,7 +2456,7 @@
         <v>223</v>
       </c>
       <c r="V16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2488,75 +2488,69 @@
         <v>61</v>
       </c>
       <c r="G17">
-        <v>6348</v>
+        <v>1875</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L17" s="1">
-        <v>46275</v>
-      </c>
-      <c r="M17" t="s">
-        <v>177</v>
+        <v>46280</v>
       </c>
       <c r="N17" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O17">
-        <v>18261362</v>
+        <v>17988662</v>
       </c>
       <c r="P17" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="Q17" t="s">
         <v>219</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="T17" t="s">
         <v>223</v>
       </c>
-      <c r="V17" t="s">
-        <v>242</v>
-      </c>
       <c r="Z17">
         <v>0</v>
       </c>
       <c r="AF17" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG17" t="s">
-        <v>334</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:33">
       <c r="A18">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
         <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F18" t="s">
         <v>61</v>
       </c>
       <c r="G18">
-        <v>1875</v>
+        <v>6805</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -2565,28 +2559,34 @@
         <v>66</v>
       </c>
       <c r="J18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L18" s="1">
-        <v>46280</v>
+        <v>46276</v>
+      </c>
+      <c r="M18" t="s">
+        <v>177</v>
       </c>
       <c r="N18" t="s">
         <v>187</v>
       </c>
       <c r="O18">
-        <v>17988662</v>
+        <v>17222743</v>
       </c>
       <c r="P18" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q18" t="s">
         <v>219</v>
       </c>
       <c r="S18">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="T18" t="s">
-        <v>223</v>
+        <v>225</v>
+      </c>
+      <c r="V18" t="s">
+        <v>242</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2600,10 +2600,10 @@
     </row>
     <row r="19" spans="1:33">
       <c r="A19">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
         <v>55</v>
@@ -2612,7 +2612,7 @@
         <v>57</v>
       </c>
       <c r="E19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F19" t="s">
         <v>61</v>
@@ -2632,17 +2632,14 @@
       <c r="L19" s="1">
         <v>46276</v>
       </c>
-      <c r="M19" t="s">
-        <v>177</v>
-      </c>
       <c r="N19" t="s">
         <v>187</v>
       </c>
       <c r="O19">
-        <v>17222743</v>
+        <v>18085519</v>
       </c>
       <c r="P19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q19" t="s">
         <v>219</v>
@@ -2651,10 +2648,7 @@
         <v>-2</v>
       </c>
       <c r="T19" t="s">
-        <v>226</v>
-      </c>
-      <c r="V19" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2668,16 +2662,16 @@
     </row>
     <row r="20" spans="1:33">
       <c r="A20">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
         <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E20" t="s">
         <v>60</v>
@@ -2704,7 +2698,7 @@
         <v>187</v>
       </c>
       <c r="O20">
-        <v>18085519</v>
+        <v>17988709</v>
       </c>
       <c r="P20" t="s">
         <v>200</v>
@@ -2730,10 +2724,10 @@
     </row>
     <row r="21" spans="1:33">
       <c r="A21">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
         <v>55</v>
@@ -2742,10 +2736,10 @@
         <v>58</v>
       </c>
       <c r="E21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G21">
         <v>6805</v>
@@ -2762,14 +2756,17 @@
       <c r="L21" s="1">
         <v>46276</v>
       </c>
+      <c r="M21" t="s">
+        <v>179</v>
+      </c>
       <c r="N21" t="s">
         <v>187</v>
       </c>
       <c r="O21">
-        <v>17988709</v>
+        <v>18220221</v>
       </c>
       <c r="P21" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q21" t="s">
         <v>219</v>
@@ -2778,7 +2775,10 @@
         <v>-2</v>
       </c>
       <c r="T21" t="s">
-        <v>223</v>
+        <v>227</v>
+      </c>
+      <c r="V21" t="s">
+        <v>243</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -2786,22 +2786,19 @@
       <c r="AF21" t="s">
         <v>332</v>
       </c>
-      <c r="AG21" t="s">
-        <v>200</v>
-      </c>
     </row>
     <row r="22" spans="1:33">
       <c r="A22">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
         <v>55</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E22" t="s">
         <v>59</v>
@@ -2831,10 +2828,10 @@
         <v>187</v>
       </c>
       <c r="O22">
-        <v>18220221</v>
+        <v>18214901</v>
       </c>
       <c r="P22" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q22" t="s">
         <v>219</v>
@@ -2843,7 +2840,7 @@
         <v>-2</v>
       </c>
       <c r="T22" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="V22" t="s">
         <v>244</v>
@@ -2854,19 +2851,22 @@
       <c r="AF22" t="s">
         <v>332</v>
       </c>
+      <c r="AG22" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="23" spans="1:33">
       <c r="A23">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
         <v>55</v>
       </c>
       <c r="D23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
         <v>59</v>
@@ -2896,10 +2896,10 @@
         <v>187</v>
       </c>
       <c r="O23">
-        <v>18214901</v>
+        <v>18186995</v>
       </c>
       <c r="P23" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q23" t="s">
         <v>219</v>
@@ -2908,7 +2908,7 @@
         <v>-2</v>
       </c>
       <c r="T23" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="V23" t="s">
         <v>245</v>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="24" spans="1:33">
       <c r="A24">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
         <v>55</v>
@@ -2964,7 +2964,7 @@
         <v>187</v>
       </c>
       <c r="O24">
-        <v>18186995</v>
+        <v>18187261</v>
       </c>
       <c r="P24" t="s">
         <v>204</v>
@@ -2979,7 +2979,7 @@
         <v>229</v>
       </c>
       <c r="V24" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -2993,10 +2993,10 @@
     </row>
     <row r="25" spans="1:33">
       <c r="A25">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
         <v>55</v>
@@ -3011,7 +3011,7 @@
         <v>62</v>
       </c>
       <c r="G25">
-        <v>6805</v>
+        <v>1866</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -3020,19 +3020,16 @@
         <v>66</v>
       </c>
       <c r="J25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L25" s="1">
-        <v>46276</v>
-      </c>
-      <c r="M25" t="s">
-        <v>179</v>
+        <v>46274</v>
       </c>
       <c r="N25" t="s">
         <v>187</v>
       </c>
       <c r="O25">
-        <v>18187261</v>
+        <v>18186946</v>
       </c>
       <c r="P25" t="s">
         <v>204</v>
@@ -3041,19 +3038,16 @@
         <v>219</v>
       </c>
       <c r="S25">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="T25" t="s">
         <v>229</v>
       </c>
-      <c r="V25" t="s">
-        <v>246</v>
-      </c>
       <c r="Z25">
         <v>0</v>
       </c>
       <c r="AF25" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG25" t="s">
         <v>200</v>
@@ -3061,10 +3055,10 @@
     </row>
     <row r="26" spans="1:33">
       <c r="A26">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
         <v>55</v>
@@ -3097,7 +3091,7 @@
         <v>187</v>
       </c>
       <c r="O26">
-        <v>18186946</v>
+        <v>18187212</v>
       </c>
       <c r="P26" t="s">
         <v>204</v>
@@ -3123,25 +3117,25 @@
     </row>
     <row r="27" spans="1:33">
       <c r="A27">
-        <v>6963</v>
+        <v>6548</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C27" t="s">
         <v>55</v>
       </c>
       <c r="D27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E27" t="s">
         <v>59</v>
       </c>
       <c r="F27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G27">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -3150,19 +3144,22 @@
         <v>66</v>
       </c>
       <c r="J27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L27" s="1">
         <v>46274</v>
       </c>
+      <c r="M27" t="s">
+        <v>176</v>
+      </c>
       <c r="N27" t="s">
         <v>187</v>
       </c>
       <c r="O27">
-        <v>18187212</v>
+        <v>17988543</v>
       </c>
       <c r="P27" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="Q27" t="s">
         <v>219</v>
@@ -3171,7 +3168,10 @@
         <v>0</v>
       </c>
       <c r="T27" t="s">
-        <v>229</v>
+        <v>225</v>
+      </c>
+      <c r="V27" t="s">
+        <v>246</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3185,22 +3185,22 @@
     </row>
     <row r="28" spans="1:33">
       <c r="A28">
-        <v>6548</v>
+        <v>6945</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C28" t="s">
         <v>55</v>
       </c>
       <c r="D28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E28" t="s">
         <v>59</v>
       </c>
       <c r="F28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G28">
         <v>1867</v>
@@ -3218,16 +3218,16 @@
         <v>46274</v>
       </c>
       <c r="M28" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N28" t="s">
         <v>187</v>
       </c>
       <c r="O28">
-        <v>17988543</v>
+        <v>18220182</v>
       </c>
       <c r="P28" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q28" t="s">
         <v>219</v>
@@ -3236,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="V28" t="s">
         <v>247</v>
@@ -3247,22 +3247,19 @@
       <c r="AF28" t="s">
         <v>331</v>
       </c>
-      <c r="AG28" t="s">
-        <v>200</v>
-      </c>
     </row>
     <row r="29" spans="1:33">
       <c r="A29">
-        <v>6945</v>
+        <v>6962</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C29" t="s">
         <v>55</v>
       </c>
       <c r="D29" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E29" t="s">
         <v>59</v>
@@ -3285,17 +3282,14 @@
       <c r="L29" s="1">
         <v>46274</v>
       </c>
-      <c r="M29" t="s">
-        <v>179</v>
-      </c>
       <c r="N29" t="s">
         <v>187</v>
       </c>
       <c r="O29">
-        <v>18220182</v>
+        <v>18186953</v>
       </c>
       <c r="P29" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q29" t="s">
         <v>219</v>
@@ -3304,10 +3298,7 @@
         <v>0</v>
       </c>
       <c r="T29" t="s">
-        <v>224</v>
-      </c>
-      <c r="V29" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3315,13 +3306,16 @@
       <c r="AF29" t="s">
         <v>331</v>
       </c>
+      <c r="AG29" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="30" spans="1:33">
       <c r="A30">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
         <v>55</v>
@@ -3354,7 +3348,7 @@
         <v>187</v>
       </c>
       <c r="O30">
-        <v>18186953</v>
+        <v>18187219</v>
       </c>
       <c r="P30" t="s">
         <v>204</v>
@@ -3380,16 +3374,16 @@
     </row>
     <row r="31" spans="1:33">
       <c r="A31">
-        <v>6963</v>
+        <v>6945</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C31" t="s">
         <v>55</v>
       </c>
       <c r="D31" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E31" t="s">
         <v>59</v>
@@ -3398,60 +3392,57 @@
         <v>62</v>
       </c>
       <c r="G31">
-        <v>1867</v>
+        <v>6886</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I31" t="s">
         <v>66</v>
       </c>
       <c r="J31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L31" s="1">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="N31" t="s">
         <v>187</v>
       </c>
       <c r="O31">
-        <v>18187219</v>
+        <v>18220227</v>
       </c>
       <c r="P31" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="Q31" t="s">
         <v>219</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T31" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="Z31">
         <v>0</v>
       </c>
       <c r="AF31" t="s">
-        <v>331</v>
-      </c>
-      <c r="AG31" t="s">
-        <v>200</v>
+        <v>330</v>
       </c>
     </row>
     <row r="32" spans="1:33">
       <c r="A32">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C32" t="s">
         <v>55</v>
       </c>
       <c r="D32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E32" t="s">
         <v>59</v>
@@ -3478,10 +3469,10 @@
         <v>187</v>
       </c>
       <c r="O32">
-        <v>18220227</v>
+        <v>18214907</v>
       </c>
       <c r="P32" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q32" t="s">
         <v>219</v>
@@ -3490,7 +3481,7 @@
         <v>-1</v>
       </c>
       <c r="T32" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3498,13 +3489,16 @@
       <c r="AF32" t="s">
         <v>330</v>
       </c>
+      <c r="AG32" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="33" spans="1:33">
       <c r="A33">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C33" t="s">
         <v>55</v>
@@ -3513,43 +3507,43 @@
         <v>57</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G33">
-        <v>6886</v>
+        <v>10674</v>
       </c>
       <c r="H33">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I33" t="s">
         <v>66</v>
       </c>
       <c r="J33" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L33" s="1">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="N33" t="s">
         <v>187</v>
       </c>
       <c r="O33">
-        <v>18214907</v>
+        <v>17968445</v>
       </c>
       <c r="P33" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="Q33" t="s">
         <v>219</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="T33" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -3563,22 +3557,22 @@
     </row>
     <row r="34" spans="1:33">
       <c r="A34">
-        <v>6627</v>
+        <v>6945</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C34" t="s">
         <v>55</v>
       </c>
       <c r="D34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G34">
         <v>10674</v>
@@ -3599,10 +3593,10 @@
         <v>187</v>
       </c>
       <c r="O34">
-        <v>17968445</v>
+        <v>18220233</v>
       </c>
       <c r="P34" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q34" t="s">
         <v>219</v>
@@ -3611,7 +3605,7 @@
         <v>-6</v>
       </c>
       <c r="T34" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -3619,22 +3613,19 @@
       <c r="AF34" t="s">
         <v>330</v>
       </c>
-      <c r="AG34" t="s">
-        <v>200</v>
-      </c>
     </row>
     <row r="35" spans="1:33">
       <c r="A35">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C35" t="s">
         <v>55</v>
       </c>
       <c r="D35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E35" t="s">
         <v>59</v>
@@ -3661,10 +3652,10 @@
         <v>187</v>
       </c>
       <c r="O35">
-        <v>18220233</v>
+        <v>18214919</v>
       </c>
       <c r="P35" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q35" t="s">
         <v>219</v>
@@ -3673,7 +3664,7 @@
         <v>-6</v>
       </c>
       <c r="T35" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -3681,19 +3672,22 @@
       <c r="AF35" t="s">
         <v>330</v>
       </c>
+      <c r="AG35" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="36" spans="1:33">
       <c r="A36">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B36" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C36" t="s">
         <v>55</v>
       </c>
       <c r="D36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E36" t="s">
         <v>59</v>
@@ -3720,10 +3714,10 @@
         <v>187</v>
       </c>
       <c r="O36">
-        <v>18214919</v>
+        <v>18187016</v>
       </c>
       <c r="P36" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q36" t="s">
         <v>219</v>
@@ -3732,7 +3726,7 @@
         <v>-6</v>
       </c>
       <c r="T36" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -3746,10 +3740,10 @@
     </row>
     <row r="37" spans="1:33">
       <c r="A37">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C37" t="s">
         <v>55</v>
@@ -3782,7 +3776,7 @@
         <v>187</v>
       </c>
       <c r="O37">
-        <v>18187016</v>
+        <v>18187282</v>
       </c>
       <c r="P37" t="s">
         <v>204</v>
@@ -3808,34 +3802,34 @@
     </row>
     <row r="38" spans="1:33">
       <c r="A38">
-        <v>6963</v>
+        <v>6486</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C38" t="s">
         <v>55</v>
       </c>
       <c r="D38" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E38" t="s">
         <v>59</v>
       </c>
       <c r="F38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G38">
-        <v>10674</v>
+        <v>1837</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="I38" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J38" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L38" s="1">
         <v>46280</v>
@@ -3844,10 +3838,10 @@
         <v>187</v>
       </c>
       <c r="O38">
-        <v>18187282</v>
+        <v>16975983</v>
       </c>
       <c r="P38" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="Q38" t="s">
         <v>219</v>
@@ -3856,7 +3850,7 @@
         <v>-6</v>
       </c>
       <c r="T38" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -3865,21 +3859,21 @@
         <v>330</v>
       </c>
       <c r="AG38" t="s">
-        <v>200</v>
+        <v>333</v>
       </c>
     </row>
     <row r="39" spans="1:33">
       <c r="A39">
-        <v>6486</v>
+        <v>6705</v>
       </c>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C39" t="s">
         <v>55</v>
       </c>
       <c r="D39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E39" t="s">
         <v>59</v>
@@ -3888,16 +3882,16 @@
         <v>61</v>
       </c>
       <c r="G39">
-        <v>1837</v>
+        <v>6298</v>
       </c>
       <c r="H39">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I39" t="s">
         <v>64</v>
       </c>
       <c r="J39" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="L39" s="1">
         <v>46280</v>
@@ -3906,7 +3900,7 @@
         <v>187</v>
       </c>
       <c r="O39">
-        <v>16975983</v>
+        <v>17949009</v>
       </c>
       <c r="P39" t="s">
         <v>192</v>
@@ -3918,13 +3912,13 @@
         <v>-6</v>
       </c>
       <c r="T39" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Z39">
         <v>0</v>
       </c>
       <c r="AF39" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AG39" t="s">
         <v>333</v>
@@ -3932,16 +3926,16 @@
     </row>
     <row r="40" spans="1:33">
       <c r="A40">
-        <v>6705</v>
+        <v>5417</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C40" t="s">
         <v>55</v>
       </c>
       <c r="D40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E40" t="s">
         <v>59</v>
@@ -3950,7 +3944,7 @@
         <v>61</v>
       </c>
       <c r="G40">
-        <v>6298</v>
+        <v>6806</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -3959,16 +3953,16 @@
         <v>64</v>
       </c>
       <c r="J40" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L40" s="1">
-        <v>46280</v>
+        <v>46276</v>
       </c>
       <c r="N40" t="s">
         <v>187</v>
       </c>
       <c r="O40">
-        <v>17949009</v>
+        <v>17399230</v>
       </c>
       <c r="P40" t="s">
         <v>192</v>
@@ -3977,10 +3971,10 @@
         <v>219</v>
       </c>
       <c r="S40">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="T40" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -3994,16 +3988,16 @@
     </row>
     <row r="41" spans="1:33">
       <c r="A41">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B41" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C41" t="s">
         <v>55</v>
       </c>
       <c r="D41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E41" t="s">
         <v>59</v>
@@ -4030,7 +4024,7 @@
         <v>187</v>
       </c>
       <c r="O41">
-        <v>17399230</v>
+        <v>16962308</v>
       </c>
       <c r="P41" t="s">
         <v>192</v>
@@ -4042,7 +4036,7 @@
         <v>-2</v>
       </c>
       <c r="T41" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4056,16 +4050,16 @@
     </row>
     <row r="42" spans="1:33">
       <c r="A42">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B42" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C42" t="s">
         <v>55</v>
       </c>
       <c r="D42" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E42" t="s">
         <v>59</v>
@@ -4092,7 +4086,7 @@
         <v>187</v>
       </c>
       <c r="O42">
-        <v>16962308</v>
+        <v>16976187</v>
       </c>
       <c r="P42" t="s">
         <v>192</v>
@@ -4104,7 +4098,7 @@
         <v>-2</v>
       </c>
       <c r="T42" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4118,16 +4112,16 @@
     </row>
     <row r="43" spans="1:33">
       <c r="A43">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C43" t="s">
         <v>55</v>
       </c>
       <c r="D43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E43" t="s">
         <v>59</v>
@@ -4154,7 +4148,7 @@
         <v>187</v>
       </c>
       <c r="O43">
-        <v>16976187</v>
+        <v>17948858</v>
       </c>
       <c r="P43" t="s">
         <v>192</v>
@@ -4166,7 +4160,7 @@
         <v>-2</v>
       </c>
       <c r="T43" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4180,16 +4174,16 @@
     </row>
     <row r="44" spans="1:33">
       <c r="A44">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B44" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C44" t="s">
         <v>55</v>
       </c>
       <c r="D44" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E44" t="s">
         <v>59</v>
@@ -4216,7 +4210,7 @@
         <v>187</v>
       </c>
       <c r="O44">
-        <v>17948858</v>
+        <v>18085297</v>
       </c>
       <c r="P44" t="s">
         <v>192</v>
@@ -4228,7 +4222,7 @@
         <v>-2</v>
       </c>
       <c r="T44" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4242,16 +4236,16 @@
     </row>
     <row r="45" spans="1:33">
       <c r="A45">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B45" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C45" t="s">
         <v>55</v>
       </c>
       <c r="D45" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E45" t="s">
         <v>59</v>
@@ -4278,7 +4272,7 @@
         <v>187</v>
       </c>
       <c r="O45">
-        <v>18085297</v>
+        <v>17949029</v>
       </c>
       <c r="P45" t="s">
         <v>192</v>
@@ -4290,7 +4284,7 @@
         <v>-2</v>
       </c>
       <c r="T45" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -4304,10 +4298,10 @@
     </row>
     <row r="46" spans="1:33">
       <c r="A46">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B46" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C46" t="s">
         <v>55</v>
@@ -4340,7 +4334,7 @@
         <v>187</v>
       </c>
       <c r="O46">
-        <v>17949029</v>
+        <v>18085066</v>
       </c>
       <c r="P46" t="s">
         <v>192</v>
@@ -4352,7 +4346,7 @@
         <v>-2</v>
       </c>
       <c r="T46" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -4366,16 +4360,16 @@
     </row>
     <row r="47" spans="1:33">
       <c r="A47">
-        <v>6779</v>
+        <v>5417</v>
       </c>
       <c r="B47" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C47" t="s">
         <v>55</v>
       </c>
       <c r="D47" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E47" t="s">
         <v>59</v>
@@ -4384,25 +4378,25 @@
         <v>61</v>
       </c>
       <c r="G47">
-        <v>6806</v>
+        <v>7884</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>9114</v>
       </c>
       <c r="I47" t="s">
         <v>64</v>
       </c>
       <c r="J47" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="L47" s="1">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="N47" t="s">
         <v>187</v>
       </c>
       <c r="O47">
-        <v>18085066</v>
+        <v>17399340</v>
       </c>
       <c r="P47" t="s">
         <v>192</v>
@@ -4411,16 +4405,16 @@
         <v>219</v>
       </c>
       <c r="S47">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="T47" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="Z47">
         <v>0</v>
       </c>
       <c r="AF47" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AG47" t="s">
         <v>333</v>
@@ -4428,16 +4422,16 @@
     </row>
     <row r="48" spans="1:33">
       <c r="A48">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B48" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C48" t="s">
         <v>55</v>
       </c>
       <c r="D48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E48" t="s">
         <v>59</v>
@@ -4446,25 +4440,25 @@
         <v>61</v>
       </c>
       <c r="G48">
-        <v>7884</v>
+        <v>1792</v>
       </c>
       <c r="H48">
-        <v>9114</v>
+        <v>0</v>
       </c>
       <c r="I48" t="s">
         <v>64</v>
       </c>
       <c r="J48" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="L48" s="1">
-        <v>46280</v>
+        <v>46275</v>
       </c>
       <c r="N48" t="s">
         <v>187</v>
       </c>
       <c r="O48">
-        <v>17399340</v>
+        <v>16962151</v>
       </c>
       <c r="P48" t="s">
         <v>192</v>
@@ -4473,16 +4467,16 @@
         <v>219</v>
       </c>
       <c r="S48">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="T48" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="Z48">
         <v>0</v>
       </c>
       <c r="AF48" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG48" t="s">
         <v>333</v>
@@ -4490,10 +4484,10 @@
     </row>
     <row r="49" spans="1:33">
       <c r="A49">
-        <v>6404</v>
+        <v>6703</v>
       </c>
       <c r="B49" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C49" t="s">
         <v>55</v>
@@ -4526,7 +4520,7 @@
         <v>187</v>
       </c>
       <c r="O49">
-        <v>16962151</v>
+        <v>17948756</v>
       </c>
       <c r="P49" t="s">
         <v>192</v>
@@ -4538,7 +4532,7 @@
         <v>-1</v>
       </c>
       <c r="T49" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -4552,16 +4546,16 @@
     </row>
     <row r="50" spans="1:33">
       <c r="A50">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B50" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C50" t="s">
         <v>55</v>
       </c>
       <c r="D50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E50" t="s">
         <v>59</v>
@@ -4588,7 +4582,7 @@
         <v>187</v>
       </c>
       <c r="O50">
-        <v>17948756</v>
+        <v>18085143</v>
       </c>
       <c r="P50" t="s">
         <v>192</v>
@@ -4600,7 +4594,7 @@
         <v>-1</v>
       </c>
       <c r="T50" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -4614,16 +4608,16 @@
     </row>
     <row r="51" spans="1:33">
       <c r="A51">
-        <v>6704</v>
+        <v>6404</v>
       </c>
       <c r="B51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C51" t="s">
         <v>55</v>
       </c>
       <c r="D51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E51" t="s">
         <v>59</v>
@@ -4632,7 +4626,7 @@
         <v>61</v>
       </c>
       <c r="G51">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -4641,7 +4635,7 @@
         <v>64</v>
       </c>
       <c r="J51" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L51" s="1">
         <v>46275</v>
@@ -4650,7 +4644,7 @@
         <v>187</v>
       </c>
       <c r="O51">
-        <v>18085143</v>
+        <v>16962161</v>
       </c>
       <c r="P51" t="s">
         <v>192</v>
@@ -4662,7 +4656,7 @@
         <v>-1</v>
       </c>
       <c r="T51" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -4676,16 +4670,16 @@
     </row>
     <row r="52" spans="1:33">
       <c r="A52">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B52" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C52" t="s">
         <v>55</v>
       </c>
       <c r="D52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E52" t="s">
         <v>59</v>
@@ -4712,7 +4706,7 @@
         <v>187</v>
       </c>
       <c r="O52">
-        <v>16962161</v>
+        <v>16975952</v>
       </c>
       <c r="P52" t="s">
         <v>192</v>
@@ -4724,7 +4718,7 @@
         <v>-1</v>
       </c>
       <c r="T52" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -4738,16 +4732,16 @@
     </row>
     <row r="53" spans="1:33">
       <c r="A53">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B53" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C53" t="s">
         <v>55</v>
       </c>
       <c r="D53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E53" t="s">
         <v>59</v>
@@ -4774,7 +4768,7 @@
         <v>187</v>
       </c>
       <c r="O53">
-        <v>16975952</v>
+        <v>17948766</v>
       </c>
       <c r="P53" t="s">
         <v>192</v>
@@ -4786,7 +4780,7 @@
         <v>-1</v>
       </c>
       <c r="T53" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -4800,16 +4794,16 @@
     </row>
     <row r="54" spans="1:33">
       <c r="A54">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C54" t="s">
         <v>55</v>
       </c>
       <c r="D54" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E54" t="s">
         <v>59</v>
@@ -4836,7 +4830,7 @@
         <v>187</v>
       </c>
       <c r="O54">
-        <v>17948766</v>
+        <v>18085154</v>
       </c>
       <c r="P54" t="s">
         <v>192</v>
@@ -4848,7 +4842,7 @@
         <v>-1</v>
       </c>
       <c r="T54" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -4862,16 +4856,16 @@
     </row>
     <row r="55" spans="1:33">
       <c r="A55">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B55" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C55" t="s">
         <v>55</v>
       </c>
       <c r="D55" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E55" t="s">
         <v>59</v>
@@ -4898,7 +4892,7 @@
         <v>187</v>
       </c>
       <c r="O55">
-        <v>18085154</v>
+        <v>17948928</v>
       </c>
       <c r="P55" t="s">
         <v>192</v>
@@ -4910,7 +4904,7 @@
         <v>-1</v>
       </c>
       <c r="T55" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -4924,10 +4918,10 @@
     </row>
     <row r="56" spans="1:33">
       <c r="A56">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B56" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C56" t="s">
         <v>55</v>
@@ -4960,7 +4954,7 @@
         <v>187</v>
       </c>
       <c r="O56">
-        <v>17948928</v>
+        <v>18084955</v>
       </c>
       <c r="P56" t="s">
         <v>192</v>
@@ -4972,7 +4966,7 @@
         <v>-1</v>
       </c>
       <c r="T56" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -4986,10 +4980,10 @@
     </row>
     <row r="57" spans="1:33">
       <c r="A57">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B57" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C57" t="s">
         <v>55</v>
@@ -5004,25 +4998,25 @@
         <v>61</v>
       </c>
       <c r="G57">
-        <v>1793</v>
+        <v>6294</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="I57" t="s">
         <v>64</v>
       </c>
       <c r="J57" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L57" s="1">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="N57" t="s">
         <v>187</v>
       </c>
       <c r="O57">
-        <v>18084955</v>
+        <v>17948999</v>
       </c>
       <c r="P57" t="s">
         <v>192</v>
@@ -5031,16 +5025,16 @@
         <v>219</v>
       </c>
       <c r="S57">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="T57" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z57">
         <v>0</v>
       </c>
       <c r="AF57" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG57" t="s">
         <v>333</v>
@@ -5048,16 +5042,16 @@
     </row>
     <row r="58" spans="1:33">
       <c r="A58">
-        <v>6705</v>
+        <v>6486</v>
       </c>
       <c r="B58" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C58" t="s">
         <v>55</v>
       </c>
       <c r="D58" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E58" t="s">
         <v>59</v>
@@ -5066,16 +5060,16 @@
         <v>61</v>
       </c>
       <c r="G58">
-        <v>6294</v>
+        <v>11303</v>
       </c>
       <c r="H58">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I58" t="s">
         <v>64</v>
       </c>
       <c r="J58" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L58" s="1">
         <v>46279</v>
@@ -5084,7 +5078,7 @@
         <v>187</v>
       </c>
       <c r="O58">
-        <v>17948999</v>
+        <v>16976351</v>
       </c>
       <c r="P58" t="s">
         <v>192</v>
@@ -5096,7 +5090,7 @@
         <v>-5</v>
       </c>
       <c r="T58" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -5110,10 +5104,10 @@
     </row>
     <row r="59" spans="1:33">
       <c r="A59">
-        <v>6486</v>
+        <v>6949</v>
       </c>
       <c r="B59" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C59" t="s">
         <v>55</v>
@@ -5125,72 +5119,72 @@
         <v>59</v>
       </c>
       <c r="F59" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G59">
-        <v>11303</v>
+        <v>950</v>
       </c>
       <c r="H59">
         <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J59" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L59" s="1">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="N59" t="s">
         <v>187</v>
       </c>
       <c r="O59">
-        <v>16976351</v>
+        <v>18178132</v>
       </c>
       <c r="P59" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="Q59" t="s">
         <v>219</v>
       </c>
       <c r="S59">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="T59" t="s">
-        <v>225</v>
+        <v>228</v>
+      </c>
+      <c r="V59" t="s">
+        <v>248</v>
       </c>
       <c r="Z59">
         <v>0</v>
       </c>
       <c r="AF59" t="s">
-        <v>330</v>
-      </c>
-      <c r="AG59" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="60" spans="1:33">
       <c r="A60">
-        <v>6949</v>
+        <v>6628</v>
       </c>
       <c r="B60" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C60" t="s">
         <v>55</v>
       </c>
       <c r="D60" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E60" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F60" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G60">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -5199,7 +5193,7 @@
         <v>67</v>
       </c>
       <c r="J60" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L60" s="1">
         <v>46275</v>
@@ -5208,7 +5202,7 @@
         <v>187</v>
       </c>
       <c r="O60">
-        <v>18178132</v>
+        <v>16959950</v>
       </c>
       <c r="P60" t="s">
         <v>205</v>
@@ -5220,10 +5214,7 @@
         <v>-1</v>
       </c>
       <c r="T60" t="s">
-        <v>228</v>
-      </c>
-      <c r="V60" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -5234,22 +5225,22 @@
     </row>
     <row r="61" spans="1:33">
       <c r="A61">
-        <v>6628</v>
+        <v>6949</v>
       </c>
       <c r="B61" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C61" t="s">
         <v>55</v>
       </c>
       <c r="D61" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E61" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F61" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G61">
         <v>951</v>
@@ -5270,7 +5261,7 @@
         <v>187</v>
       </c>
       <c r="O61">
-        <v>16959950</v>
+        <v>18178138</v>
       </c>
       <c r="P61" t="s">
         <v>205</v>
@@ -5282,7 +5273,10 @@
         <v>-1</v>
       </c>
       <c r="T61" t="s">
-        <v>223</v>
+        <v>228</v>
+      </c>
+      <c r="V61" t="s">
+        <v>249</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -5293,10 +5287,10 @@
     </row>
     <row r="62" spans="1:33">
       <c r="A62">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B62" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C62" t="s">
         <v>55</v>
@@ -5308,19 +5302,19 @@
         <v>59</v>
       </c>
       <c r="F62" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G62">
-        <v>951</v>
+        <v>11746</v>
       </c>
       <c r="H62">
         <v>0</v>
       </c>
       <c r="I62" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J62" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L62" s="1">
         <v>46275</v>
@@ -5329,10 +5323,10 @@
         <v>187</v>
       </c>
       <c r="O62">
-        <v>18178138</v>
+        <v>17994311</v>
       </c>
       <c r="P62" t="s">
-        <v>205</v>
+        <v>59</v>
       </c>
       <c r="Q62" t="s">
         <v>219</v>
@@ -5341,30 +5335,27 @@
         <v>-1</v>
       </c>
       <c r="T62" t="s">
-        <v>228</v>
-      </c>
-      <c r="V62" t="s">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="Z62">
         <v>0</v>
       </c>
       <c r="AF62" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="63" spans="1:33">
       <c r="A63">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B63" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C63" t="s">
         <v>55</v>
       </c>
       <c r="D63" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E63" t="s">
         <v>59</v>
@@ -5391,7 +5382,7 @@
         <v>187</v>
       </c>
       <c r="O63">
-        <v>17994311</v>
+        <v>17994675</v>
       </c>
       <c r="P63" t="s">
         <v>59</v>
@@ -5403,7 +5394,7 @@
         <v>-1</v>
       </c>
       <c r="T63" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -5414,16 +5405,16 @@
     </row>
     <row r="64" spans="1:33">
       <c r="A64">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B64" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C64" t="s">
         <v>55</v>
       </c>
       <c r="D64" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E64" t="s">
         <v>59</v>
@@ -5450,7 +5441,7 @@
         <v>187</v>
       </c>
       <c r="O64">
-        <v>17994675</v>
+        <v>17994809</v>
       </c>
       <c r="P64" t="s">
         <v>59</v>
@@ -5462,7 +5453,7 @@
         <v>-1</v>
       </c>
       <c r="T64" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -5473,7 +5464,7 @@
     </row>
     <row r="65" spans="1:33">
       <c r="A65">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B65" t="s">
         <v>38</v>
@@ -5509,7 +5500,7 @@
         <v>187</v>
       </c>
       <c r="O65">
-        <v>17994809</v>
+        <v>18006051</v>
       </c>
       <c r="P65" t="s">
         <v>59</v>
@@ -5532,19 +5523,19 @@
     </row>
     <row r="66" spans="1:33">
       <c r="A66">
-        <v>6548</v>
+        <v>6628</v>
       </c>
       <c r="B66" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C66" t="s">
         <v>55</v>
       </c>
       <c r="D66" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E66" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F66" t="s">
         <v>61</v>
@@ -5568,10 +5559,10 @@
         <v>187</v>
       </c>
       <c r="O66">
-        <v>18006051</v>
+        <v>18003256</v>
       </c>
       <c r="P66" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q66" t="s">
         <v>219</v>
@@ -5580,7 +5571,7 @@
         <v>-1</v>
       </c>
       <c r="T66" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -5591,19 +5582,19 @@
     </row>
     <row r="67" spans="1:33">
       <c r="A67">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B67" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C67" t="s">
         <v>55</v>
       </c>
       <c r="D67" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E67" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F67" t="s">
         <v>61</v>
@@ -5627,10 +5618,10 @@
         <v>187</v>
       </c>
       <c r="O67">
-        <v>18003256</v>
+        <v>18004017</v>
       </c>
       <c r="P67" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q67" t="s">
         <v>219</v>
@@ -5639,7 +5630,7 @@
         <v>-1</v>
       </c>
       <c r="T67" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -5650,16 +5641,16 @@
     </row>
     <row r="68" spans="1:33">
       <c r="A68">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B68" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C68" t="s">
         <v>55</v>
       </c>
       <c r="D68" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E68" t="s">
         <v>59</v>
@@ -5686,7 +5677,7 @@
         <v>187</v>
       </c>
       <c r="O68">
-        <v>18004017</v>
+        <v>17995164</v>
       </c>
       <c r="P68" t="s">
         <v>59</v>
@@ -5698,7 +5689,7 @@
         <v>-1</v>
       </c>
       <c r="T68" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -5709,16 +5700,16 @@
     </row>
     <row r="69" spans="1:33">
       <c r="A69">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B69" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C69" t="s">
         <v>55</v>
       </c>
       <c r="D69" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E69" t="s">
         <v>59</v>
@@ -5745,7 +5736,7 @@
         <v>187</v>
       </c>
       <c r="O69">
-        <v>17995164</v>
+        <v>18004028</v>
       </c>
       <c r="P69" t="s">
         <v>59</v>
@@ -5757,7 +5748,7 @@
         <v>-1</v>
       </c>
       <c r="T69" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -5768,16 +5759,16 @@
     </row>
     <row r="70" spans="1:33">
       <c r="A70">
-        <v>6705</v>
+        <v>6548</v>
       </c>
       <c r="B70" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C70" t="s">
         <v>55</v>
       </c>
       <c r="D70" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E70" t="s">
         <v>59</v>
@@ -5786,51 +5777,60 @@
         <v>61</v>
       </c>
       <c r="G70">
-        <v>11746</v>
+        <v>11299</v>
       </c>
       <c r="H70">
         <v>0</v>
       </c>
       <c r="I70" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J70" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L70" s="1">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="N70" t="s">
         <v>187</v>
       </c>
       <c r="O70">
-        <v>18004028</v>
+        <v>17968041</v>
       </c>
       <c r="P70" t="s">
-        <v>59</v>
+        <v>206</v>
       </c>
       <c r="Q70" t="s">
-        <v>219</v>
+        <v>220</v>
+      </c>
+      <c r="R70" s="1">
+        <v>46267.75233784723</v>
       </c>
       <c r="S70">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="T70" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="Z70">
         <v>0</v>
+      </c>
+      <c r="AA70" t="s">
+        <v>318</v>
       </c>
       <c r="AF70" t="s">
         <v>330</v>
       </c>
+      <c r="AG70" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="71" spans="1:33">
       <c r="A71">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B71" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C71" t="s">
         <v>55</v>
@@ -5839,7 +5839,7 @@
         <v>57</v>
       </c>
       <c r="E71" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F71" t="s">
         <v>61</v>
@@ -5863,22 +5863,22 @@
         <v>187</v>
       </c>
       <c r="O71">
-        <v>17968041</v>
+        <v>17042643</v>
       </c>
       <c r="P71" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q71" t="s">
         <v>220</v>
       </c>
       <c r="R71" s="1">
-        <v>46267.75233784723</v>
+        <v>46267.75233927083</v>
       </c>
       <c r="S71">
         <v>-5</v>
       </c>
       <c r="T71" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -5890,21 +5890,21 @@
         <v>330</v>
       </c>
       <c r="AG71" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:33">
       <c r="A72">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B72" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C72" t="s">
         <v>55</v>
       </c>
       <c r="D72" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E72" t="s">
         <v>60</v>
@@ -5931,7 +5931,7 @@
         <v>187</v>
       </c>
       <c r="O72">
-        <v>17042643</v>
+        <v>16960110</v>
       </c>
       <c r="P72" t="s">
         <v>207</v>
@@ -5940,7 +5940,7 @@
         <v>220</v>
       </c>
       <c r="R72" s="1">
-        <v>46267.75233927083</v>
+        <v>46267.7523394676</v>
       </c>
       <c r="S72">
         <v>-5</v>
@@ -5963,10 +5963,10 @@
     </row>
     <row r="73" spans="1:33">
       <c r="A73">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B73" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C73" t="s">
         <v>55</v>
@@ -5975,10 +5975,10 @@
         <v>58</v>
       </c>
       <c r="E73" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F73" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G73">
         <v>11299</v>
@@ -5999,22 +5999,22 @@
         <v>187</v>
       </c>
       <c r="O73">
-        <v>16960110</v>
+        <v>18163699</v>
       </c>
       <c r="P73" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q73" t="s">
         <v>220</v>
       </c>
       <c r="R73" s="1">
-        <v>46267.7523394676</v>
+        <v>46267.75234278935</v>
       </c>
       <c r="S73">
         <v>-5</v>
       </c>
       <c r="T73" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -6031,16 +6031,16 @@
     </row>
     <row r="74" spans="1:33">
       <c r="A74">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B74" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C74" t="s">
         <v>55</v>
       </c>
       <c r="D74" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E74" t="s">
         <v>59</v>
@@ -6067,22 +6067,22 @@
         <v>187</v>
       </c>
       <c r="O74">
-        <v>18163699</v>
+        <v>18178308</v>
       </c>
       <c r="P74" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q74" t="s">
         <v>220</v>
       </c>
       <c r="R74" s="1">
-        <v>46267.75234278935</v>
+        <v>46267.75234309028</v>
       </c>
       <c r="S74">
         <v>-5</v>
       </c>
       <c r="T74" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -6094,21 +6094,21 @@
         <v>330</v>
       </c>
       <c r="AG74" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:33">
       <c r="A75">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B75" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C75" t="s">
         <v>55</v>
       </c>
       <c r="D75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E75" t="s">
         <v>59</v>
@@ -6135,22 +6135,22 @@
         <v>187</v>
       </c>
       <c r="O75">
-        <v>18178308</v>
+        <v>18187978</v>
       </c>
       <c r="P75" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q75" t="s">
         <v>220</v>
       </c>
       <c r="R75" s="1">
-        <v>46267.75234309028</v>
+        <v>46267.75234383102</v>
       </c>
       <c r="S75">
         <v>-5</v>
       </c>
       <c r="T75" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -6162,15 +6162,15 @@
         <v>330</v>
       </c>
       <c r="AG75" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="76" spans="1:33">
       <c r="A76">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B76" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C76" t="s">
         <v>55</v>
@@ -6203,7 +6203,7 @@
         <v>187</v>
       </c>
       <c r="O76">
-        <v>18187978</v>
+        <v>18241249</v>
       </c>
       <c r="P76" t="s">
         <v>209</v>
@@ -6212,7 +6212,7 @@
         <v>220</v>
       </c>
       <c r="R76" s="1">
-        <v>46267.75234383102</v>
+        <v>46267.75234424769</v>
       </c>
       <c r="S76">
         <v>-5</v>
@@ -6235,31 +6235,31 @@
     </row>
     <row r="77" spans="1:33">
       <c r="A77">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B77" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C77" t="s">
         <v>55</v>
       </c>
       <c r="D77" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E77" t="s">
         <v>59</v>
       </c>
       <c r="F77" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G77">
-        <v>11299</v>
+        <v>11297</v>
       </c>
       <c r="H77">
         <v>0</v>
       </c>
       <c r="I77" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J77" t="s">
         <v>89</v>
@@ -6271,22 +6271,22 @@
         <v>187</v>
       </c>
       <c r="O77">
-        <v>18241249</v>
+        <v>17399444</v>
       </c>
       <c r="P77" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q77" t="s">
         <v>220</v>
       </c>
       <c r="R77" s="1">
-        <v>46267.75234424769</v>
+        <v>46267.75231010417</v>
       </c>
       <c r="S77">
         <v>-5</v>
       </c>
       <c r="T77" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -6298,15 +6298,15 @@
         <v>330</v>
       </c>
       <c r="AG77" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:33">
       <c r="A78">
-        <v>5417</v>
+        <v>6704</v>
       </c>
       <c r="B78" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C78" t="s">
         <v>55</v>
@@ -6339,22 +6339,22 @@
         <v>187</v>
       </c>
       <c r="O78">
-        <v>17399444</v>
+        <v>17955434</v>
       </c>
       <c r="P78" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q78" t="s">
         <v>220</v>
       </c>
       <c r="R78" s="1">
-        <v>46267.75231010417</v>
+        <v>46267.75234059028</v>
       </c>
       <c r="S78">
         <v>-5</v>
       </c>
       <c r="T78" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -6366,21 +6366,21 @@
         <v>330</v>
       </c>
       <c r="AG78" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:33">
       <c r="A79">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B79" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C79" t="s">
         <v>55</v>
       </c>
       <c r="D79" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E79" t="s">
         <v>59</v>
@@ -6407,7 +6407,7 @@
         <v>187</v>
       </c>
       <c r="O79">
-        <v>17955434</v>
+        <v>17955274</v>
       </c>
       <c r="P79" t="s">
         <v>211</v>
@@ -6416,13 +6416,13 @@
         <v>220</v>
       </c>
       <c r="R79" s="1">
-        <v>46267.75234059028</v>
+        <v>46267.7523409375</v>
       </c>
       <c r="S79">
         <v>-5</v>
       </c>
       <c r="T79" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -6439,10 +6439,10 @@
     </row>
     <row r="80" spans="1:33">
       <c r="A80">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B80" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C80" t="s">
         <v>55</v>
@@ -6475,7 +6475,7 @@
         <v>187</v>
       </c>
       <c r="O80">
-        <v>17955274</v>
+        <v>18056832</v>
       </c>
       <c r="P80" t="s">
         <v>211</v>
@@ -6484,13 +6484,13 @@
         <v>220</v>
       </c>
       <c r="R80" s="1">
-        <v>46267.7523409375</v>
+        <v>46267.75234170139</v>
       </c>
       <c r="S80">
         <v>-5</v>
       </c>
       <c r="T80" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -6507,10 +6507,10 @@
     </row>
     <row r="81" spans="1:33">
       <c r="A81">
-        <v>6779</v>
+        <v>6628</v>
       </c>
       <c r="B81" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C81" t="s">
         <v>55</v>
@@ -6519,66 +6519,72 @@
         <v>58</v>
       </c>
       <c r="E81" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F81" t="s">
         <v>61</v>
       </c>
       <c r="G81">
-        <v>11297</v>
+        <v>5859</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I81" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J81" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L81" s="1">
-        <v>46279</v>
+        <v>46269</v>
+      </c>
+      <c r="M81" t="s">
+        <v>180</v>
       </c>
       <c r="N81" t="s">
         <v>187</v>
       </c>
       <c r="O81">
-        <v>18056832</v>
+        <v>18052440</v>
       </c>
       <c r="P81" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="Q81" t="s">
         <v>220</v>
       </c>
       <c r="R81" s="1">
-        <v>46267.75234170139</v>
+        <v>46268.37896984954</v>
       </c>
       <c r="S81">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="T81" t="s">
-        <v>227</v>
+        <v>223</v>
+      </c>
+      <c r="V81" t="s">
+        <v>250</v>
       </c>
       <c r="Z81">
         <v>0</v>
       </c>
       <c r="AA81" t="s">
-        <v>318</v>
+        <v>194</v>
       </c>
       <c r="AF81" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG81" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="82" spans="1:33">
       <c r="A82">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B82" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C82" t="s">
         <v>55</v>
@@ -6587,10 +6593,10 @@
         <v>58</v>
       </c>
       <c r="E82" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F82" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G82">
         <v>5859</v>
@@ -6607,58 +6613,52 @@
       <c r="L82" s="1">
         <v>46269</v>
       </c>
-      <c r="M82" t="s">
-        <v>180</v>
-      </c>
       <c r="N82" t="s">
         <v>187</v>
       </c>
       <c r="O82">
-        <v>18052440</v>
+        <v>18179096</v>
       </c>
       <c r="P82" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q82" t="s">
         <v>220</v>
       </c>
       <c r="R82" s="1">
-        <v>46268.37896984954</v>
+        <v>46269.71652982639</v>
       </c>
       <c r="S82">
         <v>5</v>
       </c>
       <c r="T82" t="s">
-        <v>223</v>
-      </c>
-      <c r="V82" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="Z82">
         <v>0</v>
       </c>
       <c r="AA82" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AF82" t="s">
         <v>331</v>
       </c>
       <c r="AG82" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="83" spans="1:33">
       <c r="A83">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B83" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C83" t="s">
         <v>55</v>
       </c>
       <c r="D83" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E83" t="s">
         <v>59</v>
@@ -6676,37 +6676,43 @@
         <v>65</v>
       </c>
       <c r="J83" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L83" s="1">
-        <v>46269</v>
+        <v>46273</v>
+      </c>
+      <c r="M83" t="s">
+        <v>181</v>
       </c>
       <c r="N83" t="s">
         <v>187</v>
       </c>
       <c r="O83">
-        <v>18179096</v>
+        <v>18233928</v>
       </c>
       <c r="P83" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q83" t="s">
         <v>220</v>
       </c>
       <c r="R83" s="1">
-        <v>46269.71652982639</v>
+        <v>46269.71069613426</v>
       </c>
       <c r="S83">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T83" t="s">
-        <v>224</v>
+        <v>228</v>
+      </c>
+      <c r="V83" t="s">
+        <v>251</v>
       </c>
       <c r="Z83">
         <v>0</v>
       </c>
       <c r="AA83" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AF83" t="s">
         <v>331</v>
@@ -6717,10 +6723,10 @@
     </row>
     <row r="84" spans="1:33">
       <c r="A84">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B84" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C84" t="s">
         <v>55</v>
@@ -6732,46 +6738,46 @@
         <v>59</v>
       </c>
       <c r="F84" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G84">
-        <v>5859</v>
+        <v>11542</v>
       </c>
       <c r="H84">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I84" t="s">
         <v>65</v>
       </c>
       <c r="J84" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L84" s="1">
-        <v>46273</v>
+        <v>46266</v>
       </c>
       <c r="M84" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N84" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O84">
-        <v>18233928</v>
+        <v>18248555</v>
       </c>
       <c r="P84" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="Q84" t="s">
         <v>220</v>
       </c>
       <c r="R84" s="1">
-        <v>46269.71069613426</v>
+        <v>46267.55838734953</v>
       </c>
       <c r="S84">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T84" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="V84" t="s">
         <v>252</v>
@@ -6780,21 +6786,18 @@
         <v>0</v>
       </c>
       <c r="AA84" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="AF84" t="s">
-        <v>331</v>
-      </c>
-      <c r="AG84" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="85" spans="1:33">
       <c r="A85">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B85" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C85" t="s">
         <v>55</v>
@@ -6823,46 +6826,43 @@
       <c r="L85" s="1">
         <v>46266</v>
       </c>
-      <c r="M85" t="s">
-        <v>182</v>
-      </c>
       <c r="N85" t="s">
         <v>188</v>
       </c>
       <c r="O85">
-        <v>18248555</v>
+        <v>16976372</v>
       </c>
       <c r="P85" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q85" t="s">
         <v>220</v>
       </c>
       <c r="R85" s="1">
-        <v>46267.55838734953</v>
+        <v>46258.63662372685</v>
       </c>
       <c r="S85">
         <v>8</v>
       </c>
       <c r="T85" t="s">
-        <v>222</v>
-      </c>
-      <c r="V85" t="s">
-        <v>253</v>
+        <v>224</v>
       </c>
       <c r="Z85">
         <v>0</v>
       </c>
       <c r="AA85" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AF85" t="s">
         <v>332</v>
       </c>
+      <c r="AG85" t="s">
+        <v>334</v>
+      </c>
     </row>
     <row r="86" spans="1:33">
       <c r="A86">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B86" t="s">
         <v>38</v>
@@ -6894,20 +6894,23 @@
       <c r="L86" s="1">
         <v>46266</v>
       </c>
+      <c r="M86" t="s">
+        <v>183</v>
+      </c>
       <c r="N86" t="s">
         <v>188</v>
       </c>
       <c r="O86">
-        <v>16976372</v>
+        <v>17222968</v>
       </c>
       <c r="P86" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q86" t="s">
         <v>220</v>
       </c>
       <c r="R86" s="1">
-        <v>46258.63662372685</v>
+        <v>46259.74277608797</v>
       </c>
       <c r="S86">
         <v>8</v>
@@ -6915,11 +6918,14 @@
       <c r="T86" t="s">
         <v>225</v>
       </c>
+      <c r="V86" t="s">
+        <v>253</v>
+      </c>
       <c r="Z86">
         <v>0</v>
       </c>
       <c r="AA86" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF86" t="s">
         <v>332</v>
@@ -6930,16 +6936,16 @@
     </row>
     <row r="87" spans="1:33">
       <c r="A87">
-        <v>6548</v>
+        <v>6703</v>
       </c>
       <c r="B87" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C87" t="s">
         <v>55</v>
       </c>
       <c r="D87" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E87" t="s">
         <v>59</v>
@@ -6963,13 +6969,13 @@
         <v>46266</v>
       </c>
       <c r="M87" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N87" t="s">
         <v>188</v>
       </c>
       <c r="O87">
-        <v>17222968</v>
+        <v>18077185</v>
       </c>
       <c r="P87" t="s">
         <v>196</v>
@@ -6978,13 +6984,13 @@
         <v>220</v>
       </c>
       <c r="R87" s="1">
-        <v>46259.74277608797</v>
+        <v>46258.44838504629</v>
       </c>
       <c r="S87">
         <v>8</v>
       </c>
       <c r="T87" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="V87" t="s">
         <v>254</v>
@@ -7004,22 +7010,22 @@
     </row>
     <row r="88" spans="1:33">
       <c r="A88">
-        <v>6703</v>
+        <v>6949</v>
       </c>
       <c r="B88" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C88" t="s">
         <v>55</v>
       </c>
       <c r="D88" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E88" t="s">
         <v>59</v>
       </c>
       <c r="F88" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G88">
         <v>11542</v>
@@ -7036,67 +7042,61 @@
       <c r="L88" s="1">
         <v>46266</v>
       </c>
-      <c r="M88" t="s">
-        <v>184</v>
-      </c>
       <c r="N88" t="s">
         <v>188</v>
       </c>
       <c r="O88">
-        <v>18077185</v>
+        <v>18190471</v>
       </c>
       <c r="P88" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q88" t="s">
         <v>220</v>
       </c>
       <c r="R88" s="1">
-        <v>46258.44838504629</v>
+        <v>46265.43840615741</v>
       </c>
       <c r="S88">
         <v>8</v>
       </c>
       <c r="T88" t="s">
-        <v>221</v>
-      </c>
-      <c r="V88" t="s">
-        <v>255</v>
+        <v>228</v>
       </c>
       <c r="Z88">
         <v>0</v>
       </c>
       <c r="AA88" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AF88" t="s">
         <v>332</v>
       </c>
       <c r="AG88" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="89" spans="1:33">
       <c r="A89">
-        <v>6949</v>
+        <v>6404</v>
       </c>
       <c r="B89" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C89" t="s">
         <v>55</v>
       </c>
       <c r="D89" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E89" t="s">
         <v>59</v>
       </c>
       <c r="F89" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G89">
-        <v>11542</v>
+        <v>9746</v>
       </c>
       <c r="H89">
         <v>0</v>
@@ -7105,57 +7105,63 @@
         <v>65</v>
       </c>
       <c r="J89" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="L89" s="1">
-        <v>46266</v>
+        <v>46275</v>
+      </c>
+      <c r="M89" t="s">
+        <v>177</v>
       </c>
       <c r="N89" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O89">
-        <v>18190471</v>
+        <v>16962424</v>
       </c>
       <c r="P89" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="Q89" t="s">
         <v>220</v>
       </c>
       <c r="R89" s="1">
-        <v>46265.43840615741</v>
+        <v>46273.59003707176</v>
       </c>
       <c r="S89">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="T89" t="s">
-        <v>228</v>
+        <v>230</v>
+      </c>
+      <c r="V89" t="s">
+        <v>255</v>
       </c>
       <c r="Z89">
         <v>0</v>
       </c>
       <c r="AA89" t="s">
-        <v>199</v>
+        <v>319</v>
       </c>
       <c r="AF89" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AG89" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
     </row>
     <row r="90" spans="1:33">
       <c r="A90">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B90" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C90" t="s">
         <v>55</v>
       </c>
       <c r="D90" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E90" t="s">
         <v>59</v>
@@ -7179,48 +7185,48 @@
         <v>46275</v>
       </c>
       <c r="M90" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N90" t="s">
         <v>187</v>
       </c>
       <c r="O90">
-        <v>16962424</v>
+        <v>16976300</v>
       </c>
       <c r="P90" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="Q90" t="s">
         <v>220</v>
       </c>
       <c r="R90" s="1">
-        <v>46273.59003707176</v>
+        <v>46274.47210818287</v>
       </c>
       <c r="S90">
         <v>-1</v>
       </c>
       <c r="T90" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="V90" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="Z90">
         <v>0</v>
       </c>
       <c r="AA90" t="s">
-        <v>319</v>
+        <v>194</v>
       </c>
       <c r="AF90" t="s">
         <v>330</v>
       </c>
       <c r="AG90" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
     </row>
     <row r="91" spans="1:33">
       <c r="A91">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B91" t="s">
         <v>38</v>
@@ -7253,22 +7259,22 @@
         <v>46275</v>
       </c>
       <c r="M91" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="N91" t="s">
         <v>187</v>
       </c>
       <c r="O91">
-        <v>16976300</v>
+        <v>17222915</v>
       </c>
       <c r="P91" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q91" t="s">
         <v>220</v>
       </c>
       <c r="R91" s="1">
-        <v>46274.47210818287</v>
+        <v>46268.74069754629</v>
       </c>
       <c r="S91">
         <v>-1</v>
@@ -7277,13 +7283,13 @@
         <v>225</v>
       </c>
       <c r="V91" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="Z91">
         <v>0</v>
       </c>
       <c r="AA91" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF91" t="s">
         <v>330</v>
@@ -7294,16 +7300,16 @@
     </row>
     <row r="92" spans="1:33">
       <c r="A92">
-        <v>6548</v>
+        <v>6703</v>
       </c>
       <c r="B92" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C92" t="s">
         <v>55</v>
       </c>
       <c r="D92" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E92" t="s">
         <v>59</v>
@@ -7327,13 +7333,13 @@
         <v>46275</v>
       </c>
       <c r="M92" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N92" t="s">
         <v>187</v>
       </c>
       <c r="O92">
-        <v>17222915</v>
+        <v>18077163</v>
       </c>
       <c r="P92" t="s">
         <v>196</v>
@@ -7342,13 +7348,13 @@
         <v>220</v>
       </c>
       <c r="R92" s="1">
-        <v>46268.74069754629</v>
+        <v>46273.45940115741</v>
       </c>
       <c r="S92">
         <v>-1</v>
       </c>
       <c r="T92" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="V92" t="s">
         <v>257</v>
@@ -7368,16 +7374,16 @@
     </row>
     <row r="93" spans="1:33">
       <c r="A93">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B93" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C93" t="s">
         <v>55</v>
       </c>
       <c r="D93" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E93" t="s">
         <v>59</v>
@@ -7401,13 +7407,13 @@
         <v>46275</v>
       </c>
       <c r="M93" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="N93" t="s">
         <v>187</v>
       </c>
       <c r="O93">
-        <v>18077163</v>
+        <v>18090250</v>
       </c>
       <c r="P93" t="s">
         <v>197</v>
@@ -7416,13 +7422,13 @@
         <v>220</v>
       </c>
       <c r="R93" s="1">
-        <v>46273.45940115741</v>
+        <v>46274.48792050926</v>
       </c>
       <c r="S93">
         <v>-1</v>
       </c>
       <c r="T93" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="V93" t="s">
         <v>258</v>
@@ -7437,12 +7443,12 @@
         <v>330</v>
       </c>
       <c r="AG93" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
     </row>
     <row r="94" spans="1:33">
       <c r="A94">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B94" t="s">
         <v>40</v>
@@ -7457,7 +7463,7 @@
         <v>59</v>
       </c>
       <c r="F94" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G94">
         <v>9746</v>
@@ -7481,7 +7487,7 @@
         <v>187</v>
       </c>
       <c r="O94">
-        <v>18090250</v>
+        <v>18179154</v>
       </c>
       <c r="P94" t="s">
         <v>198</v>
@@ -7490,7 +7496,7 @@
         <v>220</v>
       </c>
       <c r="R94" s="1">
-        <v>46274.48792050926</v>
+        <v>46274.588374375</v>
       </c>
       <c r="S94">
         <v>-1</v>
@@ -7511,7 +7517,7 @@
         <v>330</v>
       </c>
       <c r="AG94" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
     </row>
     <row r="95" spans="1:33">
@@ -7658,7 +7664,7 @@
         <v>6486</v>
       </c>
       <c r="B97" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C97" t="s">
         <v>55</v>
@@ -7709,7 +7715,7 @@
         <v>5</v>
       </c>
       <c r="T97" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V97" t="s">
         <v>261</v>
@@ -7919,7 +7925,7 @@
         <v>18077132</v>
       </c>
       <c r="P100" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q100" t="s">
         <v>220</v>
@@ -7940,7 +7946,7 @@
         <v>0</v>
       </c>
       <c r="AA100" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF100" t="s">
         <v>332</v>
@@ -7954,7 +7960,7 @@
         <v>6779</v>
       </c>
       <c r="B101" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C101" t="s">
         <v>55</v>
@@ -7993,7 +7999,7 @@
         <v>18090219</v>
       </c>
       <c r="P101" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q101" t="s">
         <v>220</v>
@@ -8005,7 +8011,7 @@
         <v>5</v>
       </c>
       <c r="T101" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="V101" t="s">
         <v>265</v>
@@ -8014,7 +8020,7 @@
         <v>0</v>
       </c>
       <c r="AA101" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AF101" t="s">
         <v>332</v>
@@ -8028,7 +8034,7 @@
         <v>6945</v>
       </c>
       <c r="B102" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C102" t="s">
         <v>55</v>
@@ -8067,7 +8073,7 @@
         <v>18179132</v>
       </c>
       <c r="P102" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q102" t="s">
         <v>220</v>
@@ -8079,7 +8085,7 @@
         <v>5</v>
       </c>
       <c r="T102" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="V102" t="s">
         <v>266</v>
@@ -8088,7 +8094,7 @@
         <v>0</v>
       </c>
       <c r="AA102" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF102" t="s">
         <v>332</v>
@@ -8241,7 +8247,7 @@
         <v>6486</v>
       </c>
       <c r="B105" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C105" t="s">
         <v>55</v>
@@ -8289,7 +8295,7 @@
         <v>1</v>
       </c>
       <c r="T105" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z105">
         <v>0</v>
@@ -8481,7 +8487,7 @@
         <v>18077091</v>
       </c>
       <c r="P108" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q108" t="s">
         <v>220</v>
@@ -8499,7 +8505,7 @@
         <v>0</v>
       </c>
       <c r="AA108" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF108" t="s">
         <v>330</v>
@@ -8513,7 +8519,7 @@
         <v>6779</v>
       </c>
       <c r="B109" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C109" t="s">
         <v>55</v>
@@ -8549,7 +8555,7 @@
         <v>18090158</v>
       </c>
       <c r="P109" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q109" t="s">
         <v>220</v>
@@ -8561,13 +8567,13 @@
         <v>1</v>
       </c>
       <c r="T109" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z109">
         <v>0</v>
       </c>
       <c r="AA109" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AF109" t="s">
         <v>330</v>
@@ -8581,7 +8587,7 @@
         <v>6945</v>
       </c>
       <c r="B110" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C110" t="s">
         <v>55</v>
@@ -8620,7 +8626,7 @@
         <v>18179089</v>
       </c>
       <c r="P110" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q110" t="s">
         <v>220</v>
@@ -8632,7 +8638,7 @@
         <v>1</v>
       </c>
       <c r="T110" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="V110" t="s">
         <v>268</v>
@@ -8641,7 +8647,7 @@
         <v>0</v>
       </c>
       <c r="AA110" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF110" t="s">
         <v>330</v>
@@ -8788,7 +8794,7 @@
         <v>6486</v>
       </c>
       <c r="B113" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C113" t="s">
         <v>55</v>
@@ -8836,7 +8842,7 @@
         <v>8</v>
       </c>
       <c r="T113" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z113">
         <v>0</v>
@@ -8856,7 +8862,7 @@
         <v>6548</v>
       </c>
       <c r="B114" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C114" t="s">
         <v>55</v>
@@ -8895,7 +8901,7 @@
         <v>17222948</v>
       </c>
       <c r="P114" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q114" t="s">
         <v>220</v>
@@ -8907,16 +8913,16 @@
         <v>8</v>
       </c>
       <c r="T114" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="V114" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Z114">
         <v>0</v>
       </c>
       <c r="AA114" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AF114" t="s">
         <v>332</v>
@@ -8969,7 +8975,7 @@
         <v>18077175</v>
       </c>
       <c r="P115" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q115" t="s">
         <v>220</v>
@@ -8984,13 +8990,13 @@
         <v>221</v>
       </c>
       <c r="V115" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Z115">
         <v>0</v>
       </c>
       <c r="AA115" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF115" t="s">
         <v>332</v>
@@ -9137,7 +9143,7 @@
         <v>6486</v>
       </c>
       <c r="B118" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C118" t="s">
         <v>55</v>
@@ -9185,7 +9191,7 @@
         <v>1</v>
       </c>
       <c r="T118" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z118">
         <v>0</v>
@@ -9205,7 +9211,7 @@
         <v>6548</v>
       </c>
       <c r="B119" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C119" t="s">
         <v>55</v>
@@ -9241,7 +9247,7 @@
         <v>17222551</v>
       </c>
       <c r="P119" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q119" t="s">
         <v>220</v>
@@ -9253,13 +9259,13 @@
         <v>1</v>
       </c>
       <c r="T119" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z119">
         <v>0</v>
       </c>
       <c r="AA119" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AF119" t="s">
         <v>330</v>
@@ -9409,7 +9415,7 @@
         <v>6779</v>
       </c>
       <c r="B122" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C122" t="s">
         <v>55</v>
@@ -9445,7 +9451,7 @@
         <v>18090124</v>
       </c>
       <c r="P122" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q122" t="s">
         <v>220</v>
@@ -9457,13 +9463,13 @@
         <v>1</v>
       </c>
       <c r="T122" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z122">
         <v>0</v>
       </c>
       <c r="AA122" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AF122" t="s">
         <v>330</v>
@@ -9477,7 +9483,7 @@
         <v>6945</v>
       </c>
       <c r="B123" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C123" t="s">
         <v>55</v>
@@ -9513,7 +9519,7 @@
         <v>18179061</v>
       </c>
       <c r="P123" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q123" t="s">
         <v>220</v>
@@ -9525,13 +9531,13 @@
         <v>1</v>
       </c>
       <c r="T123" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z123">
         <v>0</v>
       </c>
       <c r="AA123" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF123" t="s">
         <v>330</v>
@@ -9613,7 +9619,7 @@
         <v>6486</v>
       </c>
       <c r="B125" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C125" t="s">
         <v>55</v>
@@ -9664,7 +9670,7 @@
         <v>8</v>
       </c>
       <c r="T125" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V125" t="s">
         <v>269</v>
@@ -9874,7 +9880,7 @@
         <v>18195915</v>
       </c>
       <c r="P128" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q128" t="s">
         <v>220</v>
@@ -9895,7 +9901,7 @@
         <v>0</v>
       </c>
       <c r="AA128" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF128" t="s">
         <v>330</v>
@@ -9909,7 +9915,7 @@
         <v>6548</v>
       </c>
       <c r="B129" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C129" t="s">
         <v>55</v>
@@ -9945,7 +9951,7 @@
         <v>18158843</v>
       </c>
       <c r="P129" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q129" t="s">
         <v>220</v>
@@ -9957,13 +9963,13 @@
         <v>7</v>
       </c>
       <c r="T129" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z129">
         <v>0</v>
       </c>
       <c r="AA129" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AF129" t="s">
         <v>330</v>
@@ -10122,7 +10128,7 @@
         <v>6486</v>
       </c>
       <c r="B132" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C132" t="s">
         <v>55</v>
@@ -10173,7 +10179,7 @@
         <v>1</v>
       </c>
       <c r="T132" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V132" t="s">
         <v>272</v>
@@ -10383,7 +10389,7 @@
         <v>18077142</v>
       </c>
       <c r="P135" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q135" t="s">
         <v>220</v>
@@ -10404,7 +10410,7 @@
         <v>0</v>
       </c>
       <c r="AA135" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF135" t="s">
         <v>332</v>
@@ -10418,7 +10424,7 @@
         <v>6779</v>
       </c>
       <c r="B136" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C136" t="s">
         <v>55</v>
@@ -10457,7 +10463,7 @@
         <v>18090229</v>
       </c>
       <c r="P136" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q136" t="s">
         <v>220</v>
@@ -10469,7 +10475,7 @@
         <v>1</v>
       </c>
       <c r="T136" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="V136" t="s">
         <v>272</v>
@@ -10478,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="AA136" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AF136" t="s">
         <v>332</v>
@@ -10492,7 +10498,7 @@
         <v>6945</v>
       </c>
       <c r="B137" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C137" t="s">
         <v>55</v>
@@ -10531,7 +10537,7 @@
         <v>18179139</v>
       </c>
       <c r="P137" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q137" t="s">
         <v>220</v>
@@ -10543,7 +10549,7 @@
         <v>1</v>
       </c>
       <c r="T137" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="V137" t="s">
         <v>272</v>
@@ -10552,7 +10558,7 @@
         <v>0</v>
       </c>
       <c r="AA137" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF137" t="s">
         <v>332</v>
@@ -10640,7 +10646,7 @@
         <v>6486</v>
       </c>
       <c r="B139" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C139" t="s">
         <v>55</v>
@@ -10691,7 +10697,7 @@
         <v>1</v>
       </c>
       <c r="T139" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V139" t="s">
         <v>274</v>
@@ -10847,7 +10853,7 @@
         <v>6486</v>
       </c>
       <c r="B142" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C142" t="s">
         <v>55</v>
@@ -10895,7 +10901,7 @@
         <v>1</v>
       </c>
       <c r="T142" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z142">
         <v>0</v>
@@ -11087,7 +11093,7 @@
         <v>18077152</v>
       </c>
       <c r="P145" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q145" t="s">
         <v>220</v>
@@ -11105,7 +11111,7 @@
         <v>0</v>
       </c>
       <c r="AA145" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF145" t="s">
         <v>330</v>
@@ -11119,7 +11125,7 @@
         <v>6779</v>
       </c>
       <c r="B146" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C146" t="s">
         <v>55</v>
@@ -11155,7 +11161,7 @@
         <v>18090239</v>
       </c>
       <c r="P146" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q146" t="s">
         <v>220</v>
@@ -11167,13 +11173,13 @@
         <v>1</v>
       </c>
       <c r="T146" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z146">
         <v>0</v>
       </c>
       <c r="AA146" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AF146" t="s">
         <v>330</v>
@@ -11187,7 +11193,7 @@
         <v>6945</v>
       </c>
       <c r="B147" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C147" t="s">
         <v>55</v>
@@ -11223,7 +11229,7 @@
         <v>18179146</v>
       </c>
       <c r="P147" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q147" t="s">
         <v>220</v>
@@ -11235,13 +11241,13 @@
         <v>1</v>
       </c>
       <c r="T147" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z147">
         <v>0</v>
       </c>
       <c r="AA147" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF147" t="s">
         <v>330</v>
@@ -11527,7 +11533,7 @@
         <v>6548</v>
       </c>
       <c r="B152" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C152" t="s">
         <v>55</v>
@@ -11575,7 +11581,7 @@
         <v>7</v>
       </c>
       <c r="T152" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z152">
         <v>0</v>
@@ -11663,7 +11669,7 @@
         <v>6945</v>
       </c>
       <c r="B154" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C154" t="s">
         <v>55</v>
@@ -11714,7 +11720,7 @@
         <v>6</v>
       </c>
       <c r="T154" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="V154" t="s">
         <v>278</v>
@@ -11802,7 +11808,7 @@
         <v>6548</v>
       </c>
       <c r="B156" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C156" t="s">
         <v>55</v>
@@ -11850,7 +11856,7 @@
         <v>7</v>
       </c>
       <c r="T156" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z156">
         <v>0</v>
@@ -12006,7 +12012,7 @@
         <v>6945</v>
       </c>
       <c r="B159" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C159" t="s">
         <v>55</v>
@@ -12054,7 +12060,7 @@
         <v>6</v>
       </c>
       <c r="T159" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z159">
         <v>0</v>
@@ -12139,7 +12145,7 @@
         <v>6548</v>
       </c>
       <c r="B161" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C161" t="s">
         <v>55</v>
@@ -12187,7 +12193,7 @@
         <v>7</v>
       </c>
       <c r="T161" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z161">
         <v>0</v>
@@ -12343,7 +12349,7 @@
         <v>6945</v>
       </c>
       <c r="B164" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C164" t="s">
         <v>55</v>
@@ -12391,7 +12397,7 @@
         <v>6</v>
       </c>
       <c r="T164" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z164">
         <v>0</v>
@@ -12476,7 +12482,7 @@
         <v>6548</v>
       </c>
       <c r="B166" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C166" t="s">
         <v>55</v>
@@ -12524,7 +12530,7 @@
         <v>6</v>
       </c>
       <c r="T166" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z166">
         <v>0</v>
@@ -12754,7 +12760,7 @@
         <v>6945</v>
       </c>
       <c r="B170" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C170" t="s">
         <v>55</v>
@@ -12802,7 +12808,7 @@
         <v>6</v>
       </c>
       <c r="T170" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z170">
         <v>0</v>
@@ -12819,7 +12825,7 @@
         <v>6548</v>
       </c>
       <c r="B171" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C171" t="s">
         <v>55</v>
@@ -12867,7 +12873,7 @@
         <v>7</v>
       </c>
       <c r="T171" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z171">
         <v>0</v>
@@ -13023,7 +13029,7 @@
         <v>6945</v>
       </c>
       <c r="B174" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C174" t="s">
         <v>55</v>
@@ -13071,7 +13077,7 @@
         <v>6</v>
       </c>
       <c r="T174" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z174">
         <v>0</v>
@@ -13224,7 +13230,7 @@
         <v>6548</v>
       </c>
       <c r="B177" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C177" t="s">
         <v>55</v>
@@ -13272,7 +13278,7 @@
         <v>7</v>
       </c>
       <c r="T177" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z177">
         <v>0</v>
@@ -13292,7 +13298,7 @@
         <v>6945</v>
       </c>
       <c r="B178" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C178" t="s">
         <v>55</v>
@@ -13340,7 +13346,7 @@
         <v>6</v>
       </c>
       <c r="T178" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z178">
         <v>0</v>
@@ -13425,7 +13431,7 @@
         <v>6945</v>
       </c>
       <c r="B180" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C180" t="s">
         <v>55</v>
@@ -13473,7 +13479,7 @@
         <v>6</v>
       </c>
       <c r="T180" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z180">
         <v>0</v>
@@ -13558,7 +13564,7 @@
         <v>6548</v>
       </c>
       <c r="B182" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C182" t="s">
         <v>55</v>
@@ -13606,7 +13612,7 @@
         <v>7</v>
       </c>
       <c r="T182" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z182">
         <v>0</v>
@@ -13626,7 +13632,7 @@
         <v>6945</v>
       </c>
       <c r="B183" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C183" t="s">
         <v>55</v>
@@ -13674,7 +13680,7 @@
         <v>6</v>
       </c>
       <c r="T183" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z183">
         <v>0</v>
@@ -13759,7 +13765,7 @@
         <v>6548</v>
       </c>
       <c r="B185" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C185" t="s">
         <v>55</v>
@@ -13807,7 +13813,7 @@
         <v>7</v>
       </c>
       <c r="T185" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z185">
         <v>0</v>
@@ -13963,7 +13969,7 @@
         <v>6945</v>
       </c>
       <c r="B188" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C188" t="s">
         <v>55</v>
@@ -14011,7 +14017,7 @@
         <v>6</v>
       </c>
       <c r="T188" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z188">
         <v>0</v>
@@ -14096,7 +14102,7 @@
         <v>6548</v>
       </c>
       <c r="B190" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C190" t="s">
         <v>55</v>
@@ -14144,7 +14150,7 @@
         <v>7</v>
       </c>
       <c r="T190" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z190">
         <v>0</v>
@@ -14300,7 +14306,7 @@
         <v>6945</v>
       </c>
       <c r="B193" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C193" t="s">
         <v>55</v>
@@ -14348,7 +14354,7 @@
         <v>6</v>
       </c>
       <c r="T193" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z193">
         <v>0</v>
@@ -14856,7 +14862,7 @@
         <v>6486</v>
       </c>
       <c r="B201" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C201" t="s">
         <v>55</v>
@@ -14907,7 +14913,7 @@
         <v>6</v>
       </c>
       <c r="T201" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V201" t="s">
         <v>283</v>
@@ -14978,7 +14984,7 @@
         <v>6</v>
       </c>
       <c r="T202" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z202">
         <v>0</v>
@@ -15202,7 +15208,7 @@
         <v>6486</v>
       </c>
       <c r="B206" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C206" t="s">
         <v>55</v>
@@ -15253,7 +15259,7 @@
         <v>6</v>
       </c>
       <c r="T206" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V206" t="s">
         <v>283</v>
@@ -15324,7 +15330,7 @@
         <v>6</v>
       </c>
       <c r="T207" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z207">
         <v>0</v>
@@ -15480,7 +15486,7 @@
         <v>6486</v>
       </c>
       <c r="B210" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C210" t="s">
         <v>55</v>
@@ -15531,7 +15537,7 @@
         <v>6</v>
       </c>
       <c r="T210" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V210" t="s">
         <v>283</v>
@@ -15670,7 +15676,7 @@
         <v>6</v>
       </c>
       <c r="T212" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z212">
         <v>0</v>
@@ -15738,7 +15744,7 @@
         <v>6</v>
       </c>
       <c r="T213" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z213">
         <v>0</v>
@@ -15758,7 +15764,7 @@
         <v>6779</v>
       </c>
       <c r="B214" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C214" t="s">
         <v>55</v>
@@ -15806,7 +15812,7 @@
         <v>1</v>
       </c>
       <c r="T214" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z214">
         <v>0</v>
@@ -15962,7 +15968,7 @@
         <v>6486</v>
       </c>
       <c r="B217" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C217" t="s">
         <v>55</v>
@@ -16010,7 +16016,7 @@
         <v>1</v>
       </c>
       <c r="T217" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z217">
         <v>0</v>
@@ -16146,7 +16152,7 @@
         <v>1</v>
       </c>
       <c r="T219" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z219">
         <v>0</v>
@@ -16214,7 +16220,7 @@
         <v>1</v>
       </c>
       <c r="T220" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z220">
         <v>0</v>
@@ -16234,7 +16240,7 @@
         <v>6486</v>
       </c>
       <c r="B221" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C221" t="s">
         <v>55</v>
@@ -16285,7 +16291,7 @@
         <v>7</v>
       </c>
       <c r="T221" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V221" t="s">
         <v>284</v>
@@ -16308,7 +16314,7 @@
         <v>6486</v>
       </c>
       <c r="B222" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C222" t="s">
         <v>55</v>
@@ -16356,7 +16362,7 @@
         <v>1</v>
       </c>
       <c r="T222" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z222">
         <v>0</v>
@@ -16424,7 +16430,7 @@
         <v>1</v>
       </c>
       <c r="T223" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z223">
         <v>0</v>
@@ -16563,7 +16569,7 @@
         <v>-5</v>
       </c>
       <c r="T225" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z225">
         <v>0</v>
@@ -16699,7 +16705,7 @@
         <v>-1</v>
       </c>
       <c r="T227" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z227">
         <v>0</v>
@@ -16846,7 +16852,7 @@
         <v>6548</v>
       </c>
       <c r="B230" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C230" t="s">
         <v>55</v>
@@ -16894,7 +16900,7 @@
         <v>-1</v>
       </c>
       <c r="T230" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="V230" t="s">
         <v>287</v>
@@ -17030,7 +17036,7 @@
         <v>-1</v>
       </c>
       <c r="T232" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z232">
         <v>0</v>
@@ -17095,7 +17101,7 @@
         <v>-1</v>
       </c>
       <c r="T233" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z233">
         <v>0</v>
@@ -17112,7 +17118,7 @@
         <v>6779</v>
       </c>
       <c r="B234" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C234" t="s">
         <v>55</v>
@@ -17160,7 +17166,7 @@
         <v>-1</v>
       </c>
       <c r="T234" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="V234" t="s">
         <v>288</v>
@@ -17180,7 +17186,7 @@
         <v>6945</v>
       </c>
       <c r="B235" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C235" t="s">
         <v>55</v>
@@ -17228,7 +17234,7 @@
         <v>-1</v>
       </c>
       <c r="T235" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="V235" t="s">
         <v>289</v>
@@ -17520,7 +17526,7 @@
         <v>6486</v>
       </c>
       <c r="B240" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C240" t="s">
         <v>55</v>
@@ -17571,7 +17577,7 @@
         <v>6</v>
       </c>
       <c r="T240" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V240" t="s">
         <v>291</v>
@@ -17591,7 +17597,7 @@
         <v>6548</v>
       </c>
       <c r="B241" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C241" t="s">
         <v>55</v>
@@ -17642,7 +17648,7 @@
         <v>6</v>
       </c>
       <c r="T241" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="V241" t="s">
         <v>291</v>
@@ -17926,7 +17932,7 @@
         <v>6</v>
       </c>
       <c r="T245" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="V245" t="s">
         <v>291</v>
@@ -17997,7 +18003,7 @@
         <v>6</v>
       </c>
       <c r="T246" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="V246" t="s">
         <v>291</v>
@@ -18017,7 +18023,7 @@
         <v>6779</v>
       </c>
       <c r="B247" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C247" t="s">
         <v>55</v>
@@ -18068,7 +18074,7 @@
         <v>6</v>
       </c>
       <c r="T247" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="V247" t="s">
         <v>291</v>
@@ -18088,7 +18094,7 @@
         <v>6945</v>
       </c>
       <c r="B248" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C248" t="s">
         <v>55</v>
@@ -18139,7 +18145,7 @@
         <v>6</v>
       </c>
       <c r="T248" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="V248" t="s">
         <v>291</v>
@@ -18502,7 +18508,7 @@
         <v>6486</v>
       </c>
       <c r="B254" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C254" t="s">
         <v>55</v>
@@ -18550,7 +18556,7 @@
         <v>1</v>
       </c>
       <c r="T254" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z254">
         <v>0</v>
@@ -18567,7 +18573,7 @@
         <v>6548</v>
       </c>
       <c r="B255" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C255" t="s">
         <v>55</v>
@@ -18615,7 +18621,7 @@
         <v>1</v>
       </c>
       <c r="T255" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z255">
         <v>0</v>
@@ -18875,7 +18881,7 @@
         <v>1</v>
       </c>
       <c r="T259" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z259">
         <v>0</v>
@@ -18940,7 +18946,7 @@
         <v>1</v>
       </c>
       <c r="T260" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z260">
         <v>0</v>
@@ -18957,7 +18963,7 @@
         <v>6945</v>
       </c>
       <c r="B261" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C261" t="s">
         <v>55</v>
@@ -19005,7 +19011,7 @@
         <v>1</v>
       </c>
       <c r="T261" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z261">
         <v>0</v>
@@ -19217,7 +19223,7 @@
         <v>6486</v>
       </c>
       <c r="B265" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C265" t="s">
         <v>55</v>
@@ -19265,7 +19271,7 @@
         <v>8</v>
       </c>
       <c r="T265" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z265">
         <v>0</v>
@@ -19395,7 +19401,7 @@
         <v>8</v>
       </c>
       <c r="T267" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z267">
         <v>0</v>
@@ -19460,7 +19466,7 @@
         <v>8</v>
       </c>
       <c r="T268" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z268">
         <v>0</v>
@@ -19477,7 +19483,7 @@
         <v>6945</v>
       </c>
       <c r="B269" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C269" t="s">
         <v>55</v>
@@ -19525,7 +19531,7 @@
         <v>8</v>
       </c>
       <c r="T269" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z269">
         <v>0</v>
@@ -19672,7 +19678,7 @@
         <v>6486</v>
       </c>
       <c r="B272" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C272" t="s">
         <v>55</v>
@@ -19720,7 +19726,7 @@
         <v>5</v>
       </c>
       <c r="T272" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z272">
         <v>0</v>
@@ -19737,7 +19743,7 @@
         <v>6548</v>
       </c>
       <c r="B273" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C273" t="s">
         <v>55</v>
@@ -19785,7 +19791,7 @@
         <v>5</v>
       </c>
       <c r="T273" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z273">
         <v>0</v>
@@ -20045,7 +20051,7 @@
         <v>5</v>
       </c>
       <c r="T277" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z277">
         <v>0</v>
@@ -20110,7 +20116,7 @@
         <v>5</v>
       </c>
       <c r="T278" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z278">
         <v>0</v>
@@ -20127,7 +20133,7 @@
         <v>6779</v>
       </c>
       <c r="B279" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C279" t="s">
         <v>55</v>
@@ -20175,7 +20181,7 @@
         <v>5</v>
       </c>
       <c r="T279" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z279">
         <v>0</v>
@@ -20192,7 +20198,7 @@
         <v>6945</v>
       </c>
       <c r="B280" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C280" t="s">
         <v>55</v>
@@ -20240,7 +20246,7 @@
         <v>5</v>
       </c>
       <c r="T280" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z280">
         <v>0</v>
@@ -20582,7 +20588,7 @@
         <v>6486</v>
       </c>
       <c r="B286" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C286" t="s">
         <v>55</v>
@@ -20630,7 +20636,7 @@
         <v>0</v>
       </c>
       <c r="T286" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z286">
         <v>0</v>
@@ -20647,7 +20653,7 @@
         <v>6548</v>
       </c>
       <c r="B287" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C287" t="s">
         <v>55</v>
@@ -20695,7 +20701,7 @@
         <v>0</v>
       </c>
       <c r="T287" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z287">
         <v>0</v>
@@ -20955,7 +20961,7 @@
         <v>0</v>
       </c>
       <c r="T291" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z291">
         <v>0</v>
@@ -21020,7 +21026,7 @@
         <v>0</v>
       </c>
       <c r="T292" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z292">
         <v>0</v>
@@ -21037,7 +21043,7 @@
         <v>6945</v>
       </c>
       <c r="B293" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C293" t="s">
         <v>55</v>
@@ -21085,7 +21091,7 @@
         <v>0</v>
       </c>
       <c r="T293" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z293">
         <v>0</v>
@@ -21167,7 +21173,7 @@
         <v>6945</v>
       </c>
       <c r="B295" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C295" t="s">
         <v>55</v>
@@ -21215,7 +21221,7 @@
         <v>5</v>
       </c>
       <c r="T295" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="V295" t="s">
         <v>292</v>
@@ -21421,7 +21427,7 @@
         <v>6548</v>
       </c>
       <c r="B299" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C299" t="s">
         <v>55</v>
@@ -21466,7 +21472,7 @@
         <v>-16</v>
       </c>
       <c r="T299" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z299">
         <v>0</v>
@@ -21607,7 +21613,7 @@
         <v>6945</v>
       </c>
       <c r="B302" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C302" t="s">
         <v>55</v>
@@ -21652,7 +21658,7 @@
         <v>-16</v>
       </c>
       <c r="T302" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z302">
         <v>0</v>
@@ -21855,7 +21861,7 @@
         <v>6548</v>
       </c>
       <c r="B306" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C306" t="s">
         <v>55</v>
@@ -21900,7 +21906,7 @@
         <v>-16</v>
       </c>
       <c r="T306" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z306">
         <v>0</v>
@@ -22192,7 +22198,7 @@
         <v>130</v>
       </c>
       <c r="L311" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="N311" t="s">
         <v>187</v>
@@ -22207,7 +22213,7 @@
         <v>219</v>
       </c>
       <c r="S311">
-        <v>-16</v>
+        <v>-21</v>
       </c>
       <c r="T311" t="s">
         <v>229</v>
@@ -22254,7 +22260,7 @@
         <v>130</v>
       </c>
       <c r="L312" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="N312" t="s">
         <v>187</v>
@@ -22269,7 +22275,7 @@
         <v>219</v>
       </c>
       <c r="S312">
-        <v>-16</v>
+        <v>-21</v>
       </c>
       <c r="T312" t="s">
         <v>229</v>
@@ -22289,7 +22295,7 @@
         <v>6548</v>
       </c>
       <c r="B313" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C313" t="s">
         <v>55</v>
@@ -22316,7 +22322,7 @@
         <v>131</v>
       </c>
       <c r="L313" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="N313" t="s">
         <v>187</v>
@@ -22331,10 +22337,10 @@
         <v>219</v>
       </c>
       <c r="S313">
-        <v>-16</v>
+        <v>-21</v>
       </c>
       <c r="T313" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z313">
         <v>0</v>
@@ -22378,7 +22384,7 @@
         <v>131</v>
       </c>
       <c r="L314" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="N314" t="s">
         <v>187</v>
@@ -22393,7 +22399,7 @@
         <v>219</v>
       </c>
       <c r="S314">
-        <v>-16</v>
+        <v>-21</v>
       </c>
       <c r="T314" t="s">
         <v>223</v>
@@ -22440,7 +22446,7 @@
         <v>131</v>
       </c>
       <c r="L315" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="N315" t="s">
         <v>187</v>
@@ -22455,7 +22461,7 @@
         <v>219</v>
       </c>
       <c r="S315">
-        <v>-16</v>
+        <v>-21</v>
       </c>
       <c r="T315" t="s">
         <v>228</v>
@@ -22502,7 +22508,7 @@
         <v>131</v>
       </c>
       <c r="L316" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="N316" t="s">
         <v>187</v>
@@ -22517,7 +22523,7 @@
         <v>219</v>
       </c>
       <c r="S316">
-        <v>-16</v>
+        <v>-21</v>
       </c>
       <c r="T316" t="s">
         <v>229</v>
@@ -22564,7 +22570,7 @@
         <v>131</v>
       </c>
       <c r="L317" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="N317" t="s">
         <v>187</v>
@@ -22579,7 +22585,7 @@
         <v>219</v>
       </c>
       <c r="S317">
-        <v>-16</v>
+        <v>-21</v>
       </c>
       <c r="T317" t="s">
         <v>229</v>
@@ -22626,7 +22632,7 @@
         <v>132</v>
       </c>
       <c r="L318" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="N318" t="s">
         <v>187</v>
@@ -22641,7 +22647,7 @@
         <v>219</v>
       </c>
       <c r="S318">
-        <v>-16</v>
+        <v>-21</v>
       </c>
       <c r="T318" t="s">
         <v>223</v>
@@ -22661,7 +22667,7 @@
         <v>6945</v>
       </c>
       <c r="B319" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C319" t="s">
         <v>55</v>
@@ -22688,7 +22694,7 @@
         <v>132</v>
       </c>
       <c r="L319" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="N319" t="s">
         <v>187</v>
@@ -22703,10 +22709,10 @@
         <v>219</v>
       </c>
       <c r="S319">
-        <v>-16</v>
+        <v>-21</v>
       </c>
       <c r="T319" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z319">
         <v>0</v>
@@ -22723,7 +22729,7 @@
         <v>6548</v>
       </c>
       <c r="B320" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C320" t="s">
         <v>55</v>
@@ -22768,7 +22774,7 @@
         <v>-12</v>
       </c>
       <c r="T320" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z320">
         <v>0</v>
@@ -22971,7 +22977,7 @@
         <v>6486</v>
       </c>
       <c r="B324" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C324" t="s">
         <v>55</v>
@@ -23016,7 +23022,7 @@
         <v>-19</v>
       </c>
       <c r="T324" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z324">
         <v>0</v>
@@ -23157,7 +23163,7 @@
         <v>6486</v>
       </c>
       <c r="B327" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C327" t="s">
         <v>55</v>
@@ -23202,7 +23208,7 @@
         <v>-16</v>
       </c>
       <c r="T327" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z327">
         <v>0</v>
@@ -23326,7 +23332,7 @@
         <v>-16</v>
       </c>
       <c r="T329" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z329">
         <v>0</v>
@@ -23388,7 +23394,7 @@
         <v>-16</v>
       </c>
       <c r="T330" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z330">
         <v>0</v>
@@ -23405,7 +23411,7 @@
         <v>6779</v>
       </c>
       <c r="B331" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C331" t="s">
         <v>55</v>
@@ -23450,7 +23456,7 @@
         <v>-16</v>
       </c>
       <c r="T331" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z331">
         <v>0</v>
@@ -23591,7 +23597,7 @@
         <v>6486</v>
       </c>
       <c r="B334" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C334" t="s">
         <v>55</v>
@@ -23636,7 +23642,7 @@
         <v>-16</v>
       </c>
       <c r="T334" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z334">
         <v>0</v>
@@ -23760,7 +23766,7 @@
         <v>-16</v>
       </c>
       <c r="T336" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z336">
         <v>0</v>
@@ -23804,7 +23810,7 @@
         <v>130</v>
       </c>
       <c r="L337" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="N337" t="s">
         <v>187</v>
@@ -23819,7 +23825,7 @@
         <v>219</v>
       </c>
       <c r="S337">
-        <v>-16</v>
+        <v>-21</v>
       </c>
       <c r="T337" t="s">
         <v>230</v>
@@ -23866,7 +23872,7 @@
         <v>130</v>
       </c>
       <c r="L338" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="N338" t="s">
         <v>187</v>
@@ -23881,7 +23887,7 @@
         <v>219</v>
       </c>
       <c r="S338">
-        <v>-16</v>
+        <v>-21</v>
       </c>
       <c r="T338" t="s">
         <v>221</v>
@@ -23928,7 +23934,7 @@
         <v>131</v>
       </c>
       <c r="L339" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="N339" t="s">
         <v>187</v>
@@ -23943,7 +23949,7 @@
         <v>219</v>
       </c>
       <c r="S339">
-        <v>-16</v>
+        <v>-21</v>
       </c>
       <c r="T339" t="s">
         <v>222</v>
@@ -23963,7 +23969,7 @@
         <v>6486</v>
       </c>
       <c r="B340" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C340" t="s">
         <v>55</v>
@@ -23990,7 +23996,7 @@
         <v>131</v>
       </c>
       <c r="L340" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="N340" t="s">
         <v>187</v>
@@ -24005,10 +24011,10 @@
         <v>219</v>
       </c>
       <c r="S340">
-        <v>-16</v>
+        <v>-21</v>
       </c>
       <c r="T340" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z340">
         <v>0</v>
@@ -24052,7 +24058,7 @@
         <v>131</v>
       </c>
       <c r="L341" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="N341" t="s">
         <v>187</v>
@@ -24067,10 +24073,10 @@
         <v>219</v>
       </c>
       <c r="S341">
-        <v>-16</v>
+        <v>-21</v>
       </c>
       <c r="T341" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z341">
         <v>0</v>
@@ -24114,7 +24120,7 @@
         <v>132</v>
       </c>
       <c r="L342" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="N342" t="s">
         <v>187</v>
@@ -24129,10 +24135,10 @@
         <v>219</v>
       </c>
       <c r="S342">
-        <v>-16</v>
+        <v>-21</v>
       </c>
       <c r="T342" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z342">
         <v>0</v>
@@ -24149,7 +24155,7 @@
         <v>6779</v>
       </c>
       <c r="B343" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C343" t="s">
         <v>55</v>
@@ -24176,7 +24182,7 @@
         <v>132</v>
       </c>
       <c r="L343" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="N343" t="s">
         <v>187</v>
@@ -24191,10 +24197,10 @@
         <v>219</v>
       </c>
       <c r="S343">
-        <v>-16</v>
+        <v>-21</v>
       </c>
       <c r="T343" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z343">
         <v>0</v>
@@ -24459,7 +24465,7 @@
         <v>6945</v>
       </c>
       <c r="B348" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C348" t="s">
         <v>55</v>
@@ -24495,7 +24501,7 @@
         <v>18206577</v>
       </c>
       <c r="P348" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q348" t="s">
         <v>219</v>
@@ -24504,7 +24510,7 @@
         <v>-9</v>
       </c>
       <c r="T348" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z348">
         <v>0</v>
@@ -24521,7 +24527,7 @@
         <v>6548</v>
       </c>
       <c r="B349" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C349" t="s">
         <v>55</v>
@@ -24557,7 +24563,7 @@
         <v>17222602</v>
       </c>
       <c r="P349" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q349" t="s">
         <v>219</v>
@@ -24566,7 +24572,7 @@
         <v>-21</v>
       </c>
       <c r="T349" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z349">
         <v>0</v>
@@ -24583,7 +24589,7 @@
         <v>6779</v>
       </c>
       <c r="B350" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C350" t="s">
         <v>55</v>
@@ -24619,7 +24625,7 @@
         <v>18195621</v>
       </c>
       <c r="P350" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q350" t="s">
         <v>219</v>
@@ -24628,7 +24634,7 @@
         <v>-9</v>
       </c>
       <c r="T350" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z350">
         <v>0</v>
@@ -24704,7 +24710,7 @@
         <v>6486</v>
       </c>
       <c r="B352" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C352" t="s">
         <v>55</v>
@@ -24749,7 +24755,7 @@
         <v>-12</v>
       </c>
       <c r="T352" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z352">
         <v>0</v>
@@ -24766,7 +24772,7 @@
         <v>6548</v>
       </c>
       <c r="B353" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C353" t="s">
         <v>55</v>
@@ -24802,7 +24808,7 @@
         <v>17222629</v>
       </c>
       <c r="P353" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q353" t="s">
         <v>219</v>
@@ -24811,7 +24817,7 @@
         <v>-12</v>
       </c>
       <c r="T353" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z353">
         <v>0</v>
@@ -24988,7 +24994,7 @@
         <v>18077112</v>
       </c>
       <c r="P356" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q356" t="s">
         <v>219</v>
@@ -25014,7 +25020,7 @@
         <v>6779</v>
       </c>
       <c r="B357" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C357" t="s">
         <v>55</v>
@@ -25050,7 +25056,7 @@
         <v>18090189</v>
       </c>
       <c r="P357" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q357" t="s">
         <v>219</v>
@@ -25059,7 +25065,7 @@
         <v>-12</v>
       </c>
       <c r="T357" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z357">
         <v>0</v>
@@ -25076,7 +25082,7 @@
         <v>6945</v>
       </c>
       <c r="B358" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C358" t="s">
         <v>55</v>
@@ -25112,7 +25118,7 @@
         <v>18179111</v>
       </c>
       <c r="P358" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q358" t="s">
         <v>219</v>
@@ -25121,7 +25127,7 @@
         <v>-12</v>
       </c>
       <c r="T358" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z358">
         <v>0</v>
@@ -25259,7 +25265,7 @@
         <v>6486</v>
       </c>
       <c r="B361" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C361" t="s">
         <v>55</v>
@@ -25304,7 +25310,7 @@
         <v>-12</v>
       </c>
       <c r="T361" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z361">
         <v>0</v>
@@ -25321,7 +25327,7 @@
         <v>6548</v>
       </c>
       <c r="B362" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C362" t="s">
         <v>55</v>
@@ -25357,7 +25363,7 @@
         <v>17222647</v>
       </c>
       <c r="P362" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q362" t="s">
         <v>219</v>
@@ -25366,7 +25372,7 @@
         <v>-12</v>
       </c>
       <c r="T362" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z362">
         <v>0</v>
@@ -25543,7 +25549,7 @@
         <v>18077122</v>
       </c>
       <c r="P365" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q365" t="s">
         <v>219</v>
@@ -25569,7 +25575,7 @@
         <v>6779</v>
       </c>
       <c r="B366" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C366" t="s">
         <v>55</v>
@@ -25605,7 +25611,7 @@
         <v>18090199</v>
       </c>
       <c r="P366" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q366" t="s">
         <v>219</v>
@@ -25614,7 +25620,7 @@
         <v>-12</v>
       </c>
       <c r="T366" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z366">
         <v>0</v>
@@ -25631,7 +25637,7 @@
         <v>6945</v>
       </c>
       <c r="B367" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C367" t="s">
         <v>55</v>
@@ -25667,7 +25673,7 @@
         <v>18179118</v>
       </c>
       <c r="P367" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q367" t="s">
         <v>219</v>
@@ -25676,7 +25682,7 @@
         <v>-12</v>
       </c>
       <c r="T367" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z367">
         <v>0</v>
@@ -25876,7 +25882,7 @@
         <v>6486</v>
       </c>
       <c r="B371" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C371" t="s">
         <v>55</v>
@@ -25921,7 +25927,7 @@
         <v>-7</v>
       </c>
       <c r="T371" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z371">
         <v>0</v>
@@ -25938,7 +25944,7 @@
         <v>6548</v>
       </c>
       <c r="B372" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C372" t="s">
         <v>55</v>
@@ -25974,7 +25980,7 @@
         <v>18255116</v>
       </c>
       <c r="P372" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q372" t="s">
         <v>219</v>
@@ -25983,7 +25989,7 @@
         <v>-7</v>
       </c>
       <c r="T372" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z372">
         <v>0</v>
@@ -26160,7 +26166,7 @@
         <v>18256433</v>
       </c>
       <c r="P375" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q375" t="s">
         <v>219</v>
@@ -26222,7 +26228,7 @@
         <v>18254888</v>
       </c>
       <c r="P376" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q376" t="s">
         <v>219</v>
@@ -26231,7 +26237,7 @@
         <v>-7</v>
       </c>
       <c r="T376" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z376">
         <v>0</v>
@@ -26248,7 +26254,7 @@
         <v>6779</v>
       </c>
       <c r="B377" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C377" t="s">
         <v>55</v>
@@ -26284,7 +26290,7 @@
         <v>18255012</v>
       </c>
       <c r="P377" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q377" t="s">
         <v>219</v>
@@ -26293,7 +26299,7 @@
         <v>-7</v>
       </c>
       <c r="T377" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z377">
         <v>0</v>
@@ -26310,7 +26316,7 @@
         <v>6945</v>
       </c>
       <c r="B378" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C378" t="s">
         <v>55</v>
@@ -26346,7 +26352,7 @@
         <v>18254903</v>
       </c>
       <c r="P378" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q378" t="s">
         <v>219</v>
@@ -26355,7 +26361,7 @@
         <v>-7</v>
       </c>
       <c r="T378" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z378">
         <v>0</v>
@@ -26493,7 +26499,7 @@
         <v>6486</v>
       </c>
       <c r="B381" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C381" t="s">
         <v>55</v>
@@ -26538,7 +26544,7 @@
         <v>-12</v>
       </c>
       <c r="T381" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z381">
         <v>0</v>
@@ -26555,7 +26561,7 @@
         <v>6548</v>
       </c>
       <c r="B382" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C382" t="s">
         <v>55</v>
@@ -26591,7 +26597,7 @@
         <v>17222579</v>
       </c>
       <c r="P382" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q382" t="s">
         <v>219</v>
@@ -26600,7 +26606,7 @@
         <v>-12</v>
       </c>
       <c r="T382" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z382">
         <v>0</v>
@@ -26777,7 +26783,7 @@
         <v>18077082</v>
       </c>
       <c r="P385" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q385" t="s">
         <v>219</v>
@@ -26803,7 +26809,7 @@
         <v>6779</v>
       </c>
       <c r="B386" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C386" t="s">
         <v>55</v>
@@ -26839,7 +26845,7 @@
         <v>18090149</v>
       </c>
       <c r="P386" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q386" t="s">
         <v>219</v>
@@ -26848,7 +26854,7 @@
         <v>-12</v>
       </c>
       <c r="T386" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z386">
         <v>0</v>
@@ -26865,7 +26871,7 @@
         <v>6945</v>
       </c>
       <c r="B387" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C387" t="s">
         <v>55</v>
@@ -26901,7 +26907,7 @@
         <v>18179083</v>
       </c>
       <c r="P387" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q387" t="s">
         <v>219</v>
@@ -26910,7 +26916,7 @@
         <v>-12</v>
       </c>
       <c r="T387" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z387">
         <v>0</v>
@@ -26927,7 +26933,7 @@
         <v>6548</v>
       </c>
       <c r="B388" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C388" t="s">
         <v>55</v>
@@ -26963,7 +26969,7 @@
         <v>17222671</v>
       </c>
       <c r="P388" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q388" t="s">
         <v>219</v>
@@ -26972,7 +26978,7 @@
         <v>-21</v>
       </c>
       <c r="T388" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z388">
         <v>0</v>
@@ -27113,7 +27119,7 @@
         <v>6548</v>
       </c>
       <c r="B391" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C391" t="s">
         <v>55</v>
@@ -27149,7 +27155,7 @@
         <v>17222589</v>
       </c>
       <c r="P391" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q391" t="s">
         <v>219</v>
@@ -27158,7 +27164,7 @@
         <v>-21</v>
       </c>
       <c r="T391" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z391">
         <v>0</v>
@@ -27234,7 +27240,7 @@
         <v>6486</v>
       </c>
       <c r="B393" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C393" t="s">
         <v>55</v>
@@ -27279,7 +27285,7 @@
         <v>-9</v>
       </c>
       <c r="T393" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z393">
         <v>0</v>
@@ -27296,7 +27302,7 @@
         <v>6548</v>
       </c>
       <c r="B394" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C394" t="s">
         <v>55</v>
@@ -27332,7 +27338,7 @@
         <v>17222531</v>
       </c>
       <c r="P394" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q394" t="s">
         <v>219</v>
@@ -27341,7 +27347,7 @@
         <v>-9</v>
       </c>
       <c r="T394" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z394">
         <v>0</v>
@@ -27482,7 +27488,7 @@
         <v>6779</v>
       </c>
       <c r="B397" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C397" t="s">
         <v>55</v>
@@ -27518,7 +27524,7 @@
         <v>18090113</v>
       </c>
       <c r="P397" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q397" t="s">
         <v>219</v>
@@ -27527,7 +27533,7 @@
         <v>-9</v>
       </c>
       <c r="T397" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z397">
         <v>0</v>
@@ -27544,7 +27550,7 @@
         <v>6945</v>
       </c>
       <c r="B398" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C398" t="s">
         <v>55</v>
@@ -27580,7 +27586,7 @@
         <v>18179053</v>
       </c>
       <c r="P398" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q398" t="s">
         <v>219</v>
@@ -27589,7 +27595,7 @@
         <v>-9</v>
       </c>
       <c r="T398" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z398">
         <v>0</v>
@@ -27727,7 +27733,7 @@
         <v>6779</v>
       </c>
       <c r="B401" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C401" t="s">
         <v>55</v>
@@ -27763,7 +27769,7 @@
         <v>18158764</v>
       </c>
       <c r="P401" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q401" t="s">
         <v>219</v>
@@ -27772,7 +27778,7 @@
         <v>-19</v>
       </c>
       <c r="T401" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z401">
         <v>0</v>
@@ -27789,7 +27795,7 @@
         <v>6548</v>
       </c>
       <c r="B402" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C402" t="s">
         <v>55</v>
@@ -27825,7 +27831,7 @@
         <v>17222688</v>
       </c>
       <c r="P402" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q402" t="s">
         <v>219</v>
@@ -27834,7 +27840,7 @@
         <v>-21</v>
       </c>
       <c r="T402" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z402">
         <v>0</v>
@@ -27851,7 +27857,7 @@
         <v>6548</v>
       </c>
       <c r="B403" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C403" t="s">
         <v>55</v>
@@ -27887,7 +27893,7 @@
         <v>17222699</v>
       </c>
       <c r="P403" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q403" t="s">
         <v>219</v>
@@ -27896,7 +27902,7 @@
         <v>-21</v>
       </c>
       <c r="T403" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z403">
         <v>0</v>
@@ -27913,7 +27919,7 @@
         <v>6779</v>
       </c>
       <c r="B404" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C404" t="s">
         <v>55</v>
@@ -27949,7 +27955,7 @@
         <v>18195614</v>
       </c>
       <c r="P404" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q404" t="s">
         <v>219</v>
@@ -27958,7 +27964,7 @@
         <v>-9</v>
       </c>
       <c r="T404" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z404">
         <v>0</v>
@@ -27975,7 +27981,7 @@
         <v>6548</v>
       </c>
       <c r="B405" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C405" t="s">
         <v>55</v>
@@ -28020,7 +28026,7 @@
         <v>-12</v>
       </c>
       <c r="T405" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z405">
         <v>0</v>
@@ -28348,7 +28354,7 @@
         <v>229</v>
       </c>
       <c r="V410" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Z410">
         <v>0</v>
@@ -28416,7 +28422,7 @@
         <v>229</v>
       </c>
       <c r="V411" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Z411">
         <v>0</v>
@@ -28433,7 +28439,7 @@
         <v>6945</v>
       </c>
       <c r="B412" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C412" t="s">
         <v>55</v>
@@ -28478,7 +28484,7 @@
         <v>-16</v>
       </c>
       <c r="T412" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z412">
         <v>0</v>
@@ -28492,7 +28498,7 @@
         <v>6548</v>
       </c>
       <c r="B413" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C413" t="s">
         <v>55</v>
@@ -28537,7 +28543,7 @@
         <v>-9</v>
       </c>
       <c r="T413" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z413">
         <v>0</v>
@@ -28740,7 +28746,7 @@
         <v>6945</v>
       </c>
       <c r="B417" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C417" t="s">
         <v>55</v>
@@ -28785,7 +28791,7 @@
         <v>-19</v>
       </c>
       <c r="T417" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z417">
         <v>0</v>
@@ -28799,7 +28805,7 @@
         <v>6945</v>
       </c>
       <c r="B418" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C418" t="s">
         <v>55</v>
@@ -28844,7 +28850,7 @@
         <v>-7</v>
       </c>
       <c r="T418" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z418">
         <v>0</v>
@@ -28920,7 +28926,7 @@
         <v>6945</v>
       </c>
       <c r="B420" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C420" t="s">
         <v>55</v>
@@ -28965,7 +28971,7 @@
         <v>-9</v>
       </c>
       <c r="T420" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z420">
         <v>0</v>
@@ -29103,7 +29109,7 @@
         <v>6548</v>
       </c>
       <c r="B423" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C423" t="s">
         <v>55</v>
@@ -29148,7 +29154,7 @@
         <v>-13</v>
       </c>
       <c r="T423" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z423">
         <v>0</v>
@@ -29289,7 +29295,7 @@
         <v>6548</v>
       </c>
       <c r="B426" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C426" t="s">
         <v>55</v>
@@ -29334,7 +29340,7 @@
         <v>-14</v>
       </c>
       <c r="T426" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z426">
         <v>0</v>
@@ -29475,7 +29481,7 @@
         <v>6548</v>
       </c>
       <c r="B429" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C429" t="s">
         <v>55</v>
@@ -29520,7 +29526,7 @@
         <v>-12</v>
       </c>
       <c r="T429" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z429">
         <v>0</v>
@@ -29661,7 +29667,7 @@
         <v>6486</v>
       </c>
       <c r="B432" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C432" t="s">
         <v>55</v>
@@ -29706,7 +29712,7 @@
         <v>-15</v>
       </c>
       <c r="T432" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z432">
         <v>0</v>
@@ -29768,7 +29774,7 @@
         <v>-15</v>
       </c>
       <c r="T433" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z433">
         <v>0</v>
@@ -29909,7 +29915,7 @@
         <v>6486</v>
       </c>
       <c r="B436" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C436" t="s">
         <v>55</v>
@@ -29954,7 +29960,7 @@
         <v>-7</v>
       </c>
       <c r="T436" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z436">
         <v>0</v>
@@ -30016,7 +30022,7 @@
         <v>-7</v>
       </c>
       <c r="T437" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z437">
         <v>0</v>
@@ -30140,7 +30146,7 @@
         <v>-9</v>
       </c>
       <c r="T439" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z439">
         <v>0</v>
@@ -30281,7 +30287,7 @@
         <v>6486</v>
       </c>
       <c r="B442" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C442" t="s">
         <v>55</v>
@@ -30326,7 +30332,7 @@
         <v>-9</v>
       </c>
       <c r="T442" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z442">
         <v>0</v>
@@ -30388,7 +30394,7 @@
         <v>-19</v>
       </c>
       <c r="T443" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z443">
         <v>0</v>
@@ -30450,7 +30456,7 @@
         <v>-9</v>
       </c>
       <c r="T444" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z444">
         <v>0</v>
@@ -30467,7 +30473,7 @@
         <v>6779</v>
       </c>
       <c r="B445" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C445" t="s">
         <v>55</v>
@@ -30512,7 +30518,7 @@
         <v>-9</v>
       </c>
       <c r="T445" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z445">
         <v>0</v>
@@ -30822,7 +30828,7 @@
         <v>-13</v>
       </c>
       <c r="T450" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z450">
         <v>0</v>
@@ -30963,7 +30969,7 @@
         <v>6486</v>
       </c>
       <c r="B453" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C453" t="s">
         <v>55</v>
@@ -31008,7 +31014,7 @@
         <v>-14</v>
       </c>
       <c r="T453" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z453">
         <v>0</v>
@@ -31146,7 +31152,7 @@
         <v>6945</v>
       </c>
       <c r="B456" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C456" t="s">
         <v>55</v>
@@ -31191,7 +31197,7 @@
         <v>-9</v>
       </c>
       <c r="T456" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z456">
         <v>0</v>
@@ -31250,7 +31256,7 @@
         <v>-9</v>
       </c>
       <c r="T457" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z457">
         <v>0</v>
@@ -31382,7 +31388,7 @@
         <v>6486</v>
       </c>
       <c r="B460" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C460" t="s">
         <v>55</v>
@@ -31427,7 +31433,7 @@
         <v>-8</v>
       </c>
       <c r="T460" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z460">
         <v>0</v>
@@ -31441,7 +31447,7 @@
         <v>6548</v>
       </c>
       <c r="B461" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C461" t="s">
         <v>55</v>
@@ -31486,7 +31492,7 @@
         <v>-8</v>
       </c>
       <c r="T461" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z461">
         <v>0</v>
@@ -31722,7 +31728,7 @@
         <v>-8</v>
       </c>
       <c r="T465" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z465">
         <v>0</v>
@@ -31781,7 +31787,7 @@
         <v>-8</v>
       </c>
       <c r="T466" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z466">
         <v>0</v>
@@ -31795,7 +31801,7 @@
         <v>6779</v>
       </c>
       <c r="B467" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C467" t="s">
         <v>55</v>
@@ -31840,7 +31846,7 @@
         <v>-8</v>
       </c>
       <c r="T467" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z467">
         <v>0</v>
@@ -31854,7 +31860,7 @@
         <v>6945</v>
       </c>
       <c r="B468" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C468" t="s">
         <v>55</v>
@@ -31899,7 +31905,7 @@
         <v>-8</v>
       </c>
       <c r="T468" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z468">
         <v>0</v>
@@ -32208,7 +32214,7 @@
         <v>6486</v>
       </c>
       <c r="B474" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C474" t="s">
         <v>55</v>
@@ -32253,7 +32259,7 @@
         <v>-9</v>
       </c>
       <c r="T474" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z474">
         <v>0</v>
@@ -32267,7 +32273,7 @@
         <v>6548</v>
       </c>
       <c r="B475" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C475" t="s">
         <v>55</v>
@@ -32312,7 +32318,7 @@
         <v>-9</v>
       </c>
       <c r="T475" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z475">
         <v>0</v>
@@ -32548,7 +32554,7 @@
         <v>-9</v>
       </c>
       <c r="T479" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z479">
         <v>0</v>
@@ -32607,7 +32613,7 @@
         <v>-9</v>
       </c>
       <c r="T480" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z480">
         <v>0</v>
@@ -32621,7 +32627,7 @@
         <v>6945</v>
       </c>
       <c r="B481" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C481" t="s">
         <v>55</v>
@@ -32666,7 +32672,7 @@
         <v>-9</v>
       </c>
       <c r="T481" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z481">
         <v>0</v>
@@ -32798,7 +32804,7 @@
         <v>6486</v>
       </c>
       <c r="B484" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C484" t="s">
         <v>55</v>
@@ -32843,7 +32849,7 @@
         <v>-21</v>
       </c>
       <c r="T484" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z484">
         <v>0</v>
@@ -32961,7 +32967,7 @@
         <v>-21</v>
       </c>
       <c r="T486" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z486">
         <v>0</v>
@@ -33020,7 +33026,7 @@
         <v>-21</v>
       </c>
       <c r="T487" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z487">
         <v>0</v>
@@ -33329,7 +33335,7 @@
         <v>6486</v>
       </c>
       <c r="B493" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C493" t="s">
         <v>55</v>
@@ -33374,7 +33380,7 @@
         <v>-9</v>
       </c>
       <c r="T493" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z493">
         <v>0</v>
@@ -33388,7 +33394,7 @@
         <v>6548</v>
       </c>
       <c r="B494" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C494" t="s">
         <v>55</v>
@@ -33433,7 +33439,7 @@
         <v>-9</v>
       </c>
       <c r="T494" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z494">
         <v>0</v>
@@ -33669,7 +33675,7 @@
         <v>-9</v>
       </c>
       <c r="T498" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z498">
         <v>0</v>
@@ -33728,7 +33734,7 @@
         <v>-9</v>
       </c>
       <c r="T499" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z499">
         <v>0</v>
@@ -33742,7 +33748,7 @@
         <v>6779</v>
       </c>
       <c r="B500" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C500" t="s">
         <v>55</v>
@@ -33787,7 +33793,7 @@
         <v>-9</v>
       </c>
       <c r="T500" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z500">
         <v>0</v>
@@ -33801,7 +33807,7 @@
         <v>6945</v>
       </c>
       <c r="B501" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C501" t="s">
         <v>55</v>
@@ -33846,7 +33852,7 @@
         <v>-9</v>
       </c>
       <c r="T501" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z501">
         <v>0</v>
@@ -34155,7 +34161,7 @@
         <v>6486</v>
       </c>
       <c r="B507" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C507" t="s">
         <v>55</v>
@@ -34200,7 +34206,7 @@
         <v>-9</v>
       </c>
       <c r="T507" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z507">
         <v>0</v>
@@ -34214,7 +34220,7 @@
         <v>6548</v>
       </c>
       <c r="B508" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C508" t="s">
         <v>55</v>
@@ -34259,7 +34265,7 @@
         <v>-9</v>
       </c>
       <c r="T508" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z508">
         <v>0</v>
@@ -34495,7 +34501,7 @@
         <v>-9</v>
       </c>
       <c r="T512" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z512">
         <v>0</v>
@@ -34554,7 +34560,7 @@
         <v>-9</v>
       </c>
       <c r="T513" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z513">
         <v>0</v>
@@ -34568,7 +34574,7 @@
         <v>6945</v>
       </c>
       <c r="B514" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C514" t="s">
         <v>55</v>
@@ -34613,7 +34619,7 @@
         <v>-9</v>
       </c>
       <c r="T514" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z514">
         <v>0</v>
@@ -34754,7 +34760,7 @@
         <v>6945</v>
       </c>
       <c r="B517" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C517" t="s">
         <v>55</v>
@@ -34802,7 +34808,7 @@
         <v>-19</v>
       </c>
       <c r="T517" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z517">
         <v>0</v>
@@ -34822,7 +34828,7 @@
         <v>6548</v>
       </c>
       <c r="B518" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C518" t="s">
         <v>55</v>
@@ -34870,7 +34876,7 @@
         <v>-16</v>
       </c>
       <c r="T518" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="V518" t="s">
         <v>294</v>
@@ -35012,7 +35018,7 @@
         <v>-19</v>
       </c>
       <c r="T520" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z520">
         <v>0</v>
@@ -35100,7 +35106,7 @@
         <v>6486</v>
       </c>
       <c r="B522" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C522" t="s">
         <v>55</v>
@@ -35148,7 +35154,7 @@
         <v>-9</v>
       </c>
       <c r="T522" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z522">
         <v>0</v>
@@ -35425,7 +35431,7 @@
         <v>6486</v>
       </c>
       <c r="B527" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C527" t="s">
         <v>55</v>
@@ -35473,7 +35479,7 @@
         <v>-16</v>
       </c>
       <c r="T527" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z527">
         <v>0</v>
@@ -35541,7 +35547,7 @@
         <v>-16</v>
       </c>
       <c r="T528" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z528">
         <v>0</v>
@@ -35677,7 +35683,7 @@
         <v>-12</v>
       </c>
       <c r="T530" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z530">
         <v>0</v>
@@ -35745,7 +35751,7 @@
         <v>-12</v>
       </c>
       <c r="T531" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z531">
         <v>0</v>
@@ -35765,7 +35771,7 @@
         <v>6779</v>
       </c>
       <c r="B532" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C532" t="s">
         <v>55</v>
@@ -35813,7 +35819,7 @@
         <v>-12</v>
       </c>
       <c r="T532" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z532">
         <v>0</v>
@@ -35869,7 +35875,7 @@
         <v>18105120</v>
       </c>
       <c r="P533" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q533" t="s">
         <v>220</v>
@@ -35887,7 +35893,7 @@
         <v>0</v>
       </c>
       <c r="AA533" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF533" t="s">
         <v>330</v>
@@ -35969,7 +35975,7 @@
         <v>6486</v>
       </c>
       <c r="B535" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C535" t="s">
         <v>55</v>
@@ -36017,7 +36023,7 @@
         <v>-12</v>
       </c>
       <c r="T535" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z535">
         <v>0</v>
@@ -36037,7 +36043,7 @@
         <v>6779</v>
       </c>
       <c r="B536" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C536" t="s">
         <v>55</v>
@@ -36073,7 +36079,7 @@
         <v>18090118</v>
       </c>
       <c r="P536" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q536" t="s">
         <v>220</v>
@@ -36085,7 +36091,7 @@
         <v>-12</v>
       </c>
       <c r="T536" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z536">
         <v>0</v>
@@ -36105,7 +36111,7 @@
         <v>6945</v>
       </c>
       <c r="B537" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C537" t="s">
         <v>55</v>
@@ -36141,7 +36147,7 @@
         <v>18179058</v>
       </c>
       <c r="P537" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q537" t="s">
         <v>220</v>
@@ -36153,7 +36159,7 @@
         <v>-12</v>
       </c>
       <c r="T537" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z537">
         <v>0</v>
@@ -36173,7 +36179,7 @@
         <v>6548</v>
       </c>
       <c r="B538" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C538" t="s">
         <v>55</v>
@@ -36221,7 +36227,7 @@
         <v>-12</v>
       </c>
       <c r="T538" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z538">
         <v>0</v>
@@ -36493,7 +36499,7 @@
         <v>-7</v>
       </c>
       <c r="T542" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z542">
         <v>0</v>
@@ -36697,7 +36703,7 @@
         <v>-9</v>
       </c>
       <c r="T545" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z545">
         <v>0</v>
@@ -36714,7 +36720,7 @@
         <v>6779</v>
       </c>
       <c r="B546" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C546" t="s">
         <v>55</v>
@@ -36762,7 +36768,7 @@
         <v>-9</v>
       </c>
       <c r="T546" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="V546" t="s">
         <v>298</v>
@@ -36782,7 +36788,7 @@
         <v>6945</v>
       </c>
       <c r="B547" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C547" t="s">
         <v>55</v>
@@ -36830,7 +36836,7 @@
         <v>-9</v>
       </c>
       <c r="T547" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="V547" t="s">
         <v>299</v>
@@ -37164,7 +37170,7 @@
         <v>-9</v>
       </c>
       <c r="T552" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z552">
         <v>0</v>
@@ -37563,7 +37569,7 @@
         <v>-16</v>
       </c>
       <c r="T558" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z558">
         <v>0</v>
@@ -37962,7 +37968,7 @@
         <v>-9</v>
       </c>
       <c r="T564" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="V564" t="s">
         <v>310</v>
@@ -37982,7 +37988,7 @@
         <v>6945</v>
       </c>
       <c r="B565" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C565" t="s">
         <v>55</v>
@@ -38030,7 +38036,7 @@
         <v>-9</v>
       </c>
       <c r="T565" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z565">
         <v>0</v>
@@ -38381,7 +38387,7 @@
         <v>6486</v>
       </c>
       <c r="B571" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C571" t="s">
         <v>55</v>
@@ -38429,7 +38435,7 @@
         <v>-16</v>
       </c>
       <c r="T571" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V571" t="s">
         <v>314</v>
@@ -38579,7 +38585,7 @@
         <v>6486</v>
       </c>
       <c r="B574" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C574" t="s">
         <v>55</v>
@@ -38627,7 +38633,7 @@
         <v>-15</v>
       </c>
       <c r="T574" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Z574">
         <v>0</v>
@@ -39040,7 +39046,7 @@
         <v>6486</v>
       </c>
       <c r="B581" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C581" t="s">
         <v>55</v>
@@ -39088,7 +39094,7 @@
         <v>15</v>
       </c>
       <c r="T581" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V581" t="s">
         <v>316</v>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8094" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8062" uniqueCount="370">
   <si>
     <t>CodCliente</t>
   </si>
@@ -1092,9 +1092,6 @@
 Sem informações que permite identificar e aplicar modelo - Data Comentário: 08/09/2026 17:53</t>
   </si>
   <si>
-    <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 11/09/2026 - Data Comentário: 09/09/2026 17:18</t>
-  </si>
-  <si>
     <t>Comentário Colaborador + Previsão de conclusão, Previsto para 10/09/2026 - Data Comentário: 08/09/2026 08:44</t>
   </si>
   <si>
@@ -1123,9 +1120,6 @@
   </si>
   <si>
     <t>Entramos em contato com o Mauricio Lermen no dia 02/09 e o mesmo nos informou que não teria a documentação necessária para efeturar a aplicação do modelo e assim a baixa da tarefa - Data Comentário: 09/09/2026 16:05</t>
-  </si>
-  <si>
-    <t>Tarefa reaberta. A previsão de conclusão está prevista para 09/09/2026. - Data Comentário: 09/09/2026 16:06</t>
   </si>
   <si>
     <t>Imposto</t>
@@ -1491,7 +1485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AG596"/>
+  <dimension ref="A1:AG594"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:33">
@@ -1657,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:33">
@@ -1722,10 +1716,10 @@
         <v>0</v>
       </c>
       <c r="AF3" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG3" t="s">
         <v>363</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="4" spans="1:33">
@@ -1790,10 +1784,10 @@
         <v>0</v>
       </c>
       <c r="AF4" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG4" t="s">
         <v>363</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:33">
@@ -1852,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" spans="1:33">
@@ -1911,10 +1905,10 @@
         <v>0</v>
       </c>
       <c r="AF6" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG6" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" spans="1:33">
@@ -1979,10 +1973,10 @@
         <v>0</v>
       </c>
       <c r="AF7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG7" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8" spans="1:33">
@@ -2041,10 +2035,10 @@
         <v>0</v>
       </c>
       <c r="AF8" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG8" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9" spans="1:33">
@@ -2103,10 +2097,10 @@
         <v>0</v>
       </c>
       <c r="AF9" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG9" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10" spans="1:33">
@@ -2171,10 +2165,10 @@
         <v>0</v>
       </c>
       <c r="AF10" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG10" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="11" spans="1:33">
@@ -2239,10 +2233,10 @@
         <v>0</v>
       </c>
       <c r="AF11" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="12" spans="1:33">
@@ -2301,10 +2295,10 @@
         <v>0</v>
       </c>
       <c r="AF12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG12" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="13" spans="1:33">
@@ -2363,10 +2357,10 @@
         <v>0</v>
       </c>
       <c r="AF13" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG13" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="14" spans="1:33">
@@ -2425,7 +2419,7 @@
         <v>0</v>
       </c>
       <c r="AF14" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG14" t="s">
         <v>216</v>
@@ -2493,7 +2487,7 @@
         <v>0</v>
       </c>
       <c r="AF15" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG15" t="s">
         <v>216</v>
@@ -2555,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="AF16" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG16" t="s">
         <v>216</v>
@@ -2617,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="AF17" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG17" t="s">
         <v>216</v>
@@ -2685,7 +2679,7 @@
         <v>0</v>
       </c>
       <c r="AF18" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="19" spans="1:33">
@@ -2750,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="AF19" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG19" t="s">
         <v>216</v>
@@ -2818,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AF20" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG20" t="s">
         <v>216</v>
@@ -2886,7 +2880,7 @@
         <v>0</v>
       </c>
       <c r="AF21" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG21" t="s">
         <v>216</v>
@@ -2948,7 +2942,7 @@
         <v>0</v>
       </c>
       <c r="AF22" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="23" spans="1:33">
@@ -3007,7 +3001,7 @@
         <v>0</v>
       </c>
       <c r="AF23" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG23" t="s">
         <v>216</v>
@@ -3069,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="AF24" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG24" t="s">
         <v>216</v>
@@ -3131,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="AF25" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="26" spans="1:33">
@@ -3190,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="AF26" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG26" t="s">
         <v>216</v>
@@ -3252,7 +3246,7 @@
         <v>0</v>
       </c>
       <c r="AF27" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG27" t="s">
         <v>216</v>
@@ -3314,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="AF28" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG28" t="s">
         <v>216</v>
@@ -3376,10 +3370,10 @@
         <v>0</v>
       </c>
       <c r="AF29" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG29" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="30" spans="1:33">
@@ -3438,10 +3432,10 @@
         <v>0</v>
       </c>
       <c r="AF30" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG30" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="31" spans="1:33">
@@ -3500,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AF31" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG31" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="32" spans="1:33">
@@ -3562,10 +3556,10 @@
         <v>0</v>
       </c>
       <c r="AF32" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG32" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="33" spans="1:33">
@@ -3624,10 +3618,10 @@
         <v>0</v>
       </c>
       <c r="AF33" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG33" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="34" spans="1:33">
@@ -3686,10 +3680,10 @@
         <v>0</v>
       </c>
       <c r="AF34" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG34" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="35" spans="1:33">
@@ -3748,10 +3742,10 @@
         <v>0</v>
       </c>
       <c r="AF35" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG35" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="36" spans="1:33">
@@ -3810,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="AF36" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG36" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="37" spans="1:33">
@@ -3872,10 +3866,10 @@
         <v>0</v>
       </c>
       <c r="AF37" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG37" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="38" spans="1:33">
@@ -3934,10 +3928,10 @@
         <v>0</v>
       </c>
       <c r="AF38" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG38" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="39" spans="1:33">
@@ -3996,10 +3990,10 @@
         <v>0</v>
       </c>
       <c r="AF39" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG39" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="40" spans="1:33">
@@ -4058,10 +4052,10 @@
         <v>0</v>
       </c>
       <c r="AF40" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG40" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="41" spans="1:33">
@@ -4120,10 +4114,10 @@
         <v>0</v>
       </c>
       <c r="AF41" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG41" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="42" spans="1:33">
@@ -4182,10 +4176,10 @@
         <v>0</v>
       </c>
       <c r="AF42" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG42" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="43" spans="1:33">
@@ -4244,10 +4238,10 @@
         <v>0</v>
       </c>
       <c r="AF43" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG43" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="44" spans="1:33">
@@ -4306,10 +4300,10 @@
         <v>0</v>
       </c>
       <c r="AF44" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG44" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="45" spans="1:33">
@@ -4368,10 +4362,10 @@
         <v>0</v>
       </c>
       <c r="AF45" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG45" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="46" spans="1:33">
@@ -4433,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="AF46" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="47" spans="1:33">
@@ -4495,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AF47" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="48" spans="1:33">
@@ -4557,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="AF48" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="49" spans="1:33">
@@ -4619,13 +4613,13 @@
         <v>0</v>
       </c>
       <c r="AA49" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AF49" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG49" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="50" spans="1:33">
@@ -4687,13 +4681,13 @@
         <v>0</v>
       </c>
       <c r="AA50" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AF50" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG50" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="51" spans="1:33">
@@ -4755,13 +4749,13 @@
         <v>0</v>
       </c>
       <c r="AA51" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AF51" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG51" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="52" spans="1:33">
@@ -4823,13 +4817,13 @@
         <v>0</v>
       </c>
       <c r="AA52" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AF52" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG52" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="53" spans="1:33">
@@ -4891,13 +4885,13 @@
         <v>0</v>
       </c>
       <c r="AA53" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AF53" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG53" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="54" spans="1:33">
@@ -4959,13 +4953,13 @@
         <v>0</v>
       </c>
       <c r="AA54" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AF54" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG54" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="55" spans="1:33">
@@ -5027,13 +5021,13 @@
         <v>0</v>
       </c>
       <c r="AA55" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AF55" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG55" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="56" spans="1:33">
@@ -5095,13 +5089,13 @@
         <v>0</v>
       </c>
       <c r="AA56" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AF56" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG56" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="57" spans="1:33">
@@ -5163,13 +5157,13 @@
         <v>0</v>
       </c>
       <c r="AA57" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AF57" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG57" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="58" spans="1:33">
@@ -5231,13 +5225,13 @@
         <v>0</v>
       </c>
       <c r="AA58" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AF58" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG58" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="59" spans="1:33">
@@ -5299,13 +5293,13 @@
         <v>0</v>
       </c>
       <c r="AA59" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AF59" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG59" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="60" spans="1:33">
@@ -5376,10 +5370,10 @@
         <v>209</v>
       </c>
       <c r="AF60" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG60" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="61" spans="1:33">
@@ -5444,10 +5438,10 @@
         <v>214</v>
       </c>
       <c r="AF61" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG61" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="62" spans="1:33">
@@ -5518,10 +5512,10 @@
         <v>215</v>
       </c>
       <c r="AF62" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG62" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="63" spans="1:33">
@@ -5592,7 +5586,7 @@
         <v>210</v>
       </c>
       <c r="AF63" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="64" spans="1:33">
@@ -5657,10 +5651,10 @@
         <v>209</v>
       </c>
       <c r="AF64" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG64" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="65" spans="1:33">
@@ -5731,10 +5725,10 @@
         <v>211</v>
       </c>
       <c r="AF65" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG65" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="66" spans="1:33">
@@ -5805,10 +5799,10 @@
         <v>212</v>
       </c>
       <c r="AF66" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG66" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="67" spans="1:33">
@@ -5873,10 +5867,10 @@
         <v>215</v>
       </c>
       <c r="AF67" t="s">
+        <v>362</v>
+      </c>
+      <c r="AG67" t="s">
         <v>364</v>
-      </c>
-      <c r="AG67" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="68" spans="1:33">
@@ -5947,7 +5941,7 @@
         <v>210</v>
       </c>
       <c r="AF68" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="69" spans="1:33">
@@ -6015,13 +6009,13 @@
         <v>0</v>
       </c>
       <c r="AA69" t="s">
+        <v>352</v>
+      </c>
+      <c r="AF69" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG69" t="s">
         <v>353</v>
-      </c>
-      <c r="AF69" t="s">
-        <v>363</v>
-      </c>
-      <c r="AG69" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="70" spans="1:33">
@@ -6092,10 +6086,10 @@
         <v>209</v>
       </c>
       <c r="AF70" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG70" t="s">
         <v>363</v>
-      </c>
-      <c r="AG70" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="71" spans="1:33">
@@ -6166,10 +6160,10 @@
         <v>211</v>
       </c>
       <c r="AF71" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG71" t="s">
         <v>363</v>
-      </c>
-      <c r="AG71" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="72" spans="1:33">
@@ -6240,10 +6234,10 @@
         <v>212</v>
       </c>
       <c r="AF72" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG72" t="s">
         <v>363</v>
-      </c>
-      <c r="AG72" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="73" spans="1:33">
@@ -6314,10 +6308,10 @@
         <v>213</v>
       </c>
       <c r="AF73" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG73" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="74" spans="1:33">
@@ -6388,10 +6382,10 @@
         <v>214</v>
       </c>
       <c r="AF74" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG74" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="75" spans="1:33">
@@ -6456,10 +6450,10 @@
         <v>215</v>
       </c>
       <c r="AF75" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG75" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="76" spans="1:33">
@@ -6527,10 +6521,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AF76" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="77" spans="1:33">
@@ -6601,10 +6595,10 @@
         <v>209</v>
       </c>
       <c r="AF77" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG77" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="78" spans="1:33">
@@ -6675,10 +6669,10 @@
         <v>209</v>
       </c>
       <c r="AF78" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG78" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="79" spans="1:33">
@@ -6749,10 +6743,10 @@
         <v>209</v>
       </c>
       <c r="AF79" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG79" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="80" spans="1:33">
@@ -6823,10 +6817,10 @@
         <v>212</v>
       </c>
       <c r="AF80" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG80" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="81" spans="1:33">
@@ -6897,10 +6891,10 @@
         <v>213</v>
       </c>
       <c r="AF81" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG81" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="82" spans="1:33">
@@ -6971,10 +6965,10 @@
         <v>214</v>
       </c>
       <c r="AF82" t="s">
+        <v>362</v>
+      </c>
+      <c r="AG82" t="s">
         <v>364</v>
-      </c>
-      <c r="AG82" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="83" spans="1:33">
@@ -7045,10 +7039,10 @@
         <v>215</v>
       </c>
       <c r="AF83" t="s">
+        <v>362</v>
+      </c>
+      <c r="AG83" t="s">
         <v>364</v>
-      </c>
-      <c r="AG83" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="84" spans="1:33">
@@ -7113,7 +7107,7 @@
         <v>210</v>
       </c>
       <c r="AF84" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="85" spans="1:33">
@@ -7178,10 +7172,10 @@
         <v>209</v>
       </c>
       <c r="AF85" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG85" t="s">
         <v>363</v>
-      </c>
-      <c r="AG85" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="86" spans="1:33">
@@ -7246,10 +7240,10 @@
         <v>209</v>
       </c>
       <c r="AF86" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG86" t="s">
         <v>363</v>
-      </c>
-      <c r="AG86" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="87" spans="1:33">
@@ -7314,10 +7308,10 @@
         <v>209</v>
       </c>
       <c r="AF87" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG87" t="s">
         <v>363</v>
-      </c>
-      <c r="AG87" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="88" spans="1:33">
@@ -7382,10 +7376,10 @@
         <v>212</v>
       </c>
       <c r="AF88" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG88" t="s">
         <v>363</v>
-      </c>
-      <c r="AG88" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="89" spans="1:33">
@@ -7450,10 +7444,10 @@
         <v>213</v>
       </c>
       <c r="AF89" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG89" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:33">
@@ -7524,10 +7518,10 @@
         <v>214</v>
       </c>
       <c r="AF90" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG90" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="91" spans="1:33">
@@ -7592,10 +7586,10 @@
         <v>215</v>
       </c>
       <c r="AF91" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG91" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="92" spans="1:33">
@@ -7660,7 +7654,7 @@
         <v>210</v>
       </c>
       <c r="AF92" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="93" spans="1:33">
@@ -7725,10 +7719,10 @@
         <v>209</v>
       </c>
       <c r="AF93" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG93" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="94" spans="1:33">
@@ -7799,10 +7793,10 @@
         <v>211</v>
       </c>
       <c r="AF94" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG94" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="95" spans="1:33">
@@ -7873,10 +7867,10 @@
         <v>212</v>
       </c>
       <c r="AF95" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG95" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="96" spans="1:33">
@@ -7941,10 +7935,10 @@
         <v>215</v>
       </c>
       <c r="AF96" t="s">
+        <v>362</v>
+      </c>
+      <c r="AG96" t="s">
         <v>364</v>
-      </c>
-      <c r="AG96" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="97" spans="1:33">
@@ -8009,7 +8003,7 @@
         <v>210</v>
       </c>
       <c r="AF97" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:33">
@@ -8074,10 +8068,10 @@
         <v>209</v>
       </c>
       <c r="AF98" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG98" t="s">
         <v>363</v>
-      </c>
-      <c r="AG98" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:33">
@@ -8142,10 +8136,10 @@
         <v>211</v>
       </c>
       <c r="AF99" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG99" t="s">
         <v>363</v>
-      </c>
-      <c r="AG99" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:33">
@@ -8210,10 +8204,10 @@
         <v>209</v>
       </c>
       <c r="AF100" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG100" t="s">
         <v>363</v>
-      </c>
-      <c r="AG100" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:33">
@@ -8278,10 +8272,10 @@
         <v>209</v>
       </c>
       <c r="AF101" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG101" t="s">
         <v>363</v>
-      </c>
-      <c r="AG101" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:33">
@@ -8346,10 +8340,10 @@
         <v>213</v>
       </c>
       <c r="AF102" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG102" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="103" spans="1:33">
@@ -8414,10 +8408,10 @@
         <v>214</v>
       </c>
       <c r="AF103" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG103" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="104" spans="1:33">
@@ -8482,10 +8476,10 @@
         <v>215</v>
       </c>
       <c r="AF104" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG104" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="105" spans="1:33">
@@ -8556,10 +8550,10 @@
         <v>209</v>
       </c>
       <c r="AF105" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG105" t="s">
         <v>363</v>
-      </c>
-      <c r="AG105" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="106" spans="1:33">
@@ -8630,10 +8624,10 @@
         <v>209</v>
       </c>
       <c r="AF106" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG106" t="s">
         <v>363</v>
-      </c>
-      <c r="AG106" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="107" spans="1:33">
@@ -8704,10 +8698,10 @@
         <v>209</v>
       </c>
       <c r="AF107" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG107" t="s">
         <v>363</v>
-      </c>
-      <c r="AG107" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="108" spans="1:33">
@@ -8778,10 +8772,10 @@
         <v>212</v>
       </c>
       <c r="AF108" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG108" t="s">
         <v>363</v>
-      </c>
-      <c r="AG108" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="109" spans="1:33">
@@ -8846,10 +8840,10 @@
         <v>211</v>
       </c>
       <c r="AF109" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG109" t="s">
         <v>363</v>
-      </c>
-      <c r="AG109" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="110" spans="1:33">
@@ -8920,7 +8914,7 @@
         <v>210</v>
       </c>
       <c r="AF110" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="111" spans="1:33">
@@ -8988,13 +8982,13 @@
         <v>0</v>
       </c>
       <c r="AA111" t="s">
+        <v>352</v>
+      </c>
+      <c r="AF111" t="s">
+        <v>362</v>
+      </c>
+      <c r="AG111" t="s">
         <v>353</v>
-      </c>
-      <c r="AF111" t="s">
-        <v>364</v>
-      </c>
-      <c r="AG111" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="112" spans="1:33">
@@ -9065,10 +9059,10 @@
         <v>209</v>
       </c>
       <c r="AF112" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG112" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="113" spans="1:33">
@@ -9139,10 +9133,10 @@
         <v>209</v>
       </c>
       <c r="AF113" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG113" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="114" spans="1:33">
@@ -9213,10 +9207,10 @@
         <v>209</v>
       </c>
       <c r="AF114" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG114" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="115" spans="1:33">
@@ -9287,10 +9281,10 @@
         <v>212</v>
       </c>
       <c r="AF115" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG115" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="116" spans="1:33">
@@ -9361,10 +9355,10 @@
         <v>213</v>
       </c>
       <c r="AF116" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG116" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="117" spans="1:33">
@@ -9435,10 +9429,10 @@
         <v>214</v>
       </c>
       <c r="AF117" t="s">
+        <v>362</v>
+      </c>
+      <c r="AG117" t="s">
         <v>364</v>
-      </c>
-      <c r="AG117" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="118" spans="1:33">
@@ -9509,10 +9503,10 @@
         <v>215</v>
       </c>
       <c r="AF118" t="s">
+        <v>362</v>
+      </c>
+      <c r="AG118" t="s">
         <v>364</v>
-      </c>
-      <c r="AG118" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="119" spans="1:33">
@@ -9583,10 +9577,10 @@
         <v>209</v>
       </c>
       <c r="AF119" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG119" t="s">
         <v>363</v>
-      </c>
-      <c r="AG119" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="120" spans="1:33">
@@ -9651,7 +9645,7 @@
         <v>210</v>
       </c>
       <c r="AF120" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="121" spans="1:33">
@@ -9713,13 +9707,13 @@
         <v>0</v>
       </c>
       <c r="AA121" t="s">
+        <v>352</v>
+      </c>
+      <c r="AF121" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG121" t="s">
         <v>353</v>
-      </c>
-      <c r="AF121" t="s">
-        <v>363</v>
-      </c>
-      <c r="AG121" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="122" spans="1:33">
@@ -9784,10 +9778,10 @@
         <v>209</v>
       </c>
       <c r="AF122" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG122" t="s">
         <v>363</v>
-      </c>
-      <c r="AG122" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="123" spans="1:33">
@@ -9852,10 +9846,10 @@
         <v>209</v>
       </c>
       <c r="AF123" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG123" t="s">
         <v>363</v>
-      </c>
-      <c r="AG123" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="124" spans="1:33">
@@ -9920,10 +9914,10 @@
         <v>209</v>
       </c>
       <c r="AF124" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG124" t="s">
         <v>363</v>
-      </c>
-      <c r="AG124" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="125" spans="1:33">
@@ -9988,10 +9982,10 @@
         <v>212</v>
       </c>
       <c r="AF125" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG125" t="s">
         <v>363</v>
-      </c>
-      <c r="AG125" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="126" spans="1:33">
@@ -10056,10 +10050,10 @@
         <v>213</v>
       </c>
       <c r="AF126" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG126" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="127" spans="1:33">
@@ -10124,10 +10118,10 @@
         <v>214</v>
       </c>
       <c r="AF127" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG127" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="128" spans="1:33">
@@ -10192,10 +10186,10 @@
         <v>215</v>
       </c>
       <c r="AF128" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG128" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="129" spans="1:33">
@@ -10266,10 +10260,10 @@
         <v>209</v>
       </c>
       <c r="AF129" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG129" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="130" spans="1:33">
@@ -10340,10 +10334,10 @@
         <v>209</v>
       </c>
       <c r="AF130" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG130" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="131" spans="1:33">
@@ -10411,7 +10405,7 @@
         <v>215</v>
       </c>
       <c r="AF131" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="132" spans="1:33">
@@ -10479,7 +10473,7 @@
         <v>215</v>
       </c>
       <c r="AF132" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="133" spans="1:33">
@@ -10547,7 +10541,7 @@
         <v>215</v>
       </c>
       <c r="AF133" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="134" spans="1:33">
@@ -10612,7 +10606,7 @@
         <v>216</v>
       </c>
       <c r="AF134" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG134" t="s">
         <v>216</v>
@@ -10680,7 +10674,7 @@
         <v>216</v>
       </c>
       <c r="AF135" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG135" t="s">
         <v>216</v>
@@ -10754,7 +10748,7 @@
         <v>216</v>
       </c>
       <c r="AF136" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="137" spans="1:33">
@@ -10819,7 +10813,7 @@
         <v>218</v>
       </c>
       <c r="AF137" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG137" t="s">
         <v>216</v>
@@ -10887,7 +10881,7 @@
         <v>216</v>
       </c>
       <c r="AF138" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG138" t="s">
         <v>216</v>
@@ -10955,7 +10949,7 @@
         <v>216</v>
       </c>
       <c r="AF139" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG139" t="s">
         <v>216</v>
@@ -11023,7 +11017,7 @@
         <v>216</v>
       </c>
       <c r="AF140" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG140" t="s">
         <v>216</v>
@@ -11091,7 +11085,7 @@
         <v>216</v>
       </c>
       <c r="AF141" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="142" spans="1:33">
@@ -11156,7 +11150,7 @@
         <v>218</v>
       </c>
       <c r="AF142" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG142" t="s">
         <v>216</v>
@@ -11224,7 +11218,7 @@
         <v>216</v>
       </c>
       <c r="AF143" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG143" t="s">
         <v>216</v>
@@ -11292,7 +11286,7 @@
         <v>216</v>
       </c>
       <c r="AF144" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG144" t="s">
         <v>216</v>
@@ -11360,7 +11354,7 @@
         <v>216</v>
       </c>
       <c r="AF145" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG145" t="s">
         <v>216</v>
@@ -11428,7 +11422,7 @@
         <v>216</v>
       </c>
       <c r="AF146" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="147" spans="1:33">
@@ -11493,7 +11487,7 @@
         <v>218</v>
       </c>
       <c r="AF147" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG147" t="s">
         <v>216</v>
@@ -11561,7 +11555,7 @@
         <v>216</v>
       </c>
       <c r="AF148" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG148" t="s">
         <v>216</v>
@@ -11629,7 +11623,7 @@
         <v>216</v>
       </c>
       <c r="AF149" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG149" t="s">
         <v>216</v>
@@ -11697,7 +11691,7 @@
         <v>218</v>
       </c>
       <c r="AF150" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG150" t="s">
         <v>216</v>
@@ -11771,7 +11765,7 @@
         <v>216</v>
       </c>
       <c r="AF151" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG151" t="s">
         <v>216</v>
@@ -11839,7 +11833,7 @@
         <v>216</v>
       </c>
       <c r="AF152" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="153" spans="1:33">
@@ -11904,7 +11898,7 @@
         <v>216</v>
       </c>
       <c r="AF153" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG153" t="s">
         <v>216</v>
@@ -11972,7 +11966,7 @@
         <v>216</v>
       </c>
       <c r="AF154" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG154" t="s">
         <v>216</v>
@@ -12040,7 +12034,7 @@
         <v>216</v>
       </c>
       <c r="AF155" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG155" t="s">
         <v>216</v>
@@ -12108,7 +12102,7 @@
         <v>216</v>
       </c>
       <c r="AF156" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="157" spans="1:33">
@@ -12173,7 +12167,7 @@
         <v>218</v>
       </c>
       <c r="AF157" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG157" t="s">
         <v>216</v>
@@ -12241,7 +12235,7 @@
         <v>216</v>
       </c>
       <c r="AF158" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG158" t="s">
         <v>216</v>
@@ -12309,7 +12303,7 @@
         <v>216</v>
       </c>
       <c r="AF159" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG159" t="s">
         <v>216</v>
@@ -12377,7 +12371,7 @@
         <v>216</v>
       </c>
       <c r="AF160" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="161" spans="1:33">
@@ -12442,7 +12436,7 @@
         <v>218</v>
       </c>
       <c r="AF161" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG161" t="s">
         <v>216</v>
@@ -12507,10 +12501,10 @@
         <v>0</v>
       </c>
       <c r="AA162" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF162" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="163" spans="1:33">
@@ -12572,10 +12566,10 @@
         <v>0</v>
       </c>
       <c r="AA163" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF163" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG163" t="s">
         <v>216</v>
@@ -12640,10 +12634,10 @@
         <v>0</v>
       </c>
       <c r="AA164" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF164" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG164" t="s">
         <v>216</v>
@@ -12708,10 +12702,10 @@
         <v>0</v>
       </c>
       <c r="AA165" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF165" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="166" spans="1:33">
@@ -12773,10 +12767,10 @@
         <v>0</v>
       </c>
       <c r="AA166" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF166" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG166" t="s">
         <v>216</v>
@@ -12844,7 +12838,7 @@
         <v>216</v>
       </c>
       <c r="AF167" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG167" t="s">
         <v>216</v>
@@ -12912,7 +12906,7 @@
         <v>216</v>
       </c>
       <c r="AF168" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG168" t="s">
         <v>216</v>
@@ -12980,7 +12974,7 @@
         <v>216</v>
       </c>
       <c r="AF169" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG169" t="s">
         <v>216</v>
@@ -13048,7 +13042,7 @@
         <v>216</v>
       </c>
       <c r="AF170" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="171" spans="1:33">
@@ -13113,7 +13107,7 @@
         <v>218</v>
       </c>
       <c r="AF171" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG171" t="s">
         <v>216</v>
@@ -13181,7 +13175,7 @@
         <v>216</v>
       </c>
       <c r="AF172" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG172" t="s">
         <v>216</v>
@@ -13249,7 +13243,7 @@
         <v>216</v>
       </c>
       <c r="AF173" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG173" t="s">
         <v>216</v>
@@ -13317,7 +13311,7 @@
         <v>216</v>
       </c>
       <c r="AF174" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG174" t="s">
         <v>216</v>
@@ -13385,7 +13379,7 @@
         <v>216</v>
       </c>
       <c r="AF175" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="176" spans="1:33">
@@ -13450,7 +13444,7 @@
         <v>218</v>
       </c>
       <c r="AF176" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG176" t="s">
         <v>216</v>
@@ -13518,10 +13512,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AF177" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG177" t="s">
         <v>216</v>
@@ -13595,7 +13589,7 @@
         <v>218</v>
       </c>
       <c r="AF178" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG178" t="s">
         <v>216</v>
@@ -13663,10 +13657,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AF179" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG179" t="s">
         <v>216</v>
@@ -13737,7 +13731,7 @@
         <v>219</v>
       </c>
       <c r="AF180" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG180" t="s">
         <v>216</v>
@@ -13811,7 +13805,7 @@
         <v>217</v>
       </c>
       <c r="AF181" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG181" t="s">
         <v>216</v>
@@ -13879,7 +13873,7 @@
         <v>216</v>
       </c>
       <c r="AF182" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG182" t="s">
         <v>216</v>
@@ -13953,7 +13947,7 @@
         <v>218</v>
       </c>
       <c r="AF183" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG183" t="s">
         <v>216</v>
@@ -14021,7 +14015,7 @@
         <v>219</v>
       </c>
       <c r="AF184" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG184" t="s">
         <v>216</v>
@@ -14089,7 +14083,7 @@
         <v>219</v>
       </c>
       <c r="AF185" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG185" t="s">
         <v>216</v>
@@ -14157,10 +14151,10 @@
         <v>220</v>
       </c>
       <c r="AF186" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG186" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="187" spans="1:33">
@@ -14225,10 +14219,10 @@
         <v>220</v>
       </c>
       <c r="AF187" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG187" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="188" spans="1:33">
@@ -14299,10 +14293,10 @@
         <v>220</v>
       </c>
       <c r="AF188" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG188" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="189" spans="1:33">
@@ -14367,10 +14361,10 @@
         <v>220</v>
       </c>
       <c r="AF189" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG189" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="190" spans="1:33">
@@ -14435,10 +14429,10 @@
         <v>220</v>
       </c>
       <c r="AF190" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG190" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="191" spans="1:33">
@@ -14503,10 +14497,10 @@
         <v>220</v>
       </c>
       <c r="AF191" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG191" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="192" spans="1:33">
@@ -14571,10 +14565,10 @@
         <v>220</v>
       </c>
       <c r="AF192" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG192" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="193" spans="1:33">
@@ -14645,10 +14639,10 @@
         <v>220</v>
       </c>
       <c r="AF193" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG193" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="194" spans="1:33">
@@ -14713,10 +14707,10 @@
         <v>220</v>
       </c>
       <c r="AF194" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG194" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="195" spans="1:33">
@@ -14778,13 +14772,13 @@
         <v>0</v>
       </c>
       <c r="AA195" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF195" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG195" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="196" spans="1:33">
@@ -14846,13 +14840,13 @@
         <v>0</v>
       </c>
       <c r="AA196" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF196" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG196" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="197" spans="1:33">
@@ -14920,13 +14914,13 @@
         <v>0</v>
       </c>
       <c r="AA197" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF197" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG197" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="198" spans="1:33">
@@ -14988,13 +14982,13 @@
         <v>0</v>
       </c>
       <c r="AA198" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF198" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG198" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="199" spans="1:33">
@@ -15056,13 +15050,13 @@
         <v>0</v>
       </c>
       <c r="AA199" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF199" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG199" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="200" spans="1:33">
@@ -15124,13 +15118,13 @@
         <v>0</v>
       </c>
       <c r="AA200" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF200" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG200" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="201" spans="1:33">
@@ -15195,10 +15189,10 @@
         <v>220</v>
       </c>
       <c r="AF201" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG201" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="202" spans="1:33">
@@ -15260,13 +15254,13 @@
         <v>0</v>
       </c>
       <c r="AA202" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF202" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG202" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="203" spans="1:33">
@@ -15328,13 +15322,13 @@
         <v>0</v>
       </c>
       <c r="AA203" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF203" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG203" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="204" spans="1:33">
@@ -15396,13 +15390,13 @@
         <v>0</v>
       </c>
       <c r="AA204" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF204" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG204" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="205" spans="1:33">
@@ -15464,13 +15458,13 @@
         <v>0</v>
       </c>
       <c r="AA205" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF205" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG205" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="206" spans="1:33">
@@ -15532,13 +15526,13 @@
         <v>0</v>
       </c>
       <c r="AA206" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF206" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG206" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="207" spans="1:33">
@@ -15600,13 +15594,13 @@
         <v>0</v>
       </c>
       <c r="AA207" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF207" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG207" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="208" spans="1:33">
@@ -15671,10 +15665,10 @@
         <v>220</v>
       </c>
       <c r="AF208" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG208" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="209" spans="1:33">
@@ -15739,10 +15733,10 @@
         <v>220</v>
       </c>
       <c r="AF209" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG209" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="210" spans="1:33">
@@ -15807,10 +15801,10 @@
         <v>220</v>
       </c>
       <c r="AF210" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG210" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="211" spans="1:33">
@@ -15881,10 +15875,10 @@
         <v>220</v>
       </c>
       <c r="AF211" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG211" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="212" spans="1:33">
@@ -15955,10 +15949,10 @@
         <v>220</v>
       </c>
       <c r="AF212" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG212" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="213" spans="1:33">
@@ -16023,10 +16017,10 @@
         <v>220</v>
       </c>
       <c r="AF213" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG213" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="214" spans="1:33">
@@ -16091,10 +16085,10 @@
         <v>220</v>
       </c>
       <c r="AF214" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG214" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="215" spans="1:33">
@@ -16159,13 +16153,13 @@
         <v>0</v>
       </c>
       <c r="AA215" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF215" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG215" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="216" spans="1:33">
@@ -16230,13 +16224,13 @@
         <v>0</v>
       </c>
       <c r="AA216" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF216" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG216" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="217" spans="1:33">
@@ -16298,13 +16292,13 @@
         <v>0</v>
       </c>
       <c r="AA217" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AF217" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG217" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="218" spans="1:33">
@@ -16369,10 +16363,10 @@
         <v>0</v>
       </c>
       <c r="AA218" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF218" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="219" spans="1:33">
@@ -16440,7 +16434,7 @@
         <v>221</v>
       </c>
       <c r="AF219" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="220" spans="1:33">
@@ -16508,7 +16502,7 @@
         <v>221</v>
       </c>
       <c r="AF220" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="221" spans="1:33">
@@ -16576,7 +16570,7 @@
         <v>221</v>
       </c>
       <c r="AF221" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="222" spans="1:33">
@@ -16644,7 +16638,7 @@
         <v>221</v>
       </c>
       <c r="AF222" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="223" spans="1:33">
@@ -16709,7 +16703,7 @@
         <v>221</v>
       </c>
       <c r="AF223" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="224" spans="1:33">
@@ -16771,10 +16765,10 @@
         <v>0</v>
       </c>
       <c r="AA224" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF224" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="225" spans="1:32">
@@ -16836,10 +16830,10 @@
         <v>0</v>
       </c>
       <c r="AA225" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF225" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="226" spans="1:32">
@@ -16904,10 +16898,10 @@
         <v>0</v>
       </c>
       <c r="AA226" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF226" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="227" spans="1:32">
@@ -16972,10 +16966,10 @@
         <v>0</v>
       </c>
       <c r="AA227" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF227" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="228" spans="1:32">
@@ -17043,7 +17037,7 @@
         <v>221</v>
       </c>
       <c r="AF228" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="229" spans="1:32">
@@ -17111,7 +17105,7 @@
         <v>221</v>
       </c>
       <c r="AF229" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="230" spans="1:32">
@@ -17179,7 +17173,7 @@
         <v>221</v>
       </c>
       <c r="AF230" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="231" spans="1:32">
@@ -17247,10 +17241,10 @@
         <v>0</v>
       </c>
       <c r="AA231" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF231" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="232" spans="1:32">
@@ -17318,10 +17312,10 @@
         <v>0</v>
       </c>
       <c r="AA232" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF232" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="233" spans="1:32">
@@ -17389,10 +17383,10 @@
         <v>0</v>
       </c>
       <c r="AA233" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF233" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="234" spans="1:32">
@@ -17460,10 +17454,10 @@
         <v>0</v>
       </c>
       <c r="AA234" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF234" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="235" spans="1:32">
@@ -17531,10 +17525,10 @@
         <v>0</v>
       </c>
       <c r="AA235" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF235" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="236" spans="1:32">
@@ -17602,10 +17596,10 @@
         <v>0</v>
       </c>
       <c r="AA236" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF236" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="237" spans="1:32">
@@ -17673,10 +17667,10 @@
         <v>0</v>
       </c>
       <c r="AA237" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF237" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="238" spans="1:32">
@@ -17744,10 +17738,10 @@
         <v>0</v>
       </c>
       <c r="AA238" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF238" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="239" spans="1:32">
@@ -17815,10 +17809,10 @@
         <v>0</v>
       </c>
       <c r="AA239" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF239" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="240" spans="1:32">
@@ -17886,10 +17880,10 @@
         <v>0</v>
       </c>
       <c r="AA240" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF240" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="241" spans="1:32">
@@ -17957,10 +17951,10 @@
         <v>0</v>
       </c>
       <c r="AA241" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF241" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="242" spans="1:32">
@@ -18028,10 +18022,10 @@
         <v>0</v>
       </c>
       <c r="AA242" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF242" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="243" spans="1:32">
@@ -18099,10 +18093,10 @@
         <v>0</v>
       </c>
       <c r="AA243" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF243" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="244" spans="1:32">
@@ -18170,10 +18164,10 @@
         <v>0</v>
       </c>
       <c r="AA244" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF244" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="245" spans="1:32">
@@ -18235,10 +18229,10 @@
         <v>0</v>
       </c>
       <c r="AA245" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF245" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="246" spans="1:32">
@@ -18300,10 +18294,10 @@
         <v>0</v>
       </c>
       <c r="AA246" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF246" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="247" spans="1:32">
@@ -18365,10 +18359,10 @@
         <v>0</v>
       </c>
       <c r="AA247" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AF247" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="248" spans="1:32">
@@ -18430,10 +18424,10 @@
         <v>0</v>
       </c>
       <c r="AA248" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AF248" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="249" spans="1:32">
@@ -18495,10 +18489,10 @@
         <v>0</v>
       </c>
       <c r="AA249" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF249" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="250" spans="1:32">
@@ -18560,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA250" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF250" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="251" spans="1:32">
@@ -18625,10 +18619,10 @@
         <v>0</v>
       </c>
       <c r="AA251" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF251" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="252" spans="1:32">
@@ -18690,10 +18684,10 @@
         <v>0</v>
       </c>
       <c r="AA252" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF252" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="253" spans="1:32">
@@ -18755,10 +18749,10 @@
         <v>0</v>
       </c>
       <c r="AA253" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF253" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="254" spans="1:32">
@@ -18820,10 +18814,10 @@
         <v>0</v>
       </c>
       <c r="AA254" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF254" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="255" spans="1:32">
@@ -18885,10 +18879,10 @@
         <v>0</v>
       </c>
       <c r="AA255" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF255" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="256" spans="1:32">
@@ -18953,7 +18947,7 @@
         <v>221</v>
       </c>
       <c r="AF256" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="257" spans="1:32">
@@ -19018,7 +19012,7 @@
         <v>221</v>
       </c>
       <c r="AF257" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="258" spans="1:32">
@@ -19083,7 +19077,7 @@
         <v>221</v>
       </c>
       <c r="AF258" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="259" spans="1:32">
@@ -19148,7 +19142,7 @@
         <v>221</v>
       </c>
       <c r="AF259" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="260" spans="1:32">
@@ -19213,7 +19207,7 @@
         <v>221</v>
       </c>
       <c r="AF260" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="261" spans="1:32">
@@ -19278,7 +19272,7 @@
         <v>221</v>
       </c>
       <c r="AF261" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="262" spans="1:32">
@@ -19343,7 +19337,7 @@
         <v>221</v>
       </c>
       <c r="AF262" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="263" spans="1:32">
@@ -19405,10 +19399,10 @@
         <v>0</v>
       </c>
       <c r="AA263" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF263" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="264" spans="1:32">
@@ -19470,10 +19464,10 @@
         <v>0</v>
       </c>
       <c r="AA264" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF264" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="265" spans="1:32">
@@ -19535,10 +19529,10 @@
         <v>0</v>
       </c>
       <c r="AA265" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF265" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="266" spans="1:32">
@@ -19600,10 +19594,10 @@
         <v>0</v>
       </c>
       <c r="AA266" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF266" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="267" spans="1:32">
@@ -19665,10 +19659,10 @@
         <v>0</v>
       </c>
       <c r="AA267" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF267" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="268" spans="1:32">
@@ -19730,10 +19724,10 @@
         <v>0</v>
       </c>
       <c r="AA268" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF268" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="269" spans="1:32">
@@ -19795,10 +19789,10 @@
         <v>0</v>
       </c>
       <c r="AA269" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF269" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="270" spans="1:32">
@@ -19860,10 +19854,10 @@
         <v>0</v>
       </c>
       <c r="AA270" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF270" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="271" spans="1:32">
@@ -19925,10 +19919,10 @@
         <v>0</v>
       </c>
       <c r="AA271" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF271" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="272" spans="1:32">
@@ -19990,10 +19984,10 @@
         <v>0</v>
       </c>
       <c r="AA272" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF272" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="273" spans="1:32">
@@ -20055,10 +20049,10 @@
         <v>0</v>
       </c>
       <c r="AA273" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF273" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="274" spans="1:32">
@@ -20120,10 +20114,10 @@
         <v>0</v>
       </c>
       <c r="AA274" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF274" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="275" spans="1:32">
@@ -20185,10 +20179,10 @@
         <v>0</v>
       </c>
       <c r="AA275" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF275" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="276" spans="1:32">
@@ -20250,10 +20244,10 @@
         <v>0</v>
       </c>
       <c r="AA276" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AF276" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="277" spans="1:32">
@@ -20315,10 +20309,10 @@
         <v>0</v>
       </c>
       <c r="AA277" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF277" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="278" spans="1:32">
@@ -20380,10 +20374,10 @@
         <v>0</v>
       </c>
       <c r="AA278" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF278" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="279" spans="1:32">
@@ -20445,10 +20439,10 @@
         <v>0</v>
       </c>
       <c r="AA279" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AF279" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="280" spans="1:32">
@@ -20510,10 +20504,10 @@
         <v>0</v>
       </c>
       <c r="AA280" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AF280" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="281" spans="1:32">
@@ -20575,10 +20569,10 @@
         <v>0</v>
       </c>
       <c r="AA281" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF281" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="282" spans="1:32">
@@ -20640,10 +20634,10 @@
         <v>0</v>
       </c>
       <c r="AA282" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF282" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="283" spans="1:32">
@@ -20705,10 +20699,10 @@
         <v>0</v>
       </c>
       <c r="AA283" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF283" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="284" spans="1:32">
@@ -20770,10 +20764,10 @@
         <v>0</v>
       </c>
       <c r="AA284" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF284" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="285" spans="1:32">
@@ -20835,10 +20829,10 @@
         <v>0</v>
       </c>
       <c r="AA285" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF285" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="286" spans="1:32">
@@ -20900,10 +20894,10 @@
         <v>0</v>
       </c>
       <c r="AA286" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF286" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="287" spans="1:32">
@@ -20965,10 +20959,10 @@
         <v>0</v>
       </c>
       <c r="AA287" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF287" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="288" spans="1:32">
@@ -21033,7 +21027,7 @@
         <v>230</v>
       </c>
       <c r="AF288" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="289" spans="1:33">
@@ -21098,7 +21092,7 @@
         <v>230</v>
       </c>
       <c r="AF289" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="290" spans="1:33">
@@ -21163,7 +21157,7 @@
         <v>230</v>
       </c>
       <c r="AF290" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="291" spans="1:33">
@@ -21228,7 +21222,7 @@
         <v>230</v>
       </c>
       <c r="AF291" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="292" spans="1:33">
@@ -21293,7 +21287,7 @@
         <v>230</v>
       </c>
       <c r="AF292" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="293" spans="1:33">
@@ -21358,7 +21352,7 @@
         <v>230</v>
       </c>
       <c r="AF293" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="294" spans="1:33">
@@ -21423,7 +21417,7 @@
         <v>230</v>
       </c>
       <c r="AF294" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="295" spans="1:33">
@@ -21488,7 +21482,7 @@
         <v>230</v>
       </c>
       <c r="AF295" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="296" spans="1:33">
@@ -21556,7 +21550,7 @@
         <v>222</v>
       </c>
       <c r="AF296" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="297" spans="1:33">
@@ -21615,10 +21609,10 @@
         <v>0</v>
       </c>
       <c r="AF297" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG297" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="298" spans="1:33">
@@ -21677,10 +21671,10 @@
         <v>0</v>
       </c>
       <c r="AF298" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG298" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="299" spans="1:33">
@@ -21739,10 +21733,10 @@
         <v>0</v>
       </c>
       <c r="AF299" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG299" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="300" spans="1:33">
@@ -21801,10 +21795,10 @@
         <v>0</v>
       </c>
       <c r="AF300" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG300" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="301" spans="1:33">
@@ -21863,10 +21857,10 @@
         <v>0</v>
       </c>
       <c r="AF301" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG301" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="302" spans="1:33">
@@ -21925,10 +21919,10 @@
         <v>0</v>
       </c>
       <c r="AF302" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG302" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="303" spans="1:33">
@@ -21987,10 +21981,10 @@
         <v>0</v>
       </c>
       <c r="AF303" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG303" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="304" spans="1:33">
@@ -22049,10 +22043,10 @@
         <v>0</v>
       </c>
       <c r="AF304" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG304" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="305" spans="1:33">
@@ -22111,10 +22105,10 @@
         <v>0</v>
       </c>
       <c r="AF305" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG305" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="306" spans="1:33">
@@ -22173,10 +22167,10 @@
         <v>0</v>
       </c>
       <c r="AF306" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG306" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="307" spans="1:33">
@@ -22235,10 +22229,10 @@
         <v>0</v>
       </c>
       <c r="AF307" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG307" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="308" spans="1:33">
@@ -22297,10 +22291,10 @@
         <v>0</v>
       </c>
       <c r="AF308" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG308" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="309" spans="1:33">
@@ -22359,10 +22353,10 @@
         <v>0</v>
       </c>
       <c r="AF309" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG309" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="310" spans="1:33">
@@ -22421,10 +22415,10 @@
         <v>0</v>
       </c>
       <c r="AF310" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG310" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="311" spans="1:33">
@@ -22483,10 +22477,10 @@
         <v>0</v>
       </c>
       <c r="AF311" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG311" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="312" spans="1:33">
@@ -22545,10 +22539,10 @@
         <v>0</v>
       </c>
       <c r="AF312" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG312" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="313" spans="1:33">
@@ -22607,10 +22601,10 @@
         <v>0</v>
       </c>
       <c r="AF313" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG313" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="314" spans="1:33">
@@ -22669,10 +22663,10 @@
         <v>0</v>
       </c>
       <c r="AF314" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG314" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="315" spans="1:33">
@@ -22731,10 +22725,10 @@
         <v>0</v>
       </c>
       <c r="AF315" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG315" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="316" spans="1:33">
@@ -22793,10 +22787,10 @@
         <v>0</v>
       </c>
       <c r="AF316" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG316" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="317" spans="1:33">
@@ -22855,10 +22849,10 @@
         <v>0</v>
       </c>
       <c r="AF317" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG317" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="318" spans="1:33">
@@ -22917,10 +22911,10 @@
         <v>0</v>
       </c>
       <c r="AF318" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG318" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="319" spans="1:33">
@@ -22979,10 +22973,10 @@
         <v>0</v>
       </c>
       <c r="AF319" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG319" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="320" spans="1:33">
@@ -23041,10 +23035,10 @@
         <v>0</v>
       </c>
       <c r="AF320" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG320" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="321" spans="1:33">
@@ -23103,10 +23097,10 @@
         <v>0</v>
       </c>
       <c r="AF321" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG321" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="322" spans="1:33">
@@ -23165,10 +23159,10 @@
         <v>0</v>
       </c>
       <c r="AF322" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG322" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="323" spans="1:33">
@@ -23227,10 +23221,10 @@
         <v>0</v>
       </c>
       <c r="AF323" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG323" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="324" spans="1:33">
@@ -23289,10 +23283,10 @@
         <v>0</v>
       </c>
       <c r="AF324" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG324" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="325" spans="1:33">
@@ -23351,10 +23345,10 @@
         <v>0</v>
       </c>
       <c r="AF325" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG325" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="326" spans="1:33">
@@ -23413,10 +23407,10 @@
         <v>0</v>
       </c>
       <c r="AF326" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG326" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="327" spans="1:33">
@@ -23475,10 +23469,10 @@
         <v>0</v>
       </c>
       <c r="AF327" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG327" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="328" spans="1:33">
@@ -23537,10 +23531,10 @@
         <v>0</v>
       </c>
       <c r="AF328" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG328" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="329" spans="1:33">
@@ -23599,10 +23593,10 @@
         <v>0</v>
       </c>
       <c r="AF329" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG329" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="330" spans="1:33">
@@ -23661,10 +23655,10 @@
         <v>0</v>
       </c>
       <c r="AF330" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG330" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="331" spans="1:33">
@@ -23723,10 +23717,10 @@
         <v>0</v>
       </c>
       <c r="AF331" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG331" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="332" spans="1:33">
@@ -23785,10 +23779,10 @@
         <v>0</v>
       </c>
       <c r="AF332" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG332" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="333" spans="1:33">
@@ -23847,10 +23841,10 @@
         <v>0</v>
       </c>
       <c r="AF333" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG333" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="334" spans="1:33">
@@ -23909,10 +23903,10 @@
         <v>0</v>
       </c>
       <c r="AF334" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG334" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="335" spans="1:33">
@@ -23971,10 +23965,10 @@
         <v>0</v>
       </c>
       <c r="AF335" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG335" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="336" spans="1:33">
@@ -24033,10 +24027,10 @@
         <v>0</v>
       </c>
       <c r="AF336" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG336" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="337" spans="1:33">
@@ -24095,10 +24089,10 @@
         <v>0</v>
       </c>
       <c r="AF337" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG337" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="338" spans="1:33">
@@ -24157,10 +24151,10 @@
         <v>0</v>
       </c>
       <c r="AF338" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG338" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="339" spans="1:33">
@@ -24219,10 +24213,10 @@
         <v>0</v>
       </c>
       <c r="AF339" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG339" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="340" spans="1:33">
@@ -24281,10 +24275,10 @@
         <v>0</v>
       </c>
       <c r="AF340" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG340" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="341" spans="1:33">
@@ -24343,10 +24337,10 @@
         <v>0</v>
       </c>
       <c r="AF341" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG341" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="342" spans="1:33">
@@ -24405,10 +24399,10 @@
         <v>0</v>
       </c>
       <c r="AF342" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG342" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="343" spans="1:33">
@@ -24467,10 +24461,10 @@
         <v>0</v>
       </c>
       <c r="AF343" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG343" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="344" spans="1:33">
@@ -24529,10 +24523,10 @@
         <v>0</v>
       </c>
       <c r="AF344" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG344" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="345" spans="1:33">
@@ -24591,10 +24585,10 @@
         <v>0</v>
       </c>
       <c r="AF345" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG345" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="346" spans="1:33">
@@ -24653,10 +24647,10 @@
         <v>0</v>
       </c>
       <c r="AF346" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG346" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="347" spans="1:33">
@@ -24715,10 +24709,10 @@
         <v>0</v>
       </c>
       <c r="AF347" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG347" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="348" spans="1:33">
@@ -24777,10 +24771,10 @@
         <v>0</v>
       </c>
       <c r="AF348" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG348" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="349" spans="1:33">
@@ -24839,10 +24833,10 @@
         <v>0</v>
       </c>
       <c r="AF349" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG349" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="350" spans="1:33">
@@ -24901,10 +24895,10 @@
         <v>0</v>
       </c>
       <c r="AF350" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG350" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="351" spans="1:33">
@@ -24963,10 +24957,10 @@
         <v>0</v>
       </c>
       <c r="AF351" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG351" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="352" spans="1:33">
@@ -25025,7 +25019,7 @@
         <v>0</v>
       </c>
       <c r="AF352" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="353" spans="1:33">
@@ -25084,10 +25078,10 @@
         <v>0</v>
       </c>
       <c r="AF353" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG353" t="s">
         <v>363</v>
-      </c>
-      <c r="AG353" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="354" spans="1:33">
@@ -25152,10 +25146,10 @@
         <v>0</v>
       </c>
       <c r="AF354" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG354" t="s">
         <v>363</v>
-      </c>
-      <c r="AG354" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="355" spans="1:33">
@@ -25214,10 +25208,10 @@
         <v>0</v>
       </c>
       <c r="AF355" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG355" t="s">
         <v>363</v>
-      </c>
-      <c r="AG355" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="356" spans="1:33">
@@ -25276,10 +25270,10 @@
         <v>0</v>
       </c>
       <c r="AF356" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG356" t="s">
         <v>363</v>
-      </c>
-      <c r="AG356" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="357" spans="1:33">
@@ -25338,10 +25332,10 @@
         <v>0</v>
       </c>
       <c r="AF357" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG357" t="s">
         <v>363</v>
-      </c>
-      <c r="AG357" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="358" spans="1:33">
@@ -25400,10 +25394,10 @@
         <v>0</v>
       </c>
       <c r="AF358" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG358" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="359" spans="1:33">
@@ -25462,10 +25456,10 @@
         <v>0</v>
       </c>
       <c r="AF359" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG359" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="360" spans="1:33">
@@ -25524,10 +25518,10 @@
         <v>0</v>
       </c>
       <c r="AF360" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG360" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="361" spans="1:33">
@@ -25586,7 +25580,7 @@
         <v>0</v>
       </c>
       <c r="AF361" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="362" spans="1:33">
@@ -25645,10 +25639,10 @@
         <v>0</v>
       </c>
       <c r="AF362" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG362" t="s">
         <v>363</v>
-      </c>
-      <c r="AG362" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="363" spans="1:33">
@@ -25713,10 +25707,10 @@
         <v>0</v>
       </c>
       <c r="AF363" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG363" t="s">
         <v>363</v>
-      </c>
-      <c r="AG363" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="364" spans="1:33">
@@ -25775,10 +25769,10 @@
         <v>0</v>
       </c>
       <c r="AF364" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG364" t="s">
         <v>363</v>
-      </c>
-      <c r="AG364" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="365" spans="1:33">
@@ -25837,10 +25831,10 @@
         <v>0</v>
       </c>
       <c r="AF365" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG365" t="s">
         <v>363</v>
-      </c>
-      <c r="AG365" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="366" spans="1:33">
@@ -25899,10 +25893,10 @@
         <v>0</v>
       </c>
       <c r="AF366" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG366" t="s">
         <v>363</v>
-      </c>
-      <c r="AG366" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="367" spans="1:33">
@@ -25961,10 +25955,10 @@
         <v>0</v>
       </c>
       <c r="AF367" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG367" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="368" spans="1:33">
@@ -26023,10 +26017,10 @@
         <v>0</v>
       </c>
       <c r="AF368" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG368" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="369" spans="1:33">
@@ -26085,10 +26079,10 @@
         <v>0</v>
       </c>
       <c r="AF369" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG369" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="370" spans="1:33">
@@ -26147,7 +26141,7 @@
         <v>0</v>
       </c>
       <c r="AF370" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="371" spans="1:33">
@@ -26206,10 +26200,10 @@
         <v>0</v>
       </c>
       <c r="AF371" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG371" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="372" spans="1:33">
@@ -26268,10 +26262,10 @@
         <v>0</v>
       </c>
       <c r="AF372" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG372" t="s">
         <v>363</v>
-      </c>
-      <c r="AG372" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="373" spans="1:33">
@@ -26330,10 +26324,10 @@
         <v>0</v>
       </c>
       <c r="AF373" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG373" t="s">
         <v>363</v>
-      </c>
-      <c r="AG373" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="374" spans="1:33">
@@ -26392,10 +26386,10 @@
         <v>0</v>
       </c>
       <c r="AF374" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG374" t="s">
         <v>363</v>
-      </c>
-      <c r="AG374" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="375" spans="1:33">
@@ -26454,10 +26448,10 @@
         <v>0</v>
       </c>
       <c r="AF375" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG375" t="s">
         <v>363</v>
-      </c>
-      <c r="AG375" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="376" spans="1:33">
@@ -26522,10 +26516,10 @@
         <v>0</v>
       </c>
       <c r="AF376" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG376" t="s">
         <v>363</v>
-      </c>
-      <c r="AG376" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="377" spans="1:33">
@@ -26584,10 +26578,10 @@
         <v>0</v>
       </c>
       <c r="AF377" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG377" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="378" spans="1:33">
@@ -26646,10 +26640,10 @@
         <v>0</v>
       </c>
       <c r="AF378" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG378" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="379" spans="1:33">
@@ -26708,10 +26702,10 @@
         <v>0</v>
       </c>
       <c r="AF379" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG379" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="380" spans="1:33">
@@ -26770,10 +26764,10 @@
         <v>0</v>
       </c>
       <c r="AF380" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG380" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="381" spans="1:33">
@@ -26832,7 +26826,7 @@
         <v>0</v>
       </c>
       <c r="AF381" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="382" spans="1:33">
@@ -26891,10 +26885,10 @@
         <v>0</v>
       </c>
       <c r="AF382" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG382" t="s">
         <v>363</v>
-      </c>
-      <c r="AG382" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="383" spans="1:33">
@@ -26959,10 +26953,10 @@
         <v>0</v>
       </c>
       <c r="AF383" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG383" t="s">
         <v>363</v>
-      </c>
-      <c r="AG383" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="384" spans="1:33">
@@ -27021,10 +27015,10 @@
         <v>0</v>
       </c>
       <c r="AF384" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG384" t="s">
         <v>363</v>
-      </c>
-      <c r="AG384" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="385" spans="1:33">
@@ -27083,10 +27077,10 @@
         <v>0</v>
       </c>
       <c r="AF385" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG385" t="s">
         <v>363</v>
-      </c>
-      <c r="AG385" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="386" spans="1:33">
@@ -27145,10 +27139,10 @@
         <v>0</v>
       </c>
       <c r="AF386" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG386" t="s">
         <v>363</v>
-      </c>
-      <c r="AG386" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="387" spans="1:33">
@@ -27207,10 +27201,10 @@
         <v>0</v>
       </c>
       <c r="AF387" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG387" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="388" spans="1:33">
@@ -27269,10 +27263,10 @@
         <v>0</v>
       </c>
       <c r="AF388" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG388" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="389" spans="1:33">
@@ -27331,10 +27325,10 @@
         <v>0</v>
       </c>
       <c r="AF389" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG389" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="390" spans="1:33">
@@ -27393,10 +27387,10 @@
         <v>0</v>
       </c>
       <c r="AF390" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG390" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="391" spans="1:33">
@@ -27455,10 +27449,10 @@
         <v>0</v>
       </c>
       <c r="AF391" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG391" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="392" spans="1:33">
@@ -27517,10 +27511,10 @@
         <v>0</v>
       </c>
       <c r="AF392" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG392" t="s">
         <v>363</v>
-      </c>
-      <c r="AG392" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="393" spans="1:33">
@@ -27579,7 +27573,7 @@
         <v>0</v>
       </c>
       <c r="AF393" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="394" spans="1:33">
@@ -27638,10 +27632,10 @@
         <v>0</v>
       </c>
       <c r="AF394" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG394" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="395" spans="1:33">
@@ -27700,10 +27694,10 @@
         <v>0</v>
       </c>
       <c r="AF395" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG395" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="396" spans="1:33">
@@ -27762,10 +27756,10 @@
         <v>0</v>
       </c>
       <c r="AF396" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG396" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="397" spans="1:33">
@@ -27824,10 +27818,10 @@
         <v>0</v>
       </c>
       <c r="AF397" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG397" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="398" spans="1:33">
@@ -27886,10 +27880,10 @@
         <v>0</v>
       </c>
       <c r="AF398" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG398" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="399" spans="1:33">
@@ -27948,10 +27942,10 @@
         <v>0</v>
       </c>
       <c r="AF399" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG399" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="400" spans="1:33">
@@ -28010,10 +28004,10 @@
         <v>0</v>
       </c>
       <c r="AF400" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG400" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="401" spans="1:33">
@@ -28072,7 +28066,7 @@
         <v>0</v>
       </c>
       <c r="AF401" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="402" spans="1:33">
@@ -28131,10 +28125,10 @@
         <v>0</v>
       </c>
       <c r="AF402" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG402" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="403" spans="1:33">
@@ -28193,10 +28187,10 @@
         <v>0</v>
       </c>
       <c r="AF403" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG403" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="404" spans="1:33">
@@ -28255,10 +28249,10 @@
         <v>0</v>
       </c>
       <c r="AF404" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG404" t="s">
         <v>363</v>
-      </c>
-      <c r="AG404" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="405" spans="1:33">
@@ -28317,10 +28311,10 @@
         <v>0</v>
       </c>
       <c r="AF405" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG405" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="406" spans="1:33">
@@ -28385,10 +28379,10 @@
         <v>0</v>
       </c>
       <c r="AF406" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG406" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="407" spans="1:33">
@@ -28447,7 +28441,7 @@
         <v>0</v>
       </c>
       <c r="AF407" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG407" t="s">
         <v>216</v>
@@ -28509,7 +28503,7 @@
         <v>0</v>
       </c>
       <c r="AF408" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG408" t="s">
         <v>216</v>
@@ -28571,7 +28565,7 @@
         <v>0</v>
       </c>
       <c r="AF409" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG409" t="s">
         <v>216</v>
@@ -28639,7 +28633,7 @@
         <v>0</v>
       </c>
       <c r="AF410" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG410" t="s">
         <v>216</v>
@@ -28707,7 +28701,7 @@
         <v>0</v>
       </c>
       <c r="AF411" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG411" t="s">
         <v>216</v>
@@ -28775,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="AF412" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG412" t="s">
         <v>216</v>
@@ -28843,7 +28837,7 @@
         <v>0</v>
       </c>
       <c r="AF413" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG413" t="s">
         <v>216</v>
@@ -28905,7 +28899,7 @@
         <v>0</v>
       </c>
       <c r="AF414" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="415" spans="1:33">
@@ -28964,7 +28958,7 @@
         <v>0</v>
       </c>
       <c r="AF415" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG415" t="s">
         <v>216</v>
@@ -29026,7 +29020,7 @@
         <v>0</v>
       </c>
       <c r="AF416" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG416" t="s">
         <v>216</v>
@@ -29088,7 +29082,7 @@
         <v>0</v>
       </c>
       <c r="AF417" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG417" t="s">
         <v>216</v>
@@ -29150,7 +29144,7 @@
         <v>0</v>
       </c>
       <c r="AF418" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG418" t="s">
         <v>216</v>
@@ -29212,7 +29206,7 @@
         <v>0</v>
       </c>
       <c r="AF419" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="420" spans="1:33">
@@ -29271,7 +29265,7 @@
         <v>0</v>
       </c>
       <c r="AF420" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="421" spans="1:33">
@@ -29330,7 +29324,7 @@
         <v>0</v>
       </c>
       <c r="AF421" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG421" t="s">
         <v>216</v>
@@ -29392,7 +29386,7 @@
         <v>0</v>
       </c>
       <c r="AF422" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="423" spans="1:33">
@@ -29451,7 +29445,7 @@
         <v>0</v>
       </c>
       <c r="AF423" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG423" t="s">
         <v>216</v>
@@ -29513,7 +29507,7 @@
         <v>0</v>
       </c>
       <c r="AF424" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG424" t="s">
         <v>216</v>
@@ -29575,7 +29569,7 @@
         <v>0</v>
       </c>
       <c r="AF425" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG425" t="s">
         <v>216</v>
@@ -29637,7 +29631,7 @@
         <v>0</v>
       </c>
       <c r="AF426" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG426" t="s">
         <v>216</v>
@@ -29699,7 +29693,7 @@
         <v>0</v>
       </c>
       <c r="AF427" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG427" t="s">
         <v>216</v>
@@ -29761,7 +29755,7 @@
         <v>0</v>
       </c>
       <c r="AF428" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG428" t="s">
         <v>216</v>
@@ -29823,7 +29817,7 @@
         <v>0</v>
       </c>
       <c r="AF429" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG429" t="s">
         <v>216</v>
@@ -29885,7 +29879,7 @@
         <v>0</v>
       </c>
       <c r="AF430" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG430" t="s">
         <v>216</v>
@@ -29947,7 +29941,7 @@
         <v>0</v>
       </c>
       <c r="AF431" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG431" t="s">
         <v>216</v>
@@ -30009,7 +30003,7 @@
         <v>0</v>
       </c>
       <c r="AF432" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG432" t="s">
         <v>216</v>
@@ -30071,10 +30065,10 @@
         <v>0</v>
       </c>
       <c r="AF433" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG433" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="434" spans="1:33">
@@ -30133,10 +30127,10 @@
         <v>0</v>
       </c>
       <c r="AF434" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG434" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="435" spans="1:33">
@@ -30195,10 +30189,10 @@
         <v>0</v>
       </c>
       <c r="AF435" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG435" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="436" spans="1:33">
@@ -30257,10 +30251,10 @@
         <v>0</v>
       </c>
       <c r="AF436" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG436" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="437" spans="1:33">
@@ -30319,10 +30313,10 @@
         <v>0</v>
       </c>
       <c r="AF437" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG437" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="438" spans="1:33">
@@ -30381,10 +30375,10 @@
         <v>0</v>
       </c>
       <c r="AF438" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG438" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="439" spans="1:33">
@@ -30443,10 +30437,10 @@
         <v>0</v>
       </c>
       <c r="AF439" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG439" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="440" spans="1:33">
@@ -30505,10 +30499,10 @@
         <v>0</v>
       </c>
       <c r="AF440" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG440" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="441" spans="1:33">
@@ -30567,10 +30561,10 @@
         <v>0</v>
       </c>
       <c r="AF441" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG441" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="442" spans="1:33">
@@ -30629,10 +30623,10 @@
         <v>0</v>
       </c>
       <c r="AF442" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG442" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="443" spans="1:33">
@@ -30691,10 +30685,10 @@
         <v>0</v>
       </c>
       <c r="AF443" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG443" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="444" spans="1:33">
@@ -30753,10 +30747,10 @@
         <v>0</v>
       </c>
       <c r="AF444" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG444" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="445" spans="1:33">
@@ -30815,10 +30809,10 @@
         <v>0</v>
       </c>
       <c r="AF445" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG445" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="446" spans="1:33">
@@ -30877,10 +30871,10 @@
         <v>0</v>
       </c>
       <c r="AF446" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG446" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="447" spans="1:33">
@@ -30939,10 +30933,10 @@
         <v>0</v>
       </c>
       <c r="AF447" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG447" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="448" spans="1:33">
@@ -31001,10 +30995,10 @@
         <v>0</v>
       </c>
       <c r="AF448" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG448" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="449" spans="1:33">
@@ -31063,10 +31057,10 @@
         <v>0</v>
       </c>
       <c r="AF449" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG449" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="450" spans="1:33">
@@ -31125,10 +31119,10 @@
         <v>0</v>
       </c>
       <c r="AF450" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG450" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="451" spans="1:33">
@@ -31187,10 +31181,10 @@
         <v>0</v>
       </c>
       <c r="AF451" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG451" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="452" spans="1:33">
@@ -31249,10 +31243,10 @@
         <v>0</v>
       </c>
       <c r="AF452" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG452" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="453" spans="1:33">
@@ -31311,10 +31305,10 @@
         <v>0</v>
       </c>
       <c r="AF453" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG453" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="454" spans="1:33">
@@ -31373,10 +31367,10 @@
         <v>0</v>
       </c>
       <c r="AF454" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG454" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="455" spans="1:33">
@@ -31435,10 +31429,10 @@
         <v>0</v>
       </c>
       <c r="AF455" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG455" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="456" spans="1:33">
@@ -31497,7 +31491,7 @@
         <v>0</v>
       </c>
       <c r="AF456" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="457" spans="1:33">
@@ -31556,7 +31550,7 @@
         <v>0</v>
       </c>
       <c r="AF457" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="458" spans="1:33">
@@ -31615,7 +31609,7 @@
         <v>0</v>
       </c>
       <c r="AF458" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="459" spans="1:33">
@@ -31674,7 +31668,7 @@
         <v>0</v>
       </c>
       <c r="AF459" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="460" spans="1:33">
@@ -31733,7 +31727,7 @@
         <v>0</v>
       </c>
       <c r="AF460" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="461" spans="1:33">
@@ -31792,7 +31786,7 @@
         <v>0</v>
       </c>
       <c r="AF461" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="462" spans="1:33">
@@ -31851,7 +31845,7 @@
         <v>0</v>
       </c>
       <c r="AF462" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="463" spans="1:33">
@@ -31910,7 +31904,7 @@
         <v>0</v>
       </c>
       <c r="AF463" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="464" spans="1:33">
@@ -31969,7 +31963,7 @@
         <v>0</v>
       </c>
       <c r="AF464" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="465" spans="1:32">
@@ -32028,7 +32022,7 @@
         <v>0</v>
       </c>
       <c r="AF465" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="466" spans="1:32">
@@ -32087,7 +32081,7 @@
         <v>0</v>
       </c>
       <c r="AF466" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="467" spans="1:32">
@@ -32146,7 +32140,7 @@
         <v>0</v>
       </c>
       <c r="AF467" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="468" spans="1:32">
@@ -32205,7 +32199,7 @@
         <v>0</v>
       </c>
       <c r="AF468" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="469" spans="1:32">
@@ -32264,7 +32258,7 @@
         <v>0</v>
       </c>
       <c r="AF469" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="470" spans="1:32">
@@ -32323,7 +32317,7 @@
         <v>0</v>
       </c>
       <c r="AF470" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="471" spans="1:32">
@@ -32382,7 +32376,7 @@
         <v>0</v>
       </c>
       <c r="AF471" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="472" spans="1:32">
@@ -32441,7 +32435,7 @@
         <v>0</v>
       </c>
       <c r="AF472" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="473" spans="1:32">
@@ -32500,7 +32494,7 @@
         <v>0</v>
       </c>
       <c r="AF473" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="474" spans="1:32">
@@ -32559,7 +32553,7 @@
         <v>0</v>
       </c>
       <c r="AF474" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="475" spans="1:32">
@@ -32618,7 +32612,7 @@
         <v>0</v>
       </c>
       <c r="AF475" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="476" spans="1:32">
@@ -32677,7 +32671,7 @@
         <v>0</v>
       </c>
       <c r="AF476" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="477" spans="1:32">
@@ -32736,7 +32730,7 @@
         <v>0</v>
       </c>
       <c r="AF477" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="478" spans="1:32">
@@ -32795,7 +32789,7 @@
         <v>0</v>
       </c>
       <c r="AF478" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="479" spans="1:32">
@@ -32854,7 +32848,7 @@
         <v>0</v>
       </c>
       <c r="AF479" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="480" spans="1:32">
@@ -32913,7 +32907,7 @@
         <v>0</v>
       </c>
       <c r="AF480" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="481" spans="1:32">
@@ -32972,7 +32966,7 @@
         <v>0</v>
       </c>
       <c r="AF481" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="482" spans="1:32">
@@ -33031,7 +33025,7 @@
         <v>0</v>
       </c>
       <c r="AF482" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="483" spans="1:32">
@@ -33090,7 +33084,7 @@
         <v>0</v>
       </c>
       <c r="AF483" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="484" spans="1:32">
@@ -33149,7 +33143,7 @@
         <v>0</v>
       </c>
       <c r="AF484" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="485" spans="1:32">
@@ -33208,7 +33202,7 @@
         <v>0</v>
       </c>
       <c r="AF485" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="486" spans="1:32">
@@ -33267,7 +33261,7 @@
         <v>0</v>
       </c>
       <c r="AF486" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="487" spans="1:32">
@@ -33326,7 +33320,7 @@
         <v>0</v>
       </c>
       <c r="AF487" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="488" spans="1:32">
@@ -33385,7 +33379,7 @@
         <v>0</v>
       </c>
       <c r="AF488" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="489" spans="1:32">
@@ -33444,7 +33438,7 @@
         <v>0</v>
       </c>
       <c r="AF489" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="490" spans="1:32">
@@ -33503,7 +33497,7 @@
         <v>0</v>
       </c>
       <c r="AF490" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="491" spans="1:32">
@@ -33562,7 +33556,7 @@
         <v>0</v>
       </c>
       <c r="AF491" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="492" spans="1:32">
@@ -33621,7 +33615,7 @@
         <v>0</v>
       </c>
       <c r="AF492" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="493" spans="1:32">
@@ -33680,7 +33674,7 @@
         <v>0</v>
       </c>
       <c r="AF493" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="494" spans="1:32">
@@ -33739,7 +33733,7 @@
         <v>0</v>
       </c>
       <c r="AF494" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="495" spans="1:32">
@@ -33798,7 +33792,7 @@
         <v>0</v>
       </c>
       <c r="AF495" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="496" spans="1:32">
@@ -33857,7 +33851,7 @@
         <v>0</v>
       </c>
       <c r="AF496" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="497" spans="1:32">
@@ -33916,7 +33910,7 @@
         <v>0</v>
       </c>
       <c r="AF497" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="498" spans="1:32">
@@ -33975,7 +33969,7 @@
         <v>0</v>
       </c>
       <c r="AF498" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="499" spans="1:32">
@@ -34034,7 +34028,7 @@
         <v>0</v>
       </c>
       <c r="AF499" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="500" spans="1:32">
@@ -34093,7 +34087,7 @@
         <v>0</v>
       </c>
       <c r="AF500" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="501" spans="1:32">
@@ -34152,7 +34146,7 @@
         <v>0</v>
       </c>
       <c r="AF501" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="502" spans="1:32">
@@ -34211,7 +34205,7 @@
         <v>0</v>
       </c>
       <c r="AF502" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="503" spans="1:32">
@@ -34270,7 +34264,7 @@
         <v>0</v>
       </c>
       <c r="AF503" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="504" spans="1:32">
@@ -34329,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="AF504" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="505" spans="1:32">
@@ -34388,7 +34382,7 @@
         <v>0</v>
       </c>
       <c r="AF505" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="506" spans="1:32">
@@ -34447,7 +34441,7 @@
         <v>0</v>
       </c>
       <c r="AF506" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="507" spans="1:32">
@@ -34506,7 +34500,7 @@
         <v>0</v>
       </c>
       <c r="AF507" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="508" spans="1:32">
@@ -34565,7 +34559,7 @@
         <v>0</v>
       </c>
       <c r="AF508" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="509" spans="1:32">
@@ -34624,7 +34618,7 @@
         <v>0</v>
       </c>
       <c r="AF509" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="510" spans="1:32">
@@ -34683,7 +34677,7 @@
         <v>0</v>
       </c>
       <c r="AF510" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="511" spans="1:32">
@@ -34742,7 +34736,7 @@
         <v>0</v>
       </c>
       <c r="AF511" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="512" spans="1:32">
@@ -34801,7 +34795,7 @@
         <v>0</v>
       </c>
       <c r="AF512" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="513" spans="1:33">
@@ -34860,7 +34854,7 @@
         <v>0</v>
       </c>
       <c r="AF513" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="514" spans="1:33">
@@ -34919,7 +34913,7 @@
         <v>0</v>
       </c>
       <c r="AF514" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="515" spans="1:33">
@@ -34978,7 +34972,7 @@
         <v>0</v>
       </c>
       <c r="AF515" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="516" spans="1:33">
@@ -35037,7 +35031,7 @@
         <v>0</v>
       </c>
       <c r="AF516" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="517" spans="1:33">
@@ -35099,13 +35093,13 @@
         <v>0</v>
       </c>
       <c r="AA517" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF517" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG517" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="518" spans="1:33">
@@ -35167,13 +35161,13 @@
         <v>0</v>
       </c>
       <c r="AA518" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF518" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG518" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="519" spans="1:33">
@@ -35238,13 +35232,13 @@
         <v>0</v>
       </c>
       <c r="AA519" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF519" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG519" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="520" spans="1:33">
@@ -35309,13 +35303,13 @@
         <v>0</v>
       </c>
       <c r="AA520" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF520" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG520" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="521" spans="1:33">
@@ -35380,10 +35374,10 @@
         <v>228</v>
       </c>
       <c r="AF521" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG521" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="522" spans="1:33">
@@ -35445,13 +35439,13 @@
         <v>0</v>
       </c>
       <c r="AA522" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AF522" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG522" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="523" spans="1:33">
@@ -35513,13 +35507,13 @@
         <v>0</v>
       </c>
       <c r="AA523" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AF523" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG523" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="524" spans="1:33">
@@ -35584,10 +35578,10 @@
         <v>227</v>
       </c>
       <c r="AF524" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG524" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="525" spans="1:33">
@@ -35646,10 +35640,10 @@
         <v>0</v>
       </c>
       <c r="AA525" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AF525" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="526" spans="1:33">
@@ -35708,10 +35702,10 @@
         <v>0</v>
       </c>
       <c r="AA526" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AF526" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="527" spans="1:33">
@@ -35773,10 +35767,10 @@
         <v>0</v>
       </c>
       <c r="AA527" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF527" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="528" spans="1:33">
@@ -35841,10 +35835,10 @@
         <v>231</v>
       </c>
       <c r="AF528" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG528" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="529" spans="1:33">
@@ -35909,10 +35903,10 @@
         <v>228</v>
       </c>
       <c r="AF529" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG529" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="530" spans="1:33">
@@ -35977,10 +35971,10 @@
         <v>232</v>
       </c>
       <c r="AF530" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG530" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="531" spans="1:33">
@@ -36045,10 +36039,10 @@
         <v>228</v>
       </c>
       <c r="AF531" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG531" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="532" spans="1:33">
@@ -36113,10 +36107,10 @@
         <v>228</v>
       </c>
       <c r="AF532" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG532" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="533" spans="1:33">
@@ -36181,10 +36175,10 @@
         <v>228</v>
       </c>
       <c r="AF533" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG533" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="534" spans="1:33">
@@ -36249,10 +36243,10 @@
         <v>212</v>
       </c>
       <c r="AF534" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG534" t="s">
         <v>363</v>
-      </c>
-      <c r="AG534" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="535" spans="1:33">
@@ -36314,13 +36308,13 @@
         <v>0</v>
       </c>
       <c r="AA535" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF535" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG535" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="536" spans="1:33">
@@ -36382,13 +36376,13 @@
         <v>0</v>
       </c>
       <c r="AA536" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF536" t="s">
+        <v>361</v>
+      </c>
+      <c r="AG536" t="s">
         <v>363</v>
-      </c>
-      <c r="AG536" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="537" spans="1:33">
@@ -36450,13 +36444,13 @@
         <v>0</v>
       </c>
       <c r="AA537" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF537" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG537" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="538" spans="1:33">
@@ -36518,13 +36512,13 @@
         <v>0</v>
       </c>
       <c r="AA538" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF538" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG538" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="539" spans="1:33">
@@ -36589,7 +36583,7 @@
         <v>216</v>
       </c>
       <c r="AF539" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG539" t="s">
         <v>216</v>
@@ -36657,7 +36651,7 @@
         <v>216</v>
       </c>
       <c r="AF540" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG540" t="s">
         <v>216</v>
@@ -36725,7 +36719,7 @@
         <v>218</v>
       </c>
       <c r="AF541" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG541" t="s">
         <v>216</v>
@@ -36790,10 +36784,10 @@
         <v>0</v>
       </c>
       <c r="AA542" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF542" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG542" t="s">
         <v>216</v>
@@ -36861,10 +36855,10 @@
         <v>220</v>
       </c>
       <c r="AF543" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG543" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="544" spans="1:33">
@@ -36926,13 +36920,13 @@
         <v>0</v>
       </c>
       <c r="AA544" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AF544" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG544" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="545" spans="1:32">
@@ -36997,10 +36991,10 @@
         <v>0</v>
       </c>
       <c r="AA545" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF545" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="546" spans="1:32">
@@ -37062,10 +37056,10 @@
         <v>0</v>
       </c>
       <c r="AA546" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF546" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="547" spans="1:32">
@@ -37130,10 +37124,10 @@
         <v>0</v>
       </c>
       <c r="AA547" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF547" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="548" spans="1:32">
@@ -37198,10 +37192,10 @@
         <v>0</v>
       </c>
       <c r="AA548" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF548" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="549" spans="1:32">
@@ -37266,10 +37260,10 @@
         <v>0</v>
       </c>
       <c r="AA549" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF549" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="550" spans="1:32">
@@ -37328,10 +37322,10 @@
         <v>0</v>
       </c>
       <c r="AA550" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF550" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="551" spans="1:32">
@@ -37396,10 +37390,10 @@
         <v>0</v>
       </c>
       <c r="AA551" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF551" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="552" spans="1:32">
@@ -37464,10 +37458,10 @@
         <v>0</v>
       </c>
       <c r="AA552" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF552" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="553" spans="1:32">
@@ -37529,10 +37523,10 @@
         <v>0</v>
       </c>
       <c r="AA553" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF553" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="554" spans="1:32">
@@ -37597,10 +37591,10 @@
         <v>0</v>
       </c>
       <c r="AA554" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF554" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="555" spans="1:32">
@@ -37659,10 +37653,10 @@
         <v>0</v>
       </c>
       <c r="AA555" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF555" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="556" spans="1:32">
@@ -37727,10 +37721,10 @@
         <v>0</v>
       </c>
       <c r="AA556" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF556" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="557" spans="1:32">
@@ -37795,10 +37789,10 @@
         <v>0</v>
       </c>
       <c r="AA557" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF557" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="558" spans="1:32">
@@ -37863,10 +37857,10 @@
         <v>0</v>
       </c>
       <c r="AA558" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF558" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="559" spans="1:32">
@@ -37928,10 +37922,10 @@
         <v>0</v>
       </c>
       <c r="AA559" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF559" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="560" spans="1:32">
@@ -37996,10 +37990,10 @@
         <v>0</v>
       </c>
       <c r="AA560" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF560" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="561" spans="1:32">
@@ -38061,10 +38055,10 @@
         <v>0</v>
       </c>
       <c r="AA561" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF561" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="562" spans="1:32">
@@ -38126,10 +38120,10 @@
         <v>0</v>
       </c>
       <c r="AA562" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF562" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="563" spans="1:32">
@@ -38194,10 +38188,10 @@
         <v>0</v>
       </c>
       <c r="AA563" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF563" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="564" spans="1:32">
@@ -38262,10 +38256,10 @@
         <v>0</v>
       </c>
       <c r="AA564" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF564" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="565" spans="1:32">
@@ -38330,10 +38324,10 @@
         <v>0</v>
       </c>
       <c r="AA565" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF565" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="566" spans="1:32">
@@ -38395,10 +38389,10 @@
         <v>0</v>
       </c>
       <c r="AA566" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF566" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="567" spans="1:32">
@@ -38463,10 +38457,10 @@
         <v>0</v>
       </c>
       <c r="AA567" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF567" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="568" spans="1:32">
@@ -38528,10 +38522,10 @@
         <v>0</v>
       </c>
       <c r="AA568" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF568" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="569" spans="1:32">
@@ -38593,10 +38587,10 @@
         <v>0</v>
       </c>
       <c r="AA569" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF569" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="570" spans="1:32">
@@ -38661,10 +38655,10 @@
         <v>0</v>
       </c>
       <c r="AA570" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF570" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="571" spans="1:32">
@@ -38729,10 +38723,10 @@
         <v>0</v>
       </c>
       <c r="AA571" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF571" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="572" spans="1:32">
@@ -38797,10 +38791,10 @@
         <v>0</v>
       </c>
       <c r="AA572" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF572" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="573" spans="1:32">
@@ -38862,10 +38856,10 @@
         <v>0</v>
       </c>
       <c r="AA573" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF573" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="574" spans="1:32">
@@ -38927,10 +38921,10 @@
         <v>0</v>
       </c>
       <c r="AA574" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF574" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="575" spans="1:32">
@@ -38989,10 +38983,10 @@
         <v>0</v>
       </c>
       <c r="AA575" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AF575" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="576" spans="1:32">
@@ -39054,13 +39048,13 @@
         <v>349</v>
       </c>
       <c r="AD576" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AE576" t="s">
         <v>198</v>
       </c>
       <c r="AF576" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="577" spans="1:33">
@@ -39122,13 +39116,13 @@
         <v>349</v>
       </c>
       <c r="AD577" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AE577" t="s">
         <v>198</v>
       </c>
       <c r="AF577" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="578" spans="1:33">
@@ -39190,21 +39184,21 @@
         <v>349</v>
       </c>
       <c r="AD578" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AE578" t="s">
         <v>198</v>
       </c>
       <c r="AF578" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="579" spans="1:33">
       <c r="A579">
-        <v>5417</v>
+        <v>6981</v>
       </c>
       <c r="B579" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C579" t="s">
         <v>55</v>
@@ -39216,63 +39210,54 @@
         <v>59</v>
       </c>
       <c r="F579" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G579">
-        <v>7877</v>
+        <v>1792</v>
       </c>
       <c r="H579">
         <v>0</v>
       </c>
       <c r="I579" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="J579" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="L579" s="1">
-        <v>46259</v>
-      </c>
-      <c r="M579" t="s">
-        <v>190</v>
+        <v>46275</v>
       </c>
       <c r="N579" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O579">
-        <v>17399329</v>
+        <v>18201017</v>
       </c>
       <c r="P579" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
       <c r="Q579" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="S579">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="T579" t="s">
-        <v>240</v>
-      </c>
-      <c r="V579" t="s">
-        <v>350</v>
-      </c>
-      <c r="AD579" t="s">
-        <v>361</v>
-      </c>
-      <c r="AE579" t="s">
-        <v>198</v>
+        <v>252</v>
       </c>
       <c r="AF579" t="s">
-        <v>363</v>
+        <v>360</v>
+      </c>
+      <c r="AG579" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="580" spans="1:33">
       <c r="A580">
-        <v>6486</v>
+        <v>6981</v>
       </c>
       <c r="B580" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C580" t="s">
         <v>55</v>
@@ -39284,69 +39269,60 @@
         <v>59</v>
       </c>
       <c r="F580" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G580">
-        <v>9774</v>
+        <v>1793</v>
       </c>
       <c r="H580">
         <v>0</v>
       </c>
       <c r="I580" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="J580" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="L580" s="1">
-        <v>46259</v>
-      </c>
-      <c r="M580" t="s">
-        <v>190</v>
+        <v>46275</v>
       </c>
       <c r="N580" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O580">
-        <v>16976320</v>
+        <v>18201023</v>
       </c>
       <c r="P580" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
       <c r="Q580" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="S580">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="T580" t="s">
-        <v>241</v>
-      </c>
-      <c r="V580" t="s">
-        <v>350</v>
-      </c>
-      <c r="AD580" t="s">
-        <v>361</v>
-      </c>
-      <c r="AE580" t="s">
-        <v>198</v>
+        <v>252</v>
       </c>
       <c r="AF580" t="s">
-        <v>363</v>
+        <v>360</v>
+      </c>
+      <c r="AG580" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="581" spans="1:33">
       <c r="A581">
-        <v>6981</v>
+        <v>7066</v>
       </c>
       <c r="B581" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C581" t="s">
         <v>55</v>
       </c>
       <c r="D581" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E581" t="s">
         <v>59</v>
@@ -39355,28 +39331,31 @@
         <v>61</v>
       </c>
       <c r="G581">
-        <v>1792</v>
+        <v>11686</v>
       </c>
       <c r="H581">
-        <v>0</v>
+        <v>11685</v>
       </c>
       <c r="I581" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J581" t="s">
-        <v>81</v>
+        <v>176</v>
       </c>
       <c r="L581" s="1">
         <v>46275</v>
       </c>
+      <c r="M581" t="s">
+        <v>191</v>
+      </c>
       <c r="N581" t="s">
         <v>203</v>
       </c>
       <c r="O581">
-        <v>18201017</v>
+        <v>18253093</v>
       </c>
       <c r="P581" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="Q581" t="s">
         <v>236</v>
@@ -39385,27 +39364,27 @@
         <v>0</v>
       </c>
       <c r="T581" t="s">
-        <v>252</v>
+        <v>245</v>
+      </c>
+      <c r="V581" t="s">
+        <v>350</v>
       </c>
       <c r="AF581" t="s">
-        <v>362</v>
-      </c>
-      <c r="AG581" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="582" spans="1:33">
       <c r="A582">
-        <v>6981</v>
+        <v>7066</v>
       </c>
       <c r="B582" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C582" t="s">
         <v>55</v>
       </c>
       <c r="D582" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E582" t="s">
         <v>59</v>
@@ -39414,28 +39393,31 @@
         <v>61</v>
       </c>
       <c r="G582">
-        <v>1793</v>
+        <v>11687</v>
       </c>
       <c r="H582">
-        <v>0</v>
+        <v>11685</v>
       </c>
       <c r="I582" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J582" t="s">
-        <v>72</v>
+        <v>177</v>
       </c>
       <c r="L582" s="1">
         <v>46275</v>
       </c>
+      <c r="M582" t="s">
+        <v>191</v>
+      </c>
       <c r="N582" t="s">
         <v>203</v>
       </c>
       <c r="O582">
-        <v>18201023</v>
+        <v>18253094</v>
       </c>
       <c r="P582" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="Q582" t="s">
         <v>236</v>
@@ -39444,13 +39426,13 @@
         <v>0</v>
       </c>
       <c r="T582" t="s">
-        <v>252</v>
+        <v>245</v>
+      </c>
+      <c r="V582" t="s">
+        <v>350</v>
       </c>
       <c r="AF582" t="s">
-        <v>362</v>
-      </c>
-      <c r="AG582" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="583" spans="1:33">
@@ -39473,7 +39455,7 @@
         <v>61</v>
       </c>
       <c r="G583">
-        <v>11686</v>
+        <v>11688</v>
       </c>
       <c r="H583">
         <v>11685</v>
@@ -39482,7 +39464,7 @@
         <v>67</v>
       </c>
       <c r="J583" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L583" s="1">
         <v>46275</v>
@@ -39494,7 +39476,7 @@
         <v>203</v>
       </c>
       <c r="O583">
-        <v>18253093</v>
+        <v>18253095</v>
       </c>
       <c r="P583" t="s">
         <v>230</v>
@@ -39509,10 +39491,10 @@
         <v>245</v>
       </c>
       <c r="V583" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AF583" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="584" spans="1:33">
@@ -39535,7 +39517,7 @@
         <v>61</v>
       </c>
       <c r="G584">
-        <v>11687</v>
+        <v>11689</v>
       </c>
       <c r="H584">
         <v>11685</v>
@@ -39544,7 +39526,7 @@
         <v>67</v>
       </c>
       <c r="J584" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L584" s="1">
         <v>46275</v>
@@ -39556,7 +39538,7 @@
         <v>203</v>
       </c>
       <c r="O584">
-        <v>18253094</v>
+        <v>18253096</v>
       </c>
       <c r="P584" t="s">
         <v>230</v>
@@ -39571,10 +39553,10 @@
         <v>245</v>
       </c>
       <c r="V584" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AF584" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="585" spans="1:33">
@@ -39597,16 +39579,16 @@
         <v>61</v>
       </c>
       <c r="G585">
-        <v>11688</v>
+        <v>11070</v>
       </c>
       <c r="H585">
-        <v>11685</v>
+        <v>0</v>
       </c>
       <c r="I585" t="s">
         <v>67</v>
       </c>
       <c r="J585" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L585" s="1">
         <v>46275</v>
@@ -39618,7 +39600,7 @@
         <v>203</v>
       </c>
       <c r="O585">
-        <v>18253095</v>
+        <v>18253080</v>
       </c>
       <c r="P585" t="s">
         <v>230</v>
@@ -39633,10 +39615,10 @@
         <v>245</v>
       </c>
       <c r="V585" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AF585" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="586" spans="1:33">
@@ -39659,16 +39641,16 @@
         <v>61</v>
       </c>
       <c r="G586">
-        <v>11689</v>
+        <v>11872</v>
       </c>
       <c r="H586">
-        <v>11685</v>
+        <v>11869</v>
       </c>
       <c r="I586" t="s">
         <v>67</v>
       </c>
       <c r="J586" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L586" s="1">
         <v>46275</v>
@@ -39680,7 +39662,7 @@
         <v>203</v>
       </c>
       <c r="O586">
-        <v>18253096</v>
+        <v>18253084</v>
       </c>
       <c r="P586" t="s">
         <v>230</v>
@@ -39695,10 +39677,10 @@
         <v>245</v>
       </c>
       <c r="V586" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AF586" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="587" spans="1:33">
@@ -39721,16 +39703,16 @@
         <v>61</v>
       </c>
       <c r="G587">
-        <v>11070</v>
+        <v>11870</v>
       </c>
       <c r="H587">
-        <v>0</v>
+        <v>11869</v>
       </c>
       <c r="I587" t="s">
         <v>67</v>
       </c>
       <c r="J587" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="L587" s="1">
         <v>46275</v>
@@ -39742,7 +39724,7 @@
         <v>203</v>
       </c>
       <c r="O587">
-        <v>18253080</v>
+        <v>18253082</v>
       </c>
       <c r="P587" t="s">
         <v>230</v>
@@ -39757,10 +39739,10 @@
         <v>245</v>
       </c>
       <c r="V587" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AF587" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="588" spans="1:33">
@@ -39783,7 +39765,7 @@
         <v>61</v>
       </c>
       <c r="G588">
-        <v>11872</v>
+        <v>11871</v>
       </c>
       <c r="H588">
         <v>11869</v>
@@ -39792,7 +39774,7 @@
         <v>67</v>
       </c>
       <c r="J588" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L588" s="1">
         <v>46275</v>
@@ -39804,7 +39786,7 @@
         <v>203</v>
       </c>
       <c r="O588">
-        <v>18253084</v>
+        <v>18253083</v>
       </c>
       <c r="P588" t="s">
         <v>230</v>
@@ -39819,10 +39801,10 @@
         <v>245</v>
       </c>
       <c r="V588" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AF588" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="589" spans="1:33">
@@ -39845,16 +39827,16 @@
         <v>61</v>
       </c>
       <c r="G589">
-        <v>11870</v>
+        <v>11868</v>
       </c>
       <c r="H589">
-        <v>11869</v>
+        <v>0</v>
       </c>
       <c r="I589" t="s">
         <v>67</v>
       </c>
       <c r="J589" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L589" s="1">
         <v>46275</v>
@@ -39866,7 +39848,7 @@
         <v>203</v>
       </c>
       <c r="O589">
-        <v>18253082</v>
+        <v>18253085</v>
       </c>
       <c r="P589" t="s">
         <v>230</v>
@@ -39881,10 +39863,10 @@
         <v>245</v>
       </c>
       <c r="V589" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AF589" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="590" spans="1:33">
@@ -39907,16 +39889,16 @@
         <v>61</v>
       </c>
       <c r="G590">
-        <v>11871</v>
+        <v>11684</v>
       </c>
       <c r="H590">
-        <v>11869</v>
+        <v>11679</v>
       </c>
       <c r="I590" t="s">
         <v>67</v>
       </c>
       <c r="J590" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L590" s="1">
         <v>46275</v>
@@ -39928,7 +39910,7 @@
         <v>203</v>
       </c>
       <c r="O590">
-        <v>18253083</v>
+        <v>18253091</v>
       </c>
       <c r="P590" t="s">
         <v>230</v>
@@ -39943,10 +39925,10 @@
         <v>245</v>
       </c>
       <c r="V590" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AF590" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="591" spans="1:33">
@@ -39969,16 +39951,16 @@
         <v>61</v>
       </c>
       <c r="G591">
-        <v>11868</v>
+        <v>11681</v>
       </c>
       <c r="H591">
-        <v>0</v>
+        <v>11679</v>
       </c>
       <c r="I591" t="s">
         <v>67</v>
       </c>
       <c r="J591" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L591" s="1">
         <v>46275</v>
@@ -39990,7 +39972,7 @@
         <v>203</v>
       </c>
       <c r="O591">
-        <v>18253085</v>
+        <v>18253088</v>
       </c>
       <c r="P591" t="s">
         <v>230</v>
@@ -40005,10 +39987,10 @@
         <v>245</v>
       </c>
       <c r="V591" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AF591" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="592" spans="1:33">
@@ -40031,7 +40013,7 @@
         <v>61</v>
       </c>
       <c r="G592">
-        <v>11684</v>
+        <v>11680</v>
       </c>
       <c r="H592">
         <v>11679</v>
@@ -40040,7 +40022,7 @@
         <v>67</v>
       </c>
       <c r="J592" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L592" s="1">
         <v>46275</v>
@@ -40052,7 +40034,7 @@
         <v>203</v>
       </c>
       <c r="O592">
-        <v>18253091</v>
+        <v>18253087</v>
       </c>
       <c r="P592" t="s">
         <v>230</v>
@@ -40067,10 +40049,10 @@
         <v>245</v>
       </c>
       <c r="V592" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AF592" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="593" spans="1:32">
@@ -40093,7 +40075,7 @@
         <v>61</v>
       </c>
       <c r="G593">
-        <v>11681</v>
+        <v>11683</v>
       </c>
       <c r="H593">
         <v>11679</v>
@@ -40102,7 +40084,7 @@
         <v>67</v>
       </c>
       <c r="J593" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L593" s="1">
         <v>46275</v>
@@ -40114,7 +40096,7 @@
         <v>203</v>
       </c>
       <c r="O593">
-        <v>18253088</v>
+        <v>18253090</v>
       </c>
       <c r="P593" t="s">
         <v>230</v>
@@ -40129,10 +40111,10 @@
         <v>245</v>
       </c>
       <c r="V593" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AF593" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="594" spans="1:32">
@@ -40155,7 +40137,7 @@
         <v>61</v>
       </c>
       <c r="G594">
-        <v>11680</v>
+        <v>11682</v>
       </c>
       <c r="H594">
         <v>11679</v>
@@ -40164,7 +40146,7 @@
         <v>67</v>
       </c>
       <c r="J594" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="L594" s="1">
         <v>46275</v>
@@ -40176,7 +40158,7 @@
         <v>203</v>
       </c>
       <c r="O594">
-        <v>18253087</v>
+        <v>18253089</v>
       </c>
       <c r="P594" t="s">
         <v>230</v>
@@ -40191,134 +40173,10 @@
         <v>245</v>
       </c>
       <c r="V594" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AF594" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="595" spans="1:32">
-      <c r="A595">
-        <v>7066</v>
-      </c>
-      <c r="B595" t="s">
-        <v>54</v>
-      </c>
-      <c r="C595" t="s">
-        <v>55</v>
-      </c>
-      <c r="D595" t="s">
-        <v>56</v>
-      </c>
-      <c r="E595" t="s">
-        <v>59</v>
-      </c>
-      <c r="F595" t="s">
-        <v>61</v>
-      </c>
-      <c r="G595">
-        <v>11683</v>
-      </c>
-      <c r="H595">
-        <v>11679</v>
-      </c>
-      <c r="I595" t="s">
-        <v>67</v>
-      </c>
-      <c r="J595" t="s">
-        <v>188</v>
-      </c>
-      <c r="L595" s="1">
-        <v>46275</v>
-      </c>
-      <c r="M595" t="s">
-        <v>191</v>
-      </c>
-      <c r="N595" t="s">
-        <v>203</v>
-      </c>
-      <c r="O595">
-        <v>18253090</v>
-      </c>
-      <c r="P595" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q595" t="s">
-        <v>236</v>
-      </c>
-      <c r="S595">
-        <v>0</v>
-      </c>
-      <c r="T595" t="s">
-        <v>245</v>
-      </c>
-      <c r="V595" t="s">
-        <v>351</v>
-      </c>
-      <c r="AF595" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="596" spans="1:32">
-      <c r="A596">
-        <v>7066</v>
-      </c>
-      <c r="B596" t="s">
-        <v>54</v>
-      </c>
-      <c r="C596" t="s">
-        <v>55</v>
-      </c>
-      <c r="D596" t="s">
-        <v>56</v>
-      </c>
-      <c r="E596" t="s">
-        <v>59</v>
-      </c>
-      <c r="F596" t="s">
-        <v>61</v>
-      </c>
-      <c r="G596">
-        <v>11682</v>
-      </c>
-      <c r="H596">
-        <v>11679</v>
-      </c>
-      <c r="I596" t="s">
-        <v>67</v>
-      </c>
-      <c r="J596" t="s">
-        <v>189</v>
-      </c>
-      <c r="L596" s="1">
-        <v>46275</v>
-      </c>
-      <c r="M596" t="s">
-        <v>191</v>
-      </c>
-      <c r="N596" t="s">
-        <v>203</v>
-      </c>
-      <c r="O596">
-        <v>18253089</v>
-      </c>
-      <c r="P596" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q596" t="s">
-        <v>236</v>
-      </c>
-      <c r="S596">
-        <v>0</v>
-      </c>
-      <c r="T596" t="s">
-        <v>245</v>
-      </c>
-      <c r="V596" t="s">
-        <v>351</v>
-      </c>
-      <c r="AF596" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8198" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8184" uniqueCount="393">
   <si>
     <t>CodCliente</t>
   </si>
@@ -1129,7 +1129,10 @@
 Sem informações que permite identificar e aplicar modelo - Data Comentário: 08/09/2026 17:53</t>
   </si>
   <si>
-    <t>Comentário Colaborador + Previsão de conclusão, Previsto para 10/09/2026 - Data Comentário: 10/09/2026 18:57</t>
+    <t>Troca responsavel: sfernandes -&gt; victoriav:Alteração no Responsável Direto: sfernandes-&gt;victoriav - Data Comentário: 11/09/2026 11:11</t>
+  </si>
+  <si>
+    <t>Troca responsavel: sfernandes -&gt; victoriav:Alteração no Responsável Direto: sfernandes-&gt;victoriav - Data Comentário: 11/09/2026 11:10</t>
   </si>
   <si>
     <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1792] sendo a ultima baixa feita [1792]-10/09/2026 17:16:45.. - Data Comentário: 10/09/2026 18:34</t>
@@ -1719,10 +1722,10 @@
         <v>0</v>
       </c>
       <c r="AF2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:33">
@@ -1787,10 +1790,10 @@
         <v>0</v>
       </c>
       <c r="AF3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4" spans="1:33">
@@ -1855,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5" spans="1:33">
@@ -1920,7 +1923,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="6" spans="1:33">
@@ -1985,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="AF6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7" spans="1:33">
@@ -2050,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="AF7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="8" spans="1:33">
@@ -2115,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="AF8" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9" spans="1:33">
@@ -2180,7 +2183,7 @@
         <v>0</v>
       </c>
       <c r="AF9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10" spans="1:33">
@@ -2242,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="AF10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11" spans="1:33">
@@ -2301,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="AF11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="12" spans="1:33">
@@ -2360,10 +2363,10 @@
         <v>0</v>
       </c>
       <c r="AF12" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG12" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" spans="1:33">
@@ -2428,10 +2431,10 @@
         <v>0</v>
       </c>
       <c r="AF13" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="14" spans="1:33">
@@ -2490,10 +2493,10 @@
         <v>0</v>
       </c>
       <c r="AF14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="15" spans="1:33">
@@ -2552,10 +2555,10 @@
         <v>0</v>
       </c>
       <c r="AF15" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG15" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="16" spans="1:33">
@@ -2620,10 +2623,10 @@
         <v>0</v>
       </c>
       <c r="AF16" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG16" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="17" spans="1:33">
@@ -2688,10 +2691,10 @@
         <v>0</v>
       </c>
       <c r="AF17" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG17" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="18" spans="1:33">
@@ -2750,10 +2753,10 @@
         <v>0</v>
       </c>
       <c r="AF18" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG18" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" spans="1:33">
@@ -2812,10 +2815,10 @@
         <v>0</v>
       </c>
       <c r="AF19" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG19" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="20" spans="1:33">
@@ -2874,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="AF20" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG20" t="s">
         <v>224</v>
@@ -2942,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="AF21" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG21" t="s">
         <v>224</v>
@@ -3010,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="AF22" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG22" t="s">
         <v>224</v>
@@ -3078,7 +3081,7 @@
         <v>0</v>
       </c>
       <c r="AF23" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG23" t="s">
         <v>224</v>
@@ -3146,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="AF24" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG24" t="s">
         <v>224</v>
@@ -3214,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="AF25" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG25" t="s">
         <v>224</v>
@@ -3276,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="AF26" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG26" t="s">
         <v>224</v>
@@ -3338,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="AF27" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="28" spans="1:33">
@@ -3397,7 +3400,7 @@
         <v>0</v>
       </c>
       <c r="AF28" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG28" t="s">
         <v>224</v>
@@ -3459,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="AF29" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG29" t="s">
         <v>224</v>
@@ -3521,7 +3524,7 @@
         <v>0</v>
       </c>
       <c r="AF30" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG30" t="s">
         <v>224</v>
@@ -3583,10 +3586,10 @@
         <v>0</v>
       </c>
       <c r="AF31" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG31" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="32" spans="1:33">
@@ -3645,10 +3648,10 @@
         <v>0</v>
       </c>
       <c r="AF32" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG32" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="33" spans="1:33">
@@ -3707,10 +3710,10 @@
         <v>0</v>
       </c>
       <c r="AF33" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG33" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="34" spans="1:33">
@@ -3769,10 +3772,10 @@
         <v>0</v>
       </c>
       <c r="AF34" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG34" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="35" spans="1:33">
@@ -3831,10 +3834,10 @@
         <v>0</v>
       </c>
       <c r="AF35" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG35" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="36" spans="1:33">
@@ -3893,10 +3896,10 @@
         <v>0</v>
       </c>
       <c r="AF36" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG36" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="37" spans="1:33">
@@ -3955,10 +3958,10 @@
         <v>0</v>
       </c>
       <c r="AF37" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG37" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="38" spans="1:33">
@@ -4017,10 +4020,10 @@
         <v>0</v>
       </c>
       <c r="AF38" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG38" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="39" spans="1:33">
@@ -4079,10 +4082,10 @@
         <v>0</v>
       </c>
       <c r="AF39" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG39" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="40" spans="1:33">
@@ -4141,10 +4144,10 @@
         <v>0</v>
       </c>
       <c r="AF40" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG40" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="41" spans="1:33">
@@ -4203,10 +4206,10 @@
         <v>0</v>
       </c>
       <c r="AF41" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG41" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="42" spans="1:33">
@@ -4268,10 +4271,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AF42" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG42" t="s">
         <v>243</v>
@@ -4336,13 +4339,13 @@
         <v>0</v>
       </c>
       <c r="AA43" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AF43" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG43" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="44" spans="1:33">
@@ -4404,13 +4407,13 @@
         <v>0</v>
       </c>
       <c r="AA44" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AF44" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG44" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="45" spans="1:33">
@@ -4472,13 +4475,13 @@
         <v>0</v>
       </c>
       <c r="AA45" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AF45" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG45" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="46" spans="1:33">
@@ -4540,10 +4543,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AF46" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG46" t="s">
         <v>243</v>
@@ -4608,13 +4611,13 @@
         <v>0</v>
       </c>
       <c r="AA47" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AF47" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG47" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="48" spans="1:33">
@@ -4676,13 +4679,13 @@
         <v>0</v>
       </c>
       <c r="AA48" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AF48" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG48" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="49" spans="1:33">
@@ -4744,13 +4747,13 @@
         <v>0</v>
       </c>
       <c r="AA49" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AF49" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG49" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="50" spans="1:33">
@@ -4812,13 +4815,13 @@
         <v>0</v>
       </c>
       <c r="AA50" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AF50" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG50" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="51" spans="1:33">
@@ -4880,13 +4883,13 @@
         <v>0</v>
       </c>
       <c r="AA51" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AF51" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG51" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="52" spans="1:33">
@@ -4948,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="AA52" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AF52" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG52" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="53" spans="1:33">
@@ -5025,10 +5028,10 @@
         <v>216</v>
       </c>
       <c r="AF53" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG53" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="54" spans="1:33">
@@ -5093,10 +5096,10 @@
         <v>222</v>
       </c>
       <c r="AF54" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG54" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="55" spans="1:33">
@@ -5167,10 +5170,10 @@
         <v>223</v>
       </c>
       <c r="AF55" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG55" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="56" spans="1:33">
@@ -5241,7 +5244,7 @@
         <v>218</v>
       </c>
       <c r="AF56" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="57" spans="1:33">
@@ -5306,10 +5309,10 @@
         <v>216</v>
       </c>
       <c r="AF57" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG57" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="58" spans="1:33">
@@ -5380,10 +5383,10 @@
         <v>219</v>
       </c>
       <c r="AF58" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG58" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="59" spans="1:33">
@@ -5454,10 +5457,10 @@
         <v>220</v>
       </c>
       <c r="AF59" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG59" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="60" spans="1:33">
@@ -5522,10 +5525,10 @@
         <v>223</v>
       </c>
       <c r="AF60" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG60" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="61" spans="1:33">
@@ -5596,7 +5599,7 @@
         <v>218</v>
       </c>
       <c r="AF61" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="62" spans="1:33">
@@ -5664,13 +5667,13 @@
         <v>0</v>
       </c>
       <c r="AA62" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AF62" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG62" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="63" spans="1:33">
@@ -5741,10 +5744,10 @@
         <v>216</v>
       </c>
       <c r="AF63" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG63" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="64" spans="1:33">
@@ -5815,10 +5818,10 @@
         <v>219</v>
       </c>
       <c r="AF64" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG64" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="65" spans="1:33">
@@ -5889,10 +5892,10 @@
         <v>220</v>
       </c>
       <c r="AF65" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG65" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="66" spans="1:33">
@@ -5963,10 +5966,10 @@
         <v>221</v>
       </c>
       <c r="AF66" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG66" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="67" spans="1:33">
@@ -6037,10 +6040,10 @@
         <v>222</v>
       </c>
       <c r="AF67" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG67" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="68" spans="1:33">
@@ -6105,10 +6108,10 @@
         <v>223</v>
       </c>
       <c r="AF68" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG68" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="69" spans="1:33">
@@ -6176,10 +6179,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AF69" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="70" spans="1:33">
@@ -6250,10 +6253,10 @@
         <v>216</v>
       </c>
       <c r="AF70" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG70" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="71" spans="1:33">
@@ -6324,10 +6327,10 @@
         <v>216</v>
       </c>
       <c r="AF71" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG71" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="72" spans="1:33">
@@ -6398,10 +6401,10 @@
         <v>216</v>
       </c>
       <c r="AF72" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG72" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="73" spans="1:33">
@@ -6472,10 +6475,10 @@
         <v>220</v>
       </c>
       <c r="AF73" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG73" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="74" spans="1:33">
@@ -6546,10 +6549,10 @@
         <v>221</v>
       </c>
       <c r="AF74" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG74" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="75" spans="1:33">
@@ -6620,10 +6623,10 @@
         <v>222</v>
       </c>
       <c r="AF75" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG75" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="76" spans="1:33">
@@ -6694,10 +6697,10 @@
         <v>223</v>
       </c>
       <c r="AF76" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG76" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="77" spans="1:33">
@@ -6762,7 +6765,7 @@
         <v>218</v>
       </c>
       <c r="AF77" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="78" spans="1:33">
@@ -6827,10 +6830,10 @@
         <v>216</v>
       </c>
       <c r="AF78" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG78" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="79" spans="1:33">
@@ -6895,10 +6898,10 @@
         <v>216</v>
       </c>
       <c r="AF79" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG79" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="80" spans="1:33">
@@ -6963,10 +6966,10 @@
         <v>216</v>
       </c>
       <c r="AF80" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG80" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="81" spans="1:33">
@@ -7031,10 +7034,10 @@
         <v>220</v>
       </c>
       <c r="AF81" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG81" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="82" spans="1:33">
@@ -7099,10 +7102,10 @@
         <v>221</v>
       </c>
       <c r="AF82" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG82" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="83" spans="1:33">
@@ -7173,10 +7176,10 @@
         <v>222</v>
       </c>
       <c r="AF83" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG83" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="84" spans="1:33">
@@ -7241,10 +7244,10 @@
         <v>223</v>
       </c>
       <c r="AF84" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG84" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="85" spans="1:33">
@@ -7309,7 +7312,7 @@
         <v>218</v>
       </c>
       <c r="AF85" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="86" spans="1:33">
@@ -7374,10 +7377,10 @@
         <v>216</v>
       </c>
       <c r="AF86" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG86" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="87" spans="1:33">
@@ -7448,10 +7451,10 @@
         <v>219</v>
       </c>
       <c r="AF87" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG87" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="88" spans="1:33">
@@ -7522,10 +7525,10 @@
         <v>220</v>
       </c>
       <c r="AF88" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG88" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="89" spans="1:33">
@@ -7590,10 +7593,10 @@
         <v>223</v>
       </c>
       <c r="AF89" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG89" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="90" spans="1:33">
@@ -7658,7 +7661,7 @@
         <v>218</v>
       </c>
       <c r="AF90" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="91" spans="1:33">
@@ -7723,10 +7726,10 @@
         <v>216</v>
       </c>
       <c r="AF91" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG91" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="92" spans="1:33">
@@ -7791,10 +7794,10 @@
         <v>219</v>
       </c>
       <c r="AF92" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG92" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="93" spans="1:33">
@@ -7859,10 +7862,10 @@
         <v>216</v>
       </c>
       <c r="AF93" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG93" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="94" spans="1:33">
@@ -7927,10 +7930,10 @@
         <v>216</v>
       </c>
       <c r="AF94" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG94" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="95" spans="1:33">
@@ -7995,10 +7998,10 @@
         <v>221</v>
       </c>
       <c r="AF95" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG95" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="96" spans="1:33">
@@ -8063,10 +8066,10 @@
         <v>222</v>
       </c>
       <c r="AF96" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG96" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="97" spans="1:33">
@@ -8131,10 +8134,10 @@
         <v>223</v>
       </c>
       <c r="AF97" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG97" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="98" spans="1:33">
@@ -8205,10 +8208,10 @@
         <v>216</v>
       </c>
       <c r="AF98" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG98" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="99" spans="1:33">
@@ -8279,10 +8282,10 @@
         <v>216</v>
       </c>
       <c r="AF99" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG99" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="100" spans="1:33">
@@ -8353,10 +8356,10 @@
         <v>216</v>
       </c>
       <c r="AF100" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG100" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="101" spans="1:33">
@@ -8427,10 +8430,10 @@
         <v>220</v>
       </c>
       <c r="AF101" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG101" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="102" spans="1:33">
@@ -8495,10 +8498,10 @@
         <v>219</v>
       </c>
       <c r="AF102" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG102" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="103" spans="1:33">
@@ -8569,7 +8572,7 @@
         <v>218</v>
       </c>
       <c r="AF103" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="104" spans="1:33">
@@ -8637,13 +8640,13 @@
         <v>0</v>
       </c>
       <c r="AA104" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AF104" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG104" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="105" spans="1:33">
@@ -8714,10 +8717,10 @@
         <v>216</v>
       </c>
       <c r="AF105" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG105" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="106" spans="1:33">
@@ -8788,10 +8791,10 @@
         <v>216</v>
       </c>
       <c r="AF106" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG106" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="107" spans="1:33">
@@ -8862,10 +8865,10 @@
         <v>216</v>
       </c>
       <c r="AF107" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG107" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="108" spans="1:33">
@@ -8936,10 +8939,10 @@
         <v>220</v>
       </c>
       <c r="AF108" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG108" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="109" spans="1:33">
@@ -9010,10 +9013,10 @@
         <v>221</v>
       </c>
       <c r="AF109" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG109" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:33">
@@ -9084,10 +9087,10 @@
         <v>222</v>
       </c>
       <c r="AF110" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG110" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="111" spans="1:33">
@@ -9158,10 +9161,10 @@
         <v>223</v>
       </c>
       <c r="AF111" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG111" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="112" spans="1:33">
@@ -9232,10 +9235,10 @@
         <v>216</v>
       </c>
       <c r="AF112" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG112" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="113" spans="1:33">
@@ -9300,7 +9303,7 @@
         <v>218</v>
       </c>
       <c r="AF113" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="114" spans="1:33">
@@ -9362,13 +9365,13 @@
         <v>0</v>
       </c>
       <c r="AA114" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AF114" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG114" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="115" spans="1:33">
@@ -9433,10 +9436,10 @@
         <v>216</v>
       </c>
       <c r="AF115" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG115" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="116" spans="1:33">
@@ -9501,10 +9504,10 @@
         <v>216</v>
       </c>
       <c r="AF116" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG116" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="117" spans="1:33">
@@ -9569,10 +9572,10 @@
         <v>216</v>
       </c>
       <c r="AF117" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG117" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="118" spans="1:33">
@@ -9637,10 +9640,10 @@
         <v>220</v>
       </c>
       <c r="AF118" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG118" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="119" spans="1:33">
@@ -9705,10 +9708,10 @@
         <v>221</v>
       </c>
       <c r="AF119" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG119" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="120" spans="1:33">
@@ -9773,10 +9776,10 @@
         <v>222</v>
       </c>
       <c r="AF120" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG120" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="121" spans="1:33">
@@ -9841,10 +9844,10 @@
         <v>223</v>
       </c>
       <c r="AF121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG121" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122" spans="1:33">
@@ -9912,7 +9915,7 @@
         <v>216</v>
       </c>
       <c r="AF122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:33">
@@ -9980,7 +9983,7 @@
         <v>216</v>
       </c>
       <c r="AF123" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="124" spans="1:33">
@@ -10048,7 +10051,7 @@
         <v>223</v>
       </c>
       <c r="AF124" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="125" spans="1:33">
@@ -10116,7 +10119,7 @@
         <v>223</v>
       </c>
       <c r="AF125" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="126" spans="1:33">
@@ -10184,7 +10187,7 @@
         <v>223</v>
       </c>
       <c r="AF126" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="127" spans="1:33">
@@ -10249,7 +10252,7 @@
         <v>224</v>
       </c>
       <c r="AF127" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG127" t="s">
         <v>224</v>
@@ -10317,7 +10320,7 @@
         <v>224</v>
       </c>
       <c r="AF128" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG128" t="s">
         <v>224</v>
@@ -10388,7 +10391,7 @@
         <v>224</v>
       </c>
       <c r="AF129" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="130" spans="1:33">
@@ -10450,7 +10453,7 @@
         <v>226</v>
       </c>
       <c r="AF130" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="131" spans="1:33">
@@ -10515,7 +10518,7 @@
         <v>224</v>
       </c>
       <c r="AF131" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG131" t="s">
         <v>224</v>
@@ -10583,7 +10586,7 @@
         <v>224</v>
       </c>
       <c r="AF132" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG132" t="s">
         <v>224</v>
@@ -10651,7 +10654,7 @@
         <v>224</v>
       </c>
       <c r="AF133" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG133" t="s">
         <v>224</v>
@@ -10716,7 +10719,7 @@
         <v>224</v>
       </c>
       <c r="AF134" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="135" spans="1:33">
@@ -10778,7 +10781,7 @@
         <v>226</v>
       </c>
       <c r="AF135" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="136" spans="1:33">
@@ -10843,7 +10846,7 @@
         <v>224</v>
       </c>
       <c r="AF136" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG136" t="s">
         <v>224</v>
@@ -10911,7 +10914,7 @@
         <v>224</v>
       </c>
       <c r="AF137" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG137" t="s">
         <v>224</v>
@@ -10979,7 +10982,7 @@
         <v>224</v>
       </c>
       <c r="AF138" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG138" t="s">
         <v>224</v>
@@ -11044,7 +11047,7 @@
         <v>224</v>
       </c>
       <c r="AF139" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="140" spans="1:33">
@@ -11106,7 +11109,7 @@
         <v>226</v>
       </c>
       <c r="AF140" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="141" spans="1:33">
@@ -11171,7 +11174,7 @@
         <v>224</v>
       </c>
       <c r="AF141" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG141" t="s">
         <v>224</v>
@@ -11239,7 +11242,7 @@
         <v>224</v>
       </c>
       <c r="AF142" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG142" t="s">
         <v>224</v>
@@ -11307,7 +11310,7 @@
         <v>226</v>
       </c>
       <c r="AF143" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG143" t="s">
         <v>224</v>
@@ -11381,7 +11384,7 @@
         <v>224</v>
       </c>
       <c r="AF144" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG144" t="s">
         <v>224</v>
@@ -11449,7 +11452,7 @@
         <v>224</v>
       </c>
       <c r="AF145" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="146" spans="1:33">
@@ -11514,7 +11517,7 @@
         <v>224</v>
       </c>
       <c r="AF146" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG146" t="s">
         <v>224</v>
@@ -11582,7 +11585,7 @@
         <v>224</v>
       </c>
       <c r="AF147" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG147" t="s">
         <v>224</v>
@@ -11650,7 +11653,7 @@
         <v>224</v>
       </c>
       <c r="AF148" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG148" t="s">
         <v>224</v>
@@ -11715,7 +11718,7 @@
         <v>224</v>
       </c>
       <c r="AF149" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="150" spans="1:33">
@@ -11777,7 +11780,7 @@
         <v>226</v>
       </c>
       <c r="AF150" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="151" spans="1:33">
@@ -11842,7 +11845,7 @@
         <v>224</v>
       </c>
       <c r="AF151" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG151" t="s">
         <v>224</v>
@@ -11910,7 +11913,7 @@
         <v>224</v>
       </c>
       <c r="AF152" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG152" t="s">
         <v>224</v>
@@ -11978,7 +11981,7 @@
         <v>224</v>
       </c>
       <c r="AF153" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="154" spans="1:33">
@@ -12043,7 +12046,7 @@
         <v>226</v>
       </c>
       <c r="AF154" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG154" t="s">
         <v>224</v>
@@ -12108,10 +12111,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF155" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="156" spans="1:33">
@@ -12173,10 +12176,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF156" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG156" t="s">
         <v>224</v>
@@ -12241,10 +12244,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF157" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG157" t="s">
         <v>224</v>
@@ -12309,10 +12312,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF158" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="159" spans="1:33">
@@ -12374,10 +12377,10 @@
         <v>0</v>
       </c>
       <c r="AA159" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF159" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG159" t="s">
         <v>224</v>
@@ -12445,7 +12448,7 @@
         <v>224</v>
       </c>
       <c r="AF160" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG160" t="s">
         <v>224</v>
@@ -12513,7 +12516,7 @@
         <v>224</v>
       </c>
       <c r="AF161" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG161" t="s">
         <v>224</v>
@@ -12581,7 +12584,7 @@
         <v>224</v>
       </c>
       <c r="AF162" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG162" t="s">
         <v>224</v>
@@ -12646,7 +12649,7 @@
         <v>224</v>
       </c>
       <c r="AF163" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="164" spans="1:33">
@@ -12708,7 +12711,7 @@
         <v>226</v>
       </c>
       <c r="AF164" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="165" spans="1:33">
@@ -12773,7 +12776,7 @@
         <v>224</v>
       </c>
       <c r="AF165" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG165" t="s">
         <v>224</v>
@@ -12841,7 +12844,7 @@
         <v>224</v>
       </c>
       <c r="AF166" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG166" t="s">
         <v>224</v>
@@ -12909,7 +12912,7 @@
         <v>224</v>
       </c>
       <c r="AF167" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG167" t="s">
         <v>224</v>
@@ -12974,7 +12977,7 @@
         <v>224</v>
       </c>
       <c r="AF168" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="169" spans="1:33">
@@ -13036,7 +13039,7 @@
         <v>226</v>
       </c>
       <c r="AF169" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="170" spans="1:33">
@@ -13101,7 +13104,7 @@
         <v>224</v>
       </c>
       <c r="AF170" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG170" t="s">
         <v>224</v>
@@ -13175,7 +13178,7 @@
         <v>228</v>
       </c>
       <c r="AF171" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="172" spans="1:33">
@@ -13240,10 +13243,10 @@
         <v>0</v>
       </c>
       <c r="AA172" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AF172" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG172" t="s">
         <v>224</v>
@@ -13317,7 +13320,7 @@
         <v>226</v>
       </c>
       <c r="AF173" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG173" t="s">
         <v>224</v>
@@ -13385,10 +13388,10 @@
         <v>0</v>
       </c>
       <c r="AA174" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AF174" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG174" t="s">
         <v>224</v>
@@ -13459,7 +13462,7 @@
         <v>227</v>
       </c>
       <c r="AF175" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG175" t="s">
         <v>224</v>
@@ -13533,7 +13536,7 @@
         <v>225</v>
       </c>
       <c r="AF176" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG176" t="s">
         <v>224</v>
@@ -13601,7 +13604,7 @@
         <v>224</v>
       </c>
       <c r="AF177" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG177" t="s">
         <v>224</v>
@@ -13675,7 +13678,7 @@
         <v>228</v>
       </c>
       <c r="AF178" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="179" spans="1:33">
@@ -13746,7 +13749,7 @@
         <v>226</v>
       </c>
       <c r="AF179" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG179" t="s">
         <v>224</v>
@@ -13814,7 +13817,7 @@
         <v>227</v>
       </c>
       <c r="AF180" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG180" t="s">
         <v>224</v>
@@ -13882,7 +13885,7 @@
         <v>227</v>
       </c>
       <c r="AF181" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG181" t="s">
         <v>224</v>
@@ -13950,7 +13953,7 @@
         <v>226</v>
       </c>
       <c r="AF182" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG182" t="s">
         <v>224</v>
@@ -14018,10 +14021,10 @@
         <v>229</v>
       </c>
       <c r="AF183" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG183" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="184" spans="1:33">
@@ -14086,10 +14089,10 @@
         <v>229</v>
       </c>
       <c r="AF184" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG184" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="185" spans="1:33">
@@ -14160,10 +14163,10 @@
         <v>229</v>
       </c>
       <c r="AF185" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG185" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="186" spans="1:33">
@@ -14228,10 +14231,10 @@
         <v>229</v>
       </c>
       <c r="AF186" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG186" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="187" spans="1:33">
@@ -14296,10 +14299,10 @@
         <v>229</v>
       </c>
       <c r="AF187" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG187" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="188" spans="1:33">
@@ -14364,10 +14367,10 @@
         <v>229</v>
       </c>
       <c r="AF188" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG188" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="189" spans="1:33">
@@ -14432,10 +14435,10 @@
         <v>229</v>
       </c>
       <c r="AF189" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG189" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="190" spans="1:33">
@@ -14506,10 +14509,10 @@
         <v>229</v>
       </c>
       <c r="AF190" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG190" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="191" spans="1:33">
@@ -14574,10 +14577,10 @@
         <v>229</v>
       </c>
       <c r="AF191" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG191" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="192" spans="1:33">
@@ -14639,13 +14642,13 @@
         <v>0</v>
       </c>
       <c r="AA192" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF192" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG192" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="193" spans="1:33">
@@ -14707,13 +14710,13 @@
         <v>0</v>
       </c>
       <c r="AA193" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF193" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG193" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="194" spans="1:33">
@@ -14781,13 +14784,13 @@
         <v>0</v>
       </c>
       <c r="AA194" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF194" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG194" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="195" spans="1:33">
@@ -14849,13 +14852,13 @@
         <v>0</v>
       </c>
       <c r="AA195" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF195" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG195" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="196" spans="1:33">
@@ -14917,13 +14920,13 @@
         <v>0</v>
       </c>
       <c r="AA196" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF196" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG196" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="197" spans="1:33">
@@ -14985,13 +14988,13 @@
         <v>0</v>
       </c>
       <c r="AA197" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF197" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG197" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="198" spans="1:33">
@@ -15056,10 +15059,10 @@
         <v>229</v>
       </c>
       <c r="AF198" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG198" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="199" spans="1:33">
@@ -15121,13 +15124,13 @@
         <v>0</v>
       </c>
       <c r="AA199" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF199" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG199" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="200" spans="1:33">
@@ -15189,13 +15192,13 @@
         <v>0</v>
       </c>
       <c r="AA200" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF200" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG200" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="201" spans="1:33">
@@ -15257,13 +15260,13 @@
         <v>0</v>
       </c>
       <c r="AA201" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF201" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG201" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="202" spans="1:33">
@@ -15325,13 +15328,13 @@
         <v>0</v>
       </c>
       <c r="AA202" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF202" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG202" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="203" spans="1:33">
@@ -15393,13 +15396,13 @@
         <v>0</v>
       </c>
       <c r="AA203" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF203" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG203" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="204" spans="1:33">
@@ -15461,13 +15464,13 @@
         <v>0</v>
       </c>
       <c r="AA204" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF204" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG204" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="205" spans="1:33">
@@ -15532,10 +15535,10 @@
         <v>229</v>
       </c>
       <c r="AF205" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG205" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="206" spans="1:33">
@@ -15600,10 +15603,10 @@
         <v>229</v>
       </c>
       <c r="AF206" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG206" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="207" spans="1:33">
@@ -15668,10 +15671,10 @@
         <v>229</v>
       </c>
       <c r="AF207" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG207" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="208" spans="1:33">
@@ -15736,10 +15739,10 @@
         <v>229</v>
       </c>
       <c r="AF208" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG208" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="209" spans="1:33">
@@ -15804,10 +15807,10 @@
         <v>229</v>
       </c>
       <c r="AF209" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG209" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="210" spans="1:33">
@@ -15872,10 +15875,10 @@
         <v>229</v>
       </c>
       <c r="AF210" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG210" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="211" spans="1:33">
@@ -15940,10 +15943,10 @@
         <v>229</v>
       </c>
       <c r="AF211" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG211" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="212" spans="1:33">
@@ -16008,10 +16011,10 @@
         <v>229</v>
       </c>
       <c r="AF212" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG212" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="213" spans="1:33">
@@ -16076,10 +16079,10 @@
         <v>229</v>
       </c>
       <c r="AF213" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG213" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="214" spans="1:33">
@@ -16150,10 +16153,10 @@
         <v>229</v>
       </c>
       <c r="AF214" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG214" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="215" spans="1:33">
@@ -16224,10 +16227,10 @@
         <v>229</v>
       </c>
       <c r="AF215" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG215" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="216" spans="1:33">
@@ -16292,10 +16295,10 @@
         <v>229</v>
       </c>
       <c r="AF216" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG216" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="217" spans="1:33">
@@ -16360,10 +16363,10 @@
         <v>229</v>
       </c>
       <c r="AF217" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG217" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="218" spans="1:33">
@@ -16428,13 +16431,13 @@
         <v>0</v>
       </c>
       <c r="AA218" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF218" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG218" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="219" spans="1:33">
@@ -16499,13 +16502,13 @@
         <v>0</v>
       </c>
       <c r="AA219" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF219" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG219" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="220" spans="1:33">
@@ -16567,13 +16570,13 @@
         <v>0</v>
       </c>
       <c r="AA220" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AF220" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG220" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="221" spans="1:33">
@@ -16641,7 +16644,7 @@
         <v>217</v>
       </c>
       <c r="AF221" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="222" spans="1:33">
@@ -16709,7 +16712,7 @@
         <v>217</v>
       </c>
       <c r="AF222" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="223" spans="1:33">
@@ -16777,7 +16780,7 @@
         <v>217</v>
       </c>
       <c r="AF223" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="224" spans="1:33">
@@ -16845,7 +16848,7 @@
         <v>217</v>
       </c>
       <c r="AF224" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="225" spans="1:32">
@@ -16910,7 +16913,7 @@
         <v>217</v>
       </c>
       <c r="AF225" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="226" spans="1:32">
@@ -16978,7 +16981,7 @@
         <v>217</v>
       </c>
       <c r="AF226" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="227" spans="1:32">
@@ -17046,7 +17049,7 @@
         <v>217</v>
       </c>
       <c r="AF227" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="228" spans="1:32">
@@ -17114,7 +17117,7 @@
         <v>217</v>
       </c>
       <c r="AF228" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="229" spans="1:32">
@@ -17182,10 +17185,10 @@
         <v>0</v>
       </c>
       <c r="AA229" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF229" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="230" spans="1:32">
@@ -17253,10 +17256,10 @@
         <v>0</v>
       </c>
       <c r="AA230" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF230" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="231" spans="1:32">
@@ -17324,10 +17327,10 @@
         <v>0</v>
       </c>
       <c r="AA231" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF231" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="232" spans="1:32">
@@ -17395,10 +17398,10 @@
         <v>0</v>
       </c>
       <c r="AA232" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF232" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="233" spans="1:32">
@@ -17466,10 +17469,10 @@
         <v>0</v>
       </c>
       <c r="AA233" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF233" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="234" spans="1:32">
@@ -17537,10 +17540,10 @@
         <v>0</v>
       </c>
       <c r="AA234" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF234" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="235" spans="1:32">
@@ -17608,10 +17611,10 @@
         <v>0</v>
       </c>
       <c r="AA235" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF235" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="236" spans="1:32">
@@ -17679,10 +17682,10 @@
         <v>0</v>
       </c>
       <c r="AA236" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF236" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="237" spans="1:32">
@@ -17750,10 +17753,10 @@
         <v>0</v>
       </c>
       <c r="AA237" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF237" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="238" spans="1:32">
@@ -17821,10 +17824,10 @@
         <v>0</v>
       </c>
       <c r="AA238" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF238" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="239" spans="1:32">
@@ -17892,10 +17895,10 @@
         <v>0</v>
       </c>
       <c r="AA239" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF239" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="240" spans="1:32">
@@ -17963,10 +17966,10 @@
         <v>0</v>
       </c>
       <c r="AA240" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF240" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="241" spans="1:32">
@@ -18034,10 +18037,10 @@
         <v>0</v>
       </c>
       <c r="AA241" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF241" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="242" spans="1:32">
@@ -18105,10 +18108,10 @@
         <v>0</v>
       </c>
       <c r="AA242" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF242" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="243" spans="1:32">
@@ -18170,10 +18173,10 @@
         <v>0</v>
       </c>
       <c r="AA243" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF243" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="244" spans="1:32">
@@ -18235,10 +18238,10 @@
         <v>0</v>
       </c>
       <c r="AA244" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF244" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="245" spans="1:32">
@@ -18300,10 +18303,10 @@
         <v>0</v>
       </c>
       <c r="AA245" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AF245" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="246" spans="1:32">
@@ -18365,10 +18368,10 @@
         <v>0</v>
       </c>
       <c r="AA246" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AF246" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="247" spans="1:32">
@@ -18430,10 +18433,10 @@
         <v>0</v>
       </c>
       <c r="AA247" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF247" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="248" spans="1:32">
@@ -18495,10 +18498,10 @@
         <v>0</v>
       </c>
       <c r="AA248" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF248" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="249" spans="1:32">
@@ -18560,10 +18563,10 @@
         <v>0</v>
       </c>
       <c r="AA249" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF249" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="250" spans="1:32">
@@ -18625,10 +18628,10 @@
         <v>0</v>
       </c>
       <c r="AA250" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF250" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="251" spans="1:32">
@@ -18690,10 +18693,10 @@
         <v>0</v>
       </c>
       <c r="AA251" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF251" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="252" spans="1:32">
@@ -18755,10 +18758,10 @@
         <v>0</v>
       </c>
       <c r="AA252" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF252" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="253" spans="1:32">
@@ -18820,10 +18823,10 @@
         <v>0</v>
       </c>
       <c r="AA253" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF253" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="254" spans="1:32">
@@ -18888,7 +18891,7 @@
         <v>217</v>
       </c>
       <c r="AF254" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="255" spans="1:32">
@@ -18953,7 +18956,7 @@
         <v>217</v>
       </c>
       <c r="AF255" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="256" spans="1:32">
@@ -19018,7 +19021,7 @@
         <v>217</v>
       </c>
       <c r="AF256" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="257" spans="1:32">
@@ -19083,7 +19086,7 @@
         <v>217</v>
       </c>
       <c r="AF257" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="258" spans="1:32">
@@ -19148,7 +19151,7 @@
         <v>217</v>
       </c>
       <c r="AF258" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="259" spans="1:32">
@@ -19213,7 +19216,7 @@
         <v>217</v>
       </c>
       <c r="AF259" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="260" spans="1:32">
@@ -19278,7 +19281,7 @@
         <v>217</v>
       </c>
       <c r="AF260" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="261" spans="1:32">
@@ -19340,10 +19343,10 @@
         <v>0</v>
       </c>
       <c r="AA261" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF261" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="262" spans="1:32">
@@ -19405,10 +19408,10 @@
         <v>0</v>
       </c>
       <c r="AA262" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF262" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="263" spans="1:32">
@@ -19470,10 +19473,10 @@
         <v>0</v>
       </c>
       <c r="AA263" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF263" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="264" spans="1:32">
@@ -19535,10 +19538,10 @@
         <v>0</v>
       </c>
       <c r="AA264" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF264" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="265" spans="1:32">
@@ -19600,10 +19603,10 @@
         <v>0</v>
       </c>
       <c r="AA265" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF265" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="266" spans="1:32">
@@ -19665,10 +19668,10 @@
         <v>0</v>
       </c>
       <c r="AA266" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF266" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="267" spans="1:32">
@@ -19730,10 +19733,10 @@
         <v>0</v>
       </c>
       <c r="AA267" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF267" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="268" spans="1:32">
@@ -19795,10 +19798,10 @@
         <v>0</v>
       </c>
       <c r="AA268" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF268" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="269" spans="1:32">
@@ -19860,10 +19863,10 @@
         <v>0</v>
       </c>
       <c r="AA269" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF269" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="270" spans="1:32">
@@ -19925,10 +19928,10 @@
         <v>0</v>
       </c>
       <c r="AA270" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF270" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="271" spans="1:32">
@@ -19990,10 +19993,10 @@
         <v>0</v>
       </c>
       <c r="AA271" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF271" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="272" spans="1:32">
@@ -20055,10 +20058,10 @@
         <v>0</v>
       </c>
       <c r="AA272" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF272" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="273" spans="1:32">
@@ -20120,10 +20123,10 @@
         <v>0</v>
       </c>
       <c r="AA273" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF273" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="274" spans="1:32">
@@ -20185,10 +20188,10 @@
         <v>0</v>
       </c>
       <c r="AA274" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF274" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="275" spans="1:32">
@@ -20250,10 +20253,10 @@
         <v>0</v>
       </c>
       <c r="AA275" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF275" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="276" spans="1:32">
@@ -20315,10 +20318,10 @@
         <v>0</v>
       </c>
       <c r="AA276" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF276" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="277" spans="1:32">
@@ -20380,10 +20383,10 @@
         <v>0</v>
       </c>
       <c r="AA277" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AF277" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="278" spans="1:32">
@@ -20445,10 +20448,10 @@
         <v>0</v>
       </c>
       <c r="AA278" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AF278" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="279" spans="1:32">
@@ -20510,10 +20513,10 @@
         <v>0</v>
       </c>
       <c r="AA279" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF279" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="280" spans="1:32">
@@ -20575,10 +20578,10 @@
         <v>0</v>
       </c>
       <c r="AA280" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF280" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="281" spans="1:32">
@@ -20640,10 +20643,10 @@
         <v>0</v>
       </c>
       <c r="AA281" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF281" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="282" spans="1:32">
@@ -20705,10 +20708,10 @@
         <v>0</v>
       </c>
       <c r="AA282" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF282" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="283" spans="1:32">
@@ -20770,10 +20773,10 @@
         <v>0</v>
       </c>
       <c r="AA283" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF283" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="284" spans="1:32">
@@ -20835,10 +20838,10 @@
         <v>0</v>
       </c>
       <c r="AA284" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF284" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="285" spans="1:32">
@@ -20900,10 +20903,10 @@
         <v>0</v>
       </c>
       <c r="AA285" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF285" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="286" spans="1:32">
@@ -20968,7 +20971,7 @@
         <v>237</v>
       </c>
       <c r="AF286" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="287" spans="1:32">
@@ -21033,7 +21036,7 @@
         <v>237</v>
       </c>
       <c r="AF287" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="288" spans="1:32">
@@ -21098,7 +21101,7 @@
         <v>237</v>
       </c>
       <c r="AF288" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="289" spans="1:33">
@@ -21163,7 +21166,7 @@
         <v>237</v>
       </c>
       <c r="AF289" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="290" spans="1:33">
@@ -21228,7 +21231,7 @@
         <v>237</v>
       </c>
       <c r="AF290" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="291" spans="1:33">
@@ -21293,7 +21296,7 @@
         <v>237</v>
       </c>
       <c r="AF291" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="292" spans="1:33">
@@ -21358,7 +21361,7 @@
         <v>237</v>
       </c>
       <c r="AF292" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="293" spans="1:33">
@@ -21423,7 +21426,7 @@
         <v>237</v>
       </c>
       <c r="AF293" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="294" spans="1:33">
@@ -21494,7 +21497,7 @@
         <v>238</v>
       </c>
       <c r="AF294" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="295" spans="1:33">
@@ -21562,7 +21565,7 @@
         <v>238</v>
       </c>
       <c r="AF295" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="296" spans="1:33">
@@ -21621,10 +21624,10 @@
         <v>0</v>
       </c>
       <c r="AF296" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG296" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="297" spans="1:33">
@@ -21683,10 +21686,10 @@
         <v>0</v>
       </c>
       <c r="AF297" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG297" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="298" spans="1:33">
@@ -21745,7 +21748,7 @@
         <v>0</v>
       </c>
       <c r="AF298" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG298" t="s">
         <v>243</v>
@@ -21807,7 +21810,7 @@
         <v>0</v>
       </c>
       <c r="AF299" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG299" t="s">
         <v>243</v>
@@ -21869,10 +21872,10 @@
         <v>0</v>
       </c>
       <c r="AF300" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG300" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="301" spans="1:33">
@@ -21931,10 +21934,10 @@
         <v>0</v>
       </c>
       <c r="AF301" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG301" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="302" spans="1:33">
@@ -21993,10 +21996,10 @@
         <v>0</v>
       </c>
       <c r="AF302" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG302" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="303" spans="1:33">
@@ -22055,7 +22058,7 @@
         <v>0</v>
       </c>
       <c r="AF303" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG303" t="s">
         <v>243</v>
@@ -22117,10 +22120,10 @@
         <v>0</v>
       </c>
       <c r="AF304" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG304" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="305" spans="1:33">
@@ -22179,10 +22182,10 @@
         <v>0</v>
       </c>
       <c r="AF305" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG305" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="306" spans="1:33">
@@ -22241,7 +22244,7 @@
         <v>0</v>
       </c>
       <c r="AF306" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG306" t="s">
         <v>243</v>
@@ -22303,10 +22306,10 @@
         <v>0</v>
       </c>
       <c r="AF307" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG307" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="308" spans="1:33">
@@ -22365,7 +22368,7 @@
         <v>0</v>
       </c>
       <c r="AF308" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG308" t="s">
         <v>243</v>
@@ -22427,10 +22430,10 @@
         <v>0</v>
       </c>
       <c r="AF309" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG309" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="310" spans="1:33">
@@ -22489,10 +22492,10 @@
         <v>0</v>
       </c>
       <c r="AF310" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG310" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="311" spans="1:33">
@@ -22551,10 +22554,10 @@
         <v>0</v>
       </c>
       <c r="AF311" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG311" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="312" spans="1:33">
@@ -22613,10 +22616,10 @@
         <v>0</v>
       </c>
       <c r="AF312" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG312" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="313" spans="1:33">
@@ -22675,7 +22678,7 @@
         <v>0</v>
       </c>
       <c r="AF313" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG313" t="s">
         <v>243</v>
@@ -22737,10 +22740,10 @@
         <v>0</v>
       </c>
       <c r="AF314" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG314" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="315" spans="1:33">
@@ -22799,7 +22802,7 @@
         <v>0</v>
       </c>
       <c r="AF315" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG315" t="s">
         <v>243</v>
@@ -22861,10 +22864,10 @@
         <v>0</v>
       </c>
       <c r="AF316" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG316" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="317" spans="1:33">
@@ -22923,10 +22926,10 @@
         <v>0</v>
       </c>
       <c r="AF317" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG317" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="318" spans="1:33">
@@ -22985,10 +22988,10 @@
         <v>0</v>
       </c>
       <c r="AF318" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG318" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="319" spans="1:33">
@@ -23047,10 +23050,10 @@
         <v>0</v>
       </c>
       <c r="AF319" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG319" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="320" spans="1:33">
@@ -23109,7 +23112,7 @@
         <v>0</v>
       </c>
       <c r="AF320" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG320" t="s">
         <v>243</v>
@@ -23171,10 +23174,10 @@
         <v>0</v>
       </c>
       <c r="AF321" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG321" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="322" spans="1:33">
@@ -23233,7 +23236,7 @@
         <v>0</v>
       </c>
       <c r="AF322" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG322" t="s">
         <v>243</v>
@@ -23295,10 +23298,10 @@
         <v>0</v>
       </c>
       <c r="AF323" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG323" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="324" spans="1:33">
@@ -23357,10 +23360,10 @@
         <v>0</v>
       </c>
       <c r="AF324" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG324" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="325" spans="1:33">
@@ -23419,10 +23422,10 @@
         <v>0</v>
       </c>
       <c r="AF325" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG325" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="326" spans="1:33">
@@ -23481,10 +23484,10 @@
         <v>0</v>
       </c>
       <c r="AF326" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG326" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="327" spans="1:33">
@@ -23543,10 +23546,10 @@
         <v>0</v>
       </c>
       <c r="AF327" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG327" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="328" spans="1:33">
@@ -23605,10 +23608,10 @@
         <v>0</v>
       </c>
       <c r="AF328" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG328" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="329" spans="1:33">
@@ -23667,10 +23670,10 @@
         <v>0</v>
       </c>
       <c r="AF329" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG329" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="330" spans="1:33">
@@ -23729,10 +23732,10 @@
         <v>0</v>
       </c>
       <c r="AF330" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG330" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="331" spans="1:33">
@@ -23791,10 +23794,10 @@
         <v>0</v>
       </c>
       <c r="AF331" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG331" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="332" spans="1:33">
@@ -23853,10 +23856,10 @@
         <v>0</v>
       </c>
       <c r="AF332" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG332" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="333" spans="1:33">
@@ -23915,10 +23918,10 @@
         <v>0</v>
       </c>
       <c r="AF333" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG333" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="334" spans="1:33">
@@ -23977,10 +23980,10 @@
         <v>0</v>
       </c>
       <c r="AF334" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG334" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="335" spans="1:33">
@@ -24039,10 +24042,10 @@
         <v>0</v>
       </c>
       <c r="AF335" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG335" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="336" spans="1:33">
@@ -24101,10 +24104,10 @@
         <v>0</v>
       </c>
       <c r="AF336" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG336" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="337" spans="1:33">
@@ -24163,10 +24166,10 @@
         <v>0</v>
       </c>
       <c r="AF337" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG337" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="338" spans="1:33">
@@ -24225,10 +24228,10 @@
         <v>0</v>
       </c>
       <c r="AF338" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG338" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="339" spans="1:33">
@@ -24287,10 +24290,10 @@
         <v>0</v>
       </c>
       <c r="AF339" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG339" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="340" spans="1:33">
@@ -24349,10 +24352,10 @@
         <v>0</v>
       </c>
       <c r="AF340" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG340" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="341" spans="1:33">
@@ -24411,10 +24414,10 @@
         <v>0</v>
       </c>
       <c r="AF341" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG341" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="342" spans="1:33">
@@ -24473,10 +24476,10 @@
         <v>0</v>
       </c>
       <c r="AF342" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG342" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="343" spans="1:33">
@@ -24535,10 +24538,10 @@
         <v>0</v>
       </c>
       <c r="AF343" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG343" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="344" spans="1:33">
@@ -24597,10 +24600,10 @@
         <v>0</v>
       </c>
       <c r="AF344" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG344" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="345" spans="1:33">
@@ -24659,10 +24662,10 @@
         <v>0</v>
       </c>
       <c r="AF345" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG345" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="346" spans="1:33">
@@ -24721,10 +24724,10 @@
         <v>0</v>
       </c>
       <c r="AF346" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG346" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="347" spans="1:33">
@@ -24783,10 +24786,10 @@
         <v>0</v>
       </c>
       <c r="AF347" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG347" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="348" spans="1:33">
@@ -24845,10 +24848,10 @@
         <v>0</v>
       </c>
       <c r="AF348" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG348" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="349" spans="1:33">
@@ -24907,10 +24910,10 @@
         <v>0</v>
       </c>
       <c r="AF349" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG349" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="350" spans="1:33">
@@ -24969,10 +24972,10 @@
         <v>0</v>
       </c>
       <c r="AF350" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG350" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="351" spans="1:33">
@@ -25031,7 +25034,7 @@
         <v>0</v>
       </c>
       <c r="AF351" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="352" spans="1:33">
@@ -25090,10 +25093,10 @@
         <v>0</v>
       </c>
       <c r="AF352" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG352" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="353" spans="1:33">
@@ -25158,10 +25161,10 @@
         <v>0</v>
       </c>
       <c r="AF353" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG353" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="354" spans="1:33">
@@ -25220,10 +25223,10 @@
         <v>0</v>
       </c>
       <c r="AF354" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG354" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="355" spans="1:33">
@@ -25282,10 +25285,10 @@
         <v>0</v>
       </c>
       <c r="AF355" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG355" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="356" spans="1:33">
@@ -25344,10 +25347,10 @@
         <v>0</v>
       </c>
       <c r="AF356" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG356" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="357" spans="1:33">
@@ -25406,10 +25409,10 @@
         <v>0</v>
       </c>
       <c r="AF357" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG357" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="358" spans="1:33">
@@ -25468,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AF358" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG358" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="359" spans="1:33">
@@ -25530,10 +25533,10 @@
         <v>0</v>
       </c>
       <c r="AF359" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG359" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="360" spans="1:33">
@@ -25592,7 +25595,7 @@
         <v>0</v>
       </c>
       <c r="AF360" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="361" spans="1:33">
@@ -25651,10 +25654,10 @@
         <v>0</v>
       </c>
       <c r="AF361" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG361" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="362" spans="1:33">
@@ -25719,10 +25722,10 @@
         <v>0</v>
       </c>
       <c r="AF362" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG362" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="363" spans="1:33">
@@ -25781,10 +25784,10 @@
         <v>0</v>
       </c>
       <c r="AF363" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG363" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="364" spans="1:33">
@@ -25843,10 +25846,10 @@
         <v>0</v>
       </c>
       <c r="AF364" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG364" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="365" spans="1:33">
@@ -25905,10 +25908,10 @@
         <v>0</v>
       </c>
       <c r="AF365" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG365" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="366" spans="1:33">
@@ -25967,10 +25970,10 @@
         <v>0</v>
       </c>
       <c r="AF366" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG366" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="367" spans="1:33">
@@ -26029,10 +26032,10 @@
         <v>0</v>
       </c>
       <c r="AF367" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG367" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="368" spans="1:33">
@@ -26091,10 +26094,10 @@
         <v>0</v>
       </c>
       <c r="AF368" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG368" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="369" spans="1:33">
@@ -26153,7 +26156,7 @@
         <v>0</v>
       </c>
       <c r="AF369" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="370" spans="1:33">
@@ -26212,10 +26215,10 @@
         <v>0</v>
       </c>
       <c r="AF370" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG370" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="371" spans="1:33">
@@ -26274,10 +26277,10 @@
         <v>0</v>
       </c>
       <c r="AF371" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG371" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="372" spans="1:33">
@@ -26336,10 +26339,10 @@
         <v>0</v>
       </c>
       <c r="AF372" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG372" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="373" spans="1:33">
@@ -26398,10 +26401,10 @@
         <v>0</v>
       </c>
       <c r="AF373" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG373" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="374" spans="1:33">
@@ -26460,10 +26463,10 @@
         <v>0</v>
       </c>
       <c r="AF374" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG374" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="375" spans="1:33">
@@ -26528,10 +26531,10 @@
         <v>0</v>
       </c>
       <c r="AF375" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG375" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="376" spans="1:33">
@@ -26590,10 +26593,10 @@
         <v>0</v>
       </c>
       <c r="AF376" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG376" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="377" spans="1:33">
@@ -26652,10 +26655,10 @@
         <v>0</v>
       </c>
       <c r="AF377" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG377" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="378" spans="1:33">
@@ -26714,10 +26717,10 @@
         <v>0</v>
       </c>
       <c r="AF378" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG378" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="379" spans="1:33">
@@ -26776,10 +26779,10 @@
         <v>0</v>
       </c>
       <c r="AF379" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG379" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="380" spans="1:33">
@@ -26838,7 +26841,7 @@
         <v>0</v>
       </c>
       <c r="AF380" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="381" spans="1:33">
@@ -26897,10 +26900,10 @@
         <v>0</v>
       </c>
       <c r="AF381" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG381" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="382" spans="1:33">
@@ -26965,10 +26968,10 @@
         <v>0</v>
       </c>
       <c r="AF382" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG382" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="383" spans="1:33">
@@ -27027,10 +27030,10 @@
         <v>0</v>
       </c>
       <c r="AF383" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG383" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="384" spans="1:33">
@@ -27089,10 +27092,10 @@
         <v>0</v>
       </c>
       <c r="AF384" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG384" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="385" spans="1:33">
@@ -27151,10 +27154,10 @@
         <v>0</v>
       </c>
       <c r="AF385" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG385" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="386" spans="1:33">
@@ -27213,10 +27216,10 @@
         <v>0</v>
       </c>
       <c r="AF386" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG386" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="387" spans="1:33">
@@ -27275,10 +27278,10 @@
         <v>0</v>
       </c>
       <c r="AF387" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG387" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="388" spans="1:33">
@@ -27337,10 +27340,10 @@
         <v>0</v>
       </c>
       <c r="AF388" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG388" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="389" spans="1:33">
@@ -27399,10 +27402,10 @@
         <v>0</v>
       </c>
       <c r="AF389" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG389" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="390" spans="1:33">
@@ -27461,10 +27464,10 @@
         <v>0</v>
       </c>
       <c r="AF390" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG390" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="391" spans="1:33">
@@ -27523,10 +27526,10 @@
         <v>0</v>
       </c>
       <c r="AF391" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG391" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="392" spans="1:33">
@@ -27585,7 +27588,7 @@
         <v>0</v>
       </c>
       <c r="AF392" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="393" spans="1:33">
@@ -27644,10 +27647,10 @@
         <v>0</v>
       </c>
       <c r="AF393" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG393" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="394" spans="1:33">
@@ -27706,10 +27709,10 @@
         <v>0</v>
       </c>
       <c r="AF394" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG394" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="395" spans="1:33">
@@ -27768,10 +27771,10 @@
         <v>0</v>
       </c>
       <c r="AF395" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG395" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="396" spans="1:33">
@@ -27830,10 +27833,10 @@
         <v>0</v>
       </c>
       <c r="AF396" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG396" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="397" spans="1:33">
@@ -27892,10 +27895,10 @@
         <v>0</v>
       </c>
       <c r="AF397" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG397" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="398" spans="1:33">
@@ -27954,10 +27957,10 @@
         <v>0</v>
       </c>
       <c r="AF398" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG398" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="399" spans="1:33">
@@ -28016,10 +28019,10 @@
         <v>0</v>
       </c>
       <c r="AF399" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG399" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="400" spans="1:33">
@@ -28078,7 +28081,7 @@
         <v>0</v>
       </c>
       <c r="AF400" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="401" spans="1:33">
@@ -28137,10 +28140,10 @@
         <v>0</v>
       </c>
       <c r="AF401" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG401" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="402" spans="1:33">
@@ -28199,10 +28202,10 @@
         <v>0</v>
       </c>
       <c r="AF402" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG402" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="403" spans="1:33">
@@ -28261,10 +28264,10 @@
         <v>0</v>
       </c>
       <c r="AF403" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG403" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="404" spans="1:33">
@@ -28323,10 +28326,10 @@
         <v>0</v>
       </c>
       <c r="AF404" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG404" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="405" spans="1:33">
@@ -28391,10 +28394,10 @@
         <v>0</v>
       </c>
       <c r="AF405" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG405" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="406" spans="1:33">
@@ -28453,7 +28456,7 @@
         <v>0</v>
       </c>
       <c r="AF406" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG406" t="s">
         <v>224</v>
@@ -28515,7 +28518,7 @@
         <v>0</v>
       </c>
       <c r="AF407" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG407" t="s">
         <v>224</v>
@@ -28577,7 +28580,7 @@
         <v>0</v>
       </c>
       <c r="AF408" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG408" t="s">
         <v>224</v>
@@ -28645,7 +28648,7 @@
         <v>0</v>
       </c>
       <c r="AF409" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG409" t="s">
         <v>224</v>
@@ -28713,7 +28716,7 @@
         <v>0</v>
       </c>
       <c r="AF410" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG410" t="s">
         <v>224</v>
@@ -28781,7 +28784,7 @@
         <v>0</v>
       </c>
       <c r="AF411" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG411" t="s">
         <v>224</v>
@@ -28849,7 +28852,7 @@
         <v>0</v>
       </c>
       <c r="AF412" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG412" t="s">
         <v>224</v>
@@ -28911,7 +28914,7 @@
         <v>0</v>
       </c>
       <c r="AF413" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="414" spans="1:33">
@@ -28970,7 +28973,7 @@
         <v>0</v>
       </c>
       <c r="AF414" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG414" t="s">
         <v>224</v>
@@ -29032,7 +29035,7 @@
         <v>0</v>
       </c>
       <c r="AF415" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG415" t="s">
         <v>224</v>
@@ -29094,7 +29097,7 @@
         <v>0</v>
       </c>
       <c r="AF416" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG416" t="s">
         <v>224</v>
@@ -29156,7 +29159,7 @@
         <v>0</v>
       </c>
       <c r="AF417" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG417" t="s">
         <v>224</v>
@@ -29218,7 +29221,7 @@
         <v>0</v>
       </c>
       <c r="AF418" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="419" spans="1:33">
@@ -29277,7 +29280,7 @@
         <v>0</v>
       </c>
       <c r="AF419" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG419" t="s">
         <v>224</v>
@@ -29339,7 +29342,7 @@
         <v>0</v>
       </c>
       <c r="AF420" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="421" spans="1:33">
@@ -29398,7 +29401,7 @@
         <v>0</v>
       </c>
       <c r="AF421" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG421" t="s">
         <v>224</v>
@@ -29460,7 +29463,7 @@
         <v>0</v>
       </c>
       <c r="AF422" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG422" t="s">
         <v>224</v>
@@ -29522,7 +29525,7 @@
         <v>0</v>
       </c>
       <c r="AF423" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG423" t="s">
         <v>224</v>
@@ -29584,7 +29587,7 @@
         <v>0</v>
       </c>
       <c r="AF424" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG424" t="s">
         <v>224</v>
@@ -29646,7 +29649,7 @@
         <v>0</v>
       </c>
       <c r="AF425" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG425" t="s">
         <v>224</v>
@@ -29708,7 +29711,7 @@
         <v>0</v>
       </c>
       <c r="AF426" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG426" t="s">
         <v>224</v>
@@ -29770,7 +29773,7 @@
         <v>0</v>
       </c>
       <c r="AF427" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG427" t="s">
         <v>224</v>
@@ -29832,7 +29835,7 @@
         <v>0</v>
       </c>
       <c r="AF428" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG428" t="s">
         <v>224</v>
@@ -29894,7 +29897,7 @@
         <v>0</v>
       </c>
       <c r="AF429" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG429" t="s">
         <v>224</v>
@@ -29956,7 +29959,7 @@
         <v>0</v>
       </c>
       <c r="AF430" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG430" t="s">
         <v>224</v>
@@ -30018,10 +30021,10 @@
         <v>0</v>
       </c>
       <c r="AF431" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG431" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="432" spans="1:33">
@@ -30080,10 +30083,10 @@
         <v>0</v>
       </c>
       <c r="AF432" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG432" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="433" spans="1:33">
@@ -30142,10 +30145,10 @@
         <v>0</v>
       </c>
       <c r="AF433" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG433" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="434" spans="1:33">
@@ -30204,10 +30207,10 @@
         <v>0</v>
       </c>
       <c r="AF434" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG434" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="435" spans="1:33">
@@ -30266,10 +30269,10 @@
         <v>0</v>
       </c>
       <c r="AF435" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG435" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="436" spans="1:33">
@@ -30328,10 +30331,10 @@
         <v>0</v>
       </c>
       <c r="AF436" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG436" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="437" spans="1:33">
@@ -30390,10 +30393,10 @@
         <v>0</v>
       </c>
       <c r="AF437" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG437" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="438" spans="1:33">
@@ -30452,10 +30455,10 @@
         <v>0</v>
       </c>
       <c r="AF438" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG438" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="439" spans="1:33">
@@ -30514,10 +30517,10 @@
         <v>0</v>
       </c>
       <c r="AF439" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG439" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="440" spans="1:33">
@@ -30576,10 +30579,10 @@
         <v>0</v>
       </c>
       <c r="AF440" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG440" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="441" spans="1:33">
@@ -30638,10 +30641,10 @@
         <v>0</v>
       </c>
       <c r="AF441" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG441" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="442" spans="1:33">
@@ -30700,10 +30703,10 @@
         <v>0</v>
       </c>
       <c r="AF442" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG442" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="443" spans="1:33">
@@ -30762,10 +30765,10 @@
         <v>0</v>
       </c>
       <c r="AF443" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG443" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="444" spans="1:33">
@@ -30824,10 +30827,10 @@
         <v>0</v>
       </c>
       <c r="AF444" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG444" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="445" spans="1:33">
@@ -30886,10 +30889,10 @@
         <v>0</v>
       </c>
       <c r="AF445" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG445" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="446" spans="1:33">
@@ -30948,10 +30951,10 @@
         <v>0</v>
       </c>
       <c r="AF446" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG446" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="447" spans="1:33">
@@ -31010,10 +31013,10 @@
         <v>0</v>
       </c>
       <c r="AF447" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG447" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="448" spans="1:33">
@@ -31072,10 +31075,10 @@
         <v>0</v>
       </c>
       <c r="AF448" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG448" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="449" spans="1:33">
@@ -31134,10 +31137,10 @@
         <v>0</v>
       </c>
       <c r="AF449" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG449" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="450" spans="1:33">
@@ -31196,10 +31199,10 @@
         <v>0</v>
       </c>
       <c r="AF450" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG450" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="451" spans="1:33">
@@ -31258,10 +31261,10 @@
         <v>0</v>
       </c>
       <c r="AF451" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG451" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="452" spans="1:33">
@@ -31320,10 +31323,10 @@
         <v>0</v>
       </c>
       <c r="AF452" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG452" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="453" spans="1:33">
@@ -31382,10 +31385,10 @@
         <v>0</v>
       </c>
       <c r="AF453" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG453" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="454" spans="1:33">
@@ -31444,7 +31447,7 @@
         <v>0</v>
       </c>
       <c r="AF454" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="455" spans="1:33">
@@ -31503,7 +31506,7 @@
         <v>0</v>
       </c>
       <c r="AF455" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="456" spans="1:33">
@@ -31562,7 +31565,7 @@
         <v>0</v>
       </c>
       <c r="AF456" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="457" spans="1:33">
@@ -31621,7 +31624,7 @@
         <v>0</v>
       </c>
       <c r="AF457" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="458" spans="1:33">
@@ -31680,7 +31683,7 @@
         <v>0</v>
       </c>
       <c r="AF458" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="459" spans="1:33">
@@ -31739,7 +31742,7 @@
         <v>0</v>
       </c>
       <c r="AF459" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="460" spans="1:33">
@@ -31798,7 +31801,7 @@
         <v>0</v>
       </c>
       <c r="AF460" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="461" spans="1:33">
@@ -31857,7 +31860,7 @@
         <v>0</v>
       </c>
       <c r="AF461" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="462" spans="1:33">
@@ -31916,7 +31919,7 @@
         <v>0</v>
       </c>
       <c r="AF462" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="463" spans="1:33">
@@ -31975,7 +31978,7 @@
         <v>0</v>
       </c>
       <c r="AF463" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="464" spans="1:33">
@@ -32034,7 +32037,7 @@
         <v>0</v>
       </c>
       <c r="AF464" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="465" spans="1:32">
@@ -32093,7 +32096,7 @@
         <v>0</v>
       </c>
       <c r="AF465" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="466" spans="1:32">
@@ -32152,7 +32155,7 @@
         <v>0</v>
       </c>
       <c r="AF466" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="467" spans="1:32">
@@ -32211,7 +32214,7 @@
         <v>0</v>
       </c>
       <c r="AF467" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="468" spans="1:32">
@@ -32270,7 +32273,7 @@
         <v>0</v>
       </c>
       <c r="AF468" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="469" spans="1:32">
@@ -32329,7 +32332,7 @@
         <v>0</v>
       </c>
       <c r="AF469" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="470" spans="1:32">
@@ -32388,7 +32391,7 @@
         <v>0</v>
       </c>
       <c r="AF470" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="471" spans="1:32">
@@ -32447,7 +32450,7 @@
         <v>0</v>
       </c>
       <c r="AF471" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="472" spans="1:32">
@@ -32506,7 +32509,7 @@
         <v>0</v>
       </c>
       <c r="AF472" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="473" spans="1:32">
@@ -32565,7 +32568,7 @@
         <v>0</v>
       </c>
       <c r="AF473" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="474" spans="1:32">
@@ -32624,7 +32627,7 @@
         <v>0</v>
       </c>
       <c r="AF474" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="475" spans="1:32">
@@ -32683,7 +32686,7 @@
         <v>0</v>
       </c>
       <c r="AF475" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="476" spans="1:32">
@@ -32742,7 +32745,7 @@
         <v>0</v>
       </c>
       <c r="AF476" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="477" spans="1:32">
@@ -32801,7 +32804,7 @@
         <v>0</v>
       </c>
       <c r="AF477" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="478" spans="1:32">
@@ -32860,7 +32863,7 @@
         <v>0</v>
       </c>
       <c r="AF478" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="479" spans="1:32">
@@ -32919,7 +32922,7 @@
         <v>0</v>
       </c>
       <c r="AF479" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="480" spans="1:32">
@@ -32978,7 +32981,7 @@
         <v>0</v>
       </c>
       <c r="AF480" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="481" spans="1:32">
@@ -33037,7 +33040,7 @@
         <v>0</v>
       </c>
       <c r="AF481" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="482" spans="1:32">
@@ -33096,7 +33099,7 @@
         <v>0</v>
       </c>
       <c r="AF482" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="483" spans="1:32">
@@ -33155,7 +33158,7 @@
         <v>0</v>
       </c>
       <c r="AF483" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="484" spans="1:32">
@@ -33214,7 +33217,7 @@
         <v>0</v>
       </c>
       <c r="AF484" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="485" spans="1:32">
@@ -33273,7 +33276,7 @@
         <v>0</v>
       </c>
       <c r="AF485" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="486" spans="1:32">
@@ -33332,7 +33335,7 @@
         <v>0</v>
       </c>
       <c r="AF486" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="487" spans="1:32">
@@ -33391,7 +33394,7 @@
         <v>0</v>
       </c>
       <c r="AF487" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="488" spans="1:32">
@@ -33450,7 +33453,7 @@
         <v>0</v>
       </c>
       <c r="AF488" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="489" spans="1:32">
@@ -33509,7 +33512,7 @@
         <v>0</v>
       </c>
       <c r="AF489" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="490" spans="1:32">
@@ -33568,7 +33571,7 @@
         <v>0</v>
       </c>
       <c r="AF490" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="491" spans="1:32">
@@ -33627,7 +33630,7 @@
         <v>0</v>
       </c>
       <c r="AF491" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="492" spans="1:32">
@@ -33686,7 +33689,7 @@
         <v>0</v>
       </c>
       <c r="AF492" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="493" spans="1:32">
@@ -33745,7 +33748,7 @@
         <v>0</v>
       </c>
       <c r="AF493" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="494" spans="1:32">
@@ -33804,7 +33807,7 @@
         <v>0</v>
       </c>
       <c r="AF494" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="495" spans="1:32">
@@ -33863,7 +33866,7 @@
         <v>0</v>
       </c>
       <c r="AF495" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="496" spans="1:32">
@@ -33922,7 +33925,7 @@
         <v>0</v>
       </c>
       <c r="AF496" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="497" spans="1:32">
@@ -33981,7 +33984,7 @@
         <v>0</v>
       </c>
       <c r="AF497" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="498" spans="1:32">
@@ -34040,7 +34043,7 @@
         <v>0</v>
       </c>
       <c r="AF498" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="499" spans="1:32">
@@ -34099,7 +34102,7 @@
         <v>0</v>
       </c>
       <c r="AF499" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="500" spans="1:32">
@@ -34158,7 +34161,7 @@
         <v>0</v>
       </c>
       <c r="AF500" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="501" spans="1:32">
@@ -34217,7 +34220,7 @@
         <v>0</v>
       </c>
       <c r="AF501" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="502" spans="1:32">
@@ -34276,7 +34279,7 @@
         <v>0</v>
       </c>
       <c r="AF502" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="503" spans="1:32">
@@ -34335,7 +34338,7 @@
         <v>0</v>
       </c>
       <c r="AF503" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="504" spans="1:32">
@@ -34394,7 +34397,7 @@
         <v>0</v>
       </c>
       <c r="AF504" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="505" spans="1:32">
@@ -34453,7 +34456,7 @@
         <v>0</v>
       </c>
       <c r="AF505" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="506" spans="1:32">
@@ -34512,7 +34515,7 @@
         <v>0</v>
       </c>
       <c r="AF506" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="507" spans="1:32">
@@ -34571,7 +34574,7 @@
         <v>0</v>
       </c>
       <c r="AF507" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="508" spans="1:32">
@@ -34630,7 +34633,7 @@
         <v>0</v>
       </c>
       <c r="AF508" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="509" spans="1:32">
@@ -34689,7 +34692,7 @@
         <v>0</v>
       </c>
       <c r="AF509" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="510" spans="1:32">
@@ -34748,7 +34751,7 @@
         <v>0</v>
       </c>
       <c r="AF510" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="511" spans="1:32">
@@ -34807,7 +34810,7 @@
         <v>0</v>
       </c>
       <c r="AF511" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="512" spans="1:32">
@@ -34866,7 +34869,7 @@
         <v>0</v>
       </c>
       <c r="AF512" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="513" spans="1:33">
@@ -34925,7 +34928,7 @@
         <v>0</v>
       </c>
       <c r="AF513" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="514" spans="1:33">
@@ -34984,7 +34987,7 @@
         <v>0</v>
       </c>
       <c r="AF514" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="515" spans="1:33">
@@ -35046,13 +35049,13 @@
         <v>0</v>
       </c>
       <c r="AA515" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF515" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG515" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="516" spans="1:33">
@@ -35114,13 +35117,13 @@
         <v>0</v>
       </c>
       <c r="AA516" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF516" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG516" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="517" spans="1:33">
@@ -35185,10 +35188,10 @@
         <v>0</v>
       </c>
       <c r="AA517" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF517" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG517" t="s">
         <v>243</v>
@@ -35256,13 +35259,13 @@
         <v>0</v>
       </c>
       <c r="AA518" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF518" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG518" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="519" spans="1:33">
@@ -35327,10 +35330,10 @@
         <v>235</v>
       </c>
       <c r="AF519" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG519" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="520" spans="1:33">
@@ -35392,13 +35395,13 @@
         <v>0</v>
       </c>
       <c r="AA520" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AF520" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG520" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="521" spans="1:33">
@@ -35460,13 +35463,13 @@
         <v>0</v>
       </c>
       <c r="AA521" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AF521" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG521" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="522" spans="1:33">
@@ -35531,10 +35534,10 @@
         <v>234</v>
       </c>
       <c r="AF522" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG522" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="523" spans="1:33">
@@ -35593,10 +35596,10 @@
         <v>0</v>
       </c>
       <c r="AA523" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AF523" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="524" spans="1:33">
@@ -35655,10 +35658,10 @@
         <v>0</v>
       </c>
       <c r="AA524" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AF524" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="525" spans="1:33">
@@ -35720,10 +35723,10 @@
         <v>0</v>
       </c>
       <c r="AA525" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF525" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="526" spans="1:33">
@@ -35788,10 +35791,10 @@
         <v>239</v>
       </c>
       <c r="AF526" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG526" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="527" spans="1:33">
@@ -35856,10 +35859,10 @@
         <v>235</v>
       </c>
       <c r="AF527" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG527" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="528" spans="1:33">
@@ -35924,10 +35927,10 @@
         <v>240</v>
       </c>
       <c r="AF528" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG528" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="529" spans="1:33">
@@ -35992,10 +35995,10 @@
         <v>235</v>
       </c>
       <c r="AF529" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG529" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="530" spans="1:33">
@@ -36060,10 +36063,10 @@
         <v>235</v>
       </c>
       <c r="AF530" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG530" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="531" spans="1:33">
@@ -36128,10 +36131,10 @@
         <v>235</v>
       </c>
       <c r="AF531" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG531" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="532" spans="1:33">
@@ -36196,10 +36199,10 @@
         <v>220</v>
       </c>
       <c r="AF532" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG532" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="533" spans="1:33">
@@ -36261,13 +36264,13 @@
         <v>0</v>
       </c>
       <c r="AA533" t="s">
+        <v>375</v>
+      </c>
+      <c r="AF533" t="s">
+        <v>385</v>
+      </c>
+      <c r="AG533" t="s">
         <v>374</v>
-      </c>
-      <c r="AF533" t="s">
-        <v>384</v>
-      </c>
-      <c r="AG533" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="534" spans="1:33">
@@ -36329,13 +36332,13 @@
         <v>0</v>
       </c>
       <c r="AA534" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF534" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG534" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="535" spans="1:33">
@@ -36397,13 +36400,13 @@
         <v>0</v>
       </c>
       <c r="AA535" t="s">
+        <v>375</v>
+      </c>
+      <c r="AF535" t="s">
+        <v>384</v>
+      </c>
+      <c r="AG535" t="s">
         <v>374</v>
-      </c>
-      <c r="AF535" t="s">
-        <v>383</v>
-      </c>
-      <c r="AG535" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="536" spans="1:33">
@@ -36465,13 +36468,13 @@
         <v>0</v>
       </c>
       <c r="AA536" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF536" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG536" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="537" spans="1:33">
@@ -36536,7 +36539,7 @@
         <v>224</v>
       </c>
       <c r="AF537" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG537" t="s">
         <v>224</v>
@@ -36604,7 +36607,7 @@
         <v>224</v>
       </c>
       <c r="AF538" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG538" t="s">
         <v>224</v>
@@ -36672,7 +36675,7 @@
         <v>226</v>
       </c>
       <c r="AF539" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG539" t="s">
         <v>224</v>
@@ -36737,10 +36740,10 @@
         <v>0</v>
       </c>
       <c r="AA540" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF540" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG540" t="s">
         <v>224</v>
@@ -36805,10 +36808,10 @@
         <v>0</v>
       </c>
       <c r="AA541" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF541" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="542" spans="1:33">
@@ -36873,10 +36876,10 @@
         <v>229</v>
       </c>
       <c r="AF542" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG542" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="543" spans="1:33">
@@ -36938,13 +36941,13 @@
         <v>0</v>
       </c>
       <c r="AA543" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AF543" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG543" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="544" spans="1:33">
@@ -37009,10 +37012,10 @@
         <v>0</v>
       </c>
       <c r="AA544" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF544" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="545" spans="1:32">
@@ -37074,10 +37077,10 @@
         <v>0</v>
       </c>
       <c r="AA545" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF545" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="546" spans="1:32">
@@ -37142,10 +37145,10 @@
         <v>0</v>
       </c>
       <c r="AA546" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF546" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="547" spans="1:32">
@@ -37210,10 +37213,10 @@
         <v>0</v>
       </c>
       <c r="AA547" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF547" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="548" spans="1:32">
@@ -37278,10 +37281,10 @@
         <v>0</v>
       </c>
       <c r="AA548" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF548" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="549" spans="1:32">
@@ -37340,10 +37343,10 @@
         <v>0</v>
       </c>
       <c r="AA549" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF549" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="550" spans="1:32">
@@ -37408,10 +37411,10 @@
         <v>0</v>
       </c>
       <c r="AA550" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF550" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="551" spans="1:32">
@@ -37476,10 +37479,10 @@
         <v>0</v>
       </c>
       <c r="AA551" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF551" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="552" spans="1:32">
@@ -37541,10 +37544,10 @@
         <v>0</v>
       </c>
       <c r="AA552" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF552" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="553" spans="1:32">
@@ -37609,10 +37612,10 @@
         <v>0</v>
       </c>
       <c r="AA553" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF553" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="554" spans="1:32">
@@ -37671,10 +37674,10 @@
         <v>0</v>
       </c>
       <c r="AA554" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF554" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="555" spans="1:32">
@@ -37739,10 +37742,10 @@
         <v>0</v>
       </c>
       <c r="AA555" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF555" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="556" spans="1:32">
@@ -37807,10 +37810,10 @@
         <v>0</v>
       </c>
       <c r="AA556" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF556" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="557" spans="1:32">
@@ -37875,10 +37878,10 @@
         <v>0</v>
       </c>
       <c r="AA557" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF557" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="558" spans="1:32">
@@ -37940,10 +37943,10 @@
         <v>0</v>
       </c>
       <c r="AA558" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF558" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="559" spans="1:32">
@@ -38008,10 +38011,10 @@
         <v>0</v>
       </c>
       <c r="AA559" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF559" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="560" spans="1:32">
@@ -38073,10 +38076,10 @@
         <v>0</v>
       </c>
       <c r="AA560" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF560" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="561" spans="1:32">
@@ -38138,10 +38141,10 @@
         <v>0</v>
       </c>
       <c r="AA561" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF561" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="562" spans="1:32">
@@ -38206,10 +38209,10 @@
         <v>0</v>
       </c>
       <c r="AA562" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF562" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="563" spans="1:32">
@@ -38274,10 +38277,10 @@
         <v>0</v>
       </c>
       <c r="AA563" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF563" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="564" spans="1:32">
@@ -38342,10 +38345,10 @@
         <v>0</v>
       </c>
       <c r="AA564" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF564" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="565" spans="1:32">
@@ -38407,10 +38410,10 @@
         <v>0</v>
       </c>
       <c r="AA565" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF565" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="566" spans="1:32">
@@ -38475,10 +38478,10 @@
         <v>0</v>
       </c>
       <c r="AA566" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF566" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="567" spans="1:32">
@@ -38540,10 +38543,10 @@
         <v>0</v>
       </c>
       <c r="AA567" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF567" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="568" spans="1:32">
@@ -38605,10 +38608,10 @@
         <v>0</v>
       </c>
       <c r="AA568" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF568" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="569" spans="1:32">
@@ -38673,10 +38676,10 @@
         <v>0</v>
       </c>
       <c r="AA569" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF569" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="570" spans="1:32">
@@ -38741,10 +38744,10 @@
         <v>0</v>
       </c>
       <c r="AA570" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF570" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="571" spans="1:32">
@@ -38809,10 +38812,10 @@
         <v>0</v>
       </c>
       <c r="AA571" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF571" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="572" spans="1:32">
@@ -38874,10 +38877,10 @@
         <v>0</v>
       </c>
       <c r="AA572" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF572" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="573" spans="1:32">
@@ -38939,10 +38942,10 @@
         <v>0</v>
       </c>
       <c r="AA573" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF573" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="574" spans="1:32">
@@ -39001,10 +39004,10 @@
         <v>0</v>
       </c>
       <c r="AA574" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF574" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="575" spans="1:32">
@@ -39066,13 +39069,13 @@
         <v>361</v>
       </c>
       <c r="AD575" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AE575" t="s">
         <v>205</v>
       </c>
       <c r="AF575" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="576" spans="1:32">
@@ -39134,13 +39137,13 @@
         <v>361</v>
       </c>
       <c r="AD576" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AE576" t="s">
         <v>205</v>
       </c>
       <c r="AF576" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="577" spans="1:32">
@@ -39202,13 +39205,13 @@
         <v>361</v>
       </c>
       <c r="AD577" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AE577" t="s">
         <v>205</v>
       </c>
       <c r="AF577" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="578" spans="1:32">
@@ -39245,9 +39248,6 @@
       <c r="L578" s="1">
         <v>46275</v>
       </c>
-      <c r="M578" t="s">
-        <v>197</v>
-      </c>
       <c r="N578" t="s">
         <v>211</v>
       </c>
@@ -39255,7 +39255,7 @@
         <v>18253093</v>
       </c>
       <c r="P578" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Q578" t="s">
         <v>244</v>
@@ -39270,7 +39270,7 @@
         <v>362</v>
       </c>
       <c r="AF578" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="579" spans="1:32">
@@ -39307,9 +39307,6 @@
       <c r="L579" s="1">
         <v>46275</v>
       </c>
-      <c r="M579" t="s">
-        <v>197</v>
-      </c>
       <c r="N579" t="s">
         <v>211</v>
       </c>
@@ -39317,7 +39314,7 @@
         <v>18253094</v>
       </c>
       <c r="P579" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Q579" t="s">
         <v>244</v>
@@ -39332,7 +39329,7 @@
         <v>362</v>
       </c>
       <c r="AF579" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="580" spans="1:32">
@@ -39369,9 +39366,6 @@
       <c r="L580" s="1">
         <v>46275</v>
       </c>
-      <c r="M580" t="s">
-        <v>197</v>
-      </c>
       <c r="N580" t="s">
         <v>211</v>
       </c>
@@ -39379,7 +39373,7 @@
         <v>18253095</v>
       </c>
       <c r="P580" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Q580" t="s">
         <v>244</v>
@@ -39394,7 +39388,7 @@
         <v>362</v>
       </c>
       <c r="AF580" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="581" spans="1:32">
@@ -39431,9 +39425,6 @@
       <c r="L581" s="1">
         <v>46275</v>
       </c>
-      <c r="M581" t="s">
-        <v>197</v>
-      </c>
       <c r="N581" t="s">
         <v>211</v>
       </c>
@@ -39441,7 +39432,7 @@
         <v>18253096</v>
       </c>
       <c r="P581" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Q581" t="s">
         <v>244</v>
@@ -39453,10 +39444,10 @@
         <v>254</v>
       </c>
       <c r="V581" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AF581" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="582" spans="1:32">
@@ -39493,9 +39484,6 @@
       <c r="L582" s="1">
         <v>46275</v>
       </c>
-      <c r="M582" t="s">
-        <v>197</v>
-      </c>
       <c r="N582" t="s">
         <v>211</v>
       </c>
@@ -39503,7 +39491,7 @@
         <v>18253080</v>
       </c>
       <c r="P582" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Q582" t="s">
         <v>244</v>
@@ -39515,10 +39503,10 @@
         <v>254</v>
       </c>
       <c r="V582" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AF582" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="583" spans="1:32">
@@ -39555,9 +39543,6 @@
       <c r="L583" s="1">
         <v>46275</v>
       </c>
-      <c r="M583" t="s">
-        <v>197</v>
-      </c>
       <c r="N583" t="s">
         <v>211</v>
       </c>
@@ -39565,7 +39550,7 @@
         <v>18253084</v>
       </c>
       <c r="P583" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Q583" t="s">
         <v>244</v>
@@ -39577,10 +39562,10 @@
         <v>254</v>
       </c>
       <c r="V583" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AF583" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="584" spans="1:32">
@@ -39617,9 +39602,6 @@
       <c r="L584" s="1">
         <v>46275</v>
       </c>
-      <c r="M584" t="s">
-        <v>197</v>
-      </c>
       <c r="N584" t="s">
         <v>211</v>
       </c>
@@ -39627,7 +39609,7 @@
         <v>18253082</v>
       </c>
       <c r="P584" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Q584" t="s">
         <v>244</v>
@@ -39642,7 +39624,7 @@
         <v>362</v>
       </c>
       <c r="AF584" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="585" spans="1:32">
@@ -39679,9 +39661,6 @@
       <c r="L585" s="1">
         <v>46275</v>
       </c>
-      <c r="M585" t="s">
-        <v>197</v>
-      </c>
       <c r="N585" t="s">
         <v>211</v>
       </c>
@@ -39689,7 +39668,7 @@
         <v>18253083</v>
       </c>
       <c r="P585" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Q585" t="s">
         <v>244</v>
@@ -39704,7 +39683,7 @@
         <v>362</v>
       </c>
       <c r="AF585" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="586" spans="1:32">
@@ -39763,16 +39742,16 @@
         <v>261</v>
       </c>
       <c r="V586" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AD586" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AE586" t="s">
         <v>197</v>
       </c>
       <c r="AF586" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="587" spans="1:32">
@@ -39831,16 +39810,16 @@
         <v>261</v>
       </c>
       <c r="V587" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AD587" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AE587" t="s">
         <v>197</v>
       </c>
       <c r="AF587" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="588" spans="1:32">
@@ -39877,9 +39856,6 @@
       <c r="L588" s="1">
         <v>46275</v>
       </c>
-      <c r="M588" t="s">
-        <v>197</v>
-      </c>
       <c r="N588" t="s">
         <v>211</v>
       </c>
@@ -39887,7 +39863,7 @@
         <v>18253085</v>
       </c>
       <c r="P588" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Q588" t="s">
         <v>244</v>
@@ -39899,10 +39875,10 @@
         <v>254</v>
       </c>
       <c r="V588" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AF588" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="589" spans="1:32">
@@ -39939,9 +39915,6 @@
       <c r="L589" s="1">
         <v>46275</v>
       </c>
-      <c r="M589" t="s">
-        <v>197</v>
-      </c>
       <c r="N589" t="s">
         <v>211</v>
       </c>
@@ -39949,7 +39922,7 @@
         <v>18253091</v>
       </c>
       <c r="P589" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Q589" t="s">
         <v>244</v>
@@ -39961,10 +39934,10 @@
         <v>254</v>
       </c>
       <c r="V589" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AF589" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="590" spans="1:32">
@@ -40001,9 +39974,6 @@
       <c r="L590" s="1">
         <v>46275</v>
       </c>
-      <c r="M590" t="s">
-        <v>197</v>
-      </c>
       <c r="N590" t="s">
         <v>211</v>
       </c>
@@ -40011,7 +39981,7 @@
         <v>18253088</v>
       </c>
       <c r="P590" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Q590" t="s">
         <v>244</v>
@@ -40026,7 +39996,7 @@
         <v>362</v>
       </c>
       <c r="AF590" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="591" spans="1:32">
@@ -40063,9 +40033,6 @@
       <c r="L591" s="1">
         <v>46275</v>
       </c>
-      <c r="M591" t="s">
-        <v>197</v>
-      </c>
       <c r="N591" t="s">
         <v>211</v>
       </c>
@@ -40073,7 +40040,7 @@
         <v>18253087</v>
       </c>
       <c r="P591" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Q591" t="s">
         <v>244</v>
@@ -40085,10 +40052,10 @@
         <v>254</v>
       </c>
       <c r="V591" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AF591" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="592" spans="1:32">
@@ -40125,9 +40092,6 @@
       <c r="L592" s="1">
         <v>46275</v>
       </c>
-      <c r="M592" t="s">
-        <v>197</v>
-      </c>
       <c r="N592" t="s">
         <v>211</v>
       </c>
@@ -40135,7 +40099,7 @@
         <v>18253090</v>
       </c>
       <c r="P592" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Q592" t="s">
         <v>244</v>
@@ -40150,7 +40114,7 @@
         <v>362</v>
       </c>
       <c r="AF592" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="593" spans="1:33">
@@ -40187,9 +40151,6 @@
       <c r="L593" s="1">
         <v>46275</v>
       </c>
-      <c r="M593" t="s">
-        <v>197</v>
-      </c>
       <c r="N593" t="s">
         <v>211</v>
       </c>
@@ -40197,7 +40158,7 @@
         <v>18253089</v>
       </c>
       <c r="P593" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Q593" t="s">
         <v>244</v>
@@ -40212,7 +40173,7 @@
         <v>362</v>
       </c>
       <c r="AF593" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="594" spans="1:33">
@@ -40271,16 +40232,16 @@
         <v>260</v>
       </c>
       <c r="V594" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AD594" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AE594" t="s">
         <v>210</v>
       </c>
       <c r="AF594" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG594" t="s">
         <v>243</v>
@@ -40342,16 +40303,16 @@
         <v>260</v>
       </c>
       <c r="V595" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AD595" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AE595" t="s">
         <v>210</v>
       </c>
       <c r="AF595" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG595" t="s">
         <v>243</v>
@@ -40413,10 +40374,10 @@
         <v>260</v>
       </c>
       <c r="V596" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AF596" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="597" spans="1:33">
@@ -40475,10 +40436,10 @@
         <v>260</v>
       </c>
       <c r="V597" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AF597" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="598" spans="1:33">
@@ -40537,10 +40498,10 @@
         <v>255</v>
       </c>
       <c r="V598" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AF598" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="599" spans="1:33">
@@ -40599,10 +40560,10 @@
         <v>254</v>
       </c>
       <c r="V599" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AF599" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="600" spans="1:33">
@@ -40658,10 +40619,10 @@
         <v>260</v>
       </c>
       <c r="V600" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AF600" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG600" t="s">
         <v>224</v>
@@ -40720,10 +40681,10 @@
         <v>260</v>
       </c>
       <c r="V601" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AF601" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG601" t="s">
         <v>224</v>
@@ -40785,10 +40746,10 @@
         <v>255</v>
       </c>
       <c r="V602" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AF602" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG602" t="s">
         <v>224</v>
@@ -40847,10 +40808,10 @@
         <v>261</v>
       </c>
       <c r="AF603" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG603" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
